--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -753,8 +753,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -893,37 +893,37 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.26</v>
+        <v>27.21</v>
       </c>
       <c r="D2">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="E2">
-        <v>37.84</v>
+        <v>37.31</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.96</v>
+        <v>-27.07</v>
       </c>
       <c r="H2">
-        <v>18.62</v>
+        <v>18.41</v>
       </c>
       <c r="I2">
-        <v>-1.66</v>
+        <v>-0.77</v>
       </c>
       <c r="J2">
-        <v>-6.61</v>
+        <v>-9.6</v>
       </c>
       <c r="K2">
-        <v>4.13</v>
+        <v>3.82</v>
       </c>
       <c r="L2">
-        <v>-29.05</v>
+        <v>-28.09</v>
       </c>
       <c r="M2">
-        <v>-11.39</v>
+        <v>-11.08</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -932,19 +932,19 @@
         <v>25</v>
       </c>
       <c r="P2">
-        <v>27.36</v>
+        <v>27.32</v>
       </c>
       <c r="Q2">
-        <v>27.6</v>
+        <v>27.45</v>
       </c>
       <c r="R2">
-        <v>28.43</v>
+        <v>28.44</v>
       </c>
       <c r="S2">
-        <v>29.04</v>
+        <v>29</v>
       </c>
       <c r="T2">
-        <v>-6.12</v>
+        <v>-6.19</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -959,43 +959,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>43.01</v>
+        <v>42.52</v>
       </c>
       <c r="Z2">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="AA2">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="AB2">
         <v>0.02</v>
       </c>
       <c r="AC2">
-        <v>52.91</v>
+        <v>44.94</v>
       </c>
       <c r="AD2">
-        <v>60.31</v>
+        <v>53.13</v>
       </c>
       <c r="AE2">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>-51.6</v>
+        <v>-34.74</v>
       </c>
       <c r="AG2">
-        <v>29.14</v>
+        <v>28.33</v>
       </c>
       <c r="AH2">
-        <v>26.06</v>
+        <v>26.57</v>
       </c>
       <c r="AI2">
-        <v>29.4</v>
+        <v>29.27</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>10.69</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1006,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.81</v>
+        <v>10.76</v>
       </c>
       <c r="D3">
-        <v>-0.92</v>
+        <v>-0.46</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1018,46 +1018,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-28.32</v>
+        <v>-28.65</v>
       </c>
       <c r="H3">
-        <v>21.87</v>
+        <v>21.31</v>
       </c>
       <c r="I3">
-        <v>-2.17</v>
+        <v>-1.47</v>
       </c>
       <c r="J3">
-        <v>-1.99</v>
+        <v>-4.27</v>
       </c>
       <c r="K3">
-        <v>2.46</v>
+        <v>1.13</v>
       </c>
       <c r="L3">
-        <v>-27.25</v>
+        <v>-26.85</v>
       </c>
       <c r="M3">
-        <v>-15.74</v>
+        <v>-15.28</v>
       </c>
       <c r="N3">
         <v>50</v>
       </c>
       <c r="O3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P3">
-        <v>10.87</v>
+        <v>10.84</v>
       </c>
       <c r="Q3">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="R3">
         <v>11.05</v>
       </c>
       <c r="S3">
-        <v>11.44</v>
+        <v>11.42</v>
       </c>
       <c r="T3">
-        <v>-5.48</v>
+        <v>-5.8</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1072,43 +1072,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.42</v>
+        <v>43.93</v>
       </c>
       <c r="Z3">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AA3">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC3">
-        <v>58.26</v>
+        <v>53.7</v>
       </c>
       <c r="AD3">
-        <v>62.14</v>
+        <v>58.72</v>
       </c>
       <c r="AE3">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="AF3">
-        <v>-1.64</v>
+        <v>-32.05</v>
       </c>
       <c r="AG3">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="AH3">
-        <v>10.59</v>
+        <v>10.6</v>
       </c>
       <c r="AI3">
-        <v>11.59</v>
+        <v>11.57</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>17.94</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,37 +1119,37 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>254</v>
+        <v>252.75</v>
       </c>
       <c r="D4">
-        <v>-1.09</v>
+        <v>-0.49</v>
       </c>
       <c r="E4">
-        <v>332.33</v>
+        <v>331.3</v>
       </c>
       <c r="F4">
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-23.57</v>
+        <v>-23.71</v>
       </c>
       <c r="H4">
-        <v>13.34</v>
+        <v>12.78</v>
       </c>
       <c r="I4">
-        <v>-3.42</v>
+        <v>-4.62</v>
       </c>
       <c r="J4">
-        <v>4.98</v>
+        <v>4.7</v>
       </c>
       <c r="K4">
-        <v>10.21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L4">
-        <v>-23.81</v>
+        <v>-23.95</v>
       </c>
       <c r="M4">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="N4">
         <v>66</v>
@@ -1158,19 +1158,19 @@
         <v>41</v>
       </c>
       <c r="P4">
-        <v>260.17</v>
+        <v>257.72</v>
       </c>
       <c r="Q4">
-        <v>246.14</v>
+        <v>246.98</v>
       </c>
       <c r="R4">
-        <v>241.09</v>
+        <v>241.45</v>
       </c>
       <c r="S4">
-        <v>261.78</v>
+        <v>261.49</v>
       </c>
       <c r="T4">
-        <v>-2.97</v>
+        <v>-3.34</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1185,34 +1185,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>56.66</v>
+        <v>55.26</v>
       </c>
       <c r="Z4">
-        <v>5.7</v>
+        <v>5.22</v>
       </c>
       <c r="AA4">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="AB4">
-        <v>1.44</v>
+        <v>0.78</v>
       </c>
       <c r="AC4">
-        <v>64.14</v>
+        <v>48.58</v>
       </c>
       <c r="AD4">
-        <v>77.37</v>
+        <v>63.25</v>
       </c>
       <c r="AE4">
-        <v>6.32</v>
+        <v>6.01</v>
       </c>
       <c r="AF4">
-        <v>-56.37</v>
+        <v>-72.29000000000001</v>
       </c>
       <c r="AG4">
-        <v>269.01</v>
+        <v>269.51</v>
       </c>
       <c r="AH4">
-        <v>223.27</v>
+        <v>224.45</v>
       </c>
       <c r="AI4">
         <v>245</v>
@@ -1221,7 +1221,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>43.93</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1232,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>687.55</v>
+        <v>694.95</v>
       </c>
       <c r="D5">
-        <v>0.62</v>
+        <v>1.08</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1244,46 +1244,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-20.14</v>
+        <v>-19.28</v>
       </c>
       <c r="H5">
-        <v>40.12</v>
+        <v>41.62</v>
       </c>
       <c r="I5">
-        <v>-3.25</v>
+        <v>-1.25</v>
       </c>
       <c r="J5">
-        <v>21.9</v>
+        <v>2.67</v>
       </c>
       <c r="K5">
-        <v>29.69</v>
+        <v>31.38</v>
       </c>
       <c r="L5">
-        <v>-17.28</v>
+        <v>-17.48</v>
       </c>
       <c r="M5">
-        <v>-6.5</v>
+        <v>-6.24</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>687.83</v>
+        <v>686.0700000000001</v>
       </c>
       <c r="Q5">
-        <v>731.54</v>
+        <v>726.78</v>
       </c>
       <c r="R5">
-        <v>619.1</v>
+        <v>622.5599999999999</v>
       </c>
       <c r="S5">
-        <v>633.96</v>
+        <v>633.47</v>
       </c>
       <c r="T5">
-        <v>8.449999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1298,34 +1298,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>51.93</v>
+        <v>53.87</v>
       </c>
       <c r="Z5">
-        <v>18.42</v>
+        <v>16.57</v>
       </c>
       <c r="AA5">
-        <v>31.24</v>
+        <v>28.31</v>
       </c>
       <c r="AB5">
-        <v>-12.82</v>
+        <v>-11.74</v>
       </c>
       <c r="AC5">
-        <v>3.38</v>
+        <v>9.48</v>
       </c>
       <c r="AD5">
-        <v>1.35</v>
+        <v>4.51</v>
       </c>
       <c r="AE5">
-        <v>29.91</v>
+        <v>29.23</v>
       </c>
       <c r="AF5">
-        <v>-96.33</v>
+        <v>-96.28</v>
       </c>
       <c r="AG5">
-        <v>804.99</v>
+        <v>796.48</v>
       </c>
       <c r="AH5">
-        <v>658.08</v>
+        <v>657.0700000000001</v>
       </c>
       <c r="AI5">
         <v>771.22</v>
@@ -1334,7 +1334,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>22.55</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,37 +1345,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>29.32</v>
+        <v>29.14</v>
       </c>
       <c r="D6">
-        <v>-0.8100000000000001</v>
+        <v>-0.61</v>
       </c>
       <c r="E6">
-        <v>58.31</v>
+        <v>57.9</v>
       </c>
       <c r="F6">
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-49.72</v>
+        <v>-49.67</v>
       </c>
       <c r="H6">
-        <v>6.54</v>
+        <v>5.89</v>
       </c>
       <c r="I6">
-        <v>-0.2</v>
+        <v>-3.03</v>
       </c>
       <c r="J6">
-        <v>-5.94</v>
+        <v>-8.34</v>
       </c>
       <c r="K6">
-        <v>-8.77</v>
+        <v>-10.56</v>
       </c>
       <c r="L6">
-        <v>-50.58</v>
+        <v>-50.03</v>
       </c>
       <c r="M6">
-        <v>-10.13</v>
+        <v>-10.36</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1384,19 +1384,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>29.69</v>
+        <v>29.51</v>
       </c>
       <c r="Q6">
-        <v>29.62</v>
+        <v>29.48</v>
       </c>
       <c r="R6">
-        <v>31.09</v>
+        <v>31.07</v>
       </c>
       <c r="S6">
-        <v>36.54</v>
+        <v>36.44</v>
       </c>
       <c r="T6">
-        <v>-19.75</v>
+        <v>-20.03</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1411,34 +1411,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>42.44</v>
+        <v>41.04</v>
       </c>
       <c r="Z6">
         <v>-0.5</v>
       </c>
       <c r="AA6">
-        <v>-0.63</v>
+        <v>-0.6</v>
       </c>
       <c r="AB6">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AC6">
-        <v>82.61</v>
+        <v>71.36</v>
       </c>
       <c r="AD6">
-        <v>86.92</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="AE6">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="AF6">
-        <v>-47.91</v>
+        <v>-49.92</v>
       </c>
       <c r="AG6">
-        <v>31.49</v>
+        <v>31</v>
       </c>
       <c r="AH6">
-        <v>27.76</v>
+        <v>27.96</v>
       </c>
       <c r="AI6">
         <v>31.46</v>
@@ -1447,7 +1447,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>20.27</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1458,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1327.3</v>
+        <v>1323.9</v>
       </c>
       <c r="D7">
-        <v>-0.5600000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1470,46 +1470,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-16.26</v>
+        <v>-16.47</v>
       </c>
       <c r="H7">
-        <v>5.44</v>
+        <v>5.17</v>
       </c>
       <c r="I7">
-        <v>0.63</v>
+        <v>2.56</v>
       </c>
       <c r="J7">
-        <v>1.49</v>
+        <v>2.08</v>
       </c>
       <c r="K7">
-        <v>-2.24</v>
+        <v>-2.12</v>
       </c>
       <c r="L7">
-        <v>-5.15</v>
+        <v>-4.05</v>
       </c>
       <c r="M7">
-        <v>7.02</v>
+        <v>6.66</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P7">
-        <v>1311.6</v>
+        <v>1318.2</v>
       </c>
       <c r="Q7">
-        <v>1298.96</v>
+        <v>1300.5</v>
       </c>
       <c r="R7">
-        <v>1300.38</v>
+        <v>1300.58</v>
       </c>
       <c r="S7">
-        <v>1402.41</v>
+        <v>1401.73</v>
       </c>
       <c r="T7">
-        <v>-5.36</v>
+        <v>-5.55</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1524,34 +1524,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>56.42</v>
+        <v>55.41</v>
       </c>
       <c r="Z7">
-        <v>3.61</v>
+        <v>4.7</v>
       </c>
       <c r="AA7">
-        <v>-1.81</v>
+        <v>-0.51</v>
       </c>
       <c r="AB7">
-        <v>5.42</v>
+        <v>5.21</v>
       </c>
       <c r="AC7">
-        <v>96.09999999999999</v>
+        <v>90.39</v>
       </c>
       <c r="AD7">
-        <v>77.47</v>
+        <v>87.78</v>
       </c>
       <c r="AE7">
-        <v>23.13</v>
+        <v>22.52</v>
       </c>
       <c r="AF7">
-        <v>-32.39</v>
+        <v>-19.92</v>
       </c>
       <c r="AG7">
-        <v>1340.75</v>
+        <v>1343.63</v>
       </c>
       <c r="AH7">
-        <v>1257.17</v>
+        <v>1257.38</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1560,7 +1560,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>17.86</v>
+        <v>16.31</v>
       </c>
     </row>
   </sheetData>
@@ -1758,13 +1758,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.84</v>
+        <v>-6.61</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.61</v>
+        <v>-9.6</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.77</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1775,13 +1775,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>0.18</v>
+        <v>-1.99</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.99</v>
+        <v>-4.27</v>
       </c>
       <c r="E8" s="6">
-        <v>-2.17</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1792,13 +1792,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>10.04</v>
+        <v>4.98</v>
       </c>
       <c r="D9" s="5">
-        <v>4.98</v>
+        <v>4.7</v>
       </c>
       <c r="E9" s="6">
-        <v>-5.06</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1809,13 +1809,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>25.01</v>
+        <v>21.9</v>
       </c>
       <c r="D10" s="5">
-        <v>21.9</v>
+        <v>2.67</v>
       </c>
       <c r="E10" s="6">
-        <v>-3.11</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1826,13 +1826,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.87</v>
+        <v>-5.94</v>
       </c>
       <c r="D11" s="5">
-        <v>-5.94</v>
+        <v>-8.34</v>
       </c>
       <c r="E11" s="6">
-        <v>-2.07</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1843,13 +1843,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>4.3</v>
+        <v>1.49</v>
       </c>
       <c r="D12" s="5">
-        <v>1.49</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-2.81</v>
+        <v>2.08</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1860,13 +1860,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-0.33</v>
+        <v>-1.66</v>
       </c>
       <c r="D13" s="5">
-        <v>-1.66</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-1.33</v>
+        <v>-0.77</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.89</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1877,13 +1877,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>1.3</v>
+        <v>-2.17</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.17</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-3.47</v>
+        <v>-1.47</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1894,13 +1894,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>0.13</v>
+        <v>-3.42</v>
       </c>
       <c r="D15" s="5">
-        <v>-3.42</v>
+        <v>-4.62</v>
       </c>
       <c r="E15" s="6">
-        <v>-3.55</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1911,13 +1911,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-4.66</v>
+        <v>-3.25</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.25</v>
+        <v>-1.25</v>
       </c>
       <c r="E16" s="7">
-        <v>1.41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1928,13 +1928,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>0.37</v>
+        <v>-0.2</v>
       </c>
       <c r="D17" s="5">
-        <v>-0.2</v>
+        <v>-3.03</v>
       </c>
       <c r="E17" s="6">
-        <v>-0.57</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1945,13 +1945,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>2.06</v>
+        <v>0.63</v>
       </c>
       <c r="D18" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.43</v>
+        <v>2.56</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.93</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1962,13 +1962,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-27.38</v>
+        <v>-29.05</v>
       </c>
       <c r="D19" s="5">
-        <v>-29.05</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.67</v>
+        <v>-28.09</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.96</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1979,13 +1979,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-27.75</v>
+        <v>-27.25</v>
       </c>
       <c r="D20" s="5">
-        <v>-27.25</v>
+        <v>-26.85</v>
       </c>
       <c r="E20" s="7">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1996,13 +1996,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-21.94</v>
+        <v>-23.81</v>
       </c>
       <c r="D21" s="5">
-        <v>-23.81</v>
+        <v>-23.95</v>
       </c>
       <c r="E21" s="6">
-        <v>-1.87</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2013,13 +2013,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>-17.44</v>
+        <v>-17.28</v>
       </c>
       <c r="D22" s="5">
-        <v>-17.28</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.16</v>
+        <v>-17.48</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2030,13 +2030,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-48.56</v>
+        <v>-50.58</v>
       </c>
       <c r="D23" s="5">
-        <v>-50.58</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2.02</v>
+        <v>-50.03</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.55</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2047,13 +2047,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-3.4</v>
+        <v>-5.15</v>
       </c>
       <c r="D24" s="5">
-        <v>-5.15</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.75</v>
+        <v>-4.05</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2064,13 +2064,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-0</v>
+        <v>4.13</v>
       </c>
       <c r="D25" s="5">
-        <v>4.13</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4.13</v>
+        <v>3.82</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2081,13 +2081,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>0.65</v>
+        <v>2.46</v>
       </c>
       <c r="D26" s="5">
-        <v>2.46</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.81</v>
+        <v>1.13</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2098,13 +2098,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="5">
-        <v>6.85</v>
+        <v>10.21</v>
       </c>
       <c r="D27" s="5">
-        <v>10.21</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3.36</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2115,13 +2115,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>27.05</v>
+        <v>29.69</v>
       </c>
       <c r="D28" s="5">
-        <v>29.69</v>
+        <v>31.38</v>
       </c>
       <c r="E28" s="7">
-        <v>2.64</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2132,13 +2132,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-11.39</v>
+        <v>-8.77</v>
       </c>
       <c r="D29" s="5">
-        <v>-8.77</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.62</v>
+        <v>-10.56</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2149,13 +2149,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-3.4</v>
+        <v>-2.24</v>
       </c>
       <c r="D30" s="5">
-        <v>-2.24</v>
+        <v>-2.12</v>
       </c>
       <c r="E30" s="7">
-        <v>1.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2166,13 +2166,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-28.89</v>
+        <v>-27.96</v>
       </c>
       <c r="D31" s="5">
-        <v>-27.96</v>
+        <v>-27.07</v>
       </c>
       <c r="E31" s="7">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2183,13 +2183,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="5">
-        <v>-27.65</v>
+        <v>-28.32</v>
       </c>
       <c r="D32" s="5">
-        <v>-28.32</v>
+        <v>-28.65</v>
       </c>
       <c r="E32" s="6">
-        <v>-0.67</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2200,13 +2200,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="5">
-        <v>-22.97</v>
+        <v>-23.57</v>
       </c>
       <c r="D33" s="5">
-        <v>-23.57</v>
+        <v>-23.71</v>
       </c>
       <c r="E33" s="6">
-        <v>-0.6</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2217,13 +2217,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="5">
-        <v>-20.63</v>
+        <v>-20.14</v>
       </c>
       <c r="D34" s="5">
-        <v>-20.14</v>
+        <v>-19.28</v>
       </c>
       <c r="E34" s="7">
-        <v>0.49</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2234,13 +2234,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-50.18</v>
+        <v>-49.72</v>
       </c>
       <c r="D35" s="5">
-        <v>-49.72</v>
+        <v>-49.67</v>
       </c>
       <c r="E35" s="7">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2251,13 +2251,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-15.78</v>
+        <v>-16.26</v>
       </c>
       <c r="D36" s="5">
-        <v>-16.26</v>
+        <v>-16.47</v>
       </c>
       <c r="E36" s="6">
-        <v>-0.48</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2268,13 +2268,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="5">
-        <v>27.32</v>
+        <v>27.26</v>
       </c>
       <c r="D37" s="5">
-        <v>27.26</v>
+        <v>27.21</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2285,13 +2285,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="5">
-        <v>10.91</v>
+        <v>10.81</v>
       </c>
       <c r="D38" s="5">
-        <v>10.81</v>
+        <v>10.76</v>
       </c>
       <c r="E38" s="6">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2302,13 +2302,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="5">
-        <v>256.8</v>
+        <v>254</v>
       </c>
       <c r="D39" s="5">
-        <v>254</v>
+        <v>252.75</v>
       </c>
       <c r="E39" s="6">
-        <v>-2.8</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2319,13 +2319,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="5">
-        <v>683.3</v>
+        <v>687.55</v>
       </c>
       <c r="D40" s="5">
-        <v>687.55</v>
+        <v>694.95</v>
       </c>
       <c r="E40" s="7">
-        <v>4.25</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2336,13 +2336,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>29.56</v>
+        <v>29.32</v>
       </c>
       <c r="D41" s="5">
-        <v>29.32</v>
+        <v>29.14</v>
       </c>
       <c r="E41" s="6">
-        <v>-0.24</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2353,13 +2353,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1334.8</v>
+        <v>1327.3</v>
       </c>
       <c r="D42" s="5">
-        <v>1327.3</v>
+        <v>1323.9</v>
       </c>
       <c r="E42" s="6">
-        <v>-7.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2370,13 +2370,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>43.58</v>
+        <v>43.01</v>
       </c>
       <c r="D43" s="5">
-        <v>43.01</v>
+        <v>42.52</v>
       </c>
       <c r="E43" s="6">
-        <v>-0.57</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2387,13 +2387,13 @@
         <v>24</v>
       </c>
       <c r="C44" s="5">
-        <v>48.47</v>
+        <v>45.42</v>
       </c>
       <c r="D44" s="5">
-        <v>45.42</v>
+        <v>43.93</v>
       </c>
       <c r="E44" s="6">
-        <v>-3.05</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="C45" s="5">
-        <v>59.82</v>
+        <v>56.66</v>
       </c>
       <c r="D45" s="5">
-        <v>56.66</v>
+        <v>55.26</v>
       </c>
       <c r="E45" s="6">
-        <v>-3.16</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2421,13 +2421,13 @@
         <v>24</v>
       </c>
       <c r="C46" s="5">
-        <v>50.83</v>
+        <v>51.93</v>
       </c>
       <c r="D46" s="5">
-        <v>51.93</v>
+        <v>53.87</v>
       </c>
       <c r="E46" s="7">
-        <v>1.1</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2438,13 +2438,13 @@
         <v>24</v>
       </c>
       <c r="C47" s="5">
-        <v>44.31</v>
+        <v>42.44</v>
       </c>
       <c r="D47" s="5">
-        <v>42.44</v>
+        <v>41.04</v>
       </c>
       <c r="E47" s="6">
-        <v>-1.87</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2455,13 +2455,13 @@
         <v>24</v>
       </c>
       <c r="C48" s="5">
-        <v>58.61</v>
+        <v>56.42</v>
       </c>
       <c r="D48" s="5">
-        <v>56.42</v>
+        <v>55.41</v>
       </c>
       <c r="E48" s="6">
-        <v>-2.19</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2472,13 +2472,13 @@
         <v>31</v>
       </c>
       <c r="C49" s="5">
-        <v>-56.86</v>
+        <v>-51.6</v>
       </c>
       <c r="D49" s="5">
-        <v>-51.6</v>
+        <v>-34.74</v>
       </c>
       <c r="E49" s="7">
-        <v>5.26</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2489,13 +2489,13 @@
         <v>31</v>
       </c>
       <c r="C50" s="5">
-        <v>-31.05</v>
+        <v>-1.64</v>
       </c>
       <c r="D50" s="5">
-        <v>-1.64</v>
-      </c>
-      <c r="E50" s="7">
-        <v>29.41</v>
+        <v>-32.05</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-30.41</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2506,13 +2506,13 @@
         <v>31</v>
       </c>
       <c r="C51" s="5">
-        <v>-51.97</v>
+        <v>-56.37</v>
       </c>
       <c r="D51" s="5">
-        <v>-56.37</v>
+        <v>-72.29000000000001</v>
       </c>
       <c r="E51" s="6">
-        <v>-4.4</v>
+        <v>-15.92</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2523,13 +2523,13 @@
         <v>31</v>
       </c>
       <c r="C52" s="5">
-        <v>-95.28</v>
+        <v>-96.33</v>
       </c>
       <c r="D52" s="5">
-        <v>-96.33</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-1.05</v>
+        <v>-96.28</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.05</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2540,13 +2540,13 @@
         <v>31</v>
       </c>
       <c r="C53" s="5">
-        <v>-61.95</v>
+        <v>-47.91</v>
       </c>
       <c r="D53" s="5">
-        <v>-47.91</v>
-      </c>
-      <c r="E53" s="7">
-        <v>14.04</v>
+        <v>-49.92</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2557,13 +2557,13 @@
         <v>31</v>
       </c>
       <c r="C54" s="5">
-        <v>-20.06</v>
+        <v>-32.39</v>
       </c>
       <c r="D54" s="5">
-        <v>-32.39</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-12.33</v>
+        <v>-19.92</v>
+      </c>
+      <c r="E54" s="7">
+        <v>12.47</v>
       </c>
     </row>
   </sheetData>
@@ -2628,16 +2628,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="10">
-        <v>49.3</v>
+        <v>48.7</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="G2" s="10">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="H2" s="10">
         <v>58.2</v>
@@ -2765,22 +2765,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13">
-        <v>0.0702</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0074</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.065</v>
+        <v>-0.0624</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.1013</v>
+        <v>-0.1036</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1139</v>
+        <v>-0.1108</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.1574</v>
+        <v>-0.1528</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +276,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +316,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,17 +392,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -753,8 +775,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -893,10 +915,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.21</v>
+        <v>26.99</v>
       </c>
       <c r="D2">
-        <v>-0.18</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E2">
         <v>37.31</v>
@@ -905,46 +927,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.07</v>
+        <v>-27.66</v>
       </c>
       <c r="H2">
-        <v>18.41</v>
+        <v>17.45</v>
       </c>
       <c r="I2">
-        <v>-0.77</v>
+        <v>-1.64</v>
       </c>
       <c r="J2">
-        <v>-9.6</v>
+        <v>-10.92</v>
       </c>
       <c r="K2">
-        <v>3.82</v>
+        <v>4.05</v>
       </c>
       <c r="L2">
-        <v>-28.09</v>
+        <v>-26.9</v>
       </c>
       <c r="M2">
-        <v>-11.08</v>
+        <v>-12.26</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2">
-        <v>27.32</v>
+        <v>27.23</v>
       </c>
       <c r="Q2">
-        <v>27.45</v>
+        <v>27.35</v>
       </c>
       <c r="R2">
-        <v>28.44</v>
+        <v>28.45</v>
       </c>
       <c r="S2">
-        <v>29</v>
+        <v>28.97</v>
       </c>
       <c r="T2">
-        <v>-6.19</v>
+        <v>-6.84</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -959,43 +981,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.52</v>
+        <v>40.32</v>
       </c>
       <c r="Z2">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
       <c r="AA2">
         <v>-0.38</v>
       </c>
       <c r="AB2">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AC2">
-        <v>44.94</v>
+        <v>27.29</v>
       </c>
       <c r="AD2">
-        <v>53.13</v>
+        <v>41.71</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF2">
-        <v>-34.74</v>
+        <v>-2.04</v>
       </c>
       <c r="AG2">
-        <v>28.33</v>
+        <v>27.9</v>
       </c>
       <c r="AH2">
-        <v>26.57</v>
+        <v>26.79</v>
       </c>
       <c r="AI2">
-        <v>29.27</v>
+        <v>29.08</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>12.25</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1028,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.76</v>
+        <v>10.67</v>
       </c>
       <c r="D3">
-        <v>-0.46</v>
+        <v>-0.84</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1018,25 +1040,25 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-28.65</v>
+        <v>-29.24</v>
       </c>
       <c r="H3">
-        <v>21.31</v>
+        <v>20.29</v>
       </c>
       <c r="I3">
-        <v>-1.47</v>
+        <v>-2.11</v>
       </c>
       <c r="J3">
-        <v>-4.27</v>
+        <v>-5.41</v>
       </c>
       <c r="K3">
-        <v>1.13</v>
+        <v>2.4</v>
       </c>
       <c r="L3">
-        <v>-26.85</v>
+        <v>-26.31</v>
       </c>
       <c r="M3">
-        <v>-15.28</v>
+        <v>-15.89</v>
       </c>
       <c r="N3">
         <v>50</v>
@@ -1045,19 +1067,19 @@
         <v>29</v>
       </c>
       <c r="P3">
-        <v>10.84</v>
+        <v>10.8</v>
       </c>
       <c r="Q3">
-        <v>10.89</v>
+        <v>10.87</v>
       </c>
       <c r="R3">
         <v>11.05</v>
       </c>
       <c r="S3">
-        <v>11.42</v>
+        <v>11.41</v>
       </c>
       <c r="T3">
-        <v>-5.8</v>
+        <v>-6.46</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1072,43 +1094,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>43.93</v>
+        <v>41.3</v>
       </c>
       <c r="Z3">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AA3">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AB3">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AC3">
-        <v>53.7</v>
+        <v>29.51</v>
       </c>
       <c r="AD3">
-        <v>58.72</v>
+        <v>47.16</v>
       </c>
       <c r="AE3">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>-32.05</v>
+        <v>-13.42</v>
       </c>
       <c r="AG3">
-        <v>11.19</v>
+        <v>11.13</v>
       </c>
       <c r="AH3">
         <v>10.6</v>
       </c>
       <c r="AI3">
-        <v>11.57</v>
+        <v>11.5</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>18.4</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,10 +1141,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>252.75</v>
+        <v>256.05</v>
       </c>
       <c r="D4">
-        <v>-0.49</v>
+        <v>1.31</v>
       </c>
       <c r="E4">
         <v>331.3</v>
@@ -1131,46 +1153,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-23.71</v>
+        <v>-22.71</v>
       </c>
       <c r="H4">
-        <v>12.78</v>
+        <v>14.26</v>
       </c>
       <c r="I4">
-        <v>-4.62</v>
+        <v>-2.25</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>8.51</v>
       </c>
       <c r="K4">
-        <v>9.199999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L4">
-        <v>-23.95</v>
+        <v>-21.47</v>
       </c>
       <c r="M4">
-        <v>0.57</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P4">
-        <v>257.72</v>
+        <v>256.54</v>
       </c>
       <c r="Q4">
-        <v>246.98</v>
+        <v>247.95</v>
       </c>
       <c r="R4">
-        <v>241.45</v>
+        <v>241.82</v>
       </c>
       <c r="S4">
-        <v>261.49</v>
+        <v>261.22</v>
       </c>
       <c r="T4">
-        <v>-3.34</v>
+        <v>-1.98</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1185,34 +1207,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>55.26</v>
+        <v>58.2</v>
       </c>
       <c r="Z4">
-        <v>5.22</v>
+        <v>5.06</v>
       </c>
       <c r="AA4">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="AB4">
-        <v>0.78</v>
+        <v>0.49</v>
       </c>
       <c r="AC4">
-        <v>48.58</v>
+        <v>45.29</v>
       </c>
       <c r="AD4">
-        <v>63.25</v>
+        <v>52.67</v>
       </c>
       <c r="AE4">
-        <v>6.01</v>
+        <v>6.08</v>
       </c>
       <c r="AF4">
-        <v>-72.29000000000001</v>
+        <v>-37.79</v>
       </c>
       <c r="AG4">
-        <v>269.51</v>
+        <v>270.27</v>
       </c>
       <c r="AH4">
-        <v>224.45</v>
+        <v>225.63</v>
       </c>
       <c r="AI4">
         <v>245</v>
@@ -1221,7 +1243,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>40.81</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1254,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>694.95</v>
+        <v>687.45</v>
       </c>
       <c r="D5">
-        <v>1.08</v>
+        <v>-1.08</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1244,46 +1266,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-19.28</v>
+        <v>-20.15</v>
       </c>
       <c r="H5">
-        <v>41.62</v>
+        <v>40.1</v>
       </c>
       <c r="I5">
-        <v>-1.25</v>
+        <v>0.65</v>
       </c>
       <c r="J5">
-        <v>2.67</v>
+        <v>-13</v>
       </c>
       <c r="K5">
-        <v>31.38</v>
+        <v>30.26</v>
       </c>
       <c r="L5">
-        <v>-17.48</v>
+        <v>-17.16</v>
       </c>
       <c r="M5">
-        <v>-6.24</v>
+        <v>-6.42</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>686.0700000000001</v>
+        <v>686.96</v>
       </c>
       <c r="Q5">
-        <v>726.78</v>
+        <v>720.95</v>
       </c>
       <c r="R5">
-        <v>622.5599999999999</v>
+        <v>625.72</v>
       </c>
       <c r="S5">
-        <v>633.47</v>
+        <v>633.02</v>
       </c>
       <c r="T5">
-        <v>9.710000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1298,34 +1320,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>53.87</v>
+        <v>51.6</v>
       </c>
       <c r="Z5">
-        <v>16.57</v>
+        <v>14.34</v>
       </c>
       <c r="AA5">
-        <v>28.31</v>
+        <v>25.51</v>
       </c>
       <c r="AB5">
-        <v>-11.74</v>
+        <v>-11.18</v>
       </c>
       <c r="AC5">
-        <v>9.48</v>
+        <v>10.91</v>
       </c>
       <c r="AD5">
-        <v>4.51</v>
+        <v>7.92</v>
       </c>
       <c r="AE5">
-        <v>29.23</v>
+        <v>29.57</v>
       </c>
       <c r="AF5">
-        <v>-96.28</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="AG5">
-        <v>796.48</v>
+        <v>782.46</v>
       </c>
       <c r="AH5">
-        <v>657.0700000000001</v>
+        <v>659.4299999999999</v>
       </c>
       <c r="AI5">
         <v>771.22</v>
@@ -1334,7 +1356,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>19.97</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,10 +1367,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>29.14</v>
+        <v>28.71</v>
       </c>
       <c r="D6">
-        <v>-0.61</v>
+        <v>-1.48</v>
       </c>
       <c r="E6">
         <v>57.9</v>
@@ -1357,46 +1379,46 @@
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-49.67</v>
+        <v>-50.41</v>
       </c>
       <c r="H6">
-        <v>5.89</v>
+        <v>4.32</v>
       </c>
       <c r="I6">
-        <v>-3.03</v>
+        <v>-3.01</v>
       </c>
       <c r="J6">
-        <v>-8.34</v>
+        <v>-10.17</v>
       </c>
       <c r="K6">
-        <v>-10.56</v>
+        <v>-12.44</v>
       </c>
       <c r="L6">
-        <v>-50.03</v>
+        <v>-49.84</v>
       </c>
       <c r="M6">
-        <v>-10.36</v>
+        <v>-10.72</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>29.51</v>
+        <v>29.33</v>
       </c>
       <c r="Q6">
-        <v>29.48</v>
+        <v>29.33</v>
       </c>
       <c r="R6">
-        <v>31.07</v>
+        <v>31.04</v>
       </c>
       <c r="S6">
-        <v>36.44</v>
+        <v>36.34</v>
       </c>
       <c r="T6">
-        <v>-20.03</v>
+        <v>-20.99</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1411,43 +1433,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>41.04</v>
+        <v>37.83</v>
       </c>
       <c r="Z6">
-        <v>-0.5</v>
+        <v>-0.53</v>
       </c>
       <c r="AA6">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="AB6">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="AC6">
-        <v>71.36</v>
+        <v>53.5</v>
       </c>
       <c r="AD6">
-        <v>79.95999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="AE6">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AF6">
-        <v>-49.92</v>
+        <v>-17.42</v>
       </c>
       <c r="AG6">
-        <v>31</v>
+        <v>30.45</v>
       </c>
       <c r="AH6">
-        <v>27.96</v>
+        <v>28.21</v>
       </c>
       <c r="AI6">
-        <v>31.46</v>
+        <v>31.25</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>20.18</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1480,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1323.9</v>
+        <v>1329</v>
       </c>
       <c r="D7">
-        <v>-0.26</v>
+        <v>0.39</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1470,49 +1492,49 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-16.47</v>
+        <v>-16.15</v>
       </c>
       <c r="H7">
-        <v>5.17</v>
+        <v>5.58</v>
       </c>
       <c r="I7">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="J7">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="K7">
-        <v>-2.12</v>
+        <v>-1.96</v>
       </c>
       <c r="L7">
-        <v>-4.05</v>
+        <v>-3.76</v>
       </c>
       <c r="M7">
-        <v>6.66</v>
+        <v>6.81</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P7">
-        <v>1318.2</v>
+        <v>1328</v>
       </c>
       <c r="Q7">
-        <v>1300.5</v>
+        <v>1302.18</v>
       </c>
       <c r="R7">
-        <v>1300.58</v>
+        <v>1300.99</v>
       </c>
       <c r="S7">
-        <v>1401.73</v>
+        <v>1401.17</v>
       </c>
       <c r="T7">
-        <v>-5.55</v>
+        <v>-5.15</v>
       </c>
       <c r="U7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V7" t="s">
         <v>44</v>
@@ -1521,37 +1543,37 @@
         <v>44</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>55.41</v>
+        <v>56.67</v>
       </c>
       <c r="Z7">
-        <v>4.7</v>
+        <v>5.91</v>
       </c>
       <c r="AA7">
-        <v>-0.51</v>
+        <v>0.77</v>
       </c>
       <c r="AB7">
-        <v>5.21</v>
+        <v>5.14</v>
       </c>
       <c r="AC7">
-        <v>90.39</v>
+        <v>86.92</v>
       </c>
       <c r="AD7">
-        <v>87.78</v>
+        <v>91.13</v>
       </c>
       <c r="AE7">
-        <v>22.52</v>
+        <v>22.33</v>
       </c>
       <c r="AF7">
-        <v>-19.92</v>
+        <v>-35.19</v>
       </c>
       <c r="AG7">
-        <v>1343.63</v>
+        <v>1347.05</v>
       </c>
       <c r="AH7">
-        <v>1257.38</v>
+        <v>1257.31</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1560,7 +1582,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>16.31</v>
+        <v>14.17</v>
       </c>
     </row>
   </sheetData>
@@ -1721,12 +1743,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1734,836 +1791,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-6.61</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-9.6</v>
       </c>
-      <c r="E7" s="6">
-        <v>-2.99</v>
+      <c r="D7" s="6">
+        <v>-10.92</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-1.99</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-4.27</v>
       </c>
-      <c r="E8" s="6">
-        <v>-2.28</v>
+      <c r="D8" s="6">
+        <v>-5.41</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>4.98</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>4.7</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.28</v>
+      <c r="D9" s="6">
+        <v>8.51</v>
+      </c>
+      <c r="E9" s="8">
+        <v>3.81</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>21.9</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>2.67</v>
       </c>
-      <c r="E10" s="6">
-        <v>-19.23</v>
+      <c r="D10" s="6">
+        <v>-13</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-15.67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-5.94</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-8.34</v>
       </c>
-      <c r="E11" s="6">
-        <v>-2.4</v>
+      <c r="D11" s="6">
+        <v>-10.17</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.83</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>1.49</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>2.08</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.59</v>
+      <c r="D12" s="6">
+        <v>2.78</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-1.66</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-0.77</v>
       </c>
+      <c r="D13" s="6">
+        <v>-1.64</v>
+      </c>
       <c r="E13" s="7">
-        <v>0.89</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-2.17</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-1.47</v>
       </c>
+      <c r="D14" s="6">
+        <v>-2.11</v>
+      </c>
       <c r="E14" s="7">
-        <v>0.7</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-3.42</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-4.62</v>
       </c>
-      <c r="E15" s="6">
-        <v>-1.2</v>
+      <c r="D15" s="6">
+        <v>-2.25</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.37</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.25</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-1.25</v>
       </c>
-      <c r="E16" s="7">
+      <c r="D16" s="6">
+        <v>0.65</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.03</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.01</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2.56</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3.83</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-28.09</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-26.9</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-26.85</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-26.31</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-23.95</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-21.47</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-17.48</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-17.16</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-50.03</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-49.84</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-4.05</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-3.76</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>3.82</v>
+      </c>
+      <c r="D25" s="6">
+        <v>4.05</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1.13</v>
+      </c>
+      <c r="D26" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D27" s="6">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>31.38</v>
+      </c>
+      <c r="D28" s="6">
+        <v>30.26</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-10.56</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-12.44</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-2.12</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-1.96</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-27.07</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-27.66</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-28.65</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-29.24</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-23.71</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-22.71</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-19.28</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-20.15</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-49.67</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-50.41</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-16.47</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-16.15</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="C37" s="6">
+        <v>27.21</v>
+      </c>
+      <c r="D37" s="6">
+        <v>26.99</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>10.76</v>
+      </c>
+      <c r="D38" s="6">
+        <v>10.67</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>252.75</v>
+      </c>
+      <c r="D39" s="6">
+        <v>256.05</v>
+      </c>
+      <c r="E39" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>694.95</v>
+      </c>
+      <c r="D40" s="6">
+        <v>687.45</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.2</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-3.03</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-2.83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>29.14</v>
+      </c>
+      <c r="D41" s="6">
+        <v>28.71</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="D18" s="5">
-        <v>2.56</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1323.9</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1329</v>
+      </c>
+      <c r="E42" s="8">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-29.05</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-28.09</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>42.52</v>
+      </c>
+      <c r="D43" s="6">
+        <v>40.32</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-27.25</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-26.85</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>43.93</v>
+      </c>
+      <c r="D44" s="6">
+        <v>41.3</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-23.81</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-23.95</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>55.26</v>
+      </c>
+      <c r="D45" s="6">
+        <v>58.2</v>
+      </c>
+      <c r="E45" s="8">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-17.28</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-17.48</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>53.87</v>
+      </c>
+      <c r="D46" s="6">
+        <v>51.6</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-50.58</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-50.03</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>41.04</v>
+      </c>
+      <c r="D47" s="6">
+        <v>37.83</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-5.15</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-4.05</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>55.41</v>
+      </c>
+      <c r="D48" s="6">
+        <v>56.67</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>4.13</v>
-      </c>
-      <c r="D25" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-34.74</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-2.04</v>
+      </c>
+      <c r="E49" s="8">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>2.46</v>
-      </c>
-      <c r="D26" s="5">
-        <v>1.13</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-32.05</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-13.42</v>
+      </c>
+      <c r="E50" s="8">
+        <v>18.63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>10.21</v>
-      </c>
-      <c r="D27" s="5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-72.29000000000001</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-37.79</v>
+      </c>
+      <c r="E51" s="8">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>29.69</v>
-      </c>
-      <c r="D28" s="5">
-        <v>31.38</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-96.28</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-96.29000000000001</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-8.77</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-10.56</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-49.92</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-17.42</v>
+      </c>
+      <c r="E53" s="8">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-2.24</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-2.12</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-27.96</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-27.07</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-28.32</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-28.65</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-23.57</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-23.71</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-20.14</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-19.28</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-49.72</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-49.67</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-16.26</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-16.47</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>27.26</v>
-      </c>
-      <c r="D37" s="5">
-        <v>27.21</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>10.81</v>
-      </c>
-      <c r="D38" s="5">
-        <v>10.76</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>254</v>
-      </c>
-      <c r="D39" s="5">
-        <v>252.75</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>687.55</v>
-      </c>
-      <c r="D40" s="5">
-        <v>694.95</v>
-      </c>
-      <c r="E40" s="7">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>29.32</v>
-      </c>
-      <c r="D41" s="5">
-        <v>29.14</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1327.3</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1323.9</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>43.01</v>
-      </c>
-      <c r="D43" s="5">
-        <v>42.52</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>45.42</v>
-      </c>
-      <c r="D44" s="5">
-        <v>43.93</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>56.66</v>
-      </c>
-      <c r="D45" s="5">
-        <v>55.26</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>51.93</v>
-      </c>
-      <c r="D46" s="5">
-        <v>53.87</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>42.44</v>
-      </c>
-      <c r="D47" s="5">
-        <v>41.04</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>56.42</v>
-      </c>
-      <c r="D48" s="5">
-        <v>55.41</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="5">
-        <v>-51.6</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-34.74</v>
-      </c>
-      <c r="E49" s="7">
-        <v>16.86</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-1.64</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-32.05</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-30.41</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-56.37</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-72.29000000000001</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-15.92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>-96.33</v>
-      </c>
-      <c r="D52" s="5">
-        <v>-96.28</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-47.91</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-49.92</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>-32.39</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C54" s="6">
         <v>-19.92</v>
       </c>
+      <c r="D54" s="6">
+        <v>-35.19</v>
+      </c>
       <c r="E54" s="7">
-        <v>12.47</v>
+        <v>-15.27</v>
       </c>
     </row>
   </sheetData>
@@ -2589,60 +2646,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>62</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>48.7</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>47.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-2.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>5.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-4.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2744,43 +2801,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.06660000000000001</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.005699999999999999</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0624</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.1036</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1108</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1528</v>
+      <c r="A2" s="14">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0101</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.06419999999999999</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1072</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1226</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1589</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,13 +184,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.6 → 48.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.6</t>
+  </si>
+  <si>
+    <t>48.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -276,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -316,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -775,8 +781,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -915,10 +921,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.99</v>
+        <v>27.69</v>
       </c>
       <c r="D2">
-        <v>-0.8100000000000001</v>
+        <v>2.59</v>
       </c>
       <c r="E2">
         <v>37.31</v>
@@ -927,46 +933,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.66</v>
+        <v>-25.78</v>
       </c>
       <c r="H2">
-        <v>17.45</v>
+        <v>20.5</v>
       </c>
       <c r="I2">
-        <v>-1.64</v>
+        <v>1.21</v>
       </c>
       <c r="J2">
-        <v>-10.92</v>
+        <v>-4.32</v>
       </c>
       <c r="K2">
-        <v>4.05</v>
+        <v>6.01</v>
       </c>
       <c r="L2">
-        <v>-26.9</v>
+        <v>-23.61</v>
       </c>
       <c r="M2">
-        <v>-12.26</v>
+        <v>-11.5</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P2">
-        <v>27.23</v>
+        <v>27.29</v>
       </c>
       <c r="Q2">
-        <v>27.35</v>
+        <v>27.32</v>
       </c>
       <c r="R2">
-        <v>28.45</v>
+        <v>28.48</v>
       </c>
       <c r="S2">
-        <v>28.97</v>
+        <v>28.94</v>
       </c>
       <c r="T2">
-        <v>-6.84</v>
+        <v>-4.33</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -981,34 +987,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.32</v>
+        <v>49.29</v>
       </c>
       <c r="Z2">
+        <v>-0.32</v>
+      </c>
+      <c r="AA2">
         <v>-0.37</v>
       </c>
-      <c r="AA2">
-        <v>-0.38</v>
-      </c>
       <c r="AB2">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="AC2">
-        <v>27.29</v>
+        <v>45.76</v>
       </c>
       <c r="AD2">
-        <v>41.71</v>
+        <v>39.33</v>
       </c>
       <c r="AE2">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AF2">
-        <v>-2.04</v>
+        <v>43.46</v>
       </c>
       <c r="AG2">
-        <v>27.9</v>
+        <v>27.74</v>
       </c>
       <c r="AH2">
-        <v>26.79</v>
+        <v>26.91</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1017,7 +1023,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>15.26</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1028,10 +1034,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.67</v>
+        <v>10.72</v>
       </c>
       <c r="D3">
-        <v>-0.84</v>
+        <v>0.47</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1040,46 +1046,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-29.24</v>
+        <v>-28.91</v>
       </c>
       <c r="H3">
-        <v>20.29</v>
+        <v>20.86</v>
       </c>
       <c r="I3">
-        <v>-2.11</v>
+        <v>-1.02</v>
       </c>
       <c r="J3">
-        <v>-5.41</v>
+        <v>-4.37</v>
       </c>
       <c r="K3">
-        <v>2.4</v>
+        <v>4.59</v>
       </c>
       <c r="L3">
-        <v>-26.31</v>
+        <v>-25.14</v>
       </c>
       <c r="M3">
-        <v>-15.89</v>
+        <v>-15.61</v>
       </c>
       <c r="N3">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P3">
-        <v>10.8</v>
+        <v>10.77</v>
       </c>
       <c r="Q3">
-        <v>10.87</v>
+        <v>10.85</v>
       </c>
       <c r="R3">
-        <v>11.05</v>
+        <v>11.06</v>
       </c>
       <c r="S3">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
       <c r="T3">
-        <v>-6.46</v>
+        <v>-5.9</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1094,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.3</v>
+        <v>43.33</v>
       </c>
       <c r="Z3">
         <v>-0.08</v>
@@ -1106,31 +1112,31 @@
         <v>-0.01</v>
       </c>
       <c r="AC3">
-        <v>29.51</v>
+        <v>19.13</v>
       </c>
       <c r="AD3">
-        <v>47.16</v>
+        <v>34.11</v>
       </c>
       <c r="AE3">
         <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>-13.42</v>
+        <v>50.23</v>
       </c>
       <c r="AG3">
-        <v>11.13</v>
+        <v>11.1</v>
       </c>
       <c r="AH3">
-        <v>10.6</v>
+        <v>10.59</v>
       </c>
       <c r="AI3">
-        <v>11.5</v>
+        <v>11.49</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>20.83</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1141,10 +1147,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>256.05</v>
+        <v>255.6</v>
       </c>
       <c r="D4">
-        <v>1.31</v>
+        <v>-0.18</v>
       </c>
       <c r="E4">
         <v>331.3</v>
@@ -1153,46 +1159,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-22.71</v>
+        <v>-22.85</v>
       </c>
       <c r="H4">
-        <v>14.26</v>
+        <v>14.06</v>
       </c>
       <c r="I4">
-        <v>-2.25</v>
+        <v>-2.85</v>
       </c>
       <c r="J4">
-        <v>8.51</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K4">
-        <v>9.359999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="L4">
-        <v>-21.47</v>
+        <v>-21.35</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>256.54</v>
+        <v>255.04</v>
       </c>
       <c r="Q4">
-        <v>247.95</v>
+        <v>248.95</v>
       </c>
       <c r="R4">
-        <v>241.82</v>
+        <v>242.23</v>
       </c>
       <c r="S4">
-        <v>261.22</v>
+        <v>260.97</v>
       </c>
       <c r="T4">
-        <v>-1.98</v>
+        <v>-2.06</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1207,34 +1213,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>58.2</v>
+        <v>57.64</v>
       </c>
       <c r="Z4">
-        <v>5.06</v>
+        <v>4.83</v>
       </c>
       <c r="AA4">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="AB4">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="AC4">
-        <v>45.29</v>
+        <v>43.71</v>
       </c>
       <c r="AD4">
-        <v>52.67</v>
+        <v>45.86</v>
       </c>
       <c r="AE4">
-        <v>6.08</v>
+        <v>6.32</v>
       </c>
       <c r="AF4">
-        <v>-37.79</v>
+        <v>126.25</v>
       </c>
       <c r="AG4">
-        <v>270.27</v>
+        <v>270.73</v>
       </c>
       <c r="AH4">
-        <v>225.63</v>
+        <v>227.17</v>
       </c>
       <c r="AI4">
         <v>245</v>
@@ -1243,7 +1249,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>36.06</v>
+        <v>35.28</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1254,10 +1260,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>687.45</v>
+        <v>677.85</v>
       </c>
       <c r="D5">
-        <v>-1.08</v>
+        <v>-1.4</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1266,46 +1272,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-20.15</v>
+        <v>-21.27</v>
       </c>
       <c r="H5">
-        <v>40.1</v>
+        <v>38.14</v>
       </c>
       <c r="I5">
-        <v>0.65</v>
+        <v>-0.54</v>
       </c>
       <c r="J5">
-        <v>-13</v>
+        <v>-15.7</v>
       </c>
       <c r="K5">
-        <v>30.26</v>
+        <v>30.02</v>
       </c>
       <c r="L5">
-        <v>-17.16</v>
+        <v>-18.85</v>
       </c>
       <c r="M5">
-        <v>-6.42</v>
+        <v>-6.67</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P5">
-        <v>686.96</v>
+        <v>686.22</v>
       </c>
       <c r="Q5">
-        <v>720.95</v>
+        <v>715.17</v>
       </c>
       <c r="R5">
-        <v>625.72</v>
+        <v>628.67</v>
       </c>
       <c r="S5">
-        <v>633.02</v>
+        <v>632.53</v>
       </c>
       <c r="T5">
-        <v>8.6</v>
+        <v>7.16</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1320,43 +1326,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>51.6</v>
+        <v>48.77</v>
       </c>
       <c r="Z5">
-        <v>14.34</v>
+        <v>11.66</v>
       </c>
       <c r="AA5">
-        <v>25.51</v>
+        <v>22.74</v>
       </c>
       <c r="AB5">
-        <v>-11.18</v>
+        <v>-11.09</v>
       </c>
       <c r="AC5">
-        <v>10.91</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="AD5">
-        <v>7.92</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AE5">
-        <v>29.57</v>
+        <v>28.34</v>
       </c>
       <c r="AF5">
-        <v>-96.29000000000001</v>
+        <v>-96.56</v>
       </c>
       <c r="AG5">
-        <v>782.46</v>
+        <v>769.3099999999999</v>
       </c>
       <c r="AH5">
-        <v>659.4299999999999</v>
+        <v>661.03</v>
       </c>
       <c r="AI5">
-        <v>771.22</v>
+        <v>766.08</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>18</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1367,10 +1373,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>28.71</v>
+        <v>29.01</v>
       </c>
       <c r="D6">
-        <v>-1.48</v>
+        <v>1.04</v>
       </c>
       <c r="E6">
         <v>57.9</v>
@@ -1379,46 +1385,46 @@
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-50.41</v>
+        <v>-49.9</v>
       </c>
       <c r="H6">
-        <v>4.32</v>
+        <v>5.41</v>
       </c>
       <c r="I6">
         <v>-3.01</v>
       </c>
       <c r="J6">
-        <v>-10.17</v>
+        <v>-8.66</v>
       </c>
       <c r="K6">
-        <v>-12.44</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L6">
-        <v>-49.84</v>
+        <v>-48.46</v>
       </c>
       <c r="M6">
-        <v>-10.72</v>
+        <v>-10.32</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>29.33</v>
+        <v>29.15</v>
       </c>
       <c r="Q6">
-        <v>29.33</v>
+        <v>29.27</v>
       </c>
       <c r="R6">
-        <v>31.04</v>
+        <v>31.02</v>
       </c>
       <c r="S6">
-        <v>36.34</v>
+        <v>36.24</v>
       </c>
       <c r="T6">
-        <v>-20.99</v>
+        <v>-19.95</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1433,34 +1439,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>37.83</v>
+        <v>41.28</v>
       </c>
       <c r="Z6">
-        <v>-0.53</v>
+        <v>-0.52</v>
       </c>
       <c r="AA6">
-        <v>-0.59</v>
+        <v>-0.57</v>
       </c>
       <c r="AB6">
         <v>0.06</v>
       </c>
       <c r="AC6">
-        <v>53.5</v>
+        <v>44.79</v>
       </c>
       <c r="AD6">
-        <v>69.16</v>
+        <v>56.55</v>
       </c>
       <c r="AE6">
         <v>0.8</v>
       </c>
       <c r="AF6">
-        <v>-17.42</v>
+        <v>-31.02</v>
       </c>
       <c r="AG6">
-        <v>30.45</v>
+        <v>30.29</v>
       </c>
       <c r="AH6">
-        <v>28.21</v>
+        <v>28.24</v>
       </c>
       <c r="AI6">
         <v>31.25</v>
@@ -1469,7 +1475,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>22.68</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1480,10 +1486,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1329</v>
+        <v>1317</v>
       </c>
       <c r="D7">
-        <v>0.39</v>
+        <v>-0.9</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1492,46 +1498,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-16.15</v>
+        <v>-16.91</v>
       </c>
       <c r="H7">
-        <v>5.58</v>
+        <v>4.62</v>
       </c>
       <c r="I7">
-        <v>3.83</v>
+        <v>-0.6</v>
       </c>
       <c r="J7">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="K7">
-        <v>-1.96</v>
+        <v>-1</v>
       </c>
       <c r="L7">
-        <v>-3.76</v>
+        <v>-4.39</v>
       </c>
       <c r="M7">
-        <v>6.81</v>
+        <v>6.27</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P7">
-        <v>1328</v>
+        <v>1326.4</v>
       </c>
       <c r="Q7">
-        <v>1302.18</v>
+        <v>1303.2</v>
       </c>
       <c r="R7">
-        <v>1300.99</v>
+        <v>1301.19</v>
       </c>
       <c r="S7">
-        <v>1401.17</v>
+        <v>1400.53</v>
       </c>
       <c r="T7">
-        <v>-5.15</v>
+        <v>-5.96</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1546,34 +1552,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>56.67</v>
+        <v>52.9</v>
       </c>
       <c r="Z7">
-        <v>5.91</v>
+        <v>5.83</v>
       </c>
       <c r="AA7">
-        <v>0.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB7">
-        <v>5.14</v>
+        <v>4.05</v>
       </c>
       <c r="AC7">
-        <v>86.92</v>
+        <v>80.63</v>
       </c>
       <c r="AD7">
-        <v>91.13</v>
+        <v>85.98</v>
       </c>
       <c r="AE7">
-        <v>22.33</v>
+        <v>22.29</v>
       </c>
       <c r="AF7">
-        <v>-35.19</v>
+        <v>-21.34</v>
       </c>
       <c r="AG7">
-        <v>1347.05</v>
+        <v>1348.46</v>
       </c>
       <c r="AH7">
-        <v>1257.31</v>
+        <v>1257.94</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1582,7 +1588,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>14.17</v>
+        <v>12.69</v>
       </c>
     </row>
   </sheetData>
@@ -1723,7 +1729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1763,7 +1769,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1775,15 +1781,15 @@
         <v>56</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1795,16 +1801,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1815,13 +1821,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.6</v>
+        <v>-10.92</v>
       </c>
       <c r="D7" s="6">
-        <v>-10.92</v>
+        <v>-4.32</v>
       </c>
       <c r="E7" s="7">
-        <v>-1.32</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1832,13 +1838,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-4.27</v>
+        <v>-5.41</v>
       </c>
       <c r="D8" s="6">
-        <v>-5.41</v>
+        <v>-4.37</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.14</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1849,13 +1855,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>4.7</v>
+        <v>8.51</v>
       </c>
       <c r="D9" s="6">
-        <v>8.51</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E9" s="8">
-        <v>3.81</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1866,13 +1872,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>2.67</v>
+        <v>-13</v>
       </c>
       <c r="D10" s="6">
-        <v>-13</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-15.67</v>
+        <v>-15.7</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1883,13 +1889,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-8.34</v>
+        <v>-10.17</v>
       </c>
       <c r="D11" s="6">
-        <v>-10.17</v>
+        <v>-8.66</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.83</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1900,13 +1906,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="D12" s="6">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="E12" s="8">
-        <v>0.7</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1917,13 +1923,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.77</v>
+        <v>-1.64</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.64</v>
+        <v>1.21</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.87</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1934,13 +1940,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.47</v>
+        <v>-2.11</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.11</v>
+        <v>-1.02</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.64</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1951,13 +1957,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.62</v>
+        <v>-2.25</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.25</v>
+        <v>-2.85</v>
       </c>
       <c r="E15" s="8">
-        <v>2.37</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1968,659 +1974,676 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.25</v>
+        <v>0.65</v>
       </c>
       <c r="D16" s="6">
-        <v>0.65</v>
+        <v>-0.54</v>
       </c>
       <c r="E16" s="8">
-        <v>1.9</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.03</v>
+        <v>3.83</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.01</v>
+        <v>-0.6</v>
       </c>
       <c r="E17" s="8">
-        <v>0.02</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>2.56</v>
+        <v>-26.9</v>
       </c>
       <c r="D18" s="6">
-        <v>3.83</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.27</v>
+        <v>-23.61</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.29</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-28.09</v>
+        <v>-26.31</v>
       </c>
       <c r="D19" s="6">
-        <v>-26.9</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.19</v>
+        <v>-25.14</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.17</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-26.85</v>
+        <v>-21.47</v>
       </c>
       <c r="D20" s="6">
-        <v>-26.31</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.54</v>
+        <v>-21.35</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-23.95</v>
+        <v>-17.16</v>
       </c>
       <c r="D21" s="6">
-        <v>-21.47</v>
+        <v>-18.85</v>
       </c>
       <c r="E21" s="8">
-        <v>2.48</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-17.48</v>
+        <v>-49.84</v>
       </c>
       <c r="D22" s="6">
-        <v>-17.16</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.32</v>
+        <v>-48.46</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.38</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-50.03</v>
+        <v>-3.76</v>
       </c>
       <c r="D23" s="6">
-        <v>-49.84</v>
+        <v>-4.39</v>
       </c>
       <c r="E23" s="8">
-        <v>0.19</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.05</v>
+        <v>4.05</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.76</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.29</v>
+        <v>6.01</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.96</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>3.82</v>
+        <v>2.4</v>
       </c>
       <c r="D25" s="6">
-        <v>4.05</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.23</v>
+        <v>4.59</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>1.13</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D26" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.27</v>
+        <v>9.67</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.31</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>9.199999999999999</v>
+        <v>30.26</v>
       </c>
       <c r="D27" s="6">
-        <v>9.359999999999999</v>
+        <v>30.02</v>
       </c>
       <c r="E27" s="8">
-        <v>0.16</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>31.38</v>
+        <v>-12.44</v>
       </c>
       <c r="D28" s="6">
-        <v>30.26</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.12</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-10.56</v>
+        <v>-1.96</v>
       </c>
       <c r="D29" s="6">
-        <v>-12.44</v>
+        <v>-1</v>
       </c>
       <c r="E29" s="7">
-        <v>-1.88</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-2.12</v>
+        <v>-27.66</v>
       </c>
       <c r="D30" s="6">
-        <v>-1.96</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.16</v>
+        <v>-25.78</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.88</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-27.07</v>
+        <v>-29.24</v>
       </c>
       <c r="D31" s="6">
-        <v>-27.66</v>
+        <v>-28.91</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.59</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-28.65</v>
+        <v>-22.71</v>
       </c>
       <c r="D32" s="6">
-        <v>-29.24</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.59</v>
+        <v>-22.85</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-23.71</v>
+        <v>-20.15</v>
       </c>
       <c r="D33" s="6">
-        <v>-22.71</v>
+        <v>-21.27</v>
       </c>
       <c r="E33" s="8">
-        <v>1</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-19.28</v>
+        <v>-50.41</v>
       </c>
       <c r="D34" s="6">
-        <v>-20.15</v>
+        <v>-49.9</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.87</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-49.67</v>
+        <v>-16.15</v>
       </c>
       <c r="D35" s="6">
-        <v>-50.41</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.74</v>
+        <v>-16.91</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>-16.47</v>
+        <v>26.99</v>
       </c>
       <c r="D36" s="6">
-        <v>-16.15</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.32</v>
+        <v>27.69</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>27.21</v>
+        <v>10.67</v>
       </c>
       <c r="D37" s="6">
-        <v>26.99</v>
+        <v>10.72</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.22</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>10.76</v>
+        <v>256.05</v>
       </c>
       <c r="D38" s="6">
-        <v>10.67</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.09</v>
+        <v>255.6</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>252.75</v>
+        <v>687.45</v>
       </c>
       <c r="D39" s="6">
-        <v>256.05</v>
+        <v>677.85</v>
       </c>
       <c r="E39" s="8">
-        <v>3.3</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>694.95</v>
+        <v>28.71</v>
       </c>
       <c r="D40" s="6">
-        <v>687.45</v>
+        <v>29.01</v>
       </c>
       <c r="E40" s="7">
-        <v>-7.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>29.14</v>
+        <v>1329</v>
       </c>
       <c r="D41" s="6">
-        <v>28.71</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.43</v>
+        <v>1317</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-12</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C42" s="6">
-        <v>1323.9</v>
+        <v>34</v>
       </c>
       <c r="D42" s="6">
-        <v>1329</v>
-      </c>
-      <c r="E42" s="8">
-        <v>5.1</v>
+        <v>50</v>
+      </c>
+      <c r="E42" s="7">
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C43" s="6">
-        <v>42.52</v>
+        <v>50</v>
       </c>
       <c r="D43" s="6">
-        <v>40.32</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-2.2</v>
+        <v>34</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-16</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>43.93</v>
+        <v>40.32</v>
       </c>
       <c r="D44" s="6">
-        <v>41.3</v>
+        <v>49.29</v>
       </c>
       <c r="E44" s="7">
-        <v>-2.63</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>55.26</v>
+        <v>41.3</v>
       </c>
       <c r="D45" s="6">
-        <v>58.2</v>
-      </c>
-      <c r="E45" s="8">
-        <v>2.94</v>
+        <v>43.33</v>
+      </c>
+      <c r="E45" s="7">
+        <v>2.03</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>53.87</v>
+        <v>58.2</v>
       </c>
       <c r="D46" s="6">
-        <v>51.6</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-2.27</v>
+        <v>57.64</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>41.04</v>
+        <v>51.6</v>
       </c>
       <c r="D47" s="6">
-        <v>37.83</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3.21</v>
+        <v>48.77</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.83</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>55.41</v>
+        <v>37.83</v>
       </c>
       <c r="D48" s="6">
-        <v>56.67</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.26</v>
+        <v>41.28</v>
+      </c>
+      <c r="E48" s="7">
+        <v>3.45</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>-34.74</v>
+        <v>56.67</v>
       </c>
       <c r="D49" s="6">
-        <v>-2.04</v>
+        <v>52.9</v>
       </c>
       <c r="E49" s="8">
-        <v>32.7</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>-32.05</v>
+        <v>-2.04</v>
       </c>
       <c r="D50" s="6">
-        <v>-13.42</v>
-      </c>
-      <c r="E50" s="8">
-        <v>18.63</v>
+        <v>43.46</v>
+      </c>
+      <c r="E50" s="7">
+        <v>45.5</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-72.29000000000001</v>
+        <v>-13.42</v>
       </c>
       <c r="D51" s="6">
-        <v>-37.79</v>
-      </c>
-      <c r="E51" s="8">
-        <v>34.5</v>
+        <v>50.23</v>
+      </c>
+      <c r="E51" s="7">
+        <v>63.65</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>-96.28</v>
+        <v>-37.79</v>
       </c>
       <c r="D52" s="6">
-        <v>-96.29000000000001</v>
+        <v>126.25</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.01</v>
+        <v>164.04</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>-49.92</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="D53" s="6">
-        <v>-17.42</v>
+        <v>-96.56</v>
       </c>
       <c r="E53" s="8">
-        <v>32.5</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-19.92</v>
+        <v>-17.42</v>
       </c>
       <c r="D54" s="6">
+        <v>-31.02</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-13.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
         <v>-35.19</v>
       </c>
-      <c r="E54" s="7">
-        <v>-15.27</v>
+      <c r="D55" s="6">
+        <v>-21.34</v>
+      </c>
+      <c r="E55" s="7">
+        <v>13.85</v>
       </c>
     </row>
   </sheetData>
@@ -2650,28 +2673,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2685,16 +2708,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>47.7</v>
+        <v>48.9</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.7</v>
+        <v>-3.9</v>
       </c>
       <c r="G2" s="11">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="H2" s="11">
         <v>58.2</v>
@@ -2822,22 +2845,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.06809999999999999</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0101</v>
+        <v>0.0095</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.06419999999999999</v>
+        <v>-0.0667</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1072</v>
+        <v>-0.1032</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1226</v>
+        <v>-0.115</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.1589</v>
+        <v>-0.1561</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.6 → 48.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.6</t>
-  </si>
-  <si>
-    <t>48.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,18 +371,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -781,8 +753,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -921,10 +892,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.69</v>
+        <v>27.51</v>
       </c>
       <c r="D2">
-        <v>2.59</v>
+        <v>-0.65</v>
       </c>
       <c r="E2">
         <v>37.31</v>
@@ -933,46 +904,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-25.78</v>
+        <v>-26.27</v>
       </c>
       <c r="H2">
-        <v>20.5</v>
+        <v>19.71</v>
       </c>
       <c r="I2">
-        <v>1.21</v>
+        <v>0.7</v>
       </c>
       <c r="J2">
-        <v>-4.32</v>
+        <v>-2.48</v>
       </c>
       <c r="K2">
-        <v>6.01</v>
+        <v>7.34</v>
       </c>
       <c r="L2">
-        <v>-23.61</v>
+        <v>-22.85</v>
       </c>
       <c r="M2">
-        <v>-11.5</v>
+        <v>-11.49</v>
       </c>
       <c r="N2">
         <v>50</v>
       </c>
       <c r="O2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>27.29</v>
+        <v>27.33</v>
       </c>
       <c r="Q2">
-        <v>27.32</v>
+        <v>27.33</v>
       </c>
       <c r="R2">
-        <v>28.48</v>
+        <v>28.5</v>
       </c>
       <c r="S2">
-        <v>28.94</v>
+        <v>28.92</v>
       </c>
       <c r="T2">
-        <v>-4.33</v>
+        <v>-4.86</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -987,31 +958,31 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>49.29</v>
+        <v>47.32</v>
       </c>
       <c r="Z2">
-        <v>-0.32</v>
+        <v>-0.29</v>
       </c>
       <c r="AA2">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="AB2">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>45.76</v>
+        <v>59.35</v>
       </c>
       <c r="AD2">
-        <v>39.33</v>
+        <v>44.13</v>
       </c>
       <c r="AE2">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="AF2">
-        <v>43.46</v>
+        <v>-38.04</v>
       </c>
       <c r="AG2">
-        <v>27.74</v>
+        <v>27.76</v>
       </c>
       <c r="AH2">
         <v>26.91</v>
@@ -1023,7 +994,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>16.78</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1005,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.72</v>
+        <v>10.6</v>
       </c>
       <c r="D3">
-        <v>0.47</v>
+        <v>-1.12</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1046,46 +1017,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-28.91</v>
+        <v>-29.71</v>
       </c>
       <c r="H3">
-        <v>20.86</v>
+        <v>19.5</v>
       </c>
       <c r="I3">
-        <v>-1.02</v>
+        <v>-2.84</v>
       </c>
       <c r="J3">
-        <v>-4.37</v>
+        <v>-4.33</v>
       </c>
       <c r="K3">
-        <v>4.59</v>
+        <v>5.58</v>
       </c>
       <c r="L3">
-        <v>-25.14</v>
+        <v>-26.54</v>
       </c>
       <c r="M3">
-        <v>-15.61</v>
+        <v>-15.51</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P3">
-        <v>10.77</v>
+        <v>10.71</v>
       </c>
       <c r="Q3">
-        <v>10.85</v>
+        <v>10.83</v>
       </c>
       <c r="R3">
         <v>11.06</v>
       </c>
       <c r="S3">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
       <c r="T3">
-        <v>-5.9</v>
+        <v>-6.82</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1100,43 +1071,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>43.33</v>
+        <v>39.77</v>
       </c>
       <c r="Z3">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AA3">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AB3">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>19.13</v>
+        <v>6.23</v>
       </c>
       <c r="AD3">
-        <v>34.11</v>
+        <v>18.29</v>
       </c>
       <c r="AE3">
         <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>50.23</v>
+        <v>21.32</v>
       </c>
       <c r="AG3">
-        <v>11.1</v>
+        <v>11.08</v>
       </c>
       <c r="AH3">
-        <v>10.59</v>
+        <v>10.57</v>
       </c>
       <c r="AI3">
-        <v>11.49</v>
+        <v>11.41</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>22.93</v>
+        <v>26.21</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1118,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>255.6</v>
+        <v>249.05</v>
       </c>
       <c r="D4">
-        <v>-0.18</v>
+        <v>-2.56</v>
       </c>
       <c r="E4">
         <v>331.3</v>
@@ -1159,46 +1130,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-22.85</v>
+        <v>-24.83</v>
       </c>
       <c r="H4">
-        <v>14.06</v>
+        <v>11.13</v>
       </c>
       <c r="I4">
-        <v>-2.85</v>
+        <v>-3.02</v>
       </c>
       <c r="J4">
-        <v>8.039999999999999</v>
+        <v>5.69</v>
       </c>
       <c r="K4">
-        <v>9.67</v>
+        <v>7.06</v>
       </c>
       <c r="L4">
-        <v>-21.35</v>
+        <v>-22.33</v>
       </c>
       <c r="M4">
-        <v>0.95</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>255.04</v>
+        <v>253.49</v>
       </c>
       <c r="Q4">
-        <v>248.95</v>
+        <v>249.25</v>
       </c>
       <c r="R4">
-        <v>242.23</v>
+        <v>242.5</v>
       </c>
       <c r="S4">
-        <v>260.97</v>
+        <v>260.69</v>
       </c>
       <c r="T4">
-        <v>-2.06</v>
+        <v>-4.46</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1213,34 +1184,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>57.64</v>
+        <v>50.13</v>
       </c>
       <c r="Z4">
-        <v>4.83</v>
+        <v>4.08</v>
       </c>
       <c r="AA4">
-        <v>4.62</v>
+        <v>4.51</v>
       </c>
       <c r="AB4">
-        <v>0.21</v>
+        <v>-0.43</v>
       </c>
       <c r="AC4">
-        <v>43.71</v>
+        <v>31.26</v>
       </c>
       <c r="AD4">
-        <v>45.86</v>
+        <v>40.08</v>
       </c>
       <c r="AE4">
-        <v>6.32</v>
+        <v>6.34</v>
       </c>
       <c r="AF4">
-        <v>126.25</v>
+        <v>-29.29</v>
       </c>
       <c r="AG4">
-        <v>270.73</v>
+        <v>270.85</v>
       </c>
       <c r="AH4">
-        <v>227.17</v>
+        <v>227.65</v>
       </c>
       <c r="AI4">
         <v>245</v>
@@ -1249,7 +1220,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>35.28</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1231,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>677.85</v>
+        <v>681</v>
       </c>
       <c r="D5">
-        <v>-1.4</v>
+        <v>0.46</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1272,46 +1243,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-21.27</v>
+        <v>-20.9</v>
       </c>
       <c r="H5">
-        <v>38.14</v>
+        <v>38.78</v>
       </c>
       <c r="I5">
-        <v>-0.54</v>
+        <v>-0.34</v>
       </c>
       <c r="J5">
-        <v>-15.7</v>
+        <v>-14.16</v>
       </c>
       <c r="K5">
-        <v>30.02</v>
+        <v>31.43</v>
       </c>
       <c r="L5">
-        <v>-18.85</v>
+        <v>-17.72</v>
       </c>
       <c r="M5">
-        <v>-6.67</v>
+        <v>-6.61</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P5">
-        <v>686.22</v>
+        <v>685.76</v>
       </c>
       <c r="Q5">
-        <v>715.17</v>
+        <v>710.86</v>
       </c>
       <c r="R5">
-        <v>628.67</v>
+        <v>631.78</v>
       </c>
       <c r="S5">
-        <v>632.53</v>
+        <v>631.98</v>
       </c>
       <c r="T5">
-        <v>7.16</v>
+        <v>7.76</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1326,43 +1297,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>48.77</v>
+        <v>49.74</v>
       </c>
       <c r="Z5">
-        <v>11.66</v>
+        <v>9.68</v>
       </c>
       <c r="AA5">
-        <v>22.74</v>
+        <v>20.13</v>
       </c>
       <c r="AB5">
-        <v>-11.09</v>
+        <v>-10.45</v>
       </c>
       <c r="AC5">
-        <v>8.210000000000001</v>
+        <v>3.69</v>
       </c>
       <c r="AD5">
-        <v>9.529999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AE5">
-        <v>28.34</v>
+        <v>27.19</v>
       </c>
       <c r="AF5">
-        <v>-96.56</v>
+        <v>-91.73</v>
       </c>
       <c r="AG5">
-        <v>769.3099999999999</v>
+        <v>761.12</v>
       </c>
       <c r="AH5">
-        <v>661.03</v>
+        <v>660.59</v>
       </c>
       <c r="AI5">
-        <v>766.08</v>
+        <v>763.77</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>16.29</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,7 +1347,7 @@
         <v>29.01</v>
       </c>
       <c r="D6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>57.9</v>
@@ -1391,19 +1362,19 @@
         <v>5.41</v>
       </c>
       <c r="I6">
-        <v>-3.01</v>
+        <v>-1.86</v>
       </c>
       <c r="J6">
-        <v>-8.66</v>
+        <v>-4.29</v>
       </c>
       <c r="K6">
-        <v>-9.960000000000001</v>
+        <v>-7.61</v>
       </c>
       <c r="L6">
-        <v>-48.46</v>
+        <v>-49.77</v>
       </c>
       <c r="M6">
-        <v>-10.32</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1412,19 +1383,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>29.15</v>
+        <v>29.04</v>
       </c>
       <c r="Q6">
-        <v>29.27</v>
+        <v>29.22</v>
       </c>
       <c r="R6">
-        <v>31.02</v>
+        <v>31</v>
       </c>
       <c r="S6">
-        <v>36.24</v>
+        <v>36.15</v>
       </c>
       <c r="T6">
-        <v>-19.95</v>
+        <v>-19.74</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1442,31 +1413,31 @@
         <v>41.28</v>
       </c>
       <c r="Z6">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="AA6">
-        <v>-0.57</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AB6">
         <v>0.06</v>
       </c>
       <c r="AC6">
-        <v>44.79</v>
+        <v>38.53</v>
       </c>
       <c r="AD6">
-        <v>56.55</v>
+        <v>45.61</v>
       </c>
       <c r="AE6">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AF6">
-        <v>-31.02</v>
+        <v>-38.32</v>
       </c>
       <c r="AG6">
-        <v>30.29</v>
+        <v>30.19</v>
       </c>
       <c r="AH6">
-        <v>28.24</v>
+        <v>28.25</v>
       </c>
       <c r="AI6">
         <v>31.25</v>
@@ -1475,7 +1446,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>22.72</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1457,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1317</v>
+        <v>1310</v>
       </c>
       <c r="D7">
-        <v>-0.9</v>
+        <v>-0.53</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1498,46 +1469,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-16.91</v>
+        <v>-17.35</v>
       </c>
       <c r="H7">
-        <v>4.62</v>
+        <v>4.07</v>
       </c>
       <c r="I7">
-        <v>-0.6</v>
+        <v>-1.86</v>
       </c>
       <c r="J7">
-        <v>1.66</v>
+        <v>1.03</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>-1.49</v>
       </c>
       <c r="L7">
-        <v>-4.39</v>
+        <v>-3.4</v>
       </c>
       <c r="M7">
-        <v>6.27</v>
+        <v>5.89</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P7">
-        <v>1326.4</v>
+        <v>1321.44</v>
       </c>
       <c r="Q7">
-        <v>1303.2</v>
+        <v>1302.34</v>
       </c>
       <c r="R7">
-        <v>1301.19</v>
+        <v>1301.43</v>
       </c>
       <c r="S7">
-        <v>1400.53</v>
+        <v>1399.69</v>
       </c>
       <c r="T7">
-        <v>-5.96</v>
+        <v>-6.41</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1552,34 +1523,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>52.9</v>
+        <v>50.78</v>
       </c>
       <c r="Z7">
-        <v>5.83</v>
+        <v>5.15</v>
       </c>
       <c r="AA7">
-        <v>1.78</v>
+        <v>2.46</v>
       </c>
       <c r="AB7">
-        <v>4.05</v>
+        <v>2.69</v>
       </c>
       <c r="AC7">
-        <v>80.63</v>
+        <v>72.36</v>
       </c>
       <c r="AD7">
-        <v>85.98</v>
+        <v>79.97</v>
       </c>
       <c r="AE7">
-        <v>22.29</v>
+        <v>21.84</v>
       </c>
       <c r="AF7">
-        <v>-21.34</v>
+        <v>-11.49</v>
       </c>
       <c r="AG7">
-        <v>1348.46</v>
+        <v>1346.32</v>
       </c>
       <c r="AH7">
-        <v>1257.94</v>
+        <v>1258.36</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1588,7 +1559,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>12.69</v>
+        <v>12.49</v>
       </c>
     </row>
   </sheetData>
@@ -1729,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1749,47 +1720,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1797,853 +1733,785 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-10.92</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-4.32</v>
       </c>
-      <c r="E7" s="7">
-        <v>6.6</v>
+      <c r="D7" s="5">
+        <v>-2.48</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.84</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.41</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-4.37</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.04</v>
+      <c r="D8" s="5">
+        <v>-4.33</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.04</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>8.51</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>8.039999999999999</v>
       </c>
-      <c r="E9" s="8">
-        <v>-0.47</v>
+      <c r="D9" s="5">
+        <v>5.69</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-13</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-15.7</v>
       </c>
-      <c r="E10" s="8">
-        <v>-2.7</v>
+      <c r="D10" s="5">
+        <v>-14.16</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.54</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-10.17</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-8.66</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.51</v>
+      <c r="D11" s="5">
+        <v>-4.29</v>
+      </c>
+      <c r="E11" s="6">
+        <v>4.37</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>2.78</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>1.66</v>
       </c>
-      <c r="E12" s="8">
-        <v>-1.12</v>
+      <c r="D12" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>-1.64</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>1.21</v>
       </c>
+      <c r="D13" s="5">
+        <v>0.7</v>
+      </c>
       <c r="E13" s="7">
-        <v>2.85</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-1.02</v>
       </c>
+      <c r="D14" s="5">
+        <v>-2.84</v>
+      </c>
       <c r="E14" s="7">
-        <v>1.09</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-2.25</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-2.85</v>
       </c>
-      <c r="E15" s="8">
+      <c r="D15" s="5">
+        <v>-3.02</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.54</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.34</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-3.01</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-1.86</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
         <v>-0.6</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D18" s="5">
+        <v>-1.86</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-23.61</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-22.85</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-25.14</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-26.54</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-21.35</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-22.33</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.54</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-18.85</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-17.72</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-48.46</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-49.77</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>3.83</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.6</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-4.43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-4.39</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-3.4</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-26.9</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-23.61</v>
-      </c>
-      <c r="E18" s="7">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>6.01</v>
+      </c>
+      <c r="D25" s="5">
+        <v>7.34</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-26.31</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-25.14</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>4.59</v>
+      </c>
+      <c r="D26" s="5">
+        <v>5.58</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-21.47</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-21.35</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>9.67</v>
+      </c>
+      <c r="D27" s="5">
+        <v>7.06</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-17.16</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-18.85</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>30.02</v>
+      </c>
+      <c r="D28" s="5">
+        <v>31.43</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-49.84</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-48.46</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-7.61</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-3.76</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-1</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-1.49</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>4.05</v>
-      </c>
-      <c r="D24" s="6">
-        <v>6.01</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-25.78</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-26.27</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="D25" s="6">
-        <v>4.59</v>
-      </c>
-      <c r="E25" s="7">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-28.91</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-29.71</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="D26" s="6">
-        <v>9.67</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-22.85</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-24.83</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>30.26</v>
-      </c>
-      <c r="D27" s="6">
-        <v>30.02</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-21.27</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-20.9</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-16.91</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-17.35</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>27.69</v>
+      </c>
+      <c r="D36" s="5">
+        <v>27.51</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>10.72</v>
+      </c>
+      <c r="D37" s="5">
+        <v>10.6</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>255.6</v>
+      </c>
+      <c r="D38" s="5">
+        <v>249.05</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-6.55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>677.85</v>
+      </c>
+      <c r="D39" s="5">
+        <v>681</v>
+      </c>
+      <c r="E39" s="6">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1317</v>
+      </c>
+      <c r="D40" s="5">
+        <v>1310</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>49.29</v>
+      </c>
+      <c r="D41" s="5">
+        <v>47.32</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="5">
+        <v>43.33</v>
+      </c>
+      <c r="D42" s="5">
+        <v>39.77</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-3.56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>57.64</v>
+      </c>
+      <c r="D43" s="5">
+        <v>50.13</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-7.51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>48.77</v>
+      </c>
+      <c r="D44" s="5">
+        <v>49.74</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>52.9</v>
+      </c>
+      <c r="D45" s="5">
+        <v>50.78</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>43.46</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-38.04</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-81.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>50.23</v>
+      </c>
+      <c r="D47" s="5">
+        <v>21.32</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-28.91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="5">
+        <v>126.25</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-29.29</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-155.54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-96.56</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-91.73</v>
+      </c>
+      <c r="E49" s="6">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-12.44</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-31.02</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-38.32</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-7.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-1.96</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-1</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-27.66</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-25.78</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-29.24</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-28.91</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-22.71</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-22.85</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-20.15</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-21.27</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-50.41</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-49.9</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-16.15</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-16.91</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>26.99</v>
-      </c>
-      <c r="D36" s="6">
-        <v>27.69</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>10.67</v>
-      </c>
-      <c r="D37" s="6">
-        <v>10.72</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>256.05</v>
-      </c>
-      <c r="D38" s="6">
-        <v>255.6</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>687.45</v>
-      </c>
-      <c r="D39" s="6">
-        <v>677.85</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-9.6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>28.71</v>
-      </c>
-      <c r="D40" s="6">
-        <v>29.01</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>1329</v>
-      </c>
-      <c r="D41" s="6">
-        <v>1317</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="6">
-        <v>34</v>
-      </c>
-      <c r="D42" s="6">
-        <v>50</v>
-      </c>
-      <c r="E42" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="6">
-        <v>50</v>
-      </c>
-      <c r="D43" s="6">
-        <v>34</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>40.32</v>
-      </c>
-      <c r="D44" s="6">
-        <v>49.29</v>
-      </c>
-      <c r="E44" s="7">
-        <v>8.970000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>41.3</v>
-      </c>
-      <c r="D45" s="6">
-        <v>43.33</v>
-      </c>
-      <c r="E45" s="7">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>58.2</v>
-      </c>
-      <c r="D46" s="6">
-        <v>57.64</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>51.6</v>
-      </c>
-      <c r="D47" s="6">
-        <v>48.77</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>37.83</v>
-      </c>
-      <c r="D48" s="6">
-        <v>41.28</v>
-      </c>
-      <c r="E48" s="7">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>56.67</v>
-      </c>
-      <c r="D49" s="6">
-        <v>52.9</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="5" t="s">
+      <c r="B51" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="6">
-        <v>-2.04</v>
-      </c>
-      <c r="D50" s="6">
-        <v>43.46</v>
-      </c>
-      <c r="E50" s="7">
-        <v>45.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-13.42</v>
-      </c>
-      <c r="D51" s="6">
-        <v>50.23</v>
-      </c>
-      <c r="E51" s="7">
-        <v>63.65</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-37.79</v>
-      </c>
-      <c r="D52" s="6">
-        <v>126.25</v>
-      </c>
-      <c r="E52" s="7">
-        <v>164.04</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-96.29000000000001</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-96.56</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>-17.42</v>
-      </c>
-      <c r="D54" s="6">
-        <v>-31.02</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-13.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>-35.19</v>
-      </c>
-      <c r="D55" s="6">
+      <c r="C51" s="5">
         <v>-21.34</v>
       </c>
-      <c r="E55" s="7">
-        <v>13.85</v>
+      <c r="D51" s="5">
+        <v>-11.49</v>
+      </c>
+      <c r="E51" s="6">
+        <v>9.85</v>
       </c>
     </row>
   </sheetData>
@@ -2669,60 +2537,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>48.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>46.5</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>6.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-3.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>7.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2824,43 +2692,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.06269999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0095</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0667</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1032</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.115</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1561</v>
+      <c r="A2" s="13">
+        <v>0.05889999999999999</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.06610000000000001</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0978</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1149</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1551</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,31 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -371,14 +395,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -895,7 +920,7 @@
         <v>27.51</v>
       </c>
       <c r="D2">
-        <v>-0.65</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>37.31</v>
@@ -910,40 +935,40 @@
         <v>19.71</v>
       </c>
       <c r="I2">
+        <v>0.92</v>
+      </c>
+      <c r="J2">
         <v>0.7</v>
       </c>
-      <c r="J2">
-        <v>-2.48</v>
-      </c>
       <c r="K2">
-        <v>7.34</v>
+        <v>2.5</v>
       </c>
       <c r="L2">
-        <v>-22.85</v>
+        <v>-22.62</v>
       </c>
       <c r="M2">
-        <v>-11.49</v>
+        <v>-10.94</v>
       </c>
       <c r="N2">
         <v>50</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P2">
-        <v>27.33</v>
+        <v>27.38</v>
       </c>
       <c r="Q2">
-        <v>27.33</v>
+        <v>27.36</v>
       </c>
       <c r="R2">
         <v>28.5</v>
       </c>
       <c r="S2">
-        <v>28.92</v>
+        <v>28.89</v>
       </c>
       <c r="T2">
-        <v>-4.86</v>
+        <v>-4.77</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -961,31 +986,31 @@
         <v>47.32</v>
       </c>
       <c r="Z2">
-        <v>-0.29</v>
+        <v>-0.26</v>
       </c>
       <c r="AA2">
-        <v>-0.35</v>
+        <v>-0.33</v>
       </c>
       <c r="AB2">
         <v>0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>59.35</v>
+        <v>85.36</v>
       </c>
       <c r="AD2">
-        <v>44.13</v>
+        <v>63.49</v>
       </c>
       <c r="AE2">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="AF2">
-        <v>-38.04</v>
+        <v>-11.62</v>
       </c>
       <c r="AG2">
         <v>27.76</v>
       </c>
       <c r="AH2">
-        <v>26.91</v>
+        <v>26.95</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -994,7 +1019,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>18.1</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1008,7 +1033,7 @@
         <v>10.6</v>
       </c>
       <c r="D3">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1023,40 +1048,40 @@
         <v>19.5</v>
       </c>
       <c r="I3">
-        <v>-2.84</v>
+        <v>-1.94</v>
       </c>
       <c r="J3">
-        <v>-4.33</v>
+        <v>-4.16</v>
       </c>
       <c r="K3">
-        <v>5.58</v>
+        <v>4.02</v>
       </c>
       <c r="L3">
-        <v>-26.54</v>
+        <v>-26.08</v>
       </c>
       <c r="M3">
-        <v>-15.51</v>
+        <v>-15.22</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P3">
-        <v>10.71</v>
+        <v>10.67</v>
       </c>
       <c r="Q3">
-        <v>10.83</v>
+        <v>10.8</v>
       </c>
       <c r="R3">
-        <v>11.06</v>
+        <v>11.05</v>
       </c>
       <c r="S3">
-        <v>11.38</v>
+        <v>11.36</v>
       </c>
       <c r="T3">
-        <v>-6.82</v>
+        <v>-6.69</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1074,10 +1099,10 @@
         <v>39.77</v>
       </c>
       <c r="Z3">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="AA3">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AB3">
         <v>-0.02</v>
@@ -1086,28 +1111,28 @@
         <v>6.23</v>
       </c>
       <c r="AD3">
-        <v>18.29</v>
+        <v>10.53</v>
       </c>
       <c r="AE3">
         <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>21.32</v>
+        <v>22.55</v>
       </c>
       <c r="AG3">
-        <v>11.08</v>
+        <v>11.05</v>
       </c>
       <c r="AH3">
-        <v>10.57</v>
+        <v>10.55</v>
       </c>
       <c r="AI3">
-        <v>11.41</v>
+        <v>11.4</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>26.21</v>
+        <v>29.07</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1118,10 +1143,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>249.05</v>
+        <v>249.75</v>
       </c>
       <c r="D4">
-        <v>-2.56</v>
+        <v>0.28</v>
       </c>
       <c r="E4">
         <v>331.3</v>
@@ -1130,25 +1155,25 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-24.83</v>
+        <v>-24.62</v>
       </c>
       <c r="H4">
-        <v>11.13</v>
+        <v>11.45</v>
       </c>
       <c r="I4">
-        <v>-3.02</v>
+        <v>-1.67</v>
       </c>
       <c r="J4">
-        <v>5.69</v>
+        <v>2.79</v>
       </c>
       <c r="K4">
         <v>7.06</v>
       </c>
       <c r="L4">
-        <v>-22.33</v>
+        <v>-23.8</v>
       </c>
       <c r="M4">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="N4">
         <v>66</v>
@@ -1157,19 +1182,19 @@
         <v>37</v>
       </c>
       <c r="P4">
-        <v>253.49</v>
+        <v>252.64</v>
       </c>
       <c r="Q4">
-        <v>249.25</v>
+        <v>249.79</v>
       </c>
       <c r="R4">
-        <v>242.5</v>
+        <v>242.75</v>
       </c>
       <c r="S4">
-        <v>260.69</v>
+        <v>260.4</v>
       </c>
       <c r="T4">
-        <v>-4.46</v>
+        <v>-4.09</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1184,34 +1209,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>50.13</v>
+        <v>50.87</v>
       </c>
       <c r="Z4">
-        <v>4.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>4.51</v>
+        <v>4.31</v>
       </c>
       <c r="AB4">
-        <v>-0.43</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AC4">
-        <v>31.26</v>
+        <v>16.32</v>
       </c>
       <c r="AD4">
-        <v>40.08</v>
+        <v>30.43</v>
       </c>
       <c r="AE4">
-        <v>6.34</v>
+        <v>6.18</v>
       </c>
       <c r="AF4">
-        <v>-29.29</v>
+        <v>-51.49</v>
       </c>
       <c r="AG4">
-        <v>270.85</v>
+        <v>270.84</v>
       </c>
       <c r="AH4">
-        <v>227.65</v>
+        <v>228.75</v>
       </c>
       <c r="AI4">
         <v>245</v>
@@ -1220,7 +1245,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>31.66</v>
+        <v>28.03</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1234,7 +1259,7 @@
         <v>681</v>
       </c>
       <c r="D5">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1249,91 +1274,91 @@
         <v>38.78</v>
       </c>
       <c r="I5">
-        <v>-0.34</v>
+        <v>-0.95</v>
       </c>
       <c r="J5">
-        <v>-14.16</v>
+        <v>-11.25</v>
       </c>
       <c r="K5">
-        <v>31.43</v>
+        <v>31.65</v>
       </c>
       <c r="L5">
-        <v>-17.72</v>
+        <v>-18.04</v>
       </c>
       <c r="M5">
-        <v>-6.61</v>
+        <v>-6.64</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>685.76</v>
+        <v>684.45</v>
       </c>
       <c r="Q5">
-        <v>710.86</v>
+        <v>707.54</v>
       </c>
       <c r="R5">
-        <v>631.78</v>
+        <v>634.92</v>
       </c>
       <c r="S5">
-        <v>631.98</v>
+        <v>631.42</v>
       </c>
       <c r="T5">
-        <v>7.76</v>
+        <v>7.85</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5">
         <v>49.74</v>
       </c>
       <c r="Z5">
-        <v>9.68</v>
+        <v>8.01</v>
       </c>
       <c r="AA5">
-        <v>20.13</v>
+        <v>17.71</v>
       </c>
       <c r="AB5">
-        <v>-10.45</v>
+        <v>-9.69</v>
       </c>
       <c r="AC5">
-        <v>3.69</v>
+        <v>3.15</v>
       </c>
       <c r="AD5">
-        <v>7.6</v>
+        <v>5.02</v>
       </c>
       <c r="AE5">
-        <v>27.19</v>
+        <v>26.12</v>
       </c>
       <c r="AF5">
-        <v>-91.73</v>
+        <v>-84.40000000000001</v>
       </c>
       <c r="AG5">
-        <v>761.12</v>
+        <v>756.4</v>
       </c>
       <c r="AH5">
-        <v>660.59</v>
+        <v>658.6799999999999</v>
       </c>
       <c r="AI5">
-        <v>763.77</v>
+        <v>760.5599999999999</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>14.53</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1344,10 +1369,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>29.01</v>
+        <v>28.95</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="E6">
         <v>57.9</v>
@@ -1356,46 +1381,46 @@
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-49.9</v>
+        <v>-50</v>
       </c>
       <c r="H6">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="I6">
-        <v>-1.86</v>
+        <v>-1.26</v>
       </c>
       <c r="J6">
-        <v>-4.29</v>
+        <v>-3.5</v>
       </c>
       <c r="K6">
-        <v>-7.61</v>
+        <v>-10.04</v>
       </c>
       <c r="L6">
-        <v>-49.77</v>
+        <v>-48.4</v>
       </c>
       <c r="M6">
-        <v>-9.779999999999999</v>
+        <v>-10.01</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>29.04</v>
+        <v>28.96</v>
       </c>
       <c r="Q6">
-        <v>29.22</v>
+        <v>29.17</v>
       </c>
       <c r="R6">
-        <v>31</v>
+        <v>30.91</v>
       </c>
       <c r="S6">
-        <v>36.15</v>
+        <v>36.05</v>
       </c>
       <c r="T6">
-        <v>-19.74</v>
+        <v>-19.69</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1410,31 +1435,31 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>41.28</v>
+        <v>40.76</v>
       </c>
       <c r="Z6">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="AA6">
-        <v>-0.5600000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="AB6">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AC6">
-        <v>38.53</v>
+        <v>39.25</v>
       </c>
       <c r="AD6">
-        <v>45.61</v>
+        <v>40.86</v>
       </c>
       <c r="AE6">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AF6">
-        <v>-38.32</v>
+        <v>-15.64</v>
       </c>
       <c r="AG6">
-        <v>30.19</v>
+        <v>30.09</v>
       </c>
       <c r="AH6">
         <v>28.25</v>
@@ -1446,7 +1471,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>22.36</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1457,10 +1482,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D7">
-        <v>-0.53</v>
+        <v>0.46</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1469,25 +1494,25 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-17.35</v>
+        <v>-16.97</v>
       </c>
       <c r="H7">
-        <v>4.07</v>
+        <v>4.54</v>
       </c>
       <c r="I7">
-        <v>-1.86</v>
+        <v>-0.85</v>
       </c>
       <c r="J7">
-        <v>1.03</v>
+        <v>-0.84</v>
       </c>
       <c r="K7">
-        <v>-1.49</v>
+        <v>-0.05</v>
       </c>
       <c r="L7">
-        <v>-3.4</v>
+        <v>-4.24</v>
       </c>
       <c r="M7">
-        <v>5.89</v>
+        <v>6.07</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1496,19 +1521,19 @@
         <v>46</v>
       </c>
       <c r="P7">
-        <v>1321.44</v>
+        <v>1319.18</v>
       </c>
       <c r="Q7">
-        <v>1302.34</v>
+        <v>1301.99</v>
       </c>
       <c r="R7">
-        <v>1301.43</v>
+        <v>1301.93</v>
       </c>
       <c r="S7">
-        <v>1399.69</v>
+        <v>1398.87</v>
       </c>
       <c r="T7">
-        <v>-6.41</v>
+        <v>-5.92</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1523,34 +1548,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>50.78</v>
+        <v>52.54</v>
       </c>
       <c r="Z7">
-        <v>5.15</v>
+        <v>5.03</v>
       </c>
       <c r="AA7">
-        <v>2.46</v>
+        <v>2.97</v>
       </c>
       <c r="AB7">
-        <v>2.69</v>
+        <v>2.06</v>
       </c>
       <c r="AC7">
-        <v>72.36</v>
+        <v>62.85</v>
       </c>
       <c r="AD7">
-        <v>79.97</v>
+        <v>71.95</v>
       </c>
       <c r="AE7">
-        <v>21.84</v>
+        <v>21.9</v>
       </c>
       <c r="AF7">
-        <v>-11.49</v>
+        <v>15.28</v>
       </c>
       <c r="AG7">
-        <v>1346.32</v>
+        <v>1345.37</v>
       </c>
       <c r="AH7">
-        <v>1258.36</v>
+        <v>1258.6</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1559,7 +1584,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>12.49</v>
+        <v>12.97</v>
       </c>
     </row>
   </sheetData>
@@ -1700,7 +1725,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1720,804 +1745,740 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.32</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-2.48</v>
       </c>
-      <c r="E7" s="6">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-4.37</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-4.33</v>
       </c>
-      <c r="E8" s="6">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-4.16</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>5.69</v>
       </c>
-      <c r="E9" s="7">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>2.79</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-15.7</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-14.16</v>
       </c>
-      <c r="E10" s="6">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-11.25</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-8.66</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-4.29</v>
       </c>
-      <c r="E11" s="6">
-        <v>4.37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-3.5</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>1.66</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>1.03</v>
       </c>
-      <c r="E12" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-0.84</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>1.21</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>0.7</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-1.02</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-2.84</v>
       </c>
-      <c r="E14" s="7">
-        <v>-1.82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-1.94</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-2.85</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-3.02</v>
       </c>
-      <c r="E15" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-1.67</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-0.54</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-0.34</v>
       </c>
-      <c r="E16" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-0.95</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-3.01</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-1.86</v>
       </c>
-      <c r="E17" s="6">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-1.26</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-0.6</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-1.86</v>
       </c>
-      <c r="E18" s="7">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-0.85</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-23.61</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-22.85</v>
       </c>
-      <c r="E19" s="6">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-22.62</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-25.14</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>-26.54</v>
       </c>
-      <c r="E20" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-26.08</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-21.35</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>-22.33</v>
       </c>
-      <c r="E21" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-23.8</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>-18.85</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>-17.72</v>
       </c>
-      <c r="E22" s="6">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>-18.04</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>-48.46</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>-49.77</v>
       </c>
-      <c r="E23" s="7">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>-48.4</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-4.39</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>-3.4</v>
       </c>
-      <c r="E24" s="6">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>-4.24</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>6.01</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>7.34</v>
       </c>
-      <c r="E25" s="6">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-4.84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>4.59</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>5.58</v>
       </c>
-      <c r="E26" s="6">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>4.02</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>31.43</v>
+      </c>
+      <c r="D28" s="6">
+        <v>31.65</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-7.61</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-10.04</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-1.49</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-0.05</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>9.67</v>
-      </c>
-      <c r="D27" s="5">
-        <v>7.06</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-24.83</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-24.62</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-49.9</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-50</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-17.35</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-16.97</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>249.05</v>
+      </c>
+      <c r="D34" s="6">
+        <v>249.75</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>29.01</v>
+      </c>
+      <c r="D35" s="6">
+        <v>28.95</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1310</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1316</v>
+      </c>
+      <c r="E36" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="6">
+        <v>50.13</v>
+      </c>
+      <c r="D37" s="6">
+        <v>50.87</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>41.28</v>
+      </c>
+      <c r="D38" s="6">
+        <v>40.76</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>50.78</v>
+      </c>
+      <c r="D39" s="6">
+        <v>52.54</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-38.04</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-11.62</v>
+      </c>
+      <c r="E40" s="7">
+        <v>26.42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="6">
+        <v>21.32</v>
+      </c>
+      <c r="D41" s="6">
+        <v>22.55</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-29.29</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-51.49</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-22.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>30.02</v>
-      </c>
-      <c r="D28" s="5">
-        <v>31.43</v>
-      </c>
-      <c r="E28" s="6">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-91.73</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-84.40000000000001</v>
+      </c>
+      <c r="E43" s="7">
+        <v>7.33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-7.61</v>
-      </c>
-      <c r="E29" s="6">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-38.32</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-15.64</v>
+      </c>
+      <c r="E44" s="7">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-1</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-1.49</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-25.78</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-26.27</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-28.91</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-29.71</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-22.85</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-24.83</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-21.27</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-20.9</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-16.91</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-17.35</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>27.69</v>
-      </c>
-      <c r="D36" s="5">
-        <v>27.51</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>10.72</v>
-      </c>
-      <c r="D37" s="5">
-        <v>10.6</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>255.6</v>
-      </c>
-      <c r="D38" s="5">
-        <v>249.05</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-6.55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>677.85</v>
-      </c>
-      <c r="D39" s="5">
-        <v>681</v>
-      </c>
-      <c r="E39" s="6">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>1317</v>
-      </c>
-      <c r="D40" s="5">
-        <v>1310</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>49.29</v>
-      </c>
-      <c r="D41" s="5">
-        <v>47.32</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>43.33</v>
-      </c>
-      <c r="D42" s="5">
-        <v>39.77</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-3.56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>57.64</v>
-      </c>
-      <c r="D43" s="5">
-        <v>50.13</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-7.51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>48.77</v>
-      </c>
-      <c r="D44" s="5">
-        <v>49.74</v>
-      </c>
-      <c r="E44" s="6">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>52.9</v>
-      </c>
-      <c r="D45" s="5">
-        <v>50.78</v>
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-11.49</v>
+      </c>
+      <c r="D45" s="6">
+        <v>15.28</v>
       </c>
       <c r="E45" s="7">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>43.46</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-38.04</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-81.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>50.23</v>
-      </c>
-      <c r="D47" s="5">
-        <v>21.32</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-28.91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>126.25</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-29.29</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-155.54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-96.56</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-91.73</v>
-      </c>
-      <c r="E49" s="6">
-        <v>4.83</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-31.02</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-38.32</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-7.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-21.34</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-11.49</v>
-      </c>
-      <c r="E51" s="6">
-        <v>9.85</v>
+        <v>26.77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2537,61 +2498,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>46.5</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>46.8</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-3.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>7.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-2.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>5.9</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
-        <v>0</v>
+      <c r="I2" s="11">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2692,43 +2653,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.05889999999999999</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0007000000000000001</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.06610000000000001</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0978</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1149</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1551</v>
+      <c r="A2" s="14">
+        <v>0.0607</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0017</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0664</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1001</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1094</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1522</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -194,6 +194,27 @@
   </si>
   <si>
     <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.1 → 46.7</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>46.7</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -395,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,6 +424,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -778,7 +800,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -917,10 +940,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.51</v>
+        <v>27.41</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="E2">
         <v>37.31</v>
@@ -929,46 +952,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.27</v>
+        <v>-26.53</v>
       </c>
       <c r="H2">
-        <v>19.71</v>
+        <v>19.28</v>
       </c>
       <c r="I2">
-        <v>0.92</v>
+        <v>0.74</v>
       </c>
       <c r="J2">
-        <v>0.7</v>
+        <v>1.48</v>
       </c>
       <c r="K2">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="L2">
-        <v>-22.62</v>
+        <v>-23.09</v>
       </c>
       <c r="M2">
-        <v>-10.94</v>
+        <v>-10.93</v>
       </c>
       <c r="N2">
         <v>50</v>
       </c>
       <c r="O2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>27.38</v>
+        <v>27.42</v>
       </c>
       <c r="Q2">
-        <v>27.36</v>
+        <v>27.37</v>
       </c>
       <c r="R2">
-        <v>28.5</v>
+        <v>28.51</v>
       </c>
       <c r="S2">
-        <v>28.89</v>
+        <v>28.86</v>
       </c>
       <c r="T2">
-        <v>-4.77</v>
+        <v>-5.02</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -983,34 +1006,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>47.32</v>
+        <v>46.14</v>
       </c>
       <c r="Z2">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="AA2">
-        <v>-0.33</v>
+        <v>-0.31</v>
       </c>
       <c r="AB2">
         <v>0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>85.36</v>
+        <v>73.63</v>
       </c>
       <c r="AD2">
-        <v>63.49</v>
+        <v>72.78</v>
       </c>
       <c r="AE2">
         <v>0.71</v>
       </c>
       <c r="AF2">
-        <v>-11.62</v>
+        <v>-45.4</v>
       </c>
       <c r="AG2">
         <v>27.76</v>
       </c>
       <c r="AH2">
-        <v>26.95</v>
+        <v>26.98</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1019,7 +1042,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>19.25</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1030,10 +1053,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.6</v>
+        <v>10.51</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1042,46 +1065,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-29.71</v>
+        <v>-30.31</v>
       </c>
       <c r="H3">
-        <v>19.5</v>
+        <v>18.49</v>
       </c>
       <c r="I3">
-        <v>-1.94</v>
+        <v>-2.32</v>
       </c>
       <c r="J3">
-        <v>-4.16</v>
+        <v>-5.14</v>
       </c>
       <c r="K3">
-        <v>4.02</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
-        <v>-26.08</v>
+        <v>-26.91</v>
       </c>
       <c r="M3">
-        <v>-15.22</v>
+        <v>-14.9</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P3">
-        <v>10.67</v>
+        <v>10.62</v>
       </c>
       <c r="Q3">
-        <v>10.8</v>
+        <v>10.78</v>
       </c>
       <c r="R3">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="S3">
-        <v>11.36</v>
+        <v>11.34</v>
       </c>
       <c r="T3">
-        <v>-6.69</v>
+        <v>-7.35</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1096,43 +1119,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>39.77</v>
+        <v>37.13</v>
       </c>
       <c r="Z3">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="AA3">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AC3">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>10.53</v>
+        <v>4.15</v>
       </c>
       <c r="AE3">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AF3">
-        <v>22.55</v>
+        <v>-27.91</v>
       </c>
       <c r="AG3">
-        <v>11.05</v>
+        <v>11.03</v>
       </c>
       <c r="AH3">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="AI3">
-        <v>11.4</v>
+        <v>11.27</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>29.07</v>
+        <v>32.19</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1143,10 +1166,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>249.75</v>
+        <v>245.8</v>
       </c>
       <c r="D4">
-        <v>0.28</v>
+        <v>-1.58</v>
       </c>
       <c r="E4">
         <v>331.3</v>
@@ -1155,46 +1178,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-24.62</v>
+        <v>-25.81</v>
       </c>
       <c r="H4">
-        <v>11.45</v>
+        <v>9.68</v>
       </c>
       <c r="I4">
-        <v>-1.67</v>
+        <v>-2.75</v>
       </c>
       <c r="J4">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="K4">
-        <v>7.06</v>
+        <v>4.74</v>
       </c>
       <c r="L4">
-        <v>-23.8</v>
+        <v>-24.83</v>
       </c>
       <c r="M4">
-        <v>0.17</v>
+        <v>-0.37</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P4">
-        <v>252.64</v>
+        <v>251.25</v>
       </c>
       <c r="Q4">
-        <v>249.79</v>
+        <v>250.08</v>
       </c>
       <c r="R4">
-        <v>242.75</v>
+        <v>243.09</v>
       </c>
       <c r="S4">
-        <v>260.4</v>
+        <v>260.08</v>
       </c>
       <c r="T4">
-        <v>-4.09</v>
+        <v>-5.49</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1209,34 +1232,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>50.87</v>
+        <v>46.67</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="AA4">
-        <v>4.31</v>
+        <v>3.99</v>
       </c>
       <c r="AB4">
-        <v>-0.8100000000000001</v>
+        <v>-1.3</v>
       </c>
       <c r="AC4">
-        <v>16.32</v>
+        <v>2.43</v>
       </c>
       <c r="AD4">
-        <v>30.43</v>
+        <v>16.67</v>
       </c>
       <c r="AE4">
-        <v>6.18</v>
+        <v>6.02</v>
       </c>
       <c r="AF4">
-        <v>-51.49</v>
+        <v>-53.26</v>
       </c>
       <c r="AG4">
-        <v>270.84</v>
+        <v>270.72</v>
       </c>
       <c r="AH4">
-        <v>228.75</v>
+        <v>229.45</v>
       </c>
       <c r="AI4">
         <v>245</v>
@@ -1245,7 +1268,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>28.03</v>
+        <v>24.88</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1256,10 +1279,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>681</v>
+        <v>661.3</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>-2.89</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1268,46 +1291,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-20.9</v>
+        <v>-23.19</v>
       </c>
       <c r="H5">
-        <v>38.78</v>
+        <v>34.77</v>
       </c>
       <c r="I5">
-        <v>-0.95</v>
+        <v>-4.84</v>
       </c>
       <c r="J5">
-        <v>-11.25</v>
+        <v>-11.51</v>
       </c>
       <c r="K5">
-        <v>31.65</v>
+        <v>28.86</v>
       </c>
       <c r="L5">
-        <v>-18.04</v>
+        <v>-20.45</v>
       </c>
       <c r="M5">
-        <v>-6.64</v>
+        <v>-7.23</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="P5">
-        <v>684.45</v>
+        <v>677.72</v>
       </c>
       <c r="Q5">
-        <v>707.54</v>
+        <v>703.4400000000001</v>
       </c>
       <c r="R5">
-        <v>634.92</v>
+        <v>637.8099999999999</v>
       </c>
       <c r="S5">
-        <v>631.42</v>
+        <v>630.79</v>
       </c>
       <c r="T5">
-        <v>7.85</v>
+        <v>4.84</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1322,43 +1345,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.74</v>
+        <v>43.72</v>
       </c>
       <c r="Z5">
-        <v>8.01</v>
+        <v>5.05</v>
       </c>
       <c r="AA5">
-        <v>17.71</v>
+        <v>15.17</v>
       </c>
       <c r="AB5">
-        <v>-9.69</v>
+        <v>-10.13</v>
       </c>
       <c r="AC5">
         <v>3.15</v>
       </c>
       <c r="AD5">
-        <v>5.02</v>
+        <v>3.33</v>
       </c>
       <c r="AE5">
-        <v>26.12</v>
+        <v>26.06</v>
       </c>
       <c r="AF5">
-        <v>-84.40000000000001</v>
+        <v>-68.58</v>
       </c>
       <c r="AG5">
-        <v>756.4</v>
+        <v>753.4</v>
       </c>
       <c r="AH5">
-        <v>658.6799999999999</v>
+        <v>653.47</v>
       </c>
       <c r="AI5">
-        <v>760.5599999999999</v>
+        <v>748.87</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>13.01</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1369,10 +1392,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>28.95</v>
+        <v>28.51</v>
       </c>
       <c r="D6">
-        <v>-0.21</v>
+        <v>-1.52</v>
       </c>
       <c r="E6">
         <v>57.9</v>
@@ -1381,46 +1404,46 @@
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-50</v>
+        <v>-50.76</v>
       </c>
       <c r="H6">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="I6">
-        <v>-1.26</v>
+        <v>-2.16</v>
       </c>
       <c r="J6">
-        <v>-3.5</v>
+        <v>-4.62</v>
       </c>
       <c r="K6">
-        <v>-10.04</v>
+        <v>-10.29</v>
       </c>
       <c r="L6">
-        <v>-48.4</v>
+        <v>-49.26</v>
       </c>
       <c r="M6">
-        <v>-10.01</v>
+        <v>-10.89</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>28.96</v>
+        <v>28.84</v>
       </c>
       <c r="Q6">
-        <v>29.17</v>
+        <v>29.12</v>
       </c>
       <c r="R6">
-        <v>30.91</v>
+        <v>30.84</v>
       </c>
       <c r="S6">
-        <v>36.05</v>
+        <v>35.95</v>
       </c>
       <c r="T6">
-        <v>-19.69</v>
+        <v>-20.69</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1435,43 +1458,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>40.76</v>
+        <v>37.03</v>
       </c>
       <c r="Z6">
-        <v>-0.49</v>
+        <v>-0.51</v>
       </c>
       <c r="AA6">
-        <v>-0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="AB6">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AC6">
-        <v>39.25</v>
+        <v>24.46</v>
       </c>
       <c r="AD6">
-        <v>40.86</v>
+        <v>34.08</v>
       </c>
       <c r="AE6">
         <v>0.77</v>
       </c>
       <c r="AF6">
-        <v>-15.64</v>
+        <v>13.48</v>
       </c>
       <c r="AG6">
-        <v>30.09</v>
+        <v>30.07</v>
       </c>
       <c r="AH6">
-        <v>28.25</v>
+        <v>28.17</v>
       </c>
       <c r="AI6">
-        <v>31.25</v>
+        <v>30.97</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>21.18</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1482,7 +1505,7 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="D7">
         <v>0.46</v>
@@ -1494,25 +1517,25 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-16.97</v>
+        <v>-16.59</v>
       </c>
       <c r="H7">
-        <v>4.54</v>
+        <v>5.02</v>
       </c>
       <c r="I7">
-        <v>-0.85</v>
+        <v>-0.14</v>
       </c>
       <c r="J7">
-        <v>-0.84</v>
+        <v>-0.08</v>
       </c>
       <c r="K7">
-        <v>-0.05</v>
+        <v>-2.32</v>
       </c>
       <c r="L7">
-        <v>-4.24</v>
+        <v>-3.4</v>
       </c>
       <c r="M7">
-        <v>6.07</v>
+        <v>6.08</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1521,22 +1544,22 @@
         <v>46</v>
       </c>
       <c r="P7">
-        <v>1319.18</v>
+        <v>1318.8</v>
       </c>
       <c r="Q7">
-        <v>1301.99</v>
+        <v>1302.9</v>
       </c>
       <c r="R7">
-        <v>1301.93</v>
+        <v>1303.11</v>
       </c>
       <c r="S7">
-        <v>1398.87</v>
+        <v>1398</v>
       </c>
       <c r="T7">
-        <v>-5.92</v>
+        <v>-5.44</v>
       </c>
       <c r="U7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V7" t="s">
         <v>44</v>
@@ -1545,34 +1568,34 @@
         <v>44</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>52.54</v>
+        <v>54.29</v>
       </c>
       <c r="Z7">
-        <v>5.03</v>
+        <v>5.36</v>
       </c>
       <c r="AA7">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="AB7">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>62.85</v>
+        <v>62.47</v>
       </c>
       <c r="AD7">
-        <v>71.95</v>
+        <v>65.89</v>
       </c>
       <c r="AE7">
-        <v>21.9</v>
+        <v>21.58</v>
       </c>
       <c r="AF7">
-        <v>15.28</v>
+        <v>-12.5</v>
       </c>
       <c r="AG7">
-        <v>1345.37</v>
+        <v>1347.2</v>
       </c>
       <c r="AH7">
         <v>1258.6</v>
@@ -1584,7 +1607,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>12.97</v>
+        <v>11.42</v>
       </c>
     </row>
   </sheetData>
@@ -1725,7 +1748,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1803,682 +1826,875 @@
         <v>45</v>
       </c>
     </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C10" s="7">
         <v>-2.48</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D10" s="7">
+        <v>1.48</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-4.33</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-5.14</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>5.69</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2.88</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-14.16</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-11.51</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-4.29</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-4.62</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1.03</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.08</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
         <v>0.7</v>
       </c>
-      <c r="E8" s="7">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D16" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-4.33</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-4.16</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-2.84</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-2.32</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>5.69</v>
-      </c>
-      <c r="D10" s="6">
-        <v>2.79</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-3.02</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-2.75</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-14.16</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-11.25</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.34</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-4.84</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-4.29</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.86</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-2.16</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1.03</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1.86</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-0.14</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.92</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-22.85</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-23.09</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.84</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-1.94</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-26.54</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-26.91</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-3.02</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.67</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-22.33</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-24.83</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-0.34</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.95</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-17.72</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-20.45</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-2.73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.26</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-49.77</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-49.26</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>7.34</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2.66</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-4.68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7">
+        <v>5.58</v>
+      </c>
+      <c r="D28" s="7">
+        <v>3.55</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>7.06</v>
+      </c>
+      <c r="D29" s="7">
+        <v>4.74</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>31.43</v>
+      </c>
+      <c r="D30" s="7">
+        <v>28.86</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-7.61</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-10.29</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-0.85</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-1.49</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-2.32</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-22.85</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-22.62</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-26.27</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-26.53</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-26.54</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-26.08</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-29.71</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-30.31</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-22.33</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-23.8</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-24.83</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-25.81</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-17.72</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-18.04</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-20.9</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-23.19</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-49.77</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-48.4</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-49.9</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-50.76</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-4.24</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-17.35</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-16.59</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>7.34</v>
-      </c>
-      <c r="D26" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-4.84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7">
+        <v>27.51</v>
+      </c>
+      <c r="D39" s="7">
+        <v>27.41</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>5.58</v>
-      </c>
-      <c r="D27" s="6">
-        <v>4.02</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="7">
+        <v>10.6</v>
+      </c>
+      <c r="D40" s="7">
+        <v>10.51</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="7">
+        <v>249.05</v>
+      </c>
+      <c r="D41" s="7">
+        <v>245.8</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>31.43</v>
-      </c>
-      <c r="D28" s="6">
-        <v>31.65</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7">
+        <v>681</v>
+      </c>
+      <c r="D42" s="7">
+        <v>661.3</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-19.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-7.61</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-10.04</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>29.01</v>
+      </c>
+      <c r="D43" s="7">
+        <v>28.51</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-1.49</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-0.05</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>1310</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1322</v>
+      </c>
+      <c r="E44" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="7">
+        <v>47.32</v>
+      </c>
+      <c r="D45" s="7">
+        <v>46.14</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="7">
+        <v>39.77</v>
+      </c>
+      <c r="D46" s="7">
+        <v>37.13</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-24.83</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-24.62</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="7">
+        <v>50.13</v>
+      </c>
+      <c r="D47" s="7">
+        <v>46.67</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="7">
+        <v>49.74</v>
+      </c>
+      <c r="D48" s="7">
+        <v>43.72</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-6.02</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-49.9</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-50</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="7">
+        <v>41.28</v>
+      </c>
+      <c r="D49" s="7">
+        <v>37.03</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-4.25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-17.35</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-16.97</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="7">
+        <v>50.78</v>
+      </c>
+      <c r="D50" s="7">
+        <v>54.29</v>
+      </c>
+      <c r="E50" s="8">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-38.04</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-45.4</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-7.36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="7">
+        <v>21.32</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-27.91</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-49.23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>249.05</v>
-      </c>
-      <c r="D34" s="6">
-        <v>249.75</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-29.29</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-53.26</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-23.97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-91.73</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-68.58</v>
+      </c>
+      <c r="E54" s="8">
+        <v>23.15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>29.01</v>
-      </c>
-      <c r="D35" s="6">
-        <v>28.95</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="7">
+        <v>-38.32</v>
+      </c>
+      <c r="D55" s="7">
+        <v>13.48</v>
+      </c>
+      <c r="E55" s="8">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1310</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1316</v>
-      </c>
-      <c r="E36" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>50.13</v>
-      </c>
-      <c r="D37" s="6">
-        <v>50.87</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>41.28</v>
-      </c>
-      <c r="D38" s="6">
-        <v>40.76</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>50.78</v>
-      </c>
-      <c r="D39" s="6">
-        <v>52.54</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="6">
-        <v>-38.04</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-11.62</v>
-      </c>
-      <c r="E40" s="7">
-        <v>26.42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="6">
-        <v>21.32</v>
-      </c>
-      <c r="D41" s="6">
-        <v>22.55</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-29.29</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-51.49</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-22.2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-91.73</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-84.40000000000001</v>
-      </c>
-      <c r="E43" s="7">
-        <v>7.33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-38.32</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-15.64</v>
-      </c>
-      <c r="E44" s="7">
-        <v>22.68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
+      <c r="C56" s="7">
         <v>-11.49</v>
       </c>
-      <c r="D45" s="6">
-        <v>15.28</v>
-      </c>
-      <c r="E45" s="7">
-        <v>26.77</v>
+      <c r="D56" s="7">
+        <v>-12.5</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-1.01</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2498,60 +2714,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>70</v>
       </c>
+      <c r="C1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>46.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>44.2</v>
+      </c>
+      <c r="E2" s="12">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-2.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>5.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-2.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H2" s="12">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>20</v>
       </c>
     </row>
@@ -2653,43 +2869,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.0607</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0017</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0664</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1001</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1094</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1522</v>
+      <c r="A2" s="15">
+        <v>0.0608</v>
+      </c>
+      <c r="B2" s="15">
+        <v>-0.0037</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0723</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.1089</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.1093</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.149</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,9 +163,6 @@
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -184,37 +181,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>50 DMA &gt; 200 DMA</t>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>No → Yes</t>
   </si>
   <si>
-    <t>🟢 GOLDEN CROSS</t>
-  </si>
-  <si>
     <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.1 → 46.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>46.7</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -416,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -424,11 +397,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -800,8 +772,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -940,10 +912,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.41</v>
+        <v>27.38</v>
       </c>
       <c r="D2">
-        <v>-0.36</v>
+        <v>-0.11</v>
       </c>
       <c r="E2">
         <v>37.31</v>
@@ -952,34 +924,34 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.53</v>
+        <v>-26.61</v>
       </c>
       <c r="H2">
-        <v>19.28</v>
+        <v>19.15</v>
       </c>
       <c r="I2">
-        <v>0.74</v>
+        <v>1.44</v>
       </c>
       <c r="J2">
-        <v>1.48</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K2">
-        <v>2.66</v>
+        <v>0.88</v>
       </c>
       <c r="L2">
-        <v>-23.09</v>
+        <v>-22.39</v>
       </c>
       <c r="M2">
-        <v>-10.93</v>
+        <v>-10.08</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P2">
-        <v>27.42</v>
+        <v>27.5</v>
       </c>
       <c r="Q2">
         <v>27.37</v>
@@ -988,7 +960,7 @@
         <v>28.51</v>
       </c>
       <c r="S2">
-        <v>28.86</v>
+        <v>28.83</v>
       </c>
       <c r="T2">
         <v>-5.02</v>
@@ -1006,28 +978,28 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>46.14</v>
+        <v>45.76</v>
       </c>
       <c r="Z2">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="AA2">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AB2">
         <v>0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>73.63</v>
+        <v>67.83</v>
       </c>
       <c r="AD2">
-        <v>72.78</v>
+        <v>75.61</v>
       </c>
       <c r="AE2">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>-45.4</v>
+        <v>-34.2</v>
       </c>
       <c r="AG2">
         <v>27.76</v>
@@ -1042,7 +1014,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>21.14</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1053,10 +1025,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.51</v>
+        <v>10.43</v>
       </c>
       <c r="D3">
-        <v>-0.85</v>
+        <v>-0.76</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1065,25 +1037,25 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-30.31</v>
+        <v>-30.84</v>
       </c>
       <c r="H3">
-        <v>18.49</v>
+        <v>17.59</v>
       </c>
       <c r="I3">
-        <v>-2.32</v>
+        <v>-2.25</v>
       </c>
       <c r="J3">
-        <v>-5.14</v>
+        <v>-5.35</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="L3">
-        <v>-26.91</v>
+        <v>-27.72</v>
       </c>
       <c r="M3">
-        <v>-14.9</v>
+        <v>-14.45</v>
       </c>
       <c r="N3">
         <v>34</v>
@@ -1092,19 +1064,19 @@
         <v>28</v>
       </c>
       <c r="P3">
-        <v>10.62</v>
+        <v>10.57</v>
       </c>
       <c r="Q3">
-        <v>10.78</v>
+        <v>10.76</v>
       </c>
       <c r="R3">
         <v>11.04</v>
       </c>
       <c r="S3">
-        <v>11.34</v>
+        <v>11.33</v>
       </c>
       <c r="T3">
-        <v>-7.35</v>
+        <v>-7.91</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1119,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>37.13</v>
+        <v>34.9</v>
       </c>
       <c r="Z3">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="AA3">
         <v>-0.09</v>
@@ -1134,28 +1106,28 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>4.15</v>
+        <v>2.08</v>
       </c>
       <c r="AE3">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AF3">
-        <v>-27.91</v>
+        <v>2.63</v>
       </c>
       <c r="AG3">
-        <v>11.03</v>
+        <v>11.05</v>
       </c>
       <c r="AH3">
-        <v>10.52</v>
+        <v>10.46</v>
       </c>
       <c r="AI3">
-        <v>11.27</v>
+        <v>11.19</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>32.19</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1166,10 +1138,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>245.8</v>
+        <v>243.15</v>
       </c>
       <c r="D4">
-        <v>-1.58</v>
+        <v>-1.08</v>
       </c>
       <c r="E4">
         <v>331.3</v>
@@ -1178,46 +1150,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-25.81</v>
+        <v>-26.61</v>
       </c>
       <c r="H4">
-        <v>9.68</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
-        <v>-2.75</v>
+        <v>-5.04</v>
       </c>
       <c r="J4">
-        <v>2.88</v>
+        <v>1.3</v>
       </c>
       <c r="K4">
-        <v>4.74</v>
+        <v>3.13</v>
       </c>
       <c r="L4">
-        <v>-24.83</v>
+        <v>-26.45</v>
       </c>
       <c r="M4">
-        <v>-0.37</v>
+        <v>-0.73</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P4">
-        <v>251.25</v>
+        <v>248.67</v>
       </c>
       <c r="Q4">
-        <v>250.08</v>
+        <v>250.5</v>
       </c>
       <c r="R4">
-        <v>243.09</v>
+        <v>243.27</v>
       </c>
       <c r="S4">
-        <v>260.08</v>
+        <v>259.74</v>
       </c>
       <c r="T4">
-        <v>-5.49</v>
+        <v>-6.39</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1232,43 +1204,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>46.67</v>
+        <v>44.05</v>
       </c>
       <c r="Z4">
-        <v>2.69</v>
+        <v>1.81</v>
       </c>
       <c r="AA4">
-        <v>3.99</v>
+        <v>3.55</v>
       </c>
       <c r="AB4">
-        <v>-1.3</v>
+        <v>-1.74</v>
       </c>
       <c r="AC4">
-        <v>2.43</v>
+        <v>1.18</v>
       </c>
       <c r="AD4">
-        <v>16.67</v>
+        <v>6.65</v>
       </c>
       <c r="AE4">
-        <v>6.02</v>
+        <v>5.93</v>
       </c>
       <c r="AF4">
-        <v>-53.26</v>
+        <v>-49.43</v>
       </c>
       <c r="AG4">
-        <v>270.72</v>
+        <v>270.15</v>
       </c>
       <c r="AH4">
-        <v>229.45</v>
+        <v>230.85</v>
       </c>
       <c r="AI4">
-        <v>245</v>
+        <v>261.7</v>
       </c>
       <c r="AJ4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AK4">
-        <v>24.88</v>
+        <v>24.29</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1279,10 +1251,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>661.3</v>
+        <v>660.45</v>
       </c>
       <c r="D5">
-        <v>-2.89</v>
+        <v>-0.13</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1291,46 +1263,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-23.19</v>
+        <v>-23.29</v>
       </c>
       <c r="H5">
-        <v>34.77</v>
+        <v>34.59</v>
       </c>
       <c r="I5">
-        <v>-4.84</v>
+        <v>-3.93</v>
       </c>
       <c r="J5">
-        <v>-11.51</v>
+        <v>-11.16</v>
       </c>
       <c r="K5">
-        <v>28.86</v>
+        <v>26.78</v>
       </c>
       <c r="L5">
-        <v>-20.45</v>
+        <v>-19.83</v>
       </c>
       <c r="M5">
-        <v>-7.23</v>
+        <v>-7.18</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P5">
-        <v>677.72</v>
+        <v>672.3200000000001</v>
       </c>
       <c r="Q5">
-        <v>703.4400000000001</v>
+        <v>700.3099999999999</v>
       </c>
       <c r="R5">
-        <v>637.8099999999999</v>
+        <v>640.42</v>
       </c>
       <c r="S5">
-        <v>630.79</v>
+        <v>630.1900000000001</v>
       </c>
       <c r="T5">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1345,43 +1317,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>43.72</v>
+        <v>43.47</v>
       </c>
       <c r="Z5">
-        <v>5.05</v>
+        <v>2.6</v>
       </c>
       <c r="AA5">
-        <v>15.17</v>
+        <v>12.66</v>
       </c>
       <c r="AB5">
-        <v>-10.13</v>
+        <v>-10.06</v>
       </c>
       <c r="AC5">
-        <v>3.15</v>
+        <v>1.58</v>
       </c>
       <c r="AD5">
-        <v>3.33</v>
+        <v>2.63</v>
       </c>
       <c r="AE5">
-        <v>26.06</v>
+        <v>25.13</v>
       </c>
       <c r="AF5">
-        <v>-68.58</v>
+        <v>-72.87</v>
       </c>
       <c r="AG5">
-        <v>753.4</v>
+        <v>752.88</v>
       </c>
       <c r="AH5">
-        <v>653.47</v>
+        <v>647.74</v>
       </c>
       <c r="AI5">
-        <v>748.87</v>
+        <v>733.89</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>15.16</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1392,10 +1364,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>28.51</v>
+        <v>28.07</v>
       </c>
       <c r="D6">
-        <v>-1.52</v>
+        <v>-1.54</v>
       </c>
       <c r="E6">
         <v>57.9</v>
@@ -1404,25 +1376,25 @@
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-50.76</v>
+        <v>-51.52</v>
       </c>
       <c r="H6">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>-2.16</v>
+        <v>-2.23</v>
       </c>
       <c r="J6">
-        <v>-4.62</v>
+        <v>-5.04</v>
       </c>
       <c r="K6">
-        <v>-10.29</v>
+        <v>-12.47</v>
       </c>
       <c r="L6">
-        <v>-49.26</v>
+        <v>-50.65</v>
       </c>
       <c r="M6">
-        <v>-10.89</v>
+        <v>-10.51</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1431,19 +1403,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>28.84</v>
+        <v>28.71</v>
       </c>
       <c r="Q6">
-        <v>29.12</v>
+        <v>29.08</v>
       </c>
       <c r="R6">
-        <v>30.84</v>
+        <v>30.77</v>
       </c>
       <c r="S6">
-        <v>35.95</v>
+        <v>35.85</v>
       </c>
       <c r="T6">
-        <v>-20.69</v>
+        <v>-21.69</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1458,43 +1430,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>37.03</v>
+        <v>33.72</v>
       </c>
       <c r="Z6">
-        <v>-0.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AA6">
         <v>-0.54</v>
       </c>
       <c r="AB6">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AC6">
-        <v>24.46</v>
+        <v>9.82</v>
       </c>
       <c r="AD6">
-        <v>34.08</v>
+        <v>24.51</v>
       </c>
       <c r="AE6">
         <v>0.77</v>
       </c>
       <c r="AF6">
-        <v>13.48</v>
+        <v>165.43</v>
       </c>
       <c r="AG6">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AH6">
-        <v>28.17</v>
+        <v>28.04</v>
       </c>
       <c r="AI6">
-        <v>30.97</v>
+        <v>30.51</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>23.19</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1505,10 +1477,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1322</v>
+        <v>1311</v>
       </c>
       <c r="D7">
-        <v>0.46</v>
+        <v>-0.83</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1517,25 +1489,25 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-16.59</v>
+        <v>-17.29</v>
       </c>
       <c r="H7">
-        <v>5.02</v>
+        <v>4.15</v>
       </c>
       <c r="I7">
-        <v>-0.14</v>
+        <v>-1.35</v>
       </c>
       <c r="J7">
-        <v>-0.08</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K7">
-        <v>-2.32</v>
+        <v>-2.41</v>
       </c>
       <c r="L7">
-        <v>-3.4</v>
+        <v>-4.36</v>
       </c>
       <c r="M7">
-        <v>6.08</v>
+        <v>6.15</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1544,22 +1516,22 @@
         <v>46</v>
       </c>
       <c r="P7">
-        <v>1318.8</v>
+        <v>1315.2</v>
       </c>
       <c r="Q7">
-        <v>1302.9</v>
+        <v>1304.02</v>
       </c>
       <c r="R7">
-        <v>1303.11</v>
+        <v>1303.94</v>
       </c>
       <c r="S7">
-        <v>1398</v>
+        <v>1397.14</v>
       </c>
       <c r="T7">
-        <v>-5.44</v>
+        <v>-6.17</v>
       </c>
       <c r="U7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V7" t="s">
         <v>44</v>
@@ -1568,37 +1540,37 @@
         <v>44</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>54.29</v>
+        <v>50.6</v>
       </c>
       <c r="Z7">
-        <v>5.36</v>
+        <v>4.68</v>
       </c>
       <c r="AA7">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>0.98</v>
       </c>
       <c r="AC7">
-        <v>62.47</v>
+        <v>56.84</v>
       </c>
       <c r="AD7">
-        <v>65.89</v>
+        <v>60.72</v>
       </c>
       <c r="AE7">
-        <v>21.58</v>
+        <v>21.36</v>
       </c>
       <c r="AF7">
-        <v>-12.5</v>
+        <v>-32.98</v>
       </c>
       <c r="AG7">
-        <v>1347.2</v>
+        <v>1347.93</v>
       </c>
       <c r="AH7">
-        <v>1258.6</v>
+        <v>1260.11</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1607,7 +1579,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>11.42</v>
+        <v>11.74</v>
       </c>
     </row>
   </sheetData>
@@ -1758,7 +1730,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1771,33 +1743,33 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>44</v>
@@ -1806,895 +1778,886 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.48</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-5.14</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-5.35</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2.88</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1.3</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-11.51</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-11.16</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-4.62</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-0.08</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.74</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.44</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.32</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.25</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.75</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-4.84</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.93</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.16</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.23</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.14</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.35</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-23.09</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-22.39</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-26.91</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-27.72</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-24.83</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-26.45</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-20.45</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-19.83</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-49.26</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-50.65</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-3.4</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-4.36</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>2.66</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>3.55</v>
+      </c>
+      <c r="D26" s="6">
+        <v>2.56</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>4.74</v>
+      </c>
+      <c r="D27" s="6">
+        <v>3.13</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>28.86</v>
+      </c>
+      <c r="D28" s="6">
+        <v>26.78</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-10.29</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-12.47</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-2.32</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-2.41</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-26.53</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-26.61</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-30.31</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-30.84</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-25.81</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-26.61</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-23.19</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-23.29</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-50.76</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-51.52</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-16.59</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-17.29</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>27.41</v>
+      </c>
+      <c r="D37" s="6">
+        <v>27.38</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>10.51</v>
+      </c>
+      <c r="D38" s="6">
+        <v>10.43</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>245.8</v>
+      </c>
+      <c r="D39" s="6">
+        <v>243.15</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>661.3</v>
+      </c>
+      <c r="D40" s="6">
+        <v>660.45</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>28.51</v>
+      </c>
+      <c r="D41" s="6">
+        <v>28.07</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1322</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1311</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="6">
+        <v>50</v>
+      </c>
+      <c r="D43" s="6">
         <v>66</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="E43" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="6">
+        <v>66</v>
+      </c>
+      <c r="D44" s="6">
+        <v>50</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-2.48</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.48</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>46.14</v>
+      </c>
+      <c r="D45" s="6">
+        <v>45.76</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-4.33</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-5.14</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>37.13</v>
+      </c>
+      <c r="D46" s="6">
+        <v>34.9</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>5.69</v>
-      </c>
-      <c r="D12" s="7">
-        <v>2.88</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>46.67</v>
+      </c>
+      <c r="D47" s="6">
+        <v>44.05</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2.62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-14.16</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-11.51</v>
-      </c>
-      <c r="E13" s="8">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>43.72</v>
+      </c>
+      <c r="D48" s="6">
+        <v>43.47</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>37.03</v>
+      </c>
+      <c r="D49" s="6">
+        <v>33.72</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-3.31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>54.29</v>
+      </c>
+      <c r="D50" s="6">
+        <v>50.6</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-3.69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-45.4</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-34.2</v>
+      </c>
+      <c r="E51" s="8">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-27.91</v>
+      </c>
+      <c r="D52" s="6">
+        <v>2.63</v>
+      </c>
+      <c r="E52" s="8">
+        <v>30.54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-53.26</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-49.43</v>
+      </c>
+      <c r="E53" s="8">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="6">
+        <v>-68.58</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-72.87</v>
+      </c>
+      <c r="E54" s="7">
         <v>-4.29</v>
       </c>
-      <c r="D14" s="7">
-        <v>-4.62</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
+        <v>13.48</v>
+      </c>
+      <c r="D55" s="6">
+        <v>165.43</v>
+      </c>
+      <c r="E55" s="8">
+        <v>151.95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1.03</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-0.08</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="D16" s="7">
-        <v>0.74</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-2.84</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-2.32</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-3.02</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-2.75</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.34</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-4.84</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.16</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-0.14</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-22.85</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-23.09</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-26.54</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-26.91</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-22.33</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-24.83</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-17.72</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-20.45</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-2.73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-49.77</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-49.26</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>7.34</v>
-      </c>
-      <c r="D27" s="7">
-        <v>2.66</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-4.68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>5.58</v>
-      </c>
-      <c r="D28" s="7">
-        <v>3.55</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>7.06</v>
-      </c>
-      <c r="D29" s="7">
-        <v>4.74</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>31.43</v>
-      </c>
-      <c r="D30" s="7">
-        <v>28.86</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-7.61</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-10.29</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-2.68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-1.49</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-2.32</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-26.27</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-26.53</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-29.71</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-30.31</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-24.83</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-25.81</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-20.9</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-23.19</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-49.9</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-50.76</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-17.35</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-16.59</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="7">
-        <v>27.51</v>
-      </c>
-      <c r="D39" s="7">
-        <v>27.41</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="7">
-        <v>10.6</v>
-      </c>
-      <c r="D40" s="7">
-        <v>10.51</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="7">
-        <v>249.05</v>
-      </c>
-      <c r="D41" s="7">
-        <v>245.8</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="7">
-        <v>681</v>
-      </c>
-      <c r="D42" s="7">
-        <v>661.3</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-19.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>29.01</v>
-      </c>
-      <c r="D43" s="7">
-        <v>28.51</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>1310</v>
-      </c>
-      <c r="D44" s="7">
-        <v>1322</v>
-      </c>
-      <c r="E44" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="7">
-        <v>47.32</v>
-      </c>
-      <c r="D45" s="7">
-        <v>46.14</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="7">
-        <v>39.77</v>
-      </c>
-      <c r="D46" s="7">
-        <v>37.13</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="7">
-        <v>50.13</v>
-      </c>
-      <c r="D47" s="7">
-        <v>46.67</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="7">
-        <v>49.74</v>
-      </c>
-      <c r="D48" s="7">
-        <v>43.72</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-6.02</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="7">
-        <v>41.28</v>
-      </c>
-      <c r="D49" s="7">
-        <v>37.03</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-4.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="7">
-        <v>50.78</v>
-      </c>
-      <c r="D50" s="7">
-        <v>54.29</v>
-      </c>
-      <c r="E50" s="8">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="7">
-        <v>-38.04</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-45.4</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-7.36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="7">
-        <v>21.32</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-27.91</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-49.23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-29.29</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-53.26</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-23.97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-91.73</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-68.58</v>
-      </c>
-      <c r="E54" s="8">
-        <v>23.15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="7">
-        <v>-38.32</v>
-      </c>
-      <c r="D55" s="7">
-        <v>13.48</v>
-      </c>
-      <c r="E55" s="8">
-        <v>51.8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="7">
-        <v>-11.49</v>
-      </c>
-      <c r="D56" s="7">
+      <c r="C56" s="6">
         <v>-12.5</v>
       </c>
-      <c r="E56" s="9">
-        <v>-1.01</v>
+      <c r="D56" s="6">
+        <v>-32.98</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-20.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2714,60 +2677,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>77</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="12">
-        <v>44.2</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>42.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="12">
-        <v>-2.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>4.5</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-3.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2869,43 +2832,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="15">
-        <v>0.0608</v>
-      </c>
-      <c r="B2" s="15">
-        <v>-0.0037</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0723</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.1089</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1093</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.149</v>
+      <c r="A2" s="14">
+        <v>0.06150000000000001</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0073</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0718</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1008</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1051</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1445</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,6 +163,9 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -181,13 +184,37 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.8 → 51.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>45.8</t>
+  </si>
+  <si>
+    <t>51.0</t>
+  </si>
+  <si>
+    <t>43.5 → 50.6</t>
+  </si>
+  <si>
+    <t>43.5</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>33.7 → 57.3</t>
+  </si>
+  <si>
+    <t>33.7</t>
+  </si>
+  <si>
+    <t>57.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -399,8 +426,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -772,8 +799,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -912,10 +938,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.38</v>
+        <v>27.75</v>
       </c>
       <c r="D2">
-        <v>-0.11</v>
+        <v>1.35</v>
       </c>
       <c r="E2">
         <v>37.31</v>
@@ -924,46 +950,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.61</v>
+        <v>-25.62</v>
       </c>
       <c r="H2">
-        <v>19.15</v>
+        <v>20.76</v>
       </c>
       <c r="I2">
-        <v>1.44</v>
+        <v>0.22</v>
       </c>
       <c r="J2">
-        <v>0.8100000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="K2">
-        <v>0.88</v>
+        <v>2.97</v>
       </c>
       <c r="L2">
-        <v>-22.39</v>
+        <v>-20.53</v>
       </c>
       <c r="M2">
-        <v>-10.08</v>
+        <v>-9.83</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P2">
-        <v>27.5</v>
+        <v>27.51</v>
       </c>
       <c r="Q2">
-        <v>27.37</v>
+        <v>27.41</v>
       </c>
       <c r="R2">
-        <v>28.51</v>
+        <v>28.53</v>
       </c>
       <c r="S2">
-        <v>28.83</v>
+        <v>28.8</v>
       </c>
       <c r="T2">
-        <v>-5.02</v>
+        <v>-3.65</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -978,34 +1004,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>45.76</v>
+        <v>51</v>
       </c>
       <c r="Z2">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="AA2">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="AB2">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AC2">
-        <v>67.83</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="AD2">
-        <v>75.61</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="AE2">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>-34.2</v>
+        <v>60.3</v>
       </c>
       <c r="AG2">
-        <v>27.76</v>
+        <v>27.79</v>
       </c>
       <c r="AH2">
-        <v>26.98</v>
+        <v>27.03</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1014,7 +1040,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>22.65</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +1051,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.43</v>
+        <v>10.54</v>
       </c>
       <c r="D3">
-        <v>-0.76</v>
+        <v>1.05</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1037,46 +1063,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-30.84</v>
+        <v>-30.11</v>
       </c>
       <c r="H3">
-        <v>17.59</v>
+        <v>18.83</v>
       </c>
       <c r="I3">
-        <v>-2.25</v>
+        <v>-1.68</v>
       </c>
       <c r="J3">
-        <v>-5.35</v>
+        <v>-2.59</v>
       </c>
       <c r="K3">
-        <v>2.56</v>
+        <v>3.94</v>
       </c>
       <c r="L3">
-        <v>-27.72</v>
+        <v>-26.5</v>
       </c>
       <c r="M3">
-        <v>-14.45</v>
+        <v>-14.26</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>10.57</v>
+        <v>10.54</v>
       </c>
       <c r="Q3">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
       <c r="R3">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
       <c r="S3">
-        <v>11.33</v>
+        <v>11.31</v>
       </c>
       <c r="T3">
-        <v>-7.91</v>
+        <v>-6.81</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1091,34 +1117,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.9</v>
+        <v>40.21</v>
       </c>
       <c r="Z3">
         <v>-0.13</v>
       </c>
       <c r="AA3">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="AB3">
         <v>-0.03</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="AD3">
-        <v>2.08</v>
+        <v>3.42</v>
       </c>
       <c r="AE3">
         <v>0.23</v>
       </c>
       <c r="AF3">
-        <v>2.63</v>
+        <v>32.93</v>
       </c>
       <c r="AG3">
-        <v>11.05</v>
+        <v>11.06</v>
       </c>
       <c r="AH3">
-        <v>10.46</v>
+        <v>10.44</v>
       </c>
       <c r="AI3">
         <v>11.19</v>
@@ -1127,7 +1153,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>35.9</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1164,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>243.15</v>
+        <v>244.6</v>
       </c>
       <c r="D4">
-        <v>-1.08</v>
+        <v>0.6</v>
       </c>
       <c r="E4">
         <v>331.3</v>
@@ -1150,25 +1176,25 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-26.61</v>
+        <v>-26.17</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>9.15</v>
       </c>
       <c r="I4">
-        <v>-5.04</v>
+        <v>-4.3</v>
       </c>
       <c r="J4">
-        <v>1.3</v>
+        <v>4.17</v>
       </c>
       <c r="K4">
-        <v>3.13</v>
+        <v>2.69</v>
       </c>
       <c r="L4">
-        <v>-26.45</v>
+        <v>-25.29</v>
       </c>
       <c r="M4">
-        <v>-0.73</v>
+        <v>-0.53</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1177,19 +1203,19 @@
         <v>32</v>
       </c>
       <c r="P4">
-        <v>248.67</v>
+        <v>246.47</v>
       </c>
       <c r="Q4">
-        <v>250.5</v>
+        <v>251.07</v>
       </c>
       <c r="R4">
-        <v>243.27</v>
+        <v>243.56</v>
       </c>
       <c r="S4">
-        <v>259.74</v>
+        <v>259.43</v>
       </c>
       <c r="T4">
-        <v>-6.39</v>
+        <v>-5.72</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1204,34 +1230,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>44.05</v>
+        <v>45.84</v>
       </c>
       <c r="Z4">
-        <v>1.81</v>
+        <v>1.22</v>
       </c>
       <c r="AA4">
-        <v>3.55</v>
+        <v>3.09</v>
       </c>
       <c r="AB4">
-        <v>-1.74</v>
+        <v>-1.87</v>
       </c>
       <c r="AC4">
-        <v>1.18</v>
+        <v>2.22</v>
       </c>
       <c r="AD4">
-        <v>6.65</v>
+        <v>1.95</v>
       </c>
       <c r="AE4">
-        <v>5.93</v>
+        <v>5.8</v>
       </c>
       <c r="AF4">
-        <v>-49.43</v>
+        <v>-53.16</v>
       </c>
       <c r="AG4">
-        <v>270.15</v>
+        <v>269.2</v>
       </c>
       <c r="AH4">
-        <v>230.85</v>
+        <v>232.94</v>
       </c>
       <c r="AI4">
         <v>261.7</v>
@@ -1240,7 +1266,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>24.29</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1251,10 +1277,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>660.45</v>
+        <v>680.65</v>
       </c>
       <c r="D5">
-        <v>-0.13</v>
+        <v>3.06</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1263,46 +1289,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-23.29</v>
+        <v>-20.94</v>
       </c>
       <c r="H5">
-        <v>34.59</v>
+        <v>38.71</v>
       </c>
       <c r="I5">
-        <v>-3.93</v>
+        <v>0.41</v>
       </c>
       <c r="J5">
-        <v>-11.16</v>
+        <v>-5.85</v>
       </c>
       <c r="K5">
-        <v>26.78</v>
+        <v>30.86</v>
       </c>
       <c r="L5">
-        <v>-19.83</v>
+        <v>-17.07</v>
       </c>
       <c r="M5">
-        <v>-7.18</v>
+        <v>-6.62</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>672.3200000000001</v>
+        <v>672.88</v>
       </c>
       <c r="Q5">
-        <v>700.3099999999999</v>
+        <v>698.12</v>
       </c>
       <c r="R5">
-        <v>640.42</v>
+        <v>643.33</v>
       </c>
       <c r="S5">
-        <v>630.1900000000001</v>
+        <v>629.72</v>
       </c>
       <c r="T5">
-        <v>4.8</v>
+        <v>8.09</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1317,34 +1343,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>43.47</v>
+        <v>50.56</v>
       </c>
       <c r="Z5">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="AA5">
-        <v>12.66</v>
+        <v>10.58</v>
       </c>
       <c r="AB5">
-        <v>-10.06</v>
+        <v>-8.32</v>
       </c>
       <c r="AC5">
-        <v>1.58</v>
+        <v>16.73</v>
       </c>
       <c r="AD5">
-        <v>2.63</v>
+        <v>7.15</v>
       </c>
       <c r="AE5">
-        <v>25.13</v>
+        <v>25.29</v>
       </c>
       <c r="AF5">
-        <v>-72.87</v>
+        <v>-42.08</v>
       </c>
       <c r="AG5">
-        <v>752.88</v>
+        <v>750.11</v>
       </c>
       <c r="AH5">
-        <v>647.74</v>
+        <v>646.13</v>
       </c>
       <c r="AI5">
         <v>733.89</v>
@@ -1353,7 +1379,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>17.9</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1364,10 +1390,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>28.07</v>
+        <v>30.59</v>
       </c>
       <c r="D6">
-        <v>-1.54</v>
+        <v>8.98</v>
       </c>
       <c r="E6">
         <v>57.9</v>
@@ -1376,46 +1402,46 @@
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-51.52</v>
+        <v>-47.17</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>11.16</v>
       </c>
       <c r="I6">
-        <v>-2.23</v>
+        <v>5.45</v>
       </c>
       <c r="J6">
-        <v>-5.04</v>
+        <v>6.36</v>
       </c>
       <c r="K6">
-        <v>-12.47</v>
+        <v>-3.87</v>
       </c>
       <c r="L6">
-        <v>-50.65</v>
+        <v>-45.58</v>
       </c>
       <c r="M6">
-        <v>-10.51</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P6">
-        <v>28.71</v>
+        <v>29.03</v>
       </c>
       <c r="Q6">
-        <v>29.08</v>
+        <v>29.21</v>
       </c>
       <c r="R6">
         <v>30.77</v>
       </c>
       <c r="S6">
-        <v>35.85</v>
+        <v>35.76</v>
       </c>
       <c r="T6">
-        <v>-21.69</v>
+        <v>-14.45</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1430,43 +1456,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>33.72</v>
+        <v>57.3</v>
       </c>
       <c r="Z6">
-        <v>-0.5600000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="AA6">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="AB6">
-        <v>-0.02</v>
+        <v>0.12</v>
       </c>
       <c r="AC6">
-        <v>9.82</v>
+        <v>33.33</v>
       </c>
       <c r="AD6">
-        <v>24.51</v>
+        <v>22.54</v>
       </c>
       <c r="AE6">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AF6">
-        <v>165.43</v>
+        <v>1621.91</v>
       </c>
       <c r="AG6">
-        <v>30.13</v>
+        <v>30.36</v>
       </c>
       <c r="AH6">
-        <v>28.04</v>
+        <v>28.06</v>
       </c>
       <c r="AI6">
-        <v>30.51</v>
+        <v>27.14</v>
       </c>
       <c r="AJ6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AK6">
-        <v>27.12</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1477,10 +1503,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1311</v>
+        <v>1313.2</v>
       </c>
       <c r="D7">
-        <v>-0.83</v>
+        <v>0.17</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1489,46 +1515,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-17.29</v>
+        <v>-17.15</v>
       </c>
       <c r="H7">
-        <v>4.15</v>
+        <v>4.32</v>
       </c>
       <c r="I7">
-        <v>-1.35</v>
+        <v>-0.29</v>
       </c>
       <c r="J7">
-        <v>0.5600000000000001</v>
+        <v>1.91</v>
       </c>
       <c r="K7">
-        <v>-2.41</v>
+        <v>-2.6</v>
       </c>
       <c r="L7">
-        <v>-4.36</v>
+        <v>-3.97</v>
       </c>
       <c r="M7">
-        <v>6.15</v>
+        <v>6.18</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P7">
-        <v>1315.2</v>
+        <v>1314.44</v>
       </c>
       <c r="Q7">
-        <v>1304.02</v>
+        <v>1306.07</v>
       </c>
       <c r="R7">
-        <v>1303.94</v>
+        <v>1305.03</v>
       </c>
       <c r="S7">
-        <v>1397.14</v>
+        <v>1396.31</v>
       </c>
       <c r="T7">
-        <v>-6.17</v>
+        <v>-5.95</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1543,34 +1569,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>50.6</v>
+        <v>51.31</v>
       </c>
       <c r="Z7">
-        <v>4.68</v>
+        <v>4.27</v>
       </c>
       <c r="AA7">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="AB7">
-        <v>0.98</v>
+        <v>0.46</v>
       </c>
       <c r="AC7">
-        <v>56.84</v>
+        <v>51.96</v>
       </c>
       <c r="AD7">
-        <v>60.72</v>
+        <v>57.09</v>
       </c>
       <c r="AE7">
-        <v>21.36</v>
+        <v>20.51</v>
       </c>
       <c r="AF7">
-        <v>-32.98</v>
+        <v>-49.37</v>
       </c>
       <c r="AG7">
-        <v>1347.93</v>
+        <v>1347.48</v>
       </c>
       <c r="AH7">
-        <v>1260.11</v>
+        <v>1264.66</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1579,7 +1605,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>11.74</v>
+        <v>12.01</v>
       </c>
     </row>
   </sheetData>
@@ -1730,7 +1756,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1743,711 +1769,717 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>45</v>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="E5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1.48</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-5.14</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-5.35</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.21</v>
+      <c r="B8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>2.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D9" s="6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.58</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-11.51</v>
+        <v>-5.35</v>
       </c>
       <c r="D10" s="6">
-        <v>-11.16</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.35</v>
+        <v>-2.59</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.76</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.62</v>
+        <v>1.3</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.04</v>
+        <v>4.17</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.42</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.08</v>
+        <v>-11.16</v>
       </c>
       <c r="D12" s="6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.64</v>
+        <v>-5.85</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5.31</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>0.74</v>
+        <v>-5.04</v>
       </c>
       <c r="D13" s="6">
-        <v>1.44</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.7</v>
+        <v>6.36</v>
+      </c>
+      <c r="E13" s="7">
+        <v>11.4</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.25</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.07000000000000001</v>
+        <v>1.91</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.75</v>
+        <v>1.44</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.29</v>
+        <v>0.22</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.84</v>
+        <v>-2.25</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.93</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.91</v>
+        <v>-1.68</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.57</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.16</v>
+        <v>-5.04</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.23</v>
+        <v>-4.3</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.07000000000000001</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.14</v>
+        <v>-3.93</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.35</v>
+        <v>0.41</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.21</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-23.09</v>
+        <v>-2.23</v>
       </c>
       <c r="D19" s="6">
-        <v>-22.39</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.7</v>
+        <v>5.45</v>
+      </c>
+      <c r="E19" s="7">
+        <v>7.68</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-26.91</v>
+        <v>-1.35</v>
       </c>
       <c r="D20" s="6">
-        <v>-27.72</v>
+        <v>-0.29</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.8100000000000001</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-24.83</v>
+        <v>-22.39</v>
       </c>
       <c r="D21" s="6">
-        <v>-26.45</v>
+        <v>-20.53</v>
       </c>
       <c r="E21" s="7">
-        <v>-1.62</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-20.45</v>
+        <v>-27.72</v>
       </c>
       <c r="D22" s="6">
-        <v>-19.83</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.62</v>
+        <v>-26.5</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.22</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-49.26</v>
+        <v>-26.45</v>
       </c>
       <c r="D23" s="6">
-        <v>-50.65</v>
+        <v>-25.29</v>
       </c>
       <c r="E23" s="7">
-        <v>-1.39</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.4</v>
+        <v>-19.83</v>
       </c>
       <c r="D24" s="6">
-        <v>-4.36</v>
+        <v>-17.07</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.96</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>2.66</v>
+        <v>-50.65</v>
       </c>
       <c r="D25" s="6">
-        <v>0.88</v>
+        <v>-45.58</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.78</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>3.55</v>
+        <v>-4.36</v>
       </c>
       <c r="D26" s="6">
-        <v>2.56</v>
+        <v>-3.97</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.99</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>4.74</v>
+        <v>0.88</v>
       </c>
       <c r="D27" s="6">
-        <v>3.13</v>
+        <v>2.97</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.61</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>28.86</v>
+        <v>2.56</v>
       </c>
       <c r="D28" s="6">
-        <v>26.78</v>
+        <v>3.94</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.08</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-10.29</v>
+        <v>3.13</v>
       </c>
       <c r="D29" s="6">
-        <v>-12.47</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.18</v>
+        <v>2.69</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-2.32</v>
+        <v>26.78</v>
       </c>
       <c r="D30" s="6">
-        <v>-2.41</v>
+        <v>30.86</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.09</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-26.53</v>
+        <v>-12.47</v>
       </c>
       <c r="D31" s="6">
-        <v>-26.61</v>
+        <v>-3.87</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.08</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-30.31</v>
+        <v>-2.41</v>
       </c>
       <c r="D32" s="6">
-        <v>-30.84</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.53</v>
+        <v>-2.6</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-25.81</v>
+        <v>-26.61</v>
       </c>
       <c r="D33" s="6">
-        <v>-26.61</v>
+        <v>-25.62</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.8</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-23.19</v>
+        <v>-30.84</v>
       </c>
       <c r="D34" s="6">
-        <v>-23.29</v>
+        <v>-30.11</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.1</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-50.76</v>
+        <v>-26.61</v>
       </c>
       <c r="D35" s="6">
-        <v>-51.52</v>
+        <v>-26.17</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.76</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-16.59</v>
+        <v>-23.29</v>
       </c>
       <c r="D36" s="6">
-        <v>-17.29</v>
+        <v>-20.94</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.7</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>27.41</v>
+        <v>-51.52</v>
       </c>
       <c r="D37" s="6">
-        <v>27.38</v>
+        <v>-47.17</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.03</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>10.51</v>
+        <v>-17.29</v>
       </c>
       <c r="D38" s="6">
-        <v>10.43</v>
+        <v>-17.15</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.08</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>245.8</v>
+        <v>27.38</v>
       </c>
       <c r="D39" s="6">
-        <v>243.15</v>
+        <v>27.75</v>
       </c>
       <c r="E39" s="7">
-        <v>-2.65</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>661.3</v>
+        <v>10.43</v>
       </c>
       <c r="D40" s="6">
-        <v>660.45</v>
+        <v>10.54</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.85</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>28.51</v>
+        <v>243.15</v>
       </c>
       <c r="D41" s="6">
-        <v>28.07</v>
+        <v>244.6</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.44</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1322</v>
+        <v>660.45</v>
       </c>
       <c r="D42" s="6">
-        <v>1311</v>
+        <v>680.65</v>
       </c>
       <c r="E42" s="7">
-        <v>-11</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>50</v>
+        <v>28.07</v>
       </c>
       <c r="D43" s="6">
-        <v>66</v>
-      </c>
-      <c r="E43" s="8">
-        <v>16</v>
+        <v>30.59</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.52</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>66</v>
+        <v>1311</v>
       </c>
       <c r="D44" s="6">
-        <v>50</v>
+        <v>1313.2</v>
       </c>
       <c r="E44" s="7">
-        <v>-16</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2458,13 +2490,13 @@
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>46.14</v>
+        <v>45.76</v>
       </c>
       <c r="D45" s="6">
-        <v>45.76</v>
+        <v>51</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.38</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2475,13 +2507,13 @@
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>37.13</v>
+        <v>34.9</v>
       </c>
       <c r="D46" s="6">
-        <v>34.9</v>
+        <v>40.21</v>
       </c>
       <c r="E46" s="7">
-        <v>-2.23</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2492,13 +2524,13 @@
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>46.67</v>
+        <v>44.05</v>
       </c>
       <c r="D47" s="6">
-        <v>44.05</v>
+        <v>45.84</v>
       </c>
       <c r="E47" s="7">
-        <v>-2.62</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2509,13 +2541,13 @@
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>43.72</v>
+        <v>43.47</v>
       </c>
       <c r="D48" s="6">
-        <v>43.47</v>
+        <v>50.56</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.25</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2526,13 +2558,13 @@
         <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>37.03</v>
+        <v>33.72</v>
       </c>
       <c r="D49" s="6">
-        <v>33.72</v>
+        <v>57.3</v>
       </c>
       <c r="E49" s="7">
-        <v>-3.31</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2543,13 +2575,13 @@
         <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>54.29</v>
+        <v>50.6</v>
       </c>
       <c r="D50" s="6">
-        <v>50.6</v>
+        <v>51.31</v>
       </c>
       <c r="E50" s="7">
-        <v>-3.69</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2560,13 +2592,13 @@
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-45.4</v>
+        <v>-34.2</v>
       </c>
       <c r="D51" s="6">
-        <v>-34.2</v>
-      </c>
-      <c r="E51" s="8">
-        <v>11.2</v>
+        <v>60.3</v>
+      </c>
+      <c r="E51" s="7">
+        <v>94.5</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2577,13 +2609,13 @@
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>-27.91</v>
+        <v>2.63</v>
       </c>
       <c r="D52" s="6">
-        <v>2.63</v>
-      </c>
-      <c r="E52" s="8">
-        <v>30.54</v>
+        <v>32.93</v>
+      </c>
+      <c r="E52" s="7">
+        <v>30.3</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2594,13 +2626,13 @@
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>-53.26</v>
+        <v>-49.43</v>
       </c>
       <c r="D53" s="6">
-        <v>-49.43</v>
+        <v>-53.16</v>
       </c>
       <c r="E53" s="8">
-        <v>3.83</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2611,13 +2643,13 @@
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-68.58</v>
+        <v>-72.87</v>
       </c>
       <c r="D54" s="6">
-        <v>-72.87</v>
+        <v>-42.08</v>
       </c>
       <c r="E54" s="7">
-        <v>-4.29</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2628,13 +2660,13 @@
         <v>31</v>
       </c>
       <c r="C55" s="6">
-        <v>13.48</v>
+        <v>165.43</v>
       </c>
       <c r="D55" s="6">
-        <v>165.43</v>
-      </c>
-      <c r="E55" s="8">
-        <v>151.95</v>
+        <v>1621.91</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1456.48</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2645,19 +2677,19 @@
         <v>31</v>
       </c>
       <c r="C56" s="6">
-        <v>-12.5</v>
+        <v>-32.98</v>
       </c>
       <c r="D56" s="6">
-        <v>-32.98</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-20.48</v>
+        <v>-49.37</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-16.39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2681,28 +2713,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2716,16 +2748,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>42.1</v>
+        <v>49.4</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.1</v>
+        <v>0.9</v>
       </c>
       <c r="G2" s="11">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="H2" s="11">
         <v>58.2</v>
@@ -2842,10 +2874,10 @@
         <v>40</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>37</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>38</v>
@@ -2853,22 +2885,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.06150000000000001</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0073</v>
+        <v>-0.0053</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0718</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1008</v>
+        <v>-0.08960000000000001</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1051</v>
+        <v>-0.0983</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.1445</v>
+        <v>-0.1426</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,34 +187,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.8 → 51.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.8</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>43.5 → 50.6</t>
-  </si>
-  <si>
-    <t>43.5</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>33.7 → 57.3</t>
-  </si>
-  <si>
-    <t>33.7</t>
-  </si>
-  <si>
-    <t>57.3</t>
+    <t>52.3 → 49.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.3</t>
+  </si>
+  <si>
+    <t>49.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -799,7 +781,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -938,10 +921,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.75</v>
+        <v>28.14</v>
       </c>
       <c r="D2">
-        <v>1.35</v>
+        <v>-0.11</v>
       </c>
       <c r="E2">
         <v>37.31</v>
@@ -950,46 +933,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-25.62</v>
+        <v>-24.58</v>
       </c>
       <c r="H2">
-        <v>20.76</v>
+        <v>22.45</v>
       </c>
       <c r="I2">
-        <v>0.22</v>
+        <v>2.29</v>
       </c>
       <c r="J2">
-        <v>1.28</v>
+        <v>3.61</v>
       </c>
       <c r="K2">
-        <v>2.97</v>
+        <v>1.55</v>
       </c>
       <c r="L2">
-        <v>-20.53</v>
+        <v>-24.09</v>
       </c>
       <c r="M2">
-        <v>-9.83</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>27.51</v>
+        <v>27.77</v>
       </c>
       <c r="Q2">
-        <v>27.41</v>
+        <v>27.5</v>
       </c>
       <c r="R2">
-        <v>28.53</v>
+        <v>28.58</v>
       </c>
       <c r="S2">
-        <v>28.8</v>
+        <v>28.75</v>
       </c>
       <c r="T2">
-        <v>-3.65</v>
+        <v>-2.11</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -1004,34 +987,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>51</v>
+        <v>55.72</v>
       </c>
       <c r="Z2">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="AA2">
-        <v>-0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="AB2">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="AC2">
-        <v>75.15000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="AD2">
-        <v>72.20999999999999</v>
+        <v>87.03</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="AF2">
-        <v>60.3</v>
+        <v>58.04</v>
       </c>
       <c r="AG2">
-        <v>27.79</v>
+        <v>28.07</v>
       </c>
       <c r="AH2">
-        <v>27.03</v>
+        <v>26.92</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1040,7 +1023,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>26.52</v>
+        <v>36.61</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1051,10 +1034,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.54</v>
+        <v>10.59</v>
       </c>
       <c r="D3">
-        <v>1.05</v>
+        <v>-0.84</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1063,46 +1046,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-30.11</v>
+        <v>-29.77</v>
       </c>
       <c r="H3">
-        <v>18.83</v>
+        <v>19.39</v>
       </c>
       <c r="I3">
-        <v>-1.68</v>
+        <v>-0.09</v>
       </c>
       <c r="J3">
-        <v>-2.59</v>
+        <v>-1.58</v>
       </c>
       <c r="K3">
-        <v>3.94</v>
+        <v>0.09</v>
       </c>
       <c r="L3">
-        <v>-26.5</v>
+        <v>-28.3</v>
       </c>
       <c r="M3">
-        <v>-14.26</v>
+        <v>-14.37</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="P3">
-        <v>10.54</v>
+        <v>10.55</v>
       </c>
       <c r="Q3">
-        <v>10.75</v>
+        <v>10.73</v>
       </c>
       <c r="R3">
-        <v>11.03</v>
+        <v>11.04</v>
       </c>
       <c r="S3">
-        <v>11.31</v>
+        <v>11.28</v>
       </c>
       <c r="T3">
-        <v>-6.81</v>
+        <v>-6.11</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1117,34 +1100,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.21</v>
+        <v>43.21</v>
       </c>
       <c r="Z3">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="AA3">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="AB3">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AC3">
-        <v>10.25</v>
+        <v>58.44</v>
       </c>
       <c r="AD3">
-        <v>3.42</v>
+        <v>35.58</v>
       </c>
       <c r="AE3">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AF3">
-        <v>32.93</v>
+        <v>102.82</v>
       </c>
       <c r="AG3">
-        <v>11.06</v>
+        <v>11.05</v>
       </c>
       <c r="AH3">
-        <v>10.44</v>
+        <v>10.42</v>
       </c>
       <c r="AI3">
         <v>11.19</v>
@@ -1153,7 +1136,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>36.22</v>
+        <v>34.54</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1164,58 +1147,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>244.6</v>
+        <v>242</v>
       </c>
       <c r="D4">
-        <v>0.6</v>
+        <v>-0.82</v>
       </c>
       <c r="E4">
-        <v>331.3</v>
+        <v>328.45</v>
       </c>
       <c r="F4">
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-26.17</v>
+        <v>-26.32</v>
       </c>
       <c r="H4">
-        <v>9.15</v>
+        <v>7.99</v>
       </c>
       <c r="I4">
-        <v>-4.3</v>
+        <v>-3.1</v>
       </c>
       <c r="J4">
-        <v>4.17</v>
+        <v>3.11</v>
       </c>
       <c r="K4">
-        <v>2.69</v>
+        <v>0.55</v>
       </c>
       <c r="L4">
-        <v>-25.29</v>
+        <v>-26.95</v>
       </c>
       <c r="M4">
-        <v>-0.53</v>
+        <v>-0.88</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P4">
-        <v>246.47</v>
+        <v>243.91</v>
       </c>
       <c r="Q4">
-        <v>251.07</v>
+        <v>251.83</v>
       </c>
       <c r="R4">
-        <v>243.56</v>
+        <v>244</v>
       </c>
       <c r="S4">
-        <v>259.43</v>
+        <v>258.82</v>
       </c>
       <c r="T4">
-        <v>-5.72</v>
+        <v>-6.5</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1230,43 +1213,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>45.84</v>
+        <v>43.02</v>
       </c>
       <c r="Z4">
-        <v>1.22</v>
+        <v>0.12</v>
       </c>
       <c r="AA4">
-        <v>3.09</v>
+        <v>2.11</v>
       </c>
       <c r="AB4">
-        <v>-1.87</v>
+        <v>-1.99</v>
       </c>
       <c r="AC4">
-        <v>2.22</v>
+        <v>3.64</v>
       </c>
       <c r="AD4">
-        <v>1.95</v>
+        <v>3.17</v>
       </c>
       <c r="AE4">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AF4">
-        <v>-53.16</v>
+        <v>-63.61</v>
       </c>
       <c r="AG4">
-        <v>269.2</v>
+        <v>267.67</v>
       </c>
       <c r="AH4">
-        <v>232.94</v>
+        <v>235.99</v>
       </c>
       <c r="AI4">
-        <v>261.7</v>
+        <v>259.86</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>23.12</v>
+        <v>22.35</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1277,10 +1260,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>680.65</v>
+        <v>664.95</v>
       </c>
       <c r="D5">
-        <v>3.06</v>
+        <v>-1.35</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1289,46 +1272,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-20.94</v>
+        <v>-22.77</v>
       </c>
       <c r="H5">
-        <v>38.71</v>
+        <v>35.51</v>
       </c>
       <c r="I5">
-        <v>0.41</v>
+        <v>-2.36</v>
       </c>
       <c r="J5">
-        <v>-5.85</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="K5">
-        <v>30.86</v>
+        <v>24.9</v>
       </c>
       <c r="L5">
-        <v>-17.07</v>
+        <v>-20.5</v>
       </c>
       <c r="M5">
-        <v>-6.62</v>
+        <v>-6.93</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="P5">
-        <v>672.88</v>
+        <v>668.28</v>
       </c>
       <c r="Q5">
-        <v>698.12</v>
+        <v>692.6900000000001</v>
       </c>
       <c r="R5">
-        <v>643.33</v>
+        <v>648.75</v>
       </c>
       <c r="S5">
-        <v>629.72</v>
+        <v>628.79</v>
       </c>
       <c r="T5">
-        <v>8.09</v>
+        <v>5.75</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1343,34 +1326,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>50.56</v>
+        <v>45.57</v>
       </c>
       <c r="Z5">
-        <v>2.26</v>
+        <v>0.06</v>
       </c>
       <c r="AA5">
-        <v>10.58</v>
+        <v>7.02</v>
       </c>
       <c r="AB5">
-        <v>-8.32</v>
+        <v>-6.95</v>
       </c>
       <c r="AC5">
-        <v>16.73</v>
+        <v>36.8</v>
       </c>
       <c r="AD5">
-        <v>7.15</v>
+        <v>27.88</v>
       </c>
       <c r="AE5">
-        <v>25.29</v>
+        <v>24.22</v>
       </c>
       <c r="AF5">
-        <v>-42.08</v>
+        <v>-74.16</v>
       </c>
       <c r="AG5">
-        <v>750.11</v>
+        <v>744.1</v>
       </c>
       <c r="AH5">
-        <v>646.13</v>
+        <v>641.28</v>
       </c>
       <c r="AI5">
         <v>733.89</v>
@@ -1379,7 +1362,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>15.8</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1390,37 +1373,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>30.59</v>
+        <v>30.34</v>
       </c>
       <c r="D6">
-        <v>8.98</v>
+        <v>1.61</v>
       </c>
       <c r="E6">
-        <v>57.9</v>
+        <v>57.63</v>
       </c>
       <c r="F6">
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-47.17</v>
+        <v>-47.35</v>
       </c>
       <c r="H6">
-        <v>11.16</v>
+        <v>10.25</v>
       </c>
       <c r="I6">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="J6">
-        <v>6.36</v>
+        <v>6.01</v>
       </c>
       <c r="K6">
-        <v>-3.87</v>
+        <v>-3.56</v>
       </c>
       <c r="L6">
-        <v>-45.58</v>
+        <v>-47.6</v>
       </c>
       <c r="M6">
-        <v>-8.960000000000001</v>
+        <v>-8.67</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1429,19 +1412,19 @@
         <v>12</v>
       </c>
       <c r="P6">
-        <v>29.03</v>
+        <v>29.47</v>
       </c>
       <c r="Q6">
-        <v>29.21</v>
+        <v>29.34</v>
       </c>
       <c r="R6">
-        <v>30.77</v>
+        <v>30.75</v>
       </c>
       <c r="S6">
-        <v>35.76</v>
+        <v>35.58</v>
       </c>
       <c r="T6">
-        <v>-14.45</v>
+        <v>-14.72</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1456,43 +1439,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>57.3</v>
+        <v>54.77</v>
       </c>
       <c r="Z6">
-        <v>-0.39</v>
+        <v>-0.2</v>
       </c>
       <c r="AA6">
-        <v>-0.51</v>
+        <v>-0.42</v>
       </c>
       <c r="AB6">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AC6">
-        <v>33.33</v>
+        <v>88.34</v>
       </c>
       <c r="AD6">
-        <v>22.54</v>
+        <v>60.08</v>
       </c>
       <c r="AE6">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AF6">
-        <v>1621.91</v>
+        <v>68.27</v>
       </c>
       <c r="AG6">
-        <v>30.36</v>
+        <v>30.57</v>
       </c>
       <c r="AH6">
-        <v>28.06</v>
+        <v>28.12</v>
       </c>
       <c r="AI6">
-        <v>27.14</v>
+        <v>27.8</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>28.64</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1503,10 +1486,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1313.2</v>
+        <v>1309.8</v>
       </c>
       <c r="D7">
-        <v>0.17</v>
+        <v>-0.47</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1515,46 +1498,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-17.15</v>
+        <v>-17.36</v>
       </c>
       <c r="H7">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="I7">
-        <v>-0.29</v>
+        <v>-0.47</v>
       </c>
       <c r="J7">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="K7">
-        <v>-2.6</v>
+        <v>-2.98</v>
       </c>
       <c r="L7">
-        <v>-3.97</v>
+        <v>-7.34</v>
       </c>
       <c r="M7">
-        <v>6.18</v>
+        <v>5.78</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="P7">
-        <v>1314.44</v>
+        <v>1314.4</v>
       </c>
       <c r="Q7">
-        <v>1306.07</v>
+        <v>1309.46</v>
       </c>
       <c r="R7">
-        <v>1305.03</v>
+        <v>1306.43</v>
       </c>
       <c r="S7">
-        <v>1396.31</v>
+        <v>1394.72</v>
       </c>
       <c r="T7">
-        <v>-5.95</v>
+        <v>-6.09</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1569,34 +1552,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>51.31</v>
+        <v>49.94</v>
       </c>
       <c r="Z7">
-        <v>4.27</v>
+        <v>3.47</v>
       </c>
       <c r="AA7">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="AB7">
-        <v>0.46</v>
+        <v>-0.33</v>
       </c>
       <c r="AC7">
-        <v>51.96</v>
+        <v>45.37</v>
       </c>
       <c r="AD7">
-        <v>57.09</v>
+        <v>48.1</v>
       </c>
       <c r="AE7">
-        <v>20.51</v>
+        <v>19.47</v>
       </c>
       <c r="AF7">
-        <v>-49.37</v>
+        <v>-29.66</v>
       </c>
       <c r="AG7">
-        <v>1347.48</v>
+        <v>1346.62</v>
       </c>
       <c r="AH7">
-        <v>1264.66</v>
+        <v>1272.3</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1605,7 +1588,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>12.01</v>
+        <v>13.88</v>
       </c>
     </row>
   </sheetData>
@@ -1746,7 +1729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1786,7 +1769,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1804,892 +1787,852 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>4.45</v>
+      </c>
+      <c r="D7" s="6">
+        <v>3.61</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.84</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>69</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-1.58</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.8100000000000001</v>
+        <v>4.65</v>
       </c>
       <c r="D9" s="6">
-        <v>1.28</v>
+        <v>3.11</v>
       </c>
       <c r="E9" s="7">
-        <v>0.47</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.35</v>
+        <v>-6.95</v>
       </c>
       <c r="D10" s="6">
-        <v>-2.59</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="E10" s="7">
-        <v>2.76</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>1.3</v>
+        <v>6.15</v>
       </c>
       <c r="D11" s="6">
-        <v>4.17</v>
+        <v>6.01</v>
       </c>
       <c r="E11" s="7">
-        <v>2.87</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-11.16</v>
+        <v>3.44</v>
       </c>
       <c r="D12" s="6">
-        <v>-5.85</v>
+        <v>2.49</v>
       </c>
       <c r="E12" s="7">
-        <v>5.31</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-5.04</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="6">
-        <v>6.36</v>
+        <v>2.29</v>
       </c>
       <c r="E13" s="7">
-        <v>11.4</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="D14" s="6">
-        <v>1.91</v>
+        <v>-0.09</v>
       </c>
       <c r="E14" s="7">
-        <v>1.35</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>1.44</v>
+        <v>-2.03</v>
       </c>
       <c r="D15" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.22</v>
+        <v>-3.1</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.25</v>
+        <v>-1.02</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.68</v>
+        <v>-2.36</v>
       </c>
       <c r="E16" s="7">
-        <v>0.57</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.04</v>
+        <v>2.93</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.3</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.74</v>
+        <v>4.8</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.87</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.93</v>
+        <v>0.46</v>
       </c>
       <c r="D18" s="6">
-        <v>0.41</v>
+        <v>-0.47</v>
       </c>
       <c r="E18" s="7">
-        <v>4.34</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.23</v>
+        <v>-20.49</v>
       </c>
       <c r="D19" s="6">
-        <v>5.45</v>
+        <v>-24.09</v>
       </c>
       <c r="E19" s="7">
-        <v>7.68</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.35</v>
+        <v>-26.09</v>
       </c>
       <c r="D20" s="6">
-        <v>-0.29</v>
+        <v>-28.3</v>
       </c>
       <c r="E20" s="7">
-        <v>1.06</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-22.39</v>
+        <v>-25.91</v>
       </c>
       <c r="D21" s="6">
-        <v>-20.53</v>
+        <v>-26.95</v>
       </c>
       <c r="E21" s="7">
-        <v>1.86</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-27.72</v>
+        <v>-18.65</v>
       </c>
       <c r="D22" s="6">
-        <v>-26.5</v>
+        <v>-20.5</v>
       </c>
       <c r="E22" s="7">
-        <v>1.22</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-26.45</v>
+        <v>-47.44</v>
       </c>
       <c r="D23" s="6">
-        <v>-25.29</v>
+        <v>-47.6</v>
       </c>
       <c r="E23" s="7">
-        <v>1.16</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-19.83</v>
+        <v>-4.31</v>
       </c>
       <c r="D24" s="6">
-        <v>-17.07</v>
+        <v>-7.34</v>
       </c>
       <c r="E24" s="7">
-        <v>2.76</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-50.65</v>
+        <v>2.32</v>
       </c>
       <c r="D25" s="6">
-        <v>-45.58</v>
+        <v>1.55</v>
       </c>
       <c r="E25" s="7">
-        <v>5.07</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-4.36</v>
+        <v>2.01</v>
       </c>
       <c r="D26" s="6">
-        <v>-3.97</v>
+        <v>0.09</v>
       </c>
       <c r="E26" s="7">
-        <v>0.39</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="D27" s="6">
-        <v>2.97</v>
+        <v>0.55</v>
       </c>
       <c r="E27" s="7">
-        <v>2.09</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>2.56</v>
+        <v>28.68</v>
       </c>
       <c r="D28" s="6">
-        <v>3.94</v>
+        <v>24.9</v>
       </c>
       <c r="E28" s="7">
-        <v>1.38</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>3.13</v>
+        <v>-5.24</v>
       </c>
       <c r="D29" s="6">
-        <v>2.69</v>
+        <v>-3.56</v>
       </c>
       <c r="E29" s="8">
-        <v>-0.44</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>26.78</v>
+        <v>-3.29</v>
       </c>
       <c r="D30" s="6">
-        <v>30.86</v>
-      </c>
-      <c r="E30" s="7">
-        <v>4.08</v>
+        <v>-2.98</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.31</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-12.47</v>
+        <v>-24.5</v>
       </c>
       <c r="D31" s="6">
-        <v>-3.87</v>
+        <v>-24.58</v>
       </c>
       <c r="E31" s="7">
-        <v>8.6</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-2.41</v>
+        <v>-29.18</v>
       </c>
       <c r="D32" s="6">
-        <v>-2.6</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.19</v>
+        <v>-29.77</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-26.61</v>
+        <v>-26.35</v>
       </c>
       <c r="D33" s="6">
-        <v>-25.62</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.99</v>
+        <v>-26.32</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.03</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-30.84</v>
+        <v>-21.71</v>
       </c>
       <c r="D34" s="6">
-        <v>-30.11</v>
+        <v>-22.77</v>
       </c>
       <c r="E34" s="7">
-        <v>0.73</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-26.61</v>
+        <v>-48.43</v>
       </c>
       <c r="D35" s="6">
-        <v>-26.17</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.44</v>
+        <v>-47.35</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.08</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-23.29</v>
+        <v>-16.97</v>
       </c>
       <c r="D36" s="6">
-        <v>-20.94</v>
+        <v>-17.36</v>
       </c>
       <c r="E36" s="7">
-        <v>2.35</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>-51.52</v>
+        <v>28.17</v>
       </c>
       <c r="D37" s="6">
-        <v>-47.17</v>
+        <v>28.14</v>
       </c>
       <c r="E37" s="7">
-        <v>4.35</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>-17.29</v>
+        <v>10.68</v>
       </c>
       <c r="D38" s="6">
-        <v>-17.15</v>
+        <v>10.59</v>
       </c>
       <c r="E38" s="7">
-        <v>0.14</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>27.38</v>
+        <v>244</v>
       </c>
       <c r="D39" s="6">
-        <v>27.75</v>
+        <v>242</v>
       </c>
       <c r="E39" s="7">
-        <v>0.37</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>10.43</v>
+        <v>674.05</v>
       </c>
       <c r="D40" s="6">
-        <v>10.54</v>
+        <v>664.95</v>
       </c>
       <c r="E40" s="7">
-        <v>0.11</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>243.15</v>
+        <v>29.86</v>
       </c>
       <c r="D41" s="6">
-        <v>244.6</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.45</v>
+        <v>30.34</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.48</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>660.45</v>
+        <v>1316</v>
       </c>
       <c r="D42" s="6">
-        <v>680.65</v>
+        <v>1309.8</v>
       </c>
       <c r="E42" s="7">
-        <v>20.2</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>28.07</v>
+        <v>56.17</v>
       </c>
       <c r="D43" s="6">
-        <v>30.59</v>
+        <v>55.72</v>
       </c>
       <c r="E43" s="7">
-        <v>2.52</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>1311</v>
+        <v>46.21</v>
       </c>
       <c r="D44" s="6">
-        <v>1313.2</v>
+        <v>43.21</v>
       </c>
       <c r="E44" s="7">
-        <v>2.2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>45.76</v>
+        <v>45.2</v>
       </c>
       <c r="D45" s="6">
-        <v>51</v>
+        <v>43.02</v>
       </c>
       <c r="E45" s="7">
-        <v>5.24</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>34.9</v>
+        <v>48.42</v>
       </c>
       <c r="D46" s="6">
-        <v>40.21</v>
+        <v>45.57</v>
       </c>
       <c r="E46" s="7">
-        <v>5.31</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>44.05</v>
+        <v>51.57</v>
       </c>
       <c r="D47" s="6">
-        <v>45.84</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.79</v>
+        <v>54.77</v>
+      </c>
+      <c r="E47" s="8">
+        <v>3.2</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>43.47</v>
+        <v>52.26</v>
       </c>
       <c r="D48" s="6">
-        <v>50.56</v>
+        <v>49.94</v>
       </c>
       <c r="E48" s="7">
-        <v>7.09</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C49" s="6">
-        <v>33.72</v>
+        <v>95.42</v>
       </c>
       <c r="D49" s="6">
-        <v>57.3</v>
+        <v>58.04</v>
       </c>
       <c r="E49" s="7">
-        <v>23.58</v>
+        <v>-37.38</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>50.6</v>
+        <v>236.44</v>
       </c>
       <c r="D50" s="6">
-        <v>51.31</v>
+        <v>102.82</v>
       </c>
       <c r="E50" s="7">
-        <v>0.71</v>
+        <v>-133.62</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-34.2</v>
+        <v>-69.67</v>
       </c>
       <c r="D51" s="6">
-        <v>60.3</v>
-      </c>
-      <c r="E51" s="7">
-        <v>94.5</v>
+        <v>-63.61</v>
+      </c>
+      <c r="E51" s="8">
+        <v>6.06</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>2.63</v>
+        <v>-53.73</v>
       </c>
       <c r="D52" s="6">
-        <v>32.93</v>
+        <v>-74.16</v>
       </c>
       <c r="E52" s="7">
-        <v>30.3</v>
+        <v>-20.43</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>-49.43</v>
+        <v>0.02</v>
       </c>
       <c r="D53" s="6">
-        <v>-53.16</v>
+        <v>68.27</v>
       </c>
       <c r="E53" s="8">
-        <v>-3.73</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-72.87</v>
+        <v>-49.05</v>
       </c>
       <c r="D54" s="6">
-        <v>-42.08</v>
-      </c>
-      <c r="E54" s="7">
-        <v>30.79</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>165.43</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1621.91</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1456.48</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="6">
-        <v>-32.98</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-49.37</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-16.39</v>
+        <v>-29.66</v>
+      </c>
+      <c r="E54" s="8">
+        <v>19.39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2713,28 +2656,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2748,16 +2691,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>49.4</v>
+        <v>48.7</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G2" s="11">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="H2" s="11">
         <v>58.2</v>
@@ -2885,22 +2828,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.06179999999999999</v>
+        <v>0.0578</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0053</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.06619999999999999</v>
+        <v>-0.0693</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.08960000000000001</v>
+        <v>-0.0867</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0983</v>
+        <v>-0.09789999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.1426</v>
+        <v>-0.1437</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -187,16 +187,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.3 → 49.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.3</t>
+    <t>49.9 → 52.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>49.9</t>
+  </si>
+  <si>
+    <t>52.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,8 +408,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -921,58 +921,58 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>28.14</v>
+        <v>28.12</v>
       </c>
       <c r="D2">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E2">
-        <v>37.31</v>
+        <v>36.85</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-24.58</v>
+        <v>-23.69</v>
       </c>
       <c r="H2">
-        <v>22.45</v>
+        <v>22.37</v>
       </c>
       <c r="I2">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="J2">
-        <v>3.61</v>
+        <v>2.74</v>
       </c>
       <c r="K2">
-        <v>1.55</v>
+        <v>0.97</v>
       </c>
       <c r="L2">
-        <v>-24.09</v>
+        <v>-24.63</v>
       </c>
       <c r="M2">
-        <v>-9.789999999999999</v>
+        <v>-9.84</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P2">
-        <v>27.77</v>
+        <v>27.91</v>
       </c>
       <c r="Q2">
-        <v>27.5</v>
+        <v>27.54</v>
       </c>
       <c r="R2">
-        <v>28.58</v>
+        <v>28.56</v>
       </c>
       <c r="S2">
-        <v>28.75</v>
+        <v>28.72</v>
       </c>
       <c r="T2">
-        <v>-2.11</v>
+        <v>-2.1</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -987,34 +987,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>55.72</v>
+        <v>55.4</v>
       </c>
       <c r="Z2">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="AA2">
-        <v>-0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="AB2">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="AC2">
-        <v>99.05</v>
+        <v>97.42</v>
       </c>
       <c r="AD2">
-        <v>87.03</v>
+        <v>94.45</v>
       </c>
       <c r="AE2">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="AF2">
-        <v>58.04</v>
+        <v>-18.13</v>
       </c>
       <c r="AG2">
-        <v>28.07</v>
+        <v>28.17</v>
       </c>
       <c r="AH2">
-        <v>26.92</v>
+        <v>26.91</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1023,7 +1023,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>36.61</v>
+        <v>39.67</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1034,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.59</v>
+        <v>10.56</v>
       </c>
       <c r="D3">
-        <v>-0.84</v>
+        <v>-0.28</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1046,46 +1046,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-29.77</v>
+        <v>-29.97</v>
       </c>
       <c r="H3">
-        <v>19.39</v>
+        <v>19.05</v>
       </c>
       <c r="I3">
-        <v>-0.09</v>
+        <v>0.48</v>
       </c>
       <c r="J3">
-        <v>-1.58</v>
+        <v>-2.94</v>
       </c>
       <c r="K3">
-        <v>0.09</v>
+        <v>-3.83</v>
       </c>
       <c r="L3">
-        <v>-28.3</v>
+        <v>-29.41</v>
       </c>
       <c r="M3">
-        <v>-14.37</v>
+        <v>-14.6</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>10.55</v>
+        <v>10.56</v>
       </c>
       <c r="Q3">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
       <c r="R3">
-        <v>11.04</v>
+        <v>11.02</v>
       </c>
       <c r="S3">
-        <v>11.28</v>
+        <v>11.27</v>
       </c>
       <c r="T3">
-        <v>-6.11</v>
+        <v>-6.26</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>43.21</v>
+        <v>42.22</v>
       </c>
       <c r="Z3">
         <v>-0.11</v>
@@ -1109,25 +1109,25 @@
         <v>-0.11</v>
       </c>
       <c r="AB3">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC3">
-        <v>58.44</v>
+        <v>66.17</v>
       </c>
       <c r="AD3">
-        <v>35.58</v>
+        <v>54.22</v>
       </c>
       <c r="AE3">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>102.82</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AG3">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="AH3">
-        <v>10.42</v>
+        <v>10.4</v>
       </c>
       <c r="AI3">
         <v>11.19</v>
@@ -1136,7 +1136,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>34.54</v>
+        <v>33.63</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,58 +1147,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>242</v>
+        <v>243.15</v>
       </c>
       <c r="D4">
-        <v>-0.82</v>
+        <v>0.48</v>
       </c>
       <c r="E4">
-        <v>328.45</v>
+        <v>323.85</v>
       </c>
       <c r="F4">
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-26.32</v>
+        <v>-24.92</v>
       </c>
       <c r="H4">
-        <v>7.99</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
-        <v>-3.1</v>
+        <v>-1.08</v>
       </c>
       <c r="J4">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="K4">
-        <v>0.55</v>
+        <v>0.11</v>
       </c>
       <c r="L4">
-        <v>-26.95</v>
+        <v>-25.97</v>
       </c>
       <c r="M4">
-        <v>-0.88</v>
+        <v>-0.72</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P4">
-        <v>243.91</v>
+        <v>243.38</v>
       </c>
       <c r="Q4">
-        <v>251.83</v>
+        <v>252.13</v>
       </c>
       <c r="R4">
-        <v>244</v>
+        <v>244.07</v>
       </c>
       <c r="S4">
-        <v>258.82</v>
+        <v>258.55</v>
       </c>
       <c r="T4">
-        <v>-6.5</v>
+        <v>-5.95</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1213,43 +1213,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>43.02</v>
+        <v>44.67</v>
       </c>
       <c r="Z4">
-        <v>0.12</v>
+        <v>-0.25</v>
       </c>
       <c r="AA4">
-        <v>2.11</v>
+        <v>1.64</v>
       </c>
       <c r="AB4">
-        <v>-1.99</v>
+        <v>-1.89</v>
       </c>
       <c r="AC4">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AD4">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="AE4">
-        <v>5.4</v>
+        <v>5.21</v>
       </c>
       <c r="AF4">
-        <v>-63.61</v>
+        <v>-45.88</v>
       </c>
       <c r="AG4">
-        <v>267.67</v>
+        <v>266.99</v>
       </c>
       <c r="AH4">
-        <v>235.99</v>
+        <v>237.28</v>
       </c>
       <c r="AI4">
-        <v>259.86</v>
+        <v>257.39</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>22.35</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1260,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>664.95</v>
+        <v>655.45</v>
       </c>
       <c r="D5">
-        <v>-1.35</v>
+        <v>-1.43</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1272,46 +1272,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-22.77</v>
+        <v>-23.87</v>
       </c>
       <c r="H5">
-        <v>35.51</v>
+        <v>33.57</v>
       </c>
       <c r="I5">
-        <v>-2.36</v>
+        <v>-0.88</v>
       </c>
       <c r="J5">
-        <v>-8.779999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="K5">
-        <v>24.9</v>
+        <v>22.63</v>
       </c>
       <c r="L5">
-        <v>-20.5</v>
+        <v>-22.1</v>
       </c>
       <c r="M5">
-        <v>-6.93</v>
+        <v>-7.09</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P5">
-        <v>668.28</v>
+        <v>667.11</v>
       </c>
       <c r="Q5">
-        <v>692.6900000000001</v>
+        <v>689.05</v>
       </c>
       <c r="R5">
-        <v>648.75</v>
+        <v>651.0599999999999</v>
       </c>
       <c r="S5">
-        <v>628.79</v>
+        <v>628.3099999999999</v>
       </c>
       <c r="T5">
-        <v>5.75</v>
+        <v>4.32</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1326,43 +1326,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>45.57</v>
+        <v>42.73</v>
       </c>
       <c r="Z5">
-        <v>0.06</v>
+        <v>-1.78</v>
       </c>
       <c r="AA5">
-        <v>7.02</v>
+        <v>5.26</v>
       </c>
       <c r="AB5">
-        <v>-6.95</v>
+        <v>-7.03</v>
       </c>
       <c r="AC5">
-        <v>36.8</v>
+        <v>20.07</v>
       </c>
       <c r="AD5">
-        <v>27.88</v>
+        <v>28.99</v>
       </c>
       <c r="AE5">
-        <v>24.22</v>
+        <v>23.44</v>
       </c>
       <c r="AF5">
-        <v>-74.16</v>
+        <v>-73.94</v>
       </c>
       <c r="AG5">
-        <v>744.1</v>
+        <v>740.16</v>
       </c>
       <c r="AH5">
-        <v>641.28</v>
+        <v>637.9400000000001</v>
       </c>
       <c r="AI5">
-        <v>733.89</v>
+        <v>729.63</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>12.82</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,58 +1373,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>30.34</v>
+        <v>30.36</v>
       </c>
       <c r="D6">
-        <v>1.61</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6">
-        <v>57.63</v>
+        <v>56.25</v>
       </c>
       <c r="F6">
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-47.35</v>
+        <v>-46.03</v>
       </c>
       <c r="H6">
-        <v>10.25</v>
+        <v>10.32</v>
       </c>
       <c r="I6">
-        <v>4.8</v>
+        <v>6.49</v>
       </c>
       <c r="J6">
-        <v>6.01</v>
+        <v>5.23</v>
       </c>
       <c r="K6">
-        <v>-3.56</v>
+        <v>-2.91</v>
       </c>
       <c r="L6">
-        <v>-47.6</v>
+        <v>-47.32</v>
       </c>
       <c r="M6">
-        <v>-8.67</v>
+        <v>-8.56</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P6">
-        <v>29.47</v>
+        <v>29.84</v>
       </c>
       <c r="Q6">
-        <v>29.34</v>
+        <v>29.42</v>
       </c>
       <c r="R6">
-        <v>30.75</v>
+        <v>30.71</v>
       </c>
       <c r="S6">
-        <v>35.58</v>
+        <v>35.49</v>
       </c>
       <c r="T6">
-        <v>-14.72</v>
+        <v>-14.46</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1439,34 +1439,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>54.77</v>
+        <v>54.91</v>
       </c>
       <c r="Z6">
-        <v>-0.2</v>
+        <v>-0.12</v>
       </c>
       <c r="AA6">
-        <v>-0.42</v>
+        <v>-0.36</v>
       </c>
       <c r="AB6">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AC6">
-        <v>88.34</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="AD6">
-        <v>60.08</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="AE6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>68.27</v>
+        <v>22.25</v>
       </c>
       <c r="AG6">
-        <v>30.57</v>
+        <v>30.7</v>
       </c>
       <c r="AH6">
-        <v>28.12</v>
+        <v>28.13</v>
       </c>
       <c r="AI6">
         <v>27.8</v>
@@ -1475,7 +1475,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>32.96</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1486,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1309.8</v>
+        <v>1317</v>
       </c>
       <c r="D7">
-        <v>-0.47</v>
+        <v>0.55</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1498,46 +1498,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-17.36</v>
+        <v>-16.91</v>
       </c>
       <c r="H7">
-        <v>4.05</v>
+        <v>4.62</v>
       </c>
       <c r="I7">
-        <v>-0.47</v>
+        <v>-0.38</v>
       </c>
       <c r="J7">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="K7">
-        <v>-2.98</v>
+        <v>-2.03</v>
       </c>
       <c r="L7">
-        <v>-7.34</v>
+        <v>-6.36</v>
       </c>
       <c r="M7">
-        <v>5.78</v>
+        <v>5.71</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P7">
-        <v>1314.4</v>
+        <v>1313.4</v>
       </c>
       <c r="Q7">
-        <v>1309.46</v>
+        <v>1311.93</v>
       </c>
       <c r="R7">
-        <v>1306.43</v>
+        <v>1306.63</v>
       </c>
       <c r="S7">
-        <v>1394.72</v>
+        <v>1393.86</v>
       </c>
       <c r="T7">
-        <v>-6.09</v>
+        <v>-5.51</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1552,34 +1552,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>49.94</v>
+        <v>52.57</v>
       </c>
       <c r="Z7">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="AA7">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="AB7">
-        <v>-0.33</v>
+        <v>-0.24</v>
       </c>
       <c r="AC7">
-        <v>45.37</v>
+        <v>40</v>
       </c>
       <c r="AD7">
-        <v>48.1</v>
+        <v>44.12</v>
       </c>
       <c r="AE7">
-        <v>19.47</v>
+        <v>19.31</v>
       </c>
       <c r="AF7">
-        <v>-29.66</v>
+        <v>-30.42</v>
       </c>
       <c r="AG7">
-        <v>1346.62</v>
+        <v>1343.55</v>
       </c>
       <c r="AH7">
-        <v>1272.3</v>
+        <v>1280.3</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1588,7 +1588,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>13.88</v>
+        <v>15.86</v>
       </c>
     </row>
   </sheetData>
@@ -1821,13 +1821,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>4.45</v>
+        <v>3.61</v>
       </c>
       <c r="D7" s="6">
-        <v>3.61</v>
+        <v>2.74</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.84</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1838,13 +1838,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>0.38</v>
+        <v>-1.58</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.58</v>
+        <v>-2.94</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.96</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1855,13 +1855,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>4.65</v>
+        <v>3.11</v>
       </c>
       <c r="D9" s="6">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.54</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1872,13 +1872,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-6.95</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="D10" s="6">
-        <v>-8.779999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.83</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1889,13 +1889,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>6.15</v>
+        <v>6.01</v>
       </c>
       <c r="D11" s="6">
-        <v>6.01</v>
+        <v>5.23</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.14</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1906,13 +1906,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="D12" s="6">
-        <v>2.49</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.95</v>
+        <v>2.89</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1923,13 +1923,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="D13" s="6">
-        <v>2.29</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.11</v>
+        <v>2.59</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1940,13 +1940,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>0.75</v>
+        <v>-0.09</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.09</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.84</v>
+        <v>0.48</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1957,13 +1957,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.03</v>
+        <v>-3.1</v>
       </c>
       <c r="D15" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.07</v>
+        <v>-1.08</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.02</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1974,13 +1974,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.02</v>
+        <v>-2.36</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.36</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.34</v>
+        <v>-0.88</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.48</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1991,13 +1991,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>2.93</v>
+        <v>4.8</v>
       </c>
       <c r="D17" s="6">
-        <v>4.8</v>
+        <v>6.49</v>
       </c>
       <c r="E17" s="8">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2008,13 +2008,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>0.46</v>
+        <v>-0.47</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.47</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.93</v>
+        <v>-0.38</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2025,13 +2025,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-20.49</v>
+        <v>-24.09</v>
       </c>
       <c r="D19" s="6">
-        <v>-24.09</v>
+        <v>-24.63</v>
       </c>
       <c r="E19" s="7">
-        <v>-3.6</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2042,13 +2042,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-26.09</v>
+        <v>-28.3</v>
       </c>
       <c r="D20" s="6">
-        <v>-28.3</v>
+        <v>-29.41</v>
       </c>
       <c r="E20" s="7">
-        <v>-2.21</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2059,13 +2059,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-25.91</v>
+        <v>-26.95</v>
       </c>
       <c r="D21" s="6">
-        <v>-26.95</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.04</v>
+        <v>-25.97</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.98</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2076,13 +2076,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-18.65</v>
+        <v>-20.5</v>
       </c>
       <c r="D22" s="6">
-        <v>-20.5</v>
+        <v>-22.1</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.85</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2093,13 +2093,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-47.44</v>
+        <v>-47.6</v>
       </c>
       <c r="D23" s="6">
-        <v>-47.6</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.16</v>
+        <v>-47.32</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2110,13 +2110,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.31</v>
+        <v>-7.34</v>
       </c>
       <c r="D24" s="6">
-        <v>-7.34</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-3.03</v>
+        <v>-6.36</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.98</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2127,13 +2127,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="D25" s="6">
-        <v>1.55</v>
+        <v>0.97</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.77</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2144,13 +2144,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>2.01</v>
+        <v>0.09</v>
       </c>
       <c r="D26" s="6">
-        <v>0.09</v>
+        <v>-3.83</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.92</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2161,13 +2161,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="D27" s="6">
-        <v>0.55</v>
+        <v>0.11</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.38</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2178,13 +2178,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>28.68</v>
+        <v>24.9</v>
       </c>
       <c r="D28" s="6">
-        <v>24.9</v>
+        <v>22.63</v>
       </c>
       <c r="E28" s="7">
-        <v>-3.78</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2195,13 +2195,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-5.24</v>
+        <v>-3.56</v>
       </c>
       <c r="D29" s="6">
-        <v>-3.56</v>
+        <v>-2.91</v>
       </c>
       <c r="E29" s="8">
-        <v>1.68</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2212,13 +2212,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-3.29</v>
+        <v>-2.98</v>
       </c>
       <c r="D30" s="6">
-        <v>-2.98</v>
+        <v>-2.03</v>
       </c>
       <c r="E30" s="8">
-        <v>0.31</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2229,13 +2229,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-24.5</v>
+        <v>-24.58</v>
       </c>
       <c r="D31" s="6">
-        <v>-24.58</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.08</v>
+        <v>-23.69</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.89</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2246,13 +2246,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-29.18</v>
+        <v>-29.77</v>
       </c>
       <c r="D32" s="6">
-        <v>-29.77</v>
+        <v>-29.97</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.59</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2263,13 +2263,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-26.35</v>
+        <v>-26.32</v>
       </c>
       <c r="D33" s="6">
-        <v>-26.32</v>
+        <v>-24.92</v>
       </c>
       <c r="E33" s="8">
-        <v>0.03</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2280,13 +2280,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-21.71</v>
+        <v>-22.77</v>
       </c>
       <c r="D34" s="6">
-        <v>-22.77</v>
+        <v>-23.87</v>
       </c>
       <c r="E34" s="7">
-        <v>-1.06</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2297,13 +2297,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-48.43</v>
+        <v>-47.35</v>
       </c>
       <c r="D35" s="6">
-        <v>-47.35</v>
+        <v>-46.03</v>
       </c>
       <c r="E35" s="8">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2314,13 +2314,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-16.97</v>
+        <v>-17.36</v>
       </c>
       <c r="D36" s="6">
-        <v>-17.36</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.39</v>
+        <v>-16.91</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.45</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2331,13 +2331,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>28.17</v>
+        <v>28.14</v>
       </c>
       <c r="D37" s="6">
-        <v>28.14</v>
+        <v>28.12</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2348,13 +2348,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>10.68</v>
+        <v>10.59</v>
       </c>
       <c r="D38" s="6">
-        <v>10.59</v>
+        <v>10.56</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2365,13 +2365,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D39" s="6">
-        <v>242</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2</v>
+        <v>243.15</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.15</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2382,13 +2382,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>674.05</v>
+        <v>664.95</v>
       </c>
       <c r="D40" s="6">
-        <v>664.95</v>
+        <v>655.45</v>
       </c>
       <c r="E40" s="7">
-        <v>-9.1</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2399,13 +2399,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>29.86</v>
+        <v>30.34</v>
       </c>
       <c r="D41" s="6">
-        <v>30.34</v>
+        <v>30.36</v>
       </c>
       <c r="E41" s="8">
-        <v>0.48</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2416,13 +2416,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1316</v>
+        <v>1309.8</v>
       </c>
       <c r="D42" s="6">
-        <v>1309.8</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-6.2</v>
+        <v>1317</v>
+      </c>
+      <c r="E42" s="8">
+        <v>7.2</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2433,13 +2433,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>56.17</v>
+        <v>55.72</v>
       </c>
       <c r="D43" s="6">
-        <v>55.72</v>
+        <v>55.4</v>
       </c>
       <c r="E43" s="7">
-        <v>-0.45</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2450,13 +2450,13 @@
         <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>46.21</v>
+        <v>43.21</v>
       </c>
       <c r="D44" s="6">
-        <v>43.21</v>
+        <v>42.22</v>
       </c>
       <c r="E44" s="7">
-        <v>-3</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2467,13 +2467,13 @@
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>45.2</v>
+        <v>43.02</v>
       </c>
       <c r="D45" s="6">
-        <v>43.02</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-2.18</v>
+        <v>44.67</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.65</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2484,13 +2484,13 @@
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>48.42</v>
+        <v>45.57</v>
       </c>
       <c r="D46" s="6">
-        <v>45.57</v>
+        <v>42.73</v>
       </c>
       <c r="E46" s="7">
-        <v>-2.85</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2501,13 +2501,13 @@
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>51.57</v>
+        <v>54.77</v>
       </c>
       <c r="D47" s="6">
-        <v>54.77</v>
+        <v>54.91</v>
       </c>
       <c r="E47" s="8">
-        <v>3.2</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2518,13 +2518,13 @@
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>52.26</v>
+        <v>49.94</v>
       </c>
       <c r="D48" s="6">
-        <v>49.94</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-2.32</v>
+        <v>52.57</v>
+      </c>
+      <c r="E48" s="8">
+        <v>2.63</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2535,13 +2535,13 @@
         <v>31</v>
       </c>
       <c r="C49" s="6">
-        <v>95.42</v>
+        <v>58.04</v>
       </c>
       <c r="D49" s="6">
-        <v>58.04</v>
+        <v>-18.13</v>
       </c>
       <c r="E49" s="7">
-        <v>-37.38</v>
+        <v>-76.17</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2552,13 +2552,13 @@
         <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>236.44</v>
+        <v>102.82</v>
       </c>
       <c r="D50" s="6">
-        <v>102.82</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E50" s="7">
-        <v>-133.62</v>
+        <v>-103.76</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2569,13 +2569,13 @@
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-69.67</v>
+        <v>-63.61</v>
       </c>
       <c r="D51" s="6">
-        <v>-63.61</v>
+        <v>-45.88</v>
       </c>
       <c r="E51" s="8">
-        <v>6.06</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2586,13 +2586,13 @@
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>-53.73</v>
+        <v>-74.16</v>
       </c>
       <c r="D52" s="6">
-        <v>-74.16</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-20.43</v>
+        <v>-73.94</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.22</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2603,13 +2603,13 @@
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>0.02</v>
+        <v>68.27</v>
       </c>
       <c r="D53" s="6">
-        <v>68.27</v>
-      </c>
-      <c r="E53" s="8">
-        <v>68.25</v>
+        <v>22.25</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-46.02</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2620,13 +2620,13 @@
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-49.05</v>
+        <v>-29.66</v>
       </c>
       <c r="D54" s="6">
-        <v>-29.66</v>
-      </c>
-      <c r="E54" s="8">
-        <v>19.39</v>
+        <v>-30.42</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-0.76</v>
       </c>
     </row>
   </sheetData>
@@ -2691,16 +2691,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G2" s="11">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="H2" s="11">
         <v>58.2</v>
@@ -2828,22 +2828,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.0578</v>
+        <v>0.0571</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.008800000000000001</v>
+        <v>-0.0072</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0693</v>
+        <v>-0.0709</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0867</v>
+        <v>-0.08560000000000001</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.09789999999999999</v>
+        <v>-0.0984</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.1437</v>
+        <v>-0.146</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,16 +187,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.9 → 52.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.9</t>
+    <t>55.4 → 48.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>55.4</t>
+  </si>
+  <si>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>52.6 → 45.8</t>
   </si>
   <si>
     <t>52.6</t>
+  </si>
+  <si>
+    <t>45.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -921,58 +930,58 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>28.12</v>
+        <v>27.68</v>
       </c>
       <c r="D2">
-        <v>-0.07000000000000001</v>
+        <v>-1.56</v>
       </c>
       <c r="E2">
-        <v>36.85</v>
+        <v>36.6</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-23.69</v>
+        <v>-24.37</v>
       </c>
       <c r="H2">
-        <v>22.37</v>
+        <v>20.45</v>
       </c>
       <c r="I2">
-        <v>2.59</v>
+        <v>1.1</v>
       </c>
       <c r="J2">
-        <v>2.74</v>
+        <v>1.65</v>
       </c>
       <c r="K2">
-        <v>0.97</v>
+        <v>-0.61</v>
       </c>
       <c r="L2">
-        <v>-24.63</v>
+        <v>-24.88</v>
       </c>
       <c r="M2">
-        <v>-9.84</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P2">
-        <v>27.91</v>
+        <v>27.97</v>
       </c>
       <c r="Q2">
-        <v>27.54</v>
+        <v>27.55</v>
       </c>
       <c r="R2">
-        <v>28.56</v>
+        <v>28.53</v>
       </c>
       <c r="S2">
-        <v>28.72</v>
+        <v>28.7</v>
       </c>
       <c r="T2">
-        <v>-2.1</v>
+        <v>-3.55</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -987,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>55.4</v>
+        <v>48.76</v>
       </c>
       <c r="Z2">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AA2">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AB2">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="AC2">
-        <v>97.42</v>
+        <v>81.83</v>
       </c>
       <c r="AD2">
-        <v>94.45</v>
+        <v>92.77</v>
       </c>
       <c r="AE2">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="AF2">
-        <v>-18.13</v>
+        <v>-7.74</v>
       </c>
       <c r="AG2">
         <v>28.17</v>
       </c>
       <c r="AH2">
-        <v>26.91</v>
+        <v>26.92</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1023,7 +1032,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>39.67</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1043,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.56</v>
+        <v>10.57</v>
       </c>
       <c r="D3">
-        <v>-0.28</v>
+        <v>0.09</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1046,46 +1055,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-29.97</v>
+        <v>-29.91</v>
       </c>
       <c r="H3">
-        <v>19.05</v>
+        <v>19.17</v>
       </c>
       <c r="I3">
-        <v>0.48</v>
+        <v>1.34</v>
       </c>
       <c r="J3">
-        <v>-2.94</v>
+        <v>-2.22</v>
       </c>
       <c r="K3">
-        <v>-3.83</v>
+        <v>-3.73</v>
       </c>
       <c r="L3">
-        <v>-29.41</v>
+        <v>-29.44</v>
       </c>
       <c r="M3">
-        <v>-14.6</v>
+        <v>-14.55</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P3">
-        <v>10.56</v>
+        <v>10.59</v>
       </c>
       <c r="Q3">
-        <v>10.72</v>
+        <v>10.71</v>
       </c>
       <c r="R3">
-        <v>11.02</v>
+        <v>11.01</v>
       </c>
       <c r="S3">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="T3">
-        <v>-6.26</v>
+        <v>-6.06</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1100,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.22</v>
+        <v>42.69</v>
       </c>
       <c r="Z3">
         <v>-0.11</v>
@@ -1112,22 +1121,22 @@
         <v>-0</v>
       </c>
       <c r="AC3">
-        <v>66.17</v>
+        <v>57.52</v>
       </c>
       <c r="AD3">
-        <v>54.22</v>
+        <v>60.71</v>
       </c>
       <c r="AE3">
         <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>-0.9399999999999999</v>
+        <v>4.44</v>
       </c>
       <c r="AG3">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
       <c r="AH3">
-        <v>10.4</v>
+        <v>10.38</v>
       </c>
       <c r="AI3">
         <v>11.19</v>
@@ -1136,7 +1145,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>33.63</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,58 +1156,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>243.15</v>
+        <v>241</v>
       </c>
       <c r="D4">
-        <v>0.48</v>
+        <v>-0.88</v>
       </c>
       <c r="E4">
-        <v>323.85</v>
+        <v>320.6</v>
       </c>
       <c r="F4">
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-24.92</v>
+        <v>-24.83</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.54</v>
       </c>
       <c r="I4">
-        <v>-1.08</v>
+        <v>-0.88</v>
       </c>
       <c r="J4">
-        <v>2.96</v>
+        <v>1.65</v>
       </c>
       <c r="K4">
-        <v>0.11</v>
+        <v>-0.78</v>
       </c>
       <c r="L4">
-        <v>-25.97</v>
+        <v>-25.58</v>
       </c>
       <c r="M4">
-        <v>-0.72</v>
+        <v>-1.01</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P4">
-        <v>243.38</v>
+        <v>242.95</v>
       </c>
       <c r="Q4">
-        <v>252.13</v>
+        <v>251.71</v>
       </c>
       <c r="R4">
-        <v>244.07</v>
+        <v>244.06</v>
       </c>
       <c r="S4">
-        <v>258.55</v>
+        <v>258.25</v>
       </c>
       <c r="T4">
-        <v>-5.95</v>
+        <v>-6.68</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1213,34 +1222,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>44.67</v>
+        <v>42.21</v>
       </c>
       <c r="Z4">
-        <v>-0.25</v>
+        <v>-0.7</v>
       </c>
       <c r="AA4">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="AB4">
-        <v>-1.89</v>
+        <v>-1.87</v>
       </c>
       <c r="AC4">
-        <v>3.65</v>
+        <v>2.23</v>
       </c>
       <c r="AD4">
-        <v>3.65</v>
+        <v>3.17</v>
       </c>
       <c r="AE4">
-        <v>5.21</v>
+        <v>5.12</v>
       </c>
       <c r="AF4">
-        <v>-45.88</v>
+        <v>-62.56</v>
       </c>
       <c r="AG4">
-        <v>266.99</v>
+        <v>267.35</v>
       </c>
       <c r="AH4">
-        <v>237.28</v>
+        <v>236.07</v>
       </c>
       <c r="AI4">
         <v>257.39</v>
@@ -1249,7 +1258,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>23.35</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1269,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>655.45</v>
+        <v>647.65</v>
       </c>
       <c r="D5">
-        <v>-1.43</v>
+        <v>-1.19</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1272,46 +1281,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-23.87</v>
+        <v>-24.77</v>
       </c>
       <c r="H5">
-        <v>33.57</v>
+        <v>31.98</v>
       </c>
       <c r="I5">
-        <v>-0.88</v>
+        <v>-1.94</v>
       </c>
       <c r="J5">
-        <v>-8.800000000000001</v>
+        <v>-11.07</v>
       </c>
       <c r="K5">
-        <v>22.63</v>
+        <v>21.17</v>
       </c>
       <c r="L5">
-        <v>-22.1</v>
+        <v>-23.02</v>
       </c>
       <c r="M5">
-        <v>-7.09</v>
+        <v>-7.38</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>667.11</v>
+        <v>664.55</v>
       </c>
       <c r="Q5">
-        <v>689.05</v>
+        <v>683.75</v>
       </c>
       <c r="R5">
-        <v>651.0599999999999</v>
+        <v>653.13</v>
       </c>
       <c r="S5">
-        <v>628.3099999999999</v>
+        <v>627.78</v>
       </c>
       <c r="T5">
-        <v>4.32</v>
+        <v>3.17</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1326,43 +1335,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>42.73</v>
+        <v>40.5</v>
       </c>
       <c r="Z5">
-        <v>-1.78</v>
+        <v>-3.82</v>
       </c>
       <c r="AA5">
-        <v>5.26</v>
+        <v>3.44</v>
       </c>
       <c r="AB5">
-        <v>-7.03</v>
+        <v>-7.26</v>
       </c>
       <c r="AC5">
-        <v>20.07</v>
+        <v>6.71</v>
       </c>
       <c r="AD5">
-        <v>28.99</v>
+        <v>21.19</v>
       </c>
       <c r="AE5">
-        <v>23.44</v>
+        <v>22.77</v>
       </c>
       <c r="AF5">
-        <v>-73.94</v>
+        <v>-59.49</v>
       </c>
       <c r="AG5">
-        <v>740.16</v>
+        <v>728.1799999999999</v>
       </c>
       <c r="AH5">
-        <v>637.9400000000001</v>
+        <v>639.3099999999999</v>
       </c>
       <c r="AI5">
-        <v>729.63</v>
+        <v>720.3099999999999</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>13.75</v>
+        <v>15.84</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,37 +1382,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>30.36</v>
+        <v>30.45</v>
       </c>
       <c r="D6">
-        <v>0.07000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="E6">
-        <v>56.25</v>
+        <v>56.22</v>
       </c>
       <c r="F6">
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-46.03</v>
+        <v>-45.84</v>
       </c>
       <c r="H6">
-        <v>10.32</v>
+        <v>10.65</v>
       </c>
       <c r="I6">
-        <v>6.49</v>
+        <v>8.48</v>
       </c>
       <c r="J6">
-        <v>5.23</v>
+        <v>5.51</v>
       </c>
       <c r="K6">
-        <v>-2.91</v>
+        <v>-2.62</v>
       </c>
       <c r="L6">
-        <v>-47.32</v>
+        <v>-45.87</v>
       </c>
       <c r="M6">
-        <v>-8.56</v>
+        <v>-8.93</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1412,19 +1421,19 @@
         <v>13</v>
       </c>
       <c r="P6">
-        <v>29.84</v>
+        <v>30.32</v>
       </c>
       <c r="Q6">
-        <v>29.42</v>
+        <v>29.48</v>
       </c>
       <c r="R6">
-        <v>30.71</v>
+        <v>30.64</v>
       </c>
       <c r="S6">
-        <v>35.49</v>
+        <v>35.41</v>
       </c>
       <c r="T6">
-        <v>-14.46</v>
+        <v>-14</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1439,34 +1448,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>54.91</v>
+        <v>55.54</v>
       </c>
       <c r="Z6">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="AA6">
-        <v>-0.36</v>
+        <v>-0.29</v>
       </c>
       <c r="AB6">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="AC6">
-        <v>84.95999999999999</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="AD6">
-        <v>77.29000000000001</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>22.25</v>
+        <v>-63.17</v>
       </c>
       <c r="AG6">
-        <v>30.7</v>
+        <v>30.84</v>
       </c>
       <c r="AH6">
-        <v>28.13</v>
+        <v>28.12</v>
       </c>
       <c r="AI6">
         <v>27.8</v>
@@ -1475,7 +1484,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>35.56</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1495,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1317</v>
+        <v>1298</v>
       </c>
       <c r="D7">
-        <v>0.55</v>
+        <v>-1.44</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1498,46 +1507,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-16.91</v>
+        <v>-18.11</v>
       </c>
       <c r="H7">
-        <v>4.62</v>
+        <v>3.11</v>
       </c>
       <c r="I7">
-        <v>-0.38</v>
+        <v>-0.99</v>
       </c>
       <c r="J7">
-        <v>2.89</v>
+        <v>2.39</v>
       </c>
       <c r="K7">
-        <v>-2.03</v>
+        <v>-3.44</v>
       </c>
       <c r="L7">
-        <v>-6.36</v>
+        <v>-8.48</v>
       </c>
       <c r="M7">
-        <v>5.71</v>
+        <v>5.14</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="P7">
-        <v>1313.4</v>
+        <v>1310.8</v>
       </c>
       <c r="Q7">
-        <v>1311.93</v>
+        <v>1313.03</v>
       </c>
       <c r="R7">
-        <v>1306.63</v>
+        <v>1306.01</v>
       </c>
       <c r="S7">
-        <v>1393.86</v>
+        <v>1392.99</v>
       </c>
       <c r="T7">
-        <v>-5.51</v>
+        <v>-6.82</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1552,34 +1561,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>52.57</v>
+        <v>45.75</v>
       </c>
       <c r="Z7">
-        <v>3.49</v>
+        <v>1.95</v>
       </c>
       <c r="AA7">
-        <v>3.73</v>
+        <v>3.37</v>
       </c>
       <c r="AB7">
-        <v>-0.24</v>
+        <v>-1.43</v>
       </c>
       <c r="AC7">
-        <v>40</v>
+        <v>22.22</v>
       </c>
       <c r="AD7">
-        <v>44.12</v>
+        <v>35.87</v>
       </c>
       <c r="AE7">
-        <v>19.31</v>
+        <v>19.28</v>
       </c>
       <c r="AF7">
-        <v>-30.42</v>
+        <v>-43.78</v>
       </c>
       <c r="AG7">
-        <v>1343.55</v>
+        <v>1340.64</v>
       </c>
       <c r="AH7">
-        <v>1280.3</v>
+        <v>1285.42</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1588,7 +1597,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>15.86</v>
+        <v>18.08</v>
       </c>
     </row>
   </sheetData>
@@ -1729,7 +1738,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1769,7 +1778,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1787,852 +1796,872 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>3.61</v>
-      </c>
-      <c r="D7" s="6">
-        <v>2.74</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.87</v>
+      <c r="C7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-1.58</v>
+        <v>2.74</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.94</v>
+        <v>1.65</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.36</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>3.11</v>
+        <v>-2.94</v>
       </c>
       <c r="D9" s="6">
-        <v>2.96</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.15</v>
+        <v>-2.22</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.72</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-8.779999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="D10" s="6">
-        <v>-8.800000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.02</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>6.01</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="D11" s="6">
-        <v>5.23</v>
+        <v>-11.07</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.78</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>2.49</v>
+        <v>5.23</v>
       </c>
       <c r="D12" s="6">
-        <v>2.89</v>
+        <v>5.51</v>
       </c>
       <c r="E12" s="8">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>2.29</v>
+        <v>2.89</v>
       </c>
       <c r="D13" s="6">
-        <v>2.59</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.3</v>
+        <v>2.39</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-0.09</v>
+        <v>2.59</v>
       </c>
       <c r="D14" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.57</v>
+        <v>1.1</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.1</v>
+        <v>0.48</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.08</v>
+        <v>1.34</v>
       </c>
       <c r="E15" s="8">
-        <v>2.02</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.36</v>
+        <v>-1.08</v>
       </c>
       <c r="D16" s="6">
         <v>-0.88</v>
       </c>
       <c r="E16" s="8">
-        <v>1.48</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>4.8</v>
+        <v>-0.88</v>
       </c>
       <c r="D17" s="6">
-        <v>6.49</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.69</v>
+        <v>-1.94</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.47</v>
+        <v>6.49</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.38</v>
+        <v>8.48</v>
       </c>
       <c r="E18" s="8">
-        <v>0.09</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-24.09</v>
+        <v>-0.38</v>
       </c>
       <c r="D19" s="6">
-        <v>-24.63</v>
+        <v>-0.99</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.54</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-28.3</v>
+        <v>-24.63</v>
       </c>
       <c r="D20" s="6">
-        <v>-29.41</v>
+        <v>-24.88</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.11</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-26.95</v>
+        <v>-29.41</v>
       </c>
       <c r="D21" s="6">
-        <v>-25.97</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.98</v>
+        <v>-29.44</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-20.5</v>
+        <v>-25.97</v>
       </c>
       <c r="D22" s="6">
-        <v>-22.1</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.6</v>
+        <v>-25.58</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.39</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-47.6</v>
+        <v>-22.1</v>
       </c>
       <c r="D23" s="6">
-        <v>-47.32</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.28</v>
+        <v>-23.02</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-7.34</v>
+        <v>-47.32</v>
       </c>
       <c r="D24" s="6">
-        <v>-6.36</v>
+        <v>-45.87</v>
       </c>
       <c r="E24" s="8">
-        <v>0.98</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>1.55</v>
+        <v>-6.36</v>
       </c>
       <c r="D25" s="6">
-        <v>0.97</v>
+        <v>-8.48</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.58</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>0.09</v>
+        <v>0.97</v>
       </c>
       <c r="D26" s="6">
-        <v>-3.83</v>
+        <v>-0.61</v>
       </c>
       <c r="E26" s="7">
-        <v>-3.92</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>0.55</v>
+        <v>-3.83</v>
       </c>
       <c r="D27" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.44</v>
+        <v>-3.73</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>24.9</v>
+        <v>0.11</v>
       </c>
       <c r="D28" s="6">
-        <v>22.63</v>
+        <v>-0.78</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.27</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-3.56</v>
+        <v>22.63</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.65</v>
+        <v>21.17</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-2.98</v>
+        <v>-2.91</v>
       </c>
       <c r="D30" s="6">
-        <v>-2.03</v>
+        <v>-2.62</v>
       </c>
       <c r="E30" s="8">
-        <v>0.95</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-24.58</v>
+        <v>-2.03</v>
       </c>
       <c r="D31" s="6">
-        <v>-23.69</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.89</v>
+        <v>-3.44</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-29.77</v>
+        <v>-23.69</v>
       </c>
       <c r="D32" s="6">
-        <v>-29.97</v>
+        <v>-24.37</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.2</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-26.32</v>
+        <v>-29.97</v>
       </c>
       <c r="D33" s="6">
-        <v>-24.92</v>
+        <v>-29.91</v>
       </c>
       <c r="E33" s="8">
-        <v>1.4</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-22.77</v>
+        <v>-24.92</v>
       </c>
       <c r="D34" s="6">
-        <v>-23.87</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.1</v>
+        <v>-24.83</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-47.35</v>
+        <v>-23.87</v>
       </c>
       <c r="D35" s="6">
-        <v>-46.03</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1.32</v>
+        <v>-24.77</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-17.36</v>
+        <v>-46.03</v>
       </c>
       <c r="D36" s="6">
-        <v>-16.91</v>
+        <v>-45.84</v>
       </c>
       <c r="E36" s="8">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>28.14</v>
+        <v>-16.91</v>
       </c>
       <c r="D37" s="6">
-        <v>28.12</v>
+        <v>-18.11</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.02</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>10.59</v>
+        <v>28.12</v>
       </c>
       <c r="D38" s="6">
-        <v>10.56</v>
+        <v>27.68</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.03</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>242</v>
+        <v>10.56</v>
       </c>
       <c r="D39" s="6">
-        <v>243.15</v>
+        <v>10.57</v>
       </c>
       <c r="E39" s="8">
-        <v>1.15</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>664.95</v>
+        <v>243.15</v>
       </c>
       <c r="D40" s="6">
-        <v>655.45</v>
+        <v>241</v>
       </c>
       <c r="E40" s="7">
-        <v>-9.5</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>30.34</v>
+        <v>655.45</v>
       </c>
       <c r="D41" s="6">
-        <v>30.36</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.02</v>
+        <v>647.65</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-7.8</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1309.8</v>
+        <v>30.36</v>
       </c>
       <c r="D42" s="6">
-        <v>1317</v>
+        <v>30.45</v>
       </c>
       <c r="E42" s="8">
-        <v>7.2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>55.72</v>
+        <v>1317</v>
       </c>
       <c r="D43" s="6">
-        <v>55.4</v>
+        <v>1298</v>
       </c>
       <c r="E43" s="7">
-        <v>-0.32</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>43.21</v>
+        <v>55.4</v>
       </c>
       <c r="D44" s="6">
-        <v>42.22</v>
+        <v>48.76</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.99</v>
+        <v>-6.64</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>43.02</v>
+        <v>42.22</v>
       </c>
       <c r="D45" s="6">
-        <v>44.67</v>
+        <v>42.69</v>
       </c>
       <c r="E45" s="8">
-        <v>1.65</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>45.57</v>
+        <v>44.67</v>
       </c>
       <c r="D46" s="6">
-        <v>42.73</v>
+        <v>42.21</v>
       </c>
       <c r="E46" s="7">
-        <v>-2.84</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>54.77</v>
+        <v>42.73</v>
       </c>
       <c r="D47" s="6">
-        <v>54.91</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.14</v>
+        <v>40.5</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>49.94</v>
+        <v>54.91</v>
       </c>
       <c r="D48" s="6">
-        <v>52.57</v>
+        <v>55.54</v>
       </c>
       <c r="E48" s="8">
-        <v>2.63</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>58.04</v>
+        <v>52.57</v>
       </c>
       <c r="D49" s="6">
-        <v>-18.13</v>
+        <v>45.75</v>
       </c>
       <c r="E49" s="7">
-        <v>-76.17</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>102.82</v>
+        <v>-18.13</v>
       </c>
       <c r="D50" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-103.76</v>
+        <v>-7.74</v>
+      </c>
+      <c r="E50" s="8">
+        <v>10.39</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-63.61</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D51" s="6">
-        <v>-45.88</v>
+        <v>4.44</v>
       </c>
       <c r="E51" s="8">
-        <v>17.73</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>-74.16</v>
+        <v>-45.88</v>
       </c>
       <c r="D52" s="6">
-        <v>-73.94</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.22</v>
+        <v>-62.56</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-16.68</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>68.27</v>
+        <v>-73.94</v>
       </c>
       <c r="D53" s="6">
-        <v>22.25</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-46.02</v>
+        <v>-59.49</v>
+      </c>
+      <c r="E53" s="8">
+        <v>14.45</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-29.66</v>
+        <v>22.25</v>
       </c>
       <c r="D54" s="6">
+        <v>-63.17</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-85.42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
         <v>-30.42</v>
       </c>
-      <c r="E54" s="7">
-        <v>-0.76</v>
+      <c r="D55" s="6">
+        <v>-43.78</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-13.36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2656,28 +2685,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2691,16 +2720,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>48.8</v>
+        <v>45.9</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="G2" s="11">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="H2" s="11">
         <v>58.2</v>
@@ -2828,22 +2857,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.0571</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0072</v>
+        <v>-0.0101</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0709</v>
+        <v>-0.0738</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.08560000000000001</v>
+        <v>-0.08929999999999999</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0984</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.146</v>
+        <v>-0.1455</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,25 +187,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>55.4 → 48.8</t>
+    <t>48.8 → 54.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>54.6</t>
+  </si>
+  <si>
+    <t>55.5 → 45.5</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>55.4</t>
-  </si>
-  <si>
-    <t>48.8</t>
-  </si>
-  <si>
-    <t>52.6 → 45.8</t>
-  </si>
-  <si>
-    <t>52.6</t>
-  </si>
-  <si>
-    <t>45.8</t>
+    <t>55.5</t>
+  </si>
+  <si>
+    <t>45.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +294,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +334,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,6 +418,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -790,8 +794,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -930,10 +934,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.68</v>
+        <v>28.12</v>
       </c>
       <c r="D2">
-        <v>-1.56</v>
+        <v>1.59</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -942,46 +946,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-24.37</v>
+        <v>-23.17</v>
       </c>
       <c r="H2">
-        <v>20.45</v>
+        <v>22.37</v>
       </c>
       <c r="I2">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="J2">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="K2">
-        <v>-0.61</v>
+        <v>1.74</v>
       </c>
       <c r="L2">
-        <v>-24.88</v>
+        <v>-22.79</v>
       </c>
       <c r="M2">
-        <v>-9.859999999999999</v>
+        <v>-9.76</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>27.97</v>
+        <v>28.05</v>
       </c>
       <c r="Q2">
-        <v>27.55</v>
+        <v>27.58</v>
       </c>
       <c r="R2">
-        <v>28.53</v>
+        <v>28.51</v>
       </c>
       <c r="S2">
-        <v>28.7</v>
+        <v>28.68</v>
       </c>
       <c r="T2">
-        <v>-3.55</v>
+        <v>-1.94</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -996,34 +1000,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>48.76</v>
+        <v>54.62</v>
       </c>
       <c r="Z2">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AA2">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AB2">
         <v>0.12</v>
       </c>
       <c r="AC2">
-        <v>81.83</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="AD2">
-        <v>92.77</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="AE2">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AF2">
-        <v>-7.74</v>
+        <v>55.96</v>
       </c>
       <c r="AG2">
-        <v>28.17</v>
+        <v>28.26</v>
       </c>
       <c r="AH2">
-        <v>26.92</v>
+        <v>26.9</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1032,7 +1036,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>37.88</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1047,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.57</v>
+        <v>10.55</v>
       </c>
       <c r="D3">
-        <v>0.09</v>
+        <v>-0.19</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1055,46 +1059,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-29.91</v>
+        <v>-30.04</v>
       </c>
       <c r="H3">
-        <v>19.17</v>
+        <v>18.94</v>
       </c>
       <c r="I3">
-        <v>1.34</v>
+        <v>0.09</v>
       </c>
       <c r="J3">
-        <v>-2.22</v>
+        <v>-2.31</v>
       </c>
       <c r="K3">
-        <v>-3.73</v>
+        <v>-2.31</v>
       </c>
       <c r="L3">
-        <v>-29.44</v>
+        <v>-28.47</v>
       </c>
       <c r="M3">
-        <v>-14.55</v>
+        <v>-14.44</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P3">
         <v>10.59</v>
       </c>
       <c r="Q3">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
       <c r="R3">
-        <v>11.01</v>
+        <v>11</v>
       </c>
       <c r="S3">
-        <v>11.25</v>
+        <v>11.24</v>
       </c>
       <c r="T3">
-        <v>-6.06</v>
+        <v>-6.12</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1109,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.69</v>
+        <v>41.96</v>
       </c>
       <c r="Z3">
         <v>-0.11</v>
@@ -1118,25 +1122,25 @@
         <v>-0.11</v>
       </c>
       <c r="AB3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>57.52</v>
+        <v>57.91</v>
       </c>
       <c r="AD3">
-        <v>60.71</v>
+        <v>60.54</v>
       </c>
       <c r="AE3">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AF3">
-        <v>4.44</v>
+        <v>-30.13</v>
       </c>
       <c r="AG3">
         <v>11.03</v>
       </c>
       <c r="AH3">
-        <v>10.38</v>
+        <v>10.37</v>
       </c>
       <c r="AI3">
         <v>11.19</v>
@@ -1145,7 +1149,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>32.84</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,58 +1160,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>241</v>
+        <v>238.1</v>
       </c>
       <c r="D4">
-        <v>-0.88</v>
+        <v>-1.2</v>
       </c>
       <c r="E4">
-        <v>320.6</v>
+        <v>319.7</v>
       </c>
       <c r="F4">
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-24.83</v>
+        <v>-25.52</v>
       </c>
       <c r="H4">
-        <v>7.54</v>
+        <v>6.25</v>
       </c>
       <c r="I4">
-        <v>-0.88</v>
+        <v>-2.66</v>
       </c>
       <c r="J4">
-        <v>1.65</v>
+        <v>-4.56</v>
       </c>
       <c r="K4">
-        <v>-0.78</v>
+        <v>-0.36</v>
       </c>
       <c r="L4">
-        <v>-25.58</v>
+        <v>-25.73</v>
       </c>
       <c r="M4">
-        <v>-1.01</v>
+        <v>-1.41</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>242.95</v>
+        <v>241.65</v>
       </c>
       <c r="Q4">
-        <v>251.71</v>
+        <v>251.27</v>
       </c>
       <c r="R4">
-        <v>244.06</v>
+        <v>243.96</v>
       </c>
       <c r="S4">
-        <v>258.25</v>
+        <v>257.93</v>
       </c>
       <c r="T4">
-        <v>-6.68</v>
+        <v>-7.69</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1222,43 +1226,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>42.21</v>
+        <v>39.09</v>
       </c>
       <c r="Z4">
-        <v>-0.7</v>
+        <v>-1.28</v>
       </c>
       <c r="AA4">
-        <v>1.17</v>
+        <v>0.68</v>
       </c>
       <c r="AB4">
-        <v>-1.87</v>
+        <v>-1.96</v>
       </c>
       <c r="AC4">
         <v>2.23</v>
       </c>
       <c r="AD4">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="AE4">
-        <v>5.12</v>
+        <v>5.08</v>
       </c>
       <c r="AF4">
-        <v>-62.56</v>
+        <v>-57.52</v>
       </c>
       <c r="AG4">
-        <v>267.35</v>
+        <v>267.94</v>
       </c>
       <c r="AH4">
-        <v>236.07</v>
+        <v>234.59</v>
       </c>
       <c r="AI4">
-        <v>257.39</v>
+        <v>255.61</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>22.4</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1273,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>647.65</v>
+        <v>640.5</v>
       </c>
       <c r="D5">
-        <v>-1.19</v>
+        <v>-1.1</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1281,46 +1285,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-24.77</v>
+        <v>-25.61</v>
       </c>
       <c r="H5">
-        <v>31.98</v>
+        <v>30.53</v>
       </c>
       <c r="I5">
-        <v>-1.94</v>
+        <v>-5.9</v>
       </c>
       <c r="J5">
-        <v>-11.07</v>
+        <v>-15.02</v>
       </c>
       <c r="K5">
-        <v>21.17</v>
+        <v>22.09</v>
       </c>
       <c r="L5">
-        <v>-23.02</v>
+        <v>-23.26</v>
       </c>
       <c r="M5">
-        <v>-7.38</v>
+        <v>-7.61</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P5">
-        <v>664.55</v>
+        <v>656.52</v>
       </c>
       <c r="Q5">
-        <v>683.75</v>
+        <v>678.6900000000001</v>
       </c>
       <c r="R5">
-        <v>653.13</v>
+        <v>654.92</v>
       </c>
       <c r="S5">
-        <v>627.78</v>
+        <v>627.25</v>
       </c>
       <c r="T5">
-        <v>3.17</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1335,43 +1339,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>40.5</v>
+        <v>38.52</v>
       </c>
       <c r="Z5">
-        <v>-3.82</v>
+        <v>-5.95</v>
       </c>
       <c r="AA5">
-        <v>3.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB5">
-        <v>-7.26</v>
+        <v>-7.51</v>
       </c>
       <c r="AC5">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>21.19</v>
+        <v>8.93</v>
       </c>
       <c r="AE5">
-        <v>22.77</v>
+        <v>22.05</v>
       </c>
       <c r="AF5">
-        <v>-59.49</v>
+        <v>-67.76000000000001</v>
       </c>
       <c r="AG5">
-        <v>728.1799999999999</v>
+        <v>718.12</v>
       </c>
       <c r="AH5">
-        <v>639.3099999999999</v>
+        <v>639.26</v>
       </c>
       <c r="AI5">
-        <v>720.3099999999999</v>
+        <v>709.8</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>15.84</v>
+        <v>18.81</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1386,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>30.45</v>
+        <v>29.14</v>
       </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>-4.3</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1394,46 +1398,46 @@
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-45.84</v>
+        <v>-48.17</v>
       </c>
       <c r="H6">
-        <v>10.65</v>
+        <v>5.89</v>
       </c>
       <c r="I6">
-        <v>8.48</v>
+        <v>-4.74</v>
       </c>
       <c r="J6">
-        <v>5.51</v>
+        <v>-0.34</v>
       </c>
       <c r="K6">
-        <v>-2.62</v>
+        <v>-6.69</v>
       </c>
       <c r="L6">
-        <v>-45.87</v>
+        <v>-47.98</v>
       </c>
       <c r="M6">
-        <v>-8.93</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>30.32</v>
+        <v>30.03</v>
       </c>
       <c r="Q6">
-        <v>29.48</v>
+        <v>29.47</v>
       </c>
       <c r="R6">
-        <v>30.64</v>
+        <v>30.54</v>
       </c>
       <c r="S6">
-        <v>35.41</v>
+        <v>35.31</v>
       </c>
       <c r="T6">
-        <v>-14</v>
+        <v>-17.48</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1448,34 +1452,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>55.54</v>
+        <v>45.48</v>
       </c>
       <c r="Z6">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="AA6">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
       <c r="AB6">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="AC6">
-        <v>90.56999999999999</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="AD6">
-        <v>87.95999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>-63.17</v>
+        <v>16.25</v>
       </c>
       <c r="AG6">
         <v>30.84</v>
       </c>
       <c r="AH6">
-        <v>28.12</v>
+        <v>28.1</v>
       </c>
       <c r="AI6">
         <v>27.8</v>
@@ -1484,7 +1488,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>37.81</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1499,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1298</v>
+        <v>1282.2</v>
       </c>
       <c r="D7">
-        <v>-1.44</v>
+        <v>-1.22</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1507,25 +1511,25 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-18.11</v>
+        <v>-19.1</v>
       </c>
       <c r="H7">
-        <v>3.11</v>
+        <v>1.86</v>
       </c>
       <c r="I7">
-        <v>-0.99</v>
+        <v>-2.36</v>
       </c>
       <c r="J7">
-        <v>2.39</v>
+        <v>0.49</v>
       </c>
       <c r="K7">
-        <v>-3.44</v>
+        <v>-2.5</v>
       </c>
       <c r="L7">
-        <v>-8.48</v>
+        <v>-8.59</v>
       </c>
       <c r="M7">
-        <v>5.14</v>
+        <v>4.91</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1534,19 +1538,19 @@
         <v>43</v>
       </c>
       <c r="P7">
-        <v>1310.8</v>
+        <v>1304.6</v>
       </c>
       <c r="Q7">
-        <v>1313.03</v>
+        <v>1312.5</v>
       </c>
       <c r="R7">
-        <v>1306.01</v>
+        <v>1305</v>
       </c>
       <c r="S7">
-        <v>1392.99</v>
+        <v>1391.99</v>
       </c>
       <c r="T7">
-        <v>-6.82</v>
+        <v>-7.89</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1561,34 +1565,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>45.75</v>
+        <v>40.99</v>
       </c>
       <c r="Z7">
-        <v>1.95</v>
+        <v>-0.54</v>
       </c>
       <c r="AA7">
-        <v>3.37</v>
+        <v>2.59</v>
       </c>
       <c r="AB7">
-        <v>-1.43</v>
+        <v>-3.13</v>
       </c>
       <c r="AC7">
-        <v>22.22</v>
+        <v>10.1</v>
       </c>
       <c r="AD7">
-        <v>35.87</v>
+        <v>24.11</v>
       </c>
       <c r="AE7">
-        <v>19.28</v>
+        <v>19.78</v>
       </c>
       <c r="AF7">
-        <v>-43.78</v>
+        <v>12.24</v>
       </c>
       <c r="AG7">
-        <v>1340.64</v>
+        <v>1342.1</v>
       </c>
       <c r="AH7">
-        <v>1285.42</v>
+        <v>1282.89</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1597,7 +1601,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>18.08</v>
+        <v>22.91</v>
       </c>
     </row>
   </sheetData>
@@ -1797,28 +1801,28 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>61</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1830,832 +1834,832 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>2.74</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="7">
         <v>1.65</v>
       </c>
-      <c r="E8" s="7">
-        <v>-1.09</v>
+      <c r="D8" s="7">
+        <v>1.96</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.31</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-2.94</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="7">
         <v>-2.22</v>
       </c>
-      <c r="E9" s="8">
-        <v>0.72</v>
+      <c r="D9" s="7">
+        <v>-2.31</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>2.96</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="7">
         <v>1.65</v>
       </c>
-      <c r="E10" s="7">
+      <c r="D10" s="7">
+        <v>-4.56</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-6.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-11.07</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-15.02</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>5.51</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-0.34</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-5.85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2.39</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1.1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.33</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1.34</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-0.88</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-2.66</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1.94</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-5.9</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-3.96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>8.48</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-4.74</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-13.22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.99</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-2.36</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-24.88</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-22.79</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-29.44</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-28.47</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-25.58</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-25.73</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-23.02</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-23.26</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-45.87</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-47.98</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-8.48</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-8.59</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-0.61</v>
+      </c>
+      <c r="D26" s="7">
+        <v>1.74</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-3.73</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-2.31</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-0.78</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-0.36</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>21.17</v>
+      </c>
+      <c r="D29" s="7">
+        <v>22.09</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-2.62</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-6.69</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-4.07</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-3.44</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-2.5</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-24.37</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-23.17</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-29.91</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-30.04</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-24.83</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-25.52</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-24.77</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-25.61</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-45.84</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-48.17</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-18.11</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-19.1</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7">
+        <v>27.68</v>
+      </c>
+      <c r="D38" s="7">
+        <v>28.12</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7">
+        <v>10.57</v>
+      </c>
+      <c r="D39" s="7">
+        <v>10.55</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="7">
+        <v>241</v>
+      </c>
+      <c r="D40" s="7">
+        <v>238.1</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="7">
+        <v>647.65</v>
+      </c>
+      <c r="D41" s="7">
+        <v>640.5</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-7.15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7">
+        <v>30.45</v>
+      </c>
+      <c r="D42" s="7">
+        <v>29.14</v>
+      </c>
+      <c r="E42" s="9">
         <v>-1.31</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1298</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1282.2</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-15.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="7">
+        <v>48.76</v>
+      </c>
+      <c r="D44" s="7">
+        <v>54.62</v>
+      </c>
+      <c r="E44" s="8">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="7">
+        <v>42.69</v>
+      </c>
+      <c r="D45" s="7">
+        <v>41.96</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="7">
+        <v>42.21</v>
+      </c>
+      <c r="D46" s="7">
+        <v>39.09</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-11.07</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="7">
+        <v>40.5</v>
+      </c>
+      <c r="D47" s="7">
+        <v>38.52</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5.23</v>
-      </c>
-      <c r="D12" s="6">
-        <v>5.51</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="7">
+        <v>55.54</v>
+      </c>
+      <c r="D48" s="7">
+        <v>45.48</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-10.06</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2.89</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2.39</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="7">
+        <v>45.75</v>
+      </c>
+      <c r="D49" s="7">
+        <v>40.99</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-4.76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2.59</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.1</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-7.74</v>
+      </c>
+      <c r="D50" s="7">
+        <v>55.96</v>
+      </c>
+      <c r="E50" s="8">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1.34</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B51" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="7">
+        <v>4.44</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-30.13</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-34.57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.08</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.88</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B52" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-62.56</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-57.52</v>
+      </c>
+      <c r="E52" s="8">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-0.88</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.94</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-59.49</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-67.76000000000001</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-8.27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>6.49</v>
-      </c>
-      <c r="D18" s="6">
-        <v>8.48</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-63.17</v>
+      </c>
+      <c r="D54" s="7">
+        <v>16.25</v>
+      </c>
+      <c r="E54" s="8">
+        <v>79.42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.38</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-0.99</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-24.63</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-24.88</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-29.41</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-29.44</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-25.97</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-25.58</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-22.1</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-23.02</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-47.32</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-45.87</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-6.36</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-8.48</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-3.83</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-3.73</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>22.63</v>
-      </c>
-      <c r="D29" s="6">
-        <v>21.17</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-2.62</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-3.44</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-23.69</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-24.37</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-29.97</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-29.91</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-24.92</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-24.83</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-23.87</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-24.77</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-46.03</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-45.84</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-16.91</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-18.11</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>28.12</v>
-      </c>
-      <c r="D38" s="6">
-        <v>27.68</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>10.56</v>
-      </c>
-      <c r="D39" s="6">
-        <v>10.57</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>243.15</v>
-      </c>
-      <c r="D40" s="6">
-        <v>241</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>655.45</v>
-      </c>
-      <c r="D41" s="6">
-        <v>647.65</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-7.8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>30.36</v>
-      </c>
-      <c r="D42" s="6">
-        <v>30.45</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>1317</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1298</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>55.4</v>
-      </c>
-      <c r="D44" s="6">
-        <v>48.76</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-6.64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>42.22</v>
-      </c>
-      <c r="D45" s="6">
-        <v>42.69</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>44.67</v>
-      </c>
-      <c r="D46" s="6">
-        <v>42.21</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>42.73</v>
-      </c>
-      <c r="D47" s="6">
-        <v>40.5</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>54.91</v>
-      </c>
-      <c r="D48" s="6">
-        <v>55.54</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>52.57</v>
-      </c>
-      <c r="D49" s="6">
-        <v>45.75</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-6.82</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="6">
-        <v>-18.13</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-7.74</v>
-      </c>
-      <c r="E50" s="8">
-        <v>10.39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="D51" s="6">
-        <v>4.44</v>
-      </c>
-      <c r="E51" s="8">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-45.88</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-62.56</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-16.68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-73.94</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-59.49</v>
-      </c>
-      <c r="E53" s="8">
-        <v>14.45</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>22.25</v>
-      </c>
-      <c r="D54" s="6">
-        <v>-63.17</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-85.42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>-30.42</v>
-      </c>
-      <c r="D55" s="6">
+      <c r="C55" s="7">
         <v>-43.78</v>
       </c>
-      <c r="E55" s="7">
-        <v>-13.36</v>
+      <c r="D55" s="7">
+        <v>12.24</v>
+      </c>
+      <c r="E55" s="8">
+        <v>56.02</v>
       </c>
     </row>
   </sheetData>
@@ -2681,60 +2685,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="I1" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>45.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>43.4</v>
+      </c>
+      <c r="E2" s="12">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-0.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-3.3</v>
+      </c>
+      <c r="G2" s="12">
+        <v>2</v>
+      </c>
+      <c r="H2" s="12">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>20</v>
       </c>
     </row>
@@ -2836,43 +2840,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.05139999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0101</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0738</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.08929999999999999</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.09859999999999999</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1455</v>
+      <c r="A2" s="15">
+        <v>0.0491</v>
+      </c>
+      <c r="B2" s="15">
+        <v>-0.0141</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0761</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.09759999999999999</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.0987</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.1444</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,28 +187,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.8 → 54.6</t>
+    <t>38.5 → 58.2</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>48.8</t>
-  </si>
-  <si>
-    <t>54.6</t>
-  </si>
-  <si>
-    <t>55.5 → 45.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>55.5</t>
-  </si>
-  <si>
-    <t>45.5</t>
+    <t>38.5</t>
+  </si>
+  <si>
+    <t>58.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -410,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -418,7 +406,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -794,8 +781,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -934,10 +921,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>28.12</v>
+        <v>28.31</v>
       </c>
       <c r="D2">
-        <v>1.59</v>
+        <v>0.68</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -946,46 +933,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-23.17</v>
+        <v>-22.65</v>
       </c>
       <c r="H2">
-        <v>22.37</v>
+        <v>23.19</v>
       </c>
       <c r="I2">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="J2">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>1.74</v>
+        <v>6.35</v>
       </c>
       <c r="L2">
-        <v>-22.79</v>
+        <v>-22.2</v>
       </c>
       <c r="M2">
-        <v>-9.76</v>
+        <v>-9.69</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>28.05</v>
+        <v>28.07</v>
       </c>
       <c r="Q2">
-        <v>27.58</v>
+        <v>27.63</v>
       </c>
       <c r="R2">
-        <v>28.51</v>
+        <v>28.45</v>
       </c>
       <c r="S2">
-        <v>28.68</v>
+        <v>28.66</v>
       </c>
       <c r="T2">
-        <v>-1.94</v>
+        <v>-1.22</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -1000,34 +987,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>54.62</v>
+        <v>56.91</v>
       </c>
       <c r="Z2">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="AA2">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="AB2">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="AC2">
-        <v>79.51000000000001</v>
+        <v>81.14</v>
       </c>
       <c r="AD2">
-        <v>86.26000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="AE2">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AF2">
-        <v>55.96</v>
+        <v>-37.32</v>
       </c>
       <c r="AG2">
-        <v>28.26</v>
+        <v>28.37</v>
       </c>
       <c r="AH2">
-        <v>26.9</v>
+        <v>26.88</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1036,7 +1023,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>37.84</v>
+        <v>37.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1047,10 +1034,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.55</v>
+        <v>10.57</v>
       </c>
       <c r="D3">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1059,46 +1046,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-30.04</v>
+        <v>-29.91</v>
       </c>
       <c r="H3">
-        <v>18.94</v>
+        <v>19.17</v>
       </c>
       <c r="I3">
-        <v>0.09</v>
+        <v>-1.03</v>
       </c>
       <c r="J3">
-        <v>-2.31</v>
+        <v>-1.67</v>
       </c>
       <c r="K3">
-        <v>-2.31</v>
+        <v>-0</v>
       </c>
       <c r="L3">
-        <v>-28.47</v>
+        <v>-28.24</v>
       </c>
       <c r="M3">
-        <v>-14.44</v>
+        <v>-14.75</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P3">
-        <v>10.59</v>
+        <v>10.57</v>
       </c>
       <c r="Q3">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
       <c r="R3">
-        <v>11</v>
+        <v>10.98</v>
       </c>
       <c r="S3">
-        <v>11.24</v>
+        <v>11.23</v>
       </c>
       <c r="T3">
-        <v>-6.12</v>
+        <v>-5.84</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1113,10 +1100,10 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.96</v>
+        <v>43.01</v>
       </c>
       <c r="Z3">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AA3">
         <v>-0.11</v>
@@ -1125,22 +1112,22 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>57.91</v>
+        <v>63.83</v>
       </c>
       <c r="AD3">
-        <v>60.54</v>
+        <v>59.75</v>
       </c>
       <c r="AE3">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AF3">
-        <v>-30.13</v>
+        <v>-14.96</v>
       </c>
       <c r="AG3">
-        <v>11.03</v>
+        <v>11.02</v>
       </c>
       <c r="AH3">
-        <v>10.37</v>
+        <v>10.35</v>
       </c>
       <c r="AI3">
         <v>11.19</v>
@@ -1149,7 +1136,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>30.51</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1160,58 +1147,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>238.1</v>
+        <v>238.4</v>
       </c>
       <c r="D4">
-        <v>-1.2</v>
+        <v>0.13</v>
       </c>
       <c r="E4">
-        <v>319.7</v>
+        <v>317.35</v>
       </c>
       <c r="F4">
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-25.52</v>
+        <v>-24.88</v>
       </c>
       <c r="H4">
-        <v>6.25</v>
+        <v>6.38</v>
       </c>
       <c r="I4">
-        <v>-2.66</v>
+        <v>-2.3</v>
       </c>
       <c r="J4">
-        <v>-4.56</v>
+        <v>-3.46</v>
       </c>
       <c r="K4">
-        <v>-0.36</v>
+        <v>1.47</v>
       </c>
       <c r="L4">
-        <v>-25.73</v>
+        <v>-25.43</v>
       </c>
       <c r="M4">
-        <v>-1.41</v>
+        <v>-1.37</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>241.65</v>
+        <v>240.53</v>
       </c>
       <c r="Q4">
-        <v>251.27</v>
+        <v>250.36</v>
       </c>
       <c r="R4">
-        <v>243.96</v>
+        <v>243.84</v>
       </c>
       <c r="S4">
-        <v>257.93</v>
+        <v>257.6</v>
       </c>
       <c r="T4">
-        <v>-7.69</v>
+        <v>-7.45</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1226,43 +1213,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>39.09</v>
+        <v>39.59</v>
       </c>
       <c r="Z4">
-        <v>-1.28</v>
+        <v>-1.69</v>
       </c>
       <c r="AA4">
-        <v>0.68</v>
+        <v>0.21</v>
       </c>
       <c r="AB4">
-        <v>-1.96</v>
+        <v>-1.9</v>
       </c>
       <c r="AC4">
-        <v>2.23</v>
+        <v>0.87</v>
       </c>
       <c r="AD4">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="AE4">
-        <v>5.08</v>
+        <v>4.89</v>
       </c>
       <c r="AF4">
-        <v>-57.52</v>
+        <v>-55.39</v>
       </c>
       <c r="AG4">
-        <v>267.94</v>
+        <v>267.79</v>
       </c>
       <c r="AH4">
-        <v>234.59</v>
+        <v>232.94</v>
       </c>
       <c r="AI4">
-        <v>255.61</v>
+        <v>253.46</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>23.35</v>
+        <v>24.47</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1273,10 +1260,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>640.5</v>
+        <v>704.55</v>
       </c>
       <c r="D5">
-        <v>-1.1</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1285,46 +1272,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-25.61</v>
+        <v>-18.17</v>
       </c>
       <c r="H5">
-        <v>30.53</v>
+        <v>43.58</v>
       </c>
       <c r="I5">
-        <v>-5.9</v>
+        <v>4.52</v>
       </c>
       <c r="J5">
-        <v>-15.02</v>
+        <v>-5</v>
       </c>
       <c r="K5">
-        <v>22.09</v>
+        <v>35.02</v>
       </c>
       <c r="L5">
-        <v>-23.26</v>
+        <v>-15.19</v>
       </c>
       <c r="M5">
-        <v>-7.61</v>
+        <v>-5.86</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>656.52</v>
+        <v>662.62</v>
       </c>
       <c r="Q5">
-        <v>678.6900000000001</v>
+        <v>678.08</v>
       </c>
       <c r="R5">
-        <v>654.92</v>
+        <v>658.02</v>
       </c>
       <c r="S5">
-        <v>627.25</v>
+        <v>627.11</v>
       </c>
       <c r="T5">
-        <v>2.11</v>
+        <v>12.35</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1339,34 +1326,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>38.52</v>
+        <v>58.24</v>
       </c>
       <c r="Z5">
-        <v>-5.95</v>
+        <v>-2.44</v>
       </c>
       <c r="AA5">
-        <v>1.56</v>
+        <v>0.76</v>
       </c>
       <c r="AB5">
-        <v>-7.51</v>
+        <v>-3.2</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="AD5">
-        <v>8.93</v>
+        <v>13.35</v>
       </c>
       <c r="AE5">
-        <v>22.05</v>
+        <v>25.05</v>
       </c>
       <c r="AF5">
-        <v>-67.76000000000001</v>
+        <v>277.2</v>
       </c>
       <c r="AG5">
-        <v>718.12</v>
+        <v>715.36</v>
       </c>
       <c r="AH5">
-        <v>639.26</v>
+        <v>640.8</v>
       </c>
       <c r="AI5">
         <v>709.8</v>
@@ -1375,7 +1362,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>18.81</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1386,10 +1373,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>29.14</v>
+        <v>28.8</v>
       </c>
       <c r="D6">
-        <v>-4.3</v>
+        <v>-1.17</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1398,46 +1385,46 @@
         <v>27.52</v>
       </c>
       <c r="G6">
-        <v>-48.17</v>
+        <v>-48.77</v>
       </c>
       <c r="H6">
-        <v>5.89</v>
+        <v>4.65</v>
       </c>
       <c r="I6">
-        <v>-4.74</v>
+        <v>-3.55</v>
       </c>
       <c r="J6">
-        <v>-0.34</v>
+        <v>-1.67</v>
       </c>
       <c r="K6">
-        <v>-6.69</v>
+        <v>-4.51</v>
       </c>
       <c r="L6">
-        <v>-47.98</v>
+        <v>-47.85</v>
       </c>
       <c r="M6">
-        <v>-9.869999999999999</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>30.03</v>
+        <v>29.82</v>
       </c>
       <c r="Q6">
-        <v>29.47</v>
+        <v>29.44</v>
       </c>
       <c r="R6">
-        <v>30.54</v>
+        <v>30.42</v>
       </c>
       <c r="S6">
-        <v>35.31</v>
+        <v>35.23</v>
       </c>
       <c r="T6">
-        <v>-17.48</v>
+        <v>-18.24</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1452,34 +1439,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>45.48</v>
+        <v>43.28</v>
       </c>
       <c r="Z6">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="AA6">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="AB6">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AC6">
-        <v>77.43000000000001</v>
+        <v>61</v>
       </c>
       <c r="AD6">
-        <v>84.31999999999999</v>
+        <v>76.33</v>
       </c>
       <c r="AE6">
         <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>16.25</v>
+        <v>-10.57</v>
       </c>
       <c r="AG6">
         <v>30.84</v>
       </c>
       <c r="AH6">
-        <v>28.1</v>
+        <v>28.04</v>
       </c>
       <c r="AI6">
         <v>27.8</v>
@@ -1488,7 +1475,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>33.2</v>
+        <v>30.09</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1499,10 +1486,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1282.2</v>
+        <v>1287</v>
       </c>
       <c r="D7">
-        <v>-1.22</v>
+        <v>0.37</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1511,46 +1498,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-19.1</v>
+        <v>-18.8</v>
       </c>
       <c r="H7">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="I7">
-        <v>-2.36</v>
+        <v>-2.2</v>
       </c>
       <c r="J7">
-        <v>0.49</v>
+        <v>-0.46</v>
       </c>
       <c r="K7">
-        <v>-2.5</v>
+        <v>-2.05</v>
       </c>
       <c r="L7">
-        <v>-8.59</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="M7">
-        <v>4.91</v>
+        <v>4.6</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P7">
-        <v>1304.6</v>
+        <v>1298.8</v>
       </c>
       <c r="Q7">
-        <v>1312.5</v>
+        <v>1311.46</v>
       </c>
       <c r="R7">
-        <v>1305</v>
+        <v>1304.18</v>
       </c>
       <c r="S7">
-        <v>1391.99</v>
+        <v>1391</v>
       </c>
       <c r="T7">
-        <v>-7.89</v>
+        <v>-7.48</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1565,34 +1552,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>40.99</v>
+        <v>42.93</v>
       </c>
       <c r="Z7">
-        <v>-0.54</v>
+        <v>-2.1</v>
       </c>
       <c r="AA7">
-        <v>2.59</v>
+        <v>1.65</v>
       </c>
       <c r="AB7">
-        <v>-3.13</v>
+        <v>-3.75</v>
       </c>
       <c r="AC7">
-        <v>10.1</v>
+        <v>4.13</v>
       </c>
       <c r="AD7">
-        <v>24.11</v>
+        <v>12.15</v>
       </c>
       <c r="AE7">
-        <v>19.78</v>
+        <v>19.21</v>
       </c>
       <c r="AF7">
-        <v>12.24</v>
+        <v>-32.52</v>
       </c>
       <c r="AG7">
-        <v>1342.1</v>
+        <v>1343.14</v>
       </c>
       <c r="AH7">
-        <v>1282.89</v>
+        <v>1279.77</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1601,7 +1588,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>22.91</v>
+        <v>27.4</v>
       </c>
     </row>
   </sheetData>
@@ -1742,7 +1729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1782,7 +1769,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1800,872 +1787,852 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.96</v>
+      </c>
+      <c r="D7" s="6">
+        <v>3.25</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-2.31</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-1.67</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-4.56</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-3.46</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-15.02</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-5</v>
+      </c>
+      <c r="E10" s="7">
+        <v>10.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-0.34</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-1.67</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.49</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-0.46</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1.65</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.96</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-2.22</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-1.03</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.66</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.3</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-5.9</v>
+      </c>
+      <c r="D16" s="6">
+        <v>4.52</v>
+      </c>
+      <c r="E16" s="7">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-4.74</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.55</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.36</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-2.2</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-22.79</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-22.2</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-28.47</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-28.24</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-25.73</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-25.43</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-23.26</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-15.19</v>
+      </c>
+      <c r="E22" s="7">
+        <v>8.07</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-47.98</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-47.85</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-8.59</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1.74</v>
+      </c>
+      <c r="D25" s="6">
+        <v>6.35</v>
+      </c>
+      <c r="E25" s="7">
+        <v>4.61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
         <v>-2.31</v>
       </c>
-      <c r="E9" s="9">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="D26" s="6">
+        <v>-0</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1.65</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-4.56</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-6.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-0.36</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1.47</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-11.07</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-15.02</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-3.95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>22.09</v>
+      </c>
+      <c r="D28" s="6">
+        <v>35.02</v>
+      </c>
+      <c r="E28" s="7">
+        <v>12.93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>5.51</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-6.69</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-4.51</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-2.5</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-2.05</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-23.17</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-22.65</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-30.04</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-29.91</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-25.52</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-24.88</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-25.61</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-18.17</v>
+      </c>
+      <c r="E34" s="7">
+        <v>7.44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-48.17</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-48.77</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-19.1</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-18.8</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>28.12</v>
+      </c>
+      <c r="D37" s="6">
+        <v>28.31</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>10.55</v>
+      </c>
+      <c r="D38" s="6">
+        <v>10.57</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>238.1</v>
+      </c>
+      <c r="D39" s="6">
+        <v>238.4</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>640.5</v>
+      </c>
+      <c r="D40" s="6">
+        <v>704.55</v>
+      </c>
+      <c r="E40" s="7">
+        <v>64.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>29.14</v>
+      </c>
+      <c r="D41" s="6">
+        <v>28.8</v>
+      </c>
+      <c r="E41" s="8">
         <v>-0.34</v>
       </c>
-      <c r="E12" s="9">
-        <v>-5.85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>2.39</v>
-      </c>
-      <c r="D13" s="7">
-        <v>0.49</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1282.2</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1287</v>
+      </c>
+      <c r="E42" s="7">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1.1</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.33</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>54.62</v>
+      </c>
+      <c r="D43" s="6">
+        <v>56.91</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1.34</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0.09</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>41.96</v>
+      </c>
+      <c r="D44" s="6">
+        <v>43.01</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-0.88</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-2.66</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>39.09</v>
+      </c>
+      <c r="D45" s="6">
+        <v>39.59</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.94</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-5.9</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-3.96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>38.52</v>
+      </c>
+      <c r="D46" s="6">
+        <v>58.24</v>
+      </c>
+      <c r="E46" s="7">
+        <v>19.72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>8.48</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-4.74</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-13.22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>45.48</v>
+      </c>
+      <c r="D47" s="6">
+        <v>43.28</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.99</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-2.36</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>40.99</v>
+      </c>
+      <c r="D48" s="6">
+        <v>42.93</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-24.88</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-22.79</v>
-      </c>
-      <c r="E20" s="8">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>55.96</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-37.32</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-93.28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-29.44</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-28.47</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-30.13</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-14.96</v>
+      </c>
+      <c r="E50" s="7">
+        <v>15.17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-25.58</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-25.73</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-57.52</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-55.39</v>
+      </c>
+      <c r="E51" s="7">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-23.02</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-23.26</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-67.76000000000001</v>
+      </c>
+      <c r="D52" s="6">
+        <v>277.2</v>
+      </c>
+      <c r="E52" s="7">
+        <v>344.96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-45.87</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-47.98</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>16.25</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-10.57</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-26.82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-8.48</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-8.59</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-0.61</v>
-      </c>
-      <c r="D26" s="7">
-        <v>1.74</v>
-      </c>
-      <c r="E26" s="8">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-3.73</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-2.31</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-0.36</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>21.17</v>
-      </c>
-      <c r="D29" s="7">
-        <v>22.09</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-2.62</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-6.69</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-4.07</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-3.44</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-2.5</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-24.37</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-23.17</v>
-      </c>
-      <c r="E32" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-29.91</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-30.04</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-24.83</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-25.52</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-24.77</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-25.61</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-45.84</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-48.17</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-18.11</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-19.1</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="7">
-        <v>27.68</v>
-      </c>
-      <c r="D38" s="7">
-        <v>28.12</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="7">
-        <v>10.57</v>
-      </c>
-      <c r="D39" s="7">
-        <v>10.55</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="7">
-        <v>241</v>
-      </c>
-      <c r="D40" s="7">
-        <v>238.1</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="7">
-        <v>647.65</v>
-      </c>
-      <c r="D41" s="7">
-        <v>640.5</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-7.15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="7">
-        <v>30.45</v>
-      </c>
-      <c r="D42" s="7">
-        <v>29.14</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1298</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1282.2</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-15.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="7">
-        <v>48.76</v>
-      </c>
-      <c r="D44" s="7">
-        <v>54.62</v>
-      </c>
-      <c r="E44" s="8">
-        <v>5.86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="7">
-        <v>42.69</v>
-      </c>
-      <c r="D45" s="7">
-        <v>41.96</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="7">
-        <v>42.21</v>
-      </c>
-      <c r="D46" s="7">
-        <v>39.09</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-3.12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="7">
-        <v>40.5</v>
-      </c>
-      <c r="D47" s="7">
-        <v>38.52</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="7">
-        <v>55.54</v>
-      </c>
-      <c r="D48" s="7">
-        <v>45.48</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-10.06</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="7">
-        <v>45.75</v>
-      </c>
-      <c r="D49" s="7">
-        <v>40.99</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-4.76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="7">
-        <v>-7.74</v>
-      </c>
-      <c r="D50" s="7">
-        <v>55.96</v>
-      </c>
-      <c r="E50" s="8">
-        <v>63.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="7">
-        <v>4.44</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-30.13</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-34.57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-62.56</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-57.52</v>
-      </c>
-      <c r="E52" s="8">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-59.49</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-67.76000000000001</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-8.27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-63.17</v>
-      </c>
-      <c r="D54" s="7">
-        <v>16.25</v>
+      <c r="C54" s="6">
+        <v>12.24</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-32.52</v>
       </c>
       <c r="E54" s="8">
-        <v>79.42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="7">
-        <v>-43.78</v>
-      </c>
-      <c r="D55" s="7">
-        <v>12.24</v>
-      </c>
-      <c r="E55" s="8">
-        <v>56.02</v>
+        <v>-44.76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2685,60 +2652,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="12">
-        <v>43.4</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>47.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="12">
-        <v>-3.3</v>
-      </c>
-      <c r="G2" s="12">
-        <v>2</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-1.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>6</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2840,43 +2807,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="15">
-        <v>0.0491</v>
-      </c>
-      <c r="B2" s="15">
-        <v>-0.0141</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0761</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.09759999999999999</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.0987</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.1444</v>
+      <c r="A2" s="14">
+        <v>0.046</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0137</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.05860000000000001</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0969</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.09970000000000001</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1475</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>38.5 → 58.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>38.5</t>
-  </si>
-  <si>
-    <t>58.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,15 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -781,8 +753,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -921,10 +892,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>28.31</v>
+        <v>28.27</v>
       </c>
       <c r="D2">
-        <v>0.68</v>
+        <v>-0.14</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -933,46 +904,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-22.65</v>
+        <v>-22.76</v>
       </c>
       <c r="H2">
-        <v>23.19</v>
+        <v>23.02</v>
       </c>
       <c r="I2">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="K2">
-        <v>6.35</v>
+        <v>6.56</v>
       </c>
       <c r="L2">
-        <v>-22.2</v>
+        <v>-20.97</v>
       </c>
       <c r="M2">
-        <v>-9.69</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2">
-        <v>28.07</v>
+        <v>28.1</v>
       </c>
       <c r="Q2">
-        <v>27.63</v>
+        <v>27.65</v>
       </c>
       <c r="R2">
-        <v>28.45</v>
+        <v>28.36</v>
       </c>
       <c r="S2">
-        <v>28.66</v>
+        <v>28.64</v>
       </c>
       <c r="T2">
-        <v>-1.22</v>
+        <v>-1.29</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -987,34 +958,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>56.91</v>
+        <v>56.27</v>
       </c>
       <c r="Z2">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AA2">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="AB2">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AC2">
-        <v>81.14</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="AD2">
-        <v>80.83</v>
+        <v>85.36</v>
       </c>
       <c r="AE2">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AF2">
-        <v>-37.32</v>
+        <v>147.17</v>
       </c>
       <c r="AG2">
-        <v>28.37</v>
+        <v>28.45</v>
       </c>
       <c r="AH2">
-        <v>26.88</v>
+        <v>26.85</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1023,7 +994,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>37.82</v>
+        <v>39.09</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1005,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.57</v>
+        <v>10.64</v>
       </c>
       <c r="D3">
-        <v>0.19</v>
+        <v>0.66</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1046,46 +1017,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-29.91</v>
+        <v>-29.44</v>
       </c>
       <c r="H3">
-        <v>19.17</v>
+        <v>19.95</v>
       </c>
       <c r="I3">
-        <v>-1.03</v>
+        <v>0.47</v>
       </c>
       <c r="J3">
-        <v>-1.67</v>
+        <v>-1.21</v>
       </c>
       <c r="K3">
-        <v>-0</v>
+        <v>-0.37</v>
       </c>
       <c r="L3">
-        <v>-28.24</v>
+        <v>-27.62</v>
       </c>
       <c r="M3">
-        <v>-14.75</v>
+        <v>-14.4</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P3">
-        <v>10.57</v>
+        <v>10.58</v>
       </c>
       <c r="Q3">
-        <v>10.69</v>
+        <v>10.67</v>
       </c>
       <c r="R3">
-        <v>10.98</v>
+        <v>10.95</v>
       </c>
       <c r="S3">
-        <v>11.23</v>
+        <v>11.21</v>
       </c>
       <c r="T3">
-        <v>-5.84</v>
+        <v>-5.1</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1100,34 +1071,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>43.01</v>
+        <v>46.67</v>
       </c>
       <c r="Z3">
+        <v>-0.09</v>
+      </c>
+      <c r="AA3">
         <v>-0.1</v>
       </c>
-      <c r="AA3">
-        <v>-0.11</v>
-      </c>
       <c r="AB3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AC3">
-        <v>63.83</v>
+        <v>78.03</v>
       </c>
       <c r="AD3">
-        <v>59.75</v>
+        <v>66.59</v>
       </c>
       <c r="AE3">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>-14.96</v>
+        <v>57.37</v>
       </c>
       <c r="AG3">
-        <v>11.02</v>
+        <v>10.96</v>
       </c>
       <c r="AH3">
-        <v>10.35</v>
+        <v>10.38</v>
       </c>
       <c r="AI3">
         <v>11.19</v>
@@ -1136,7 +1107,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>28.69</v>
+        <v>29.78</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1118,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>238.4</v>
+        <v>241.35</v>
       </c>
       <c r="D4">
-        <v>0.13</v>
+        <v>1.24</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1159,46 +1130,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-24.88</v>
+        <v>-23.95</v>
       </c>
       <c r="H4">
-        <v>6.38</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
-        <v>-2.3</v>
+        <v>-0.27</v>
       </c>
       <c r="J4">
-        <v>-3.46</v>
+        <v>-5.89</v>
       </c>
       <c r="K4">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="L4">
-        <v>-25.43</v>
+        <v>-23.56</v>
       </c>
       <c r="M4">
-        <v>-1.37</v>
+        <v>-0.96</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P4">
-        <v>240.53</v>
+        <v>240.4</v>
       </c>
       <c r="Q4">
-        <v>250.36</v>
+        <v>249.28</v>
       </c>
       <c r="R4">
-        <v>243.84</v>
+        <v>243.78</v>
       </c>
       <c r="S4">
-        <v>257.6</v>
+        <v>257.26</v>
       </c>
       <c r="T4">
-        <v>-7.45</v>
+        <v>-6.18</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1213,43 +1184,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>39.59</v>
+        <v>44.4</v>
       </c>
       <c r="Z4">
-        <v>-1.69</v>
+        <v>-1.76</v>
       </c>
       <c r="AA4">
-        <v>0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="AB4">
-        <v>-1.9</v>
+        <v>-1.58</v>
       </c>
       <c r="AC4">
-        <v>0.87</v>
+        <v>10.14</v>
       </c>
       <c r="AD4">
-        <v>1.77</v>
+        <v>4.41</v>
       </c>
       <c r="AE4">
-        <v>4.89</v>
+        <v>4.96</v>
       </c>
       <c r="AF4">
-        <v>-55.39</v>
+        <v>40.9</v>
       </c>
       <c r="AG4">
-        <v>267.79</v>
+        <v>266.08</v>
       </c>
       <c r="AH4">
-        <v>232.94</v>
+        <v>232.48</v>
       </c>
       <c r="AI4">
-        <v>253.46</v>
+        <v>253.3</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>24.47</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1231,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>704.55</v>
+        <v>710.2</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1272,46 +1243,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-18.17</v>
+        <v>-17.51</v>
       </c>
       <c r="H5">
-        <v>43.58</v>
+        <v>44.73</v>
       </c>
       <c r="I5">
-        <v>4.52</v>
+        <v>6.81</v>
       </c>
       <c r="J5">
-        <v>-5</v>
+        <v>-0.91</v>
       </c>
       <c r="K5">
-        <v>35.02</v>
+        <v>34.13</v>
       </c>
       <c r="L5">
-        <v>-15.19</v>
+        <v>-13.41</v>
       </c>
       <c r="M5">
-        <v>-5.86</v>
+        <v>-5.72</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>662.62</v>
+        <v>671.67</v>
       </c>
       <c r="Q5">
-        <v>678.08</v>
+        <v>678.0599999999999</v>
       </c>
       <c r="R5">
-        <v>658.02</v>
+        <v>661.4299999999999</v>
       </c>
       <c r="S5">
-        <v>627.11</v>
+        <v>626.92</v>
       </c>
       <c r="T5">
-        <v>12.35</v>
+        <v>13.28</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1326,43 +1297,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>58.24</v>
+        <v>59.47</v>
       </c>
       <c r="Z5">
-        <v>-2.44</v>
+        <v>0.79</v>
       </c>
       <c r="AA5">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AB5">
-        <v>-3.2</v>
+        <v>0.02</v>
       </c>
       <c r="AC5">
+        <v>66.67</v>
+      </c>
+      <c r="AD5">
         <v>33.33</v>
       </c>
-      <c r="AD5">
-        <v>13.35</v>
-      </c>
       <c r="AE5">
-        <v>25.05</v>
+        <v>26.2</v>
       </c>
       <c r="AF5">
-        <v>277.2</v>
+        <v>791.03</v>
       </c>
       <c r="AG5">
-        <v>715.36</v>
+        <v>715.25</v>
       </c>
       <c r="AH5">
-        <v>640.8</v>
+        <v>640.86</v>
       </c>
       <c r="AI5">
-        <v>709.8</v>
+        <v>634.86</v>
       </c>
       <c r="AJ5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AK5">
-        <v>20.46</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,58 +1344,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>28.8</v>
+        <v>27.23</v>
       </c>
       <c r="D6">
-        <v>-1.17</v>
+        <v>-5.45</v>
       </c>
       <c r="E6">
         <v>56.22</v>
       </c>
       <c r="F6">
-        <v>27.52</v>
+        <v>27.23</v>
       </c>
       <c r="G6">
-        <v>-48.77</v>
+        <v>-51.57</v>
       </c>
       <c r="H6">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-3.55</v>
+        <v>-10.25</v>
       </c>
       <c r="J6">
-        <v>-1.67</v>
+        <v>-7.54</v>
       </c>
       <c r="K6">
-        <v>-4.51</v>
+        <v>-10.04</v>
       </c>
       <c r="L6">
-        <v>-47.85</v>
+        <v>-49.09</v>
       </c>
       <c r="M6">
-        <v>-9.970000000000001</v>
+        <v>-11.01</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>29.82</v>
+        <v>29.2</v>
       </c>
       <c r="Q6">
-        <v>29.44</v>
+        <v>29.33</v>
       </c>
       <c r="R6">
-        <v>30.42</v>
+        <v>30.29</v>
       </c>
       <c r="S6">
-        <v>35.23</v>
+        <v>35.12</v>
       </c>
       <c r="T6">
-        <v>-18.24</v>
+        <v>-22.48</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1439,43 +1410,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>43.28</v>
+        <v>34.91</v>
       </c>
       <c r="Z6">
-        <v>-0.15</v>
+        <v>-0.32</v>
       </c>
       <c r="AA6">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="AB6">
-        <v>0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC6">
-        <v>61</v>
+        <v>31.84</v>
       </c>
       <c r="AD6">
-        <v>76.33</v>
+        <v>56.76</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>-10.57</v>
+        <v>352.61</v>
       </c>
       <c r="AG6">
-        <v>30.84</v>
+        <v>31.04</v>
       </c>
       <c r="AH6">
-        <v>28.04</v>
+        <v>27.62</v>
       </c>
       <c r="AI6">
-        <v>27.8</v>
+        <v>31.12</v>
       </c>
       <c r="AJ6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AK6">
-        <v>30.09</v>
+        <v>30.88</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1457,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1287</v>
+        <v>1277</v>
       </c>
       <c r="D7">
-        <v>0.37</v>
+        <v>-0.78</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1498,46 +1469,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-18.8</v>
+        <v>-19.43</v>
       </c>
       <c r="H7">
-        <v>2.24</v>
+        <v>1.45</v>
       </c>
       <c r="I7">
-        <v>-2.2</v>
+        <v>-2.5</v>
       </c>
       <c r="J7">
-        <v>-0.46</v>
+        <v>-2.36</v>
       </c>
       <c r="K7">
-        <v>-2.05</v>
+        <v>-2.41</v>
       </c>
       <c r="L7">
-        <v>-8.470000000000001</v>
+        <v>-7.37</v>
       </c>
       <c r="M7">
-        <v>4.6</v>
+        <v>4.54</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P7">
-        <v>1298.8</v>
+        <v>1292.24</v>
       </c>
       <c r="Q7">
-        <v>1311.46</v>
+        <v>1309.36</v>
       </c>
       <c r="R7">
-        <v>1304.18</v>
+        <v>1303.53</v>
       </c>
       <c r="S7">
-        <v>1391</v>
+        <v>1389.86</v>
       </c>
       <c r="T7">
-        <v>-7.48</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1552,34 +1523,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>42.93</v>
+        <v>39.98</v>
       </c>
       <c r="Z7">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
       <c r="AB7">
-        <v>-3.75</v>
+        <v>-4.6</v>
       </c>
       <c r="AC7">
         <v>4.13</v>
       </c>
       <c r="AD7">
-        <v>12.15</v>
+        <v>6.12</v>
       </c>
       <c r="AE7">
-        <v>19.21</v>
+        <v>19.74</v>
       </c>
       <c r="AF7">
-        <v>-32.52</v>
+        <v>252.99</v>
       </c>
       <c r="AG7">
-        <v>1343.14</v>
+        <v>1344.33</v>
       </c>
       <c r="AH7">
-        <v>1279.77</v>
+        <v>1274.38</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1588,7 +1559,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>27.4</v>
+        <v>32.38</v>
       </c>
     </row>
   </sheetData>
@@ -1749,47 +1720,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1797,836 +1733,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>1.96</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>3.25</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.29</v>
+      <c r="D7" s="5">
+        <v>3.14</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-2.31</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-1.67</v>
       </c>
+      <c r="D8" s="5">
+        <v>-1.21</v>
+      </c>
       <c r="E8" s="7">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-4.56</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-3.46</v>
       </c>
-      <c r="E9" s="7">
+      <c r="D9" s="5">
+        <v>-5.89</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-5</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-0.91</v>
+      </c>
+      <c r="E10" s="7">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-1.67</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-7.54</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-5.87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-0.46</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-2.36</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.03</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-2.3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-0.27</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4.52</v>
+      </c>
+      <c r="D16" s="5">
+        <v>6.81</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-3.55</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-10.25</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-6.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.2</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-2.5</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-22.2</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-20.97</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-28.24</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-27.62</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-25.43</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-23.56</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-15.19</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-13.41</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-47.85</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-49.09</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-7.37</v>
+      </c>
+      <c r="E24" s="7">
         <v>1.1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>6.35</v>
+      </c>
+      <c r="D25" s="5">
+        <v>6.56</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-0</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-0.37</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1.47</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1.56</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-15.02</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5</v>
-      </c>
-      <c r="E10" s="7">
-        <v>10.02</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>35.02</v>
+      </c>
+      <c r="D28" s="5">
+        <v>34.13</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-0.34</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-1.67</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-4.51</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-10.04</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-5.53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.49</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-0.46</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-2.05</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-2.41</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1.33</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-22.65</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-22.76</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-29.91</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-29.44</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.66</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.3</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-24.88</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-23.95</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.9</v>
-      </c>
-      <c r="D16" s="6">
-        <v>4.52</v>
-      </c>
-      <c r="E16" s="7">
-        <v>10.42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-18.17</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-17.51</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-4.74</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-3.55</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-48.77</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-51.57</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-2.36</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.2</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-18.8</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-19.43</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-22.79</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-22.2</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>28.31</v>
+      </c>
+      <c r="D37" s="5">
+        <v>28.27</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-28.47</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-28.24</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>10.57</v>
+      </c>
+      <c r="D38" s="5">
+        <v>10.64</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-25.73</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-25.43</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>238.4</v>
+      </c>
+      <c r="D39" s="5">
+        <v>241.35</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-23.26</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-15.19</v>
-      </c>
-      <c r="E22" s="7">
-        <v>8.07</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>704.55</v>
+      </c>
+      <c r="D40" s="5">
+        <v>710.2</v>
+      </c>
+      <c r="E40" s="7">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-47.98</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-47.85</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>28.8</v>
+      </c>
+      <c r="D41" s="5">
+        <v>27.23</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-8.59</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-8.470000000000001</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1287</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1277</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>1.74</v>
-      </c>
-      <c r="D25" s="6">
-        <v>6.35</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4.61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>56.91</v>
+      </c>
+      <c r="D43" s="5">
+        <v>56.27</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-2.31</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-0</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>43.01</v>
+      </c>
+      <c r="D44" s="5">
+        <v>46.67</v>
+      </c>
+      <c r="E44" s="7">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-0.36</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1.47</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>39.59</v>
+      </c>
+      <c r="D45" s="5">
+        <v>44.4</v>
+      </c>
+      <c r="E45" s="7">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>22.09</v>
-      </c>
-      <c r="D28" s="6">
-        <v>35.02</v>
-      </c>
-      <c r="E28" s="7">
-        <v>12.93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>58.24</v>
+      </c>
+      <c r="D46" s="5">
+        <v>59.47</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-6.69</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-4.51</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>43.28</v>
+      </c>
+      <c r="D47" s="5">
+        <v>34.91</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-8.369999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-2.5</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>42.93</v>
+      </c>
+      <c r="D48" s="5">
+        <v>39.98</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-23.17</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-22.65</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-37.32</v>
+      </c>
+      <c r="D49" s="5">
+        <v>147.17</v>
+      </c>
+      <c r="E49" s="7">
+        <v>184.49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-30.04</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-29.91</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-14.96</v>
+      </c>
+      <c r="D50" s="5">
+        <v>57.37</v>
+      </c>
+      <c r="E50" s="7">
+        <v>72.33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-25.52</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-24.88</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-55.39</v>
+      </c>
+      <c r="D51" s="5">
+        <v>40.9</v>
+      </c>
+      <c r="E51" s="7">
+        <v>96.29000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-25.61</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-18.17</v>
-      </c>
-      <c r="E34" s="7">
-        <v>7.44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>277.2</v>
+      </c>
+      <c r="D52" s="5">
+        <v>791.03</v>
+      </c>
+      <c r="E52" s="7">
+        <v>513.83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-48.17</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-48.77</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-10.57</v>
+      </c>
+      <c r="D53" s="5">
+        <v>352.61</v>
+      </c>
+      <c r="E53" s="7">
+        <v>363.18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-19.1</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-18.8</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>28.12</v>
-      </c>
-      <c r="D37" s="6">
-        <v>28.31</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>10.55</v>
-      </c>
-      <c r="D38" s="6">
-        <v>10.57</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>238.1</v>
-      </c>
-      <c r="D39" s="6">
-        <v>238.4</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>640.5</v>
-      </c>
-      <c r="D40" s="6">
-        <v>704.55</v>
-      </c>
-      <c r="E40" s="7">
-        <v>64.05</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>29.14</v>
-      </c>
-      <c r="D41" s="6">
-        <v>28.8</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1282.2</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1287</v>
-      </c>
-      <c r="E42" s="7">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>54.62</v>
-      </c>
-      <c r="D43" s="6">
-        <v>56.91</v>
-      </c>
-      <c r="E43" s="7">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>41.96</v>
-      </c>
-      <c r="D44" s="6">
-        <v>43.01</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>39.09</v>
-      </c>
-      <c r="D45" s="6">
-        <v>39.59</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>38.52</v>
-      </c>
-      <c r="D46" s="6">
-        <v>58.24</v>
-      </c>
-      <c r="E46" s="7">
-        <v>19.72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>45.48</v>
-      </c>
-      <c r="D47" s="6">
-        <v>43.28</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>40.99</v>
-      </c>
-      <c r="D48" s="6">
-        <v>42.93</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="6">
-        <v>55.96</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-37.32</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-93.28</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-30.13</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-14.96</v>
-      </c>
-      <c r="E50" s="7">
-        <v>15.17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-57.52</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-55.39</v>
-      </c>
-      <c r="E51" s="7">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-67.76000000000001</v>
-      </c>
-      <c r="D52" s="6">
-        <v>277.2</v>
-      </c>
-      <c r="E52" s="7">
-        <v>344.96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>16.25</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-10.57</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-26.82</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>12.24</v>
-      </c>
-      <c r="D54" s="6">
+      <c r="C54" s="5">
         <v>-32.52</v>
       </c>
-      <c r="E54" s="8">
-        <v>-44.76</v>
+      <c r="D54" s="5">
+        <v>252.99</v>
+      </c>
+      <c r="E54" s="7">
+        <v>285.51</v>
       </c>
     </row>
   </sheetData>
@@ -2652,60 +2588,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>47.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>46.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-2.5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>4.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2807,43 +2743,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.046</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0137</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.05860000000000001</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0969</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.09970000000000001</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1475</v>
+      <c r="A2" s="13">
+        <v>0.0454</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0572</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0955</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1101</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.144</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,46 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>40.0 → 51.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>40.0</t>
+  </si>
+  <si>
+    <t>51.5</t>
+  </si>
+  <si>
+    <t>56.3 → 48.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>56.3</t>
+  </si>
+  <si>
+    <t>48.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +294,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +334,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,17 +410,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -892,10 +933,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>28.27</v>
+        <v>27.77</v>
       </c>
       <c r="D2">
-        <v>-0.14</v>
+        <v>-1.77</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -904,46 +945,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-22.76</v>
+        <v>-24.13</v>
       </c>
       <c r="H2">
-        <v>23.02</v>
+        <v>20.84</v>
       </c>
       <c r="I2">
-        <v>0.46</v>
+        <v>-1.24</v>
       </c>
       <c r="J2">
-        <v>3.14</v>
+        <v>0.18</v>
       </c>
       <c r="K2">
-        <v>6.56</v>
+        <v>5.35</v>
       </c>
       <c r="L2">
-        <v>-20.97</v>
+        <v>-21.33</v>
       </c>
       <c r="M2">
-        <v>-9.550000000000001</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>28.1</v>
+        <v>28.03</v>
       </c>
       <c r="Q2">
-        <v>27.65</v>
+        <v>27.67</v>
       </c>
       <c r="R2">
-        <v>28.36</v>
+        <v>28.25</v>
       </c>
       <c r="S2">
-        <v>28.64</v>
+        <v>28.62</v>
       </c>
       <c r="T2">
-        <v>-1.29</v>
+        <v>-2.96</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -958,34 +999,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>56.27</v>
+        <v>48.83</v>
       </c>
       <c r="Z2">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AA2">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AB2">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AC2">
-        <v>95.43000000000001</v>
+        <v>74.53</v>
       </c>
       <c r="AD2">
-        <v>85.36</v>
+        <v>83.7</v>
       </c>
       <c r="AE2">
         <v>0.82</v>
       </c>
       <c r="AF2">
-        <v>147.17</v>
+        <v>20.9</v>
       </c>
       <c r="AG2">
-        <v>28.45</v>
+        <v>28.46</v>
       </c>
       <c r="AH2">
-        <v>26.85</v>
+        <v>26.88</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -994,7 +1035,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>39.09</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1005,10 +1046,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.64</v>
+        <v>10.5</v>
       </c>
       <c r="D3">
-        <v>0.66</v>
+        <v>-1.32</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1017,46 +1058,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-29.44</v>
+        <v>-30.37</v>
       </c>
       <c r="H3">
-        <v>19.95</v>
+        <v>18.38</v>
       </c>
       <c r="I3">
-        <v>0.47</v>
+        <v>-0.57</v>
       </c>
       <c r="J3">
-        <v>-1.21</v>
+        <v>-4.98</v>
       </c>
       <c r="K3">
-        <v>-0.37</v>
+        <v>-0.1</v>
       </c>
       <c r="L3">
-        <v>-27.62</v>
+        <v>-28.77</v>
       </c>
       <c r="M3">
-        <v>-14.4</v>
+        <v>-14.55</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P3">
-        <v>10.58</v>
+        <v>10.57</v>
       </c>
       <c r="Q3">
-        <v>10.67</v>
+        <v>10.65</v>
       </c>
       <c r="R3">
-        <v>10.95</v>
+        <v>10.91</v>
       </c>
       <c r="S3">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
       <c r="T3">
-        <v>-5.1</v>
+        <v>-6.24</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1071,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>46.67</v>
+        <v>41</v>
       </c>
       <c r="Z3">
         <v>-0.09</v>
@@ -1083,19 +1124,19 @@
         <v>0.01</v>
       </c>
       <c r="AC3">
-        <v>78.03</v>
+        <v>74.52</v>
       </c>
       <c r="AD3">
-        <v>66.59</v>
+        <v>72.13</v>
       </c>
       <c r="AE3">
         <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>57.37</v>
+        <v>-27.62</v>
       </c>
       <c r="AG3">
-        <v>10.96</v>
+        <v>10.92</v>
       </c>
       <c r="AH3">
         <v>10.38</v>
@@ -1107,7 +1148,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>29.78</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1118,10 +1159,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>241.35</v>
+        <v>235.85</v>
       </c>
       <c r="D4">
-        <v>1.24</v>
+        <v>-2.28</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1130,46 +1171,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-23.95</v>
+        <v>-25.68</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>5.24</v>
       </c>
       <c r="I4">
-        <v>-0.27</v>
+        <v>-3</v>
       </c>
       <c r="J4">
-        <v>-5.89</v>
+        <v>-10.32</v>
       </c>
       <c r="K4">
-        <v>1.56</v>
+        <v>0.35</v>
       </c>
       <c r="L4">
-        <v>-23.56</v>
+        <v>-23.94</v>
       </c>
       <c r="M4">
-        <v>-0.96</v>
+        <v>-1.71</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>240.4</v>
+        <v>238.94</v>
       </c>
       <c r="Q4">
-        <v>249.28</v>
+        <v>247.82</v>
       </c>
       <c r="R4">
-        <v>243.78</v>
+        <v>243.63</v>
       </c>
       <c r="S4">
-        <v>257.26</v>
+        <v>256.89</v>
       </c>
       <c r="T4">
-        <v>-6.18</v>
+        <v>-8.19</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1184,43 +1225,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>44.4</v>
+        <v>38.27</v>
       </c>
       <c r="Z4">
-        <v>-1.76</v>
+        <v>-2.24</v>
       </c>
       <c r="AA4">
-        <v>-0.19</v>
+        <v>-0.6</v>
       </c>
       <c r="AB4">
-        <v>-1.58</v>
+        <v>-1.64</v>
       </c>
       <c r="AC4">
         <v>10.14</v>
       </c>
       <c r="AD4">
-        <v>4.41</v>
+        <v>7.05</v>
       </c>
       <c r="AE4">
-        <v>4.96</v>
+        <v>5.06</v>
       </c>
       <c r="AF4">
-        <v>40.9</v>
+        <v>-28.97</v>
       </c>
       <c r="AG4">
-        <v>266.08</v>
+        <v>263.92</v>
       </c>
       <c r="AH4">
-        <v>232.48</v>
+        <v>231.72</v>
       </c>
       <c r="AI4">
-        <v>253.3</v>
+        <v>252.68</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>26.62</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1231,10 +1272,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>710.2</v>
+        <v>705.65</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>-0.64</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1243,46 +1284,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-17.51</v>
+        <v>-18.04</v>
       </c>
       <c r="H5">
-        <v>44.73</v>
+        <v>43.8</v>
       </c>
       <c r="I5">
-        <v>6.81</v>
+        <v>7.66</v>
       </c>
       <c r="J5">
-        <v>-0.91</v>
+        <v>-0.7</v>
       </c>
       <c r="K5">
-        <v>34.13</v>
+        <v>33.12</v>
       </c>
       <c r="L5">
-        <v>-13.41</v>
+        <v>-12.95</v>
       </c>
       <c r="M5">
-        <v>-5.72</v>
+        <v>-5.93</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>671.67</v>
+        <v>681.71</v>
       </c>
       <c r="Q5">
-        <v>678.0599999999999</v>
+        <v>678.15</v>
       </c>
       <c r="R5">
-        <v>661.4299999999999</v>
+        <v>664.5599999999999</v>
       </c>
       <c r="S5">
-        <v>626.92</v>
+        <v>626.73</v>
       </c>
       <c r="T5">
-        <v>13.28</v>
+        <v>12.59</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1297,34 +1338,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>59.47</v>
+        <v>57.99</v>
       </c>
       <c r="Z5">
-        <v>0.79</v>
+        <v>2.95</v>
       </c>
       <c r="AA5">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AB5">
-        <v>0.02</v>
+        <v>1.74</v>
       </c>
       <c r="AC5">
-        <v>66.67</v>
+        <v>97.63</v>
       </c>
       <c r="AD5">
-        <v>33.33</v>
+        <v>65.88</v>
       </c>
       <c r="AE5">
-        <v>26.2</v>
+        <v>26.62</v>
       </c>
       <c r="AF5">
-        <v>791.03</v>
+        <v>61.55</v>
       </c>
       <c r="AG5">
-        <v>715.25</v>
+        <v>715.63</v>
       </c>
       <c r="AH5">
-        <v>640.86</v>
+        <v>640.67</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1333,7 +1374,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>24.07</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1344,10 +1385,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>27.23</v>
+        <v>28.05</v>
       </c>
       <c r="D6">
-        <v>-5.45</v>
+        <v>3.01</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1356,46 +1397,46 @@
         <v>27.23</v>
       </c>
       <c r="G6">
-        <v>-51.57</v>
+        <v>-50.11</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="I6">
-        <v>-10.25</v>
+        <v>-7.61</v>
       </c>
       <c r="J6">
-        <v>-7.54</v>
+        <v>-4.53</v>
       </c>
       <c r="K6">
-        <v>-10.04</v>
+        <v>-5.84</v>
       </c>
       <c r="L6">
-        <v>-49.09</v>
+        <v>-46.82</v>
       </c>
       <c r="M6">
-        <v>-11.01</v>
+        <v>-10.39</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>29.2</v>
+        <v>28.73</v>
       </c>
       <c r="Q6">
-        <v>29.33</v>
+        <v>29.23</v>
       </c>
       <c r="R6">
-        <v>30.29</v>
+        <v>30.17</v>
       </c>
       <c r="S6">
-        <v>35.12</v>
+        <v>35.03</v>
       </c>
       <c r="T6">
-        <v>-22.48</v>
+        <v>-19.93</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1410,34 +1451,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>34.91</v>
+        <v>41.3</v>
       </c>
       <c r="Z6">
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
       <c r="AA6">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="AB6">
-        <v>-0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="AC6">
-        <v>31.84</v>
+        <v>25.93</v>
       </c>
       <c r="AD6">
-        <v>56.76</v>
+        <v>39.59</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>352.61</v>
+        <v>16.35</v>
       </c>
       <c r="AG6">
-        <v>31.04</v>
+        <v>31</v>
       </c>
       <c r="AH6">
-        <v>27.62</v>
+        <v>27.46</v>
       </c>
       <c r="AI6">
         <v>31.12</v>
@@ -1446,7 +1487,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>30.88</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1457,10 +1498,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1277</v>
+        <v>1309</v>
       </c>
       <c r="D7">
-        <v>-0.78</v>
+        <v>2.51</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1469,46 +1510,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-19.43</v>
+        <v>-17.41</v>
       </c>
       <c r="H7">
-        <v>1.45</v>
+        <v>3.99</v>
       </c>
       <c r="I7">
-        <v>-2.5</v>
+        <v>-0.61</v>
       </c>
       <c r="J7">
-        <v>-2.36</v>
+        <v>-0.76</v>
       </c>
       <c r="K7">
-        <v>-2.41</v>
+        <v>0.14</v>
       </c>
       <c r="L7">
-        <v>-7.37</v>
+        <v>-5.11</v>
       </c>
       <c r="M7">
-        <v>4.54</v>
+        <v>4.98</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P7">
-        <v>1292.24</v>
+        <v>1290.64</v>
       </c>
       <c r="Q7">
-        <v>1309.36</v>
+        <v>1310.26</v>
       </c>
       <c r="R7">
-        <v>1303.53</v>
+        <v>1303.18</v>
       </c>
       <c r="S7">
-        <v>1389.86</v>
+        <v>1388.88</v>
       </c>
       <c r="T7">
-        <v>-8.119999999999999</v>
+        <v>-5.75</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1523,34 +1564,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>39.98</v>
+        <v>51.48</v>
       </c>
       <c r="Z7">
-        <v>-4.1</v>
+        <v>-3.06</v>
       </c>
       <c r="AA7">
-        <v>0.5</v>
+        <v>-0.21</v>
       </c>
       <c r="AB7">
-        <v>-4.6</v>
+        <v>-2.85</v>
       </c>
       <c r="AC7">
-        <v>4.13</v>
+        <v>30.92</v>
       </c>
       <c r="AD7">
-        <v>6.12</v>
+        <v>13.06</v>
       </c>
       <c r="AE7">
-        <v>19.74</v>
+        <v>20.81</v>
       </c>
       <c r="AF7">
-        <v>252.99</v>
+        <v>13.51</v>
       </c>
       <c r="AG7">
-        <v>1344.33</v>
+        <v>1344.14</v>
       </c>
       <c r="AH7">
-        <v>1274.38</v>
+        <v>1276.38</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1559,7 +1600,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>32.38</v>
+        <v>31.08</v>
       </c>
     </row>
   </sheetData>
@@ -1700,7 +1741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1720,855 +1761,910 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>3.25</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="7">
         <v>3.14</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-2.96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-1.67</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="7">
         <v>-1.21</v>
       </c>
-      <c r="E8" s="7">
+      <c r="D9" s="7">
+        <v>-4.98</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-3.77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-5.89</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-10.32</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-4.43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-0.91</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-0.7</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-7.54</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-4.53</v>
+      </c>
+      <c r="E12" s="9">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-2.36</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-0.76</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7">
         <v>0.46</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D14" s="7">
+        <v>-1.24</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.47</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.57</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-3.46</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-5.89</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-0.27</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-3</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-5</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-0.91</v>
-      </c>
-      <c r="E10" s="7">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>6.81</v>
+      </c>
+      <c r="D17" s="7">
+        <v>7.66</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-1.67</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-7.54</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-5.87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-10.25</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-7.61</v>
+      </c>
+      <c r="E18" s="9">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-0.46</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-2.36</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-2.5</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-0.61</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-20.97</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-21.33</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-27.62</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-28.77</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-23.56</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-23.94</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-13.41</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-12.95</v>
+      </c>
+      <c r="E23" s="9">
         <v>0.46</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-49.09</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-46.82</v>
+      </c>
+      <c r="E24" s="9">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-7.37</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-5.11</v>
+      </c>
+      <c r="E25" s="9">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>6.56</v>
+      </c>
+      <c r="D26" s="7">
+        <v>5.35</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-1.03</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0.47</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-0.37</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-0.1</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-2.3</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-0.27</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7">
+        <v>1.56</v>
+      </c>
+      <c r="D28" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>4.52</v>
-      </c>
-      <c r="D16" s="5">
-        <v>6.81</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>34.13</v>
+      </c>
+      <c r="D29" s="7">
+        <v>33.12</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-3.55</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-10.25</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-6.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-10.04</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-5.84</v>
+      </c>
+      <c r="E30" s="9">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-2.2</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.5</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-2.41</v>
+      </c>
+      <c r="D31" s="7">
+        <v>0.14</v>
+      </c>
+      <c r="E31" s="9">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-22.2</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-20.97</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-22.76</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-24.13</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-28.24</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="B33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-29.44</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-30.37</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-23.95</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-25.68</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-17.51</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-18.04</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-51.57</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-50.11</v>
+      </c>
+      <c r="E36" s="9">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-19.43</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-17.41</v>
+      </c>
+      <c r="E37" s="9">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7">
+        <v>28.27</v>
+      </c>
+      <c r="D38" s="7">
+        <v>27.77</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7">
+        <v>10.64</v>
+      </c>
+      <c r="D39" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="7">
+        <v>241.35</v>
+      </c>
+      <c r="D40" s="7">
+        <v>235.85</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="7">
+        <v>710.2</v>
+      </c>
+      <c r="D41" s="7">
+        <v>705.65</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7">
+        <v>27.23</v>
+      </c>
+      <c r="D42" s="7">
+        <v>28.05</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1277</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1309</v>
+      </c>
+      <c r="E43" s="9">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="7">
+        <v>56.27</v>
+      </c>
+      <c r="D44" s="7">
+        <v>48.83</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-7.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46.67</v>
+      </c>
+      <c r="D45" s="7">
+        <v>41</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-5.67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="7">
+        <v>44.4</v>
+      </c>
+      <c r="D46" s="7">
+        <v>38.27</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-6.13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="7">
+        <v>59.47</v>
+      </c>
+      <c r="D47" s="7">
+        <v>57.99</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="7">
+        <v>34.91</v>
+      </c>
+      <c r="D48" s="7">
+        <v>41.3</v>
+      </c>
+      <c r="E48" s="9">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="7">
+        <v>39.98</v>
+      </c>
+      <c r="D49" s="7">
+        <v>51.48</v>
+      </c>
+      <c r="E49" s="9">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="7">
+        <v>147.17</v>
+      </c>
+      <c r="D50" s="7">
+        <v>20.9</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-126.27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="7">
+        <v>57.37</v>
+      </c>
+      <c r="D51" s="7">
         <v>-27.62</v>
       </c>
-      <c r="E20" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="E51" s="8">
+        <v>-84.98999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-25.43</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-23.56</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="7">
+        <v>40.9</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-28.97</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-69.87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-15.19</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-13.41</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="7">
+        <v>791.03</v>
+      </c>
+      <c r="D53" s="7">
+        <v>61.55</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-729.48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-47.85</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-49.09</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="7">
+        <v>352.61</v>
+      </c>
+      <c r="D54" s="7">
+        <v>16.35</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-336.26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-8.470000000000001</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-7.37</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>6.35</v>
-      </c>
-      <c r="D25" s="5">
-        <v>6.56</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-0</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-0.37</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="D27" s="5">
-        <v>1.56</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>35.02</v>
-      </c>
-      <c r="D28" s="5">
-        <v>34.13</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-4.51</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-10.04</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-5.53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-2.05</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-2.41</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-22.65</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-22.76</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-29.91</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-29.44</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-24.88</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-23.95</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-18.17</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-17.51</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-48.77</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-51.57</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-18.8</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-19.43</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>28.31</v>
-      </c>
-      <c r="D37" s="5">
-        <v>28.27</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>10.57</v>
-      </c>
-      <c r="D38" s="5">
-        <v>10.64</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>238.4</v>
-      </c>
-      <c r="D39" s="5">
-        <v>241.35</v>
-      </c>
-      <c r="E39" s="7">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>704.55</v>
-      </c>
-      <c r="D40" s="5">
-        <v>710.2</v>
-      </c>
-      <c r="E40" s="7">
-        <v>5.65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>28.8</v>
-      </c>
-      <c r="D41" s="5">
-        <v>27.23</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1287</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1277</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>56.91</v>
-      </c>
-      <c r="D43" s="5">
-        <v>56.27</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>43.01</v>
-      </c>
-      <c r="D44" s="5">
-        <v>46.67</v>
-      </c>
-      <c r="E44" s="7">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>39.59</v>
-      </c>
-      <c r="D45" s="5">
-        <v>44.4</v>
-      </c>
-      <c r="E45" s="7">
-        <v>4.81</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>58.24</v>
-      </c>
-      <c r="D46" s="5">
-        <v>59.47</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>43.28</v>
-      </c>
-      <c r="D47" s="5">
-        <v>34.91</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-8.369999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>42.93</v>
-      </c>
-      <c r="D48" s="5">
-        <v>39.98</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="B55" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="5">
-        <v>-37.32</v>
-      </c>
-      <c r="D49" s="5">
-        <v>147.17</v>
-      </c>
-      <c r="E49" s="7">
-        <v>184.49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-14.96</v>
-      </c>
-      <c r="D50" s="5">
-        <v>57.37</v>
-      </c>
-      <c r="E50" s="7">
-        <v>72.33</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-55.39</v>
-      </c>
-      <c r="D51" s="5">
-        <v>40.9</v>
-      </c>
-      <c r="E51" s="7">
-        <v>96.29000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>277.2</v>
-      </c>
-      <c r="D52" s="5">
-        <v>791.03</v>
-      </c>
-      <c r="E52" s="7">
-        <v>513.83</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-10.57</v>
-      </c>
-      <c r="D53" s="5">
-        <v>352.61</v>
-      </c>
-      <c r="E53" s="7">
-        <v>363.18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>-32.52</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C55" s="7">
         <v>252.99</v>
       </c>
-      <c r="E54" s="7">
-        <v>285.51</v>
+      <c r="D55" s="7">
+        <v>13.51</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-239.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2588,60 +2684,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
+      <c r="B1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="12">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="13">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>46.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="12">
+        <v>46.5</v>
+      </c>
+      <c r="E2" s="12">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-2.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>4.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="12">
+        <v>-3.5</v>
+      </c>
+      <c r="G2" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="12">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>20</v>
       </c>
     </row>
@@ -2743,43 +2839,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.0454</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.009599999999999999</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0572</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0955</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1101</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.144</v>
+      <c r="A2" s="15">
+        <v>0.0498</v>
+      </c>
+      <c r="B2" s="15">
+        <v>-0.0171</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0593</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.09949999999999999</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.1039</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.1455</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,46 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>40.0 → 51.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>40.0</t>
-  </si>
-  <si>
-    <t>51.5</t>
-  </si>
-  <si>
-    <t>56.3 → 48.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>56.3</t>
-  </si>
-  <si>
-    <t>48.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -410,19 +371,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -933,10 +892,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.77</v>
+        <v>27.85</v>
       </c>
       <c r="D2">
-        <v>-1.77</v>
+        <v>0.29</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -945,46 +904,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-24.13</v>
+        <v>-23.91</v>
       </c>
       <c r="H2">
-        <v>20.84</v>
+        <v>21.19</v>
       </c>
       <c r="I2">
-        <v>-1.24</v>
+        <v>0.61</v>
       </c>
       <c r="J2">
-        <v>0.18</v>
+        <v>1.57</v>
       </c>
       <c r="K2">
-        <v>5.35</v>
+        <v>4.39</v>
       </c>
       <c r="L2">
-        <v>-21.33</v>
+        <v>-20.52</v>
       </c>
       <c r="M2">
-        <v>-9.949999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>28.03</v>
+        <v>28.06</v>
       </c>
       <c r="Q2">
-        <v>27.67</v>
+        <v>27.69</v>
       </c>
       <c r="R2">
-        <v>28.25</v>
+        <v>28.18</v>
       </c>
       <c r="S2">
-        <v>28.62</v>
+        <v>28.6</v>
       </c>
       <c r="T2">
-        <v>-2.96</v>
+        <v>-2.62</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -999,34 +958,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>48.83</v>
+        <v>49.97</v>
       </c>
       <c r="Z2">
+        <v>0.05</v>
+      </c>
+      <c r="AA2">
+        <v>-0.01</v>
+      </c>
+      <c r="AB2">
         <v>0.06</v>
       </c>
-      <c r="AA2">
-        <v>-0.03</v>
-      </c>
-      <c r="AB2">
-        <v>0.09</v>
-      </c>
       <c r="AC2">
-        <v>74.53</v>
+        <v>53.76</v>
       </c>
       <c r="AD2">
-        <v>83.7</v>
+        <v>74.58</v>
       </c>
       <c r="AE2">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AF2">
-        <v>20.9</v>
+        <v>-11.83</v>
       </c>
       <c r="AG2">
-        <v>28.46</v>
+        <v>28.48</v>
       </c>
       <c r="AH2">
-        <v>26.88</v>
+        <v>26.9</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1035,7 +994,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>36.08</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,10 +1005,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.5</v>
+        <v>10.34</v>
       </c>
       <c r="D3">
-        <v>-1.32</v>
+        <v>-1.52</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1058,46 +1017,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-30.37</v>
+        <v>-31.43</v>
       </c>
       <c r="H3">
-        <v>18.38</v>
+        <v>16.57</v>
       </c>
       <c r="I3">
-        <v>-0.57</v>
+        <v>-2.18</v>
       </c>
       <c r="J3">
-        <v>-4.98</v>
+        <v>-5.31</v>
       </c>
       <c r="K3">
-        <v>-0.1</v>
+        <v>-2.18</v>
       </c>
       <c r="L3">
-        <v>-28.77</v>
+        <v>-29.23</v>
       </c>
       <c r="M3">
-        <v>-14.55</v>
+        <v>-14.96</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P3">
-        <v>10.57</v>
+        <v>10.52</v>
       </c>
       <c r="Q3">
-        <v>10.65</v>
+        <v>10.62</v>
       </c>
       <c r="R3">
-        <v>10.91</v>
+        <v>10.89</v>
       </c>
       <c r="S3">
-        <v>11.2</v>
+        <v>11.18</v>
       </c>
       <c r="T3">
-        <v>-6.24</v>
+        <v>-7.55</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1112,43 +1071,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41</v>
+        <v>35.67</v>
       </c>
       <c r="Z3">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="AA3">
         <v>-0.1</v>
       </c>
       <c r="AB3">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC3">
-        <v>74.52</v>
+        <v>52.81</v>
       </c>
       <c r="AD3">
-        <v>72.13</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="AE3">
         <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>-27.62</v>
+        <v>-1.98</v>
       </c>
       <c r="AG3">
-        <v>10.92</v>
+        <v>10.9</v>
       </c>
       <c r="AH3">
-        <v>10.38</v>
+        <v>10.34</v>
       </c>
       <c r="AI3">
-        <v>11.19</v>
+        <v>11.11</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>30.72</v>
+        <v>27.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1159,10 +1118,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>235.85</v>
+        <v>236.9</v>
       </c>
       <c r="D4">
-        <v>-2.28</v>
+        <v>0.45</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1171,46 +1130,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-25.68</v>
+        <v>-25.35</v>
       </c>
       <c r="H4">
-        <v>5.24</v>
+        <v>5.71</v>
       </c>
       <c r="I4">
-        <v>-3</v>
+        <v>-1.7</v>
       </c>
       <c r="J4">
-        <v>-10.32</v>
+        <v>-10.6</v>
       </c>
       <c r="K4">
-        <v>0.35</v>
+        <v>0.49</v>
       </c>
       <c r="L4">
-        <v>-23.94</v>
+        <v>-24</v>
       </c>
       <c r="M4">
-        <v>-1.71</v>
+        <v>-1.56</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>238.94</v>
+        <v>238.12</v>
       </c>
       <c r="Q4">
-        <v>247.82</v>
+        <v>246.57</v>
       </c>
       <c r="R4">
-        <v>243.63</v>
+        <v>243.61</v>
       </c>
       <c r="S4">
-        <v>256.89</v>
+        <v>256.5</v>
       </c>
       <c r="T4">
-        <v>-8.19</v>
+        <v>-7.64</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1225,43 +1184,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>38.27</v>
+        <v>39.98</v>
       </c>
       <c r="Z4">
-        <v>-2.24</v>
+        <v>-2.5</v>
       </c>
       <c r="AA4">
-        <v>-0.6</v>
+        <v>-0.98</v>
       </c>
       <c r="AB4">
-        <v>-1.64</v>
+        <v>-1.52</v>
       </c>
       <c r="AC4">
-        <v>10.14</v>
+        <v>13.78</v>
       </c>
       <c r="AD4">
-        <v>7.05</v>
+        <v>11.35</v>
       </c>
       <c r="AE4">
         <v>5.06</v>
       </c>
       <c r="AF4">
-        <v>-28.97</v>
+        <v>19.11</v>
       </c>
       <c r="AG4">
-        <v>263.92</v>
+        <v>261.92</v>
       </c>
       <c r="AH4">
-        <v>231.72</v>
+        <v>231.22</v>
       </c>
       <c r="AI4">
-        <v>252.68</v>
+        <v>250.03</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>28.75</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1272,10 +1231,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>705.65</v>
+        <v>697.85</v>
       </c>
       <c r="D5">
-        <v>-0.64</v>
+        <v>-1.11</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1284,46 +1243,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-18.04</v>
+        <v>-18.94</v>
       </c>
       <c r="H5">
-        <v>43.8</v>
+        <v>42.22</v>
       </c>
       <c r="I5">
-        <v>7.66</v>
+        <v>7.75</v>
       </c>
       <c r="J5">
-        <v>-0.7</v>
+        <v>-0.84</v>
       </c>
       <c r="K5">
-        <v>33.12</v>
+        <v>32.72</v>
       </c>
       <c r="L5">
-        <v>-12.95</v>
+        <v>-13.73</v>
       </c>
       <c r="M5">
-        <v>-5.93</v>
+        <v>-6.6</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>681.71</v>
+        <v>691.75</v>
       </c>
       <c r="Q5">
-        <v>678.15</v>
+        <v>678.9</v>
       </c>
       <c r="R5">
-        <v>664.5599999999999</v>
+        <v>667.59</v>
       </c>
       <c r="S5">
-        <v>626.73</v>
+        <v>626.54</v>
       </c>
       <c r="T5">
-        <v>12.59</v>
+        <v>11.38</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1338,34 +1297,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>57.99</v>
+        <v>55.43</v>
       </c>
       <c r="Z5">
-        <v>2.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA5">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB5">
-        <v>1.74</v>
+        <v>2.22</v>
       </c>
       <c r="AC5">
-        <v>97.63</v>
+        <v>91.2</v>
       </c>
       <c r="AD5">
-        <v>65.88</v>
+        <v>85.17</v>
       </c>
       <c r="AE5">
-        <v>26.62</v>
+        <v>25.73</v>
       </c>
       <c r="AF5">
-        <v>61.55</v>
+        <v>-40.25</v>
       </c>
       <c r="AG5">
-        <v>715.63</v>
+        <v>717.36</v>
       </c>
       <c r="AH5">
-        <v>640.67</v>
+        <v>640.4299999999999</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1374,7 +1333,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>27.21</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1385,10 +1344,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>28.05</v>
+        <v>27.24</v>
       </c>
       <c r="D6">
-        <v>3.01</v>
+        <v>-2.89</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1397,46 +1356,46 @@
         <v>27.23</v>
       </c>
       <c r="G6">
-        <v>-50.11</v>
+        <v>-51.55</v>
       </c>
       <c r="H6">
-        <v>3.01</v>
+        <v>0.04</v>
       </c>
       <c r="I6">
-        <v>-7.61</v>
+        <v>-10.54</v>
       </c>
       <c r="J6">
-        <v>-4.53</v>
+        <v>-9.35</v>
       </c>
       <c r="K6">
-        <v>-5.84</v>
+        <v>-9.17</v>
       </c>
       <c r="L6">
-        <v>-46.82</v>
+        <v>-48.44</v>
       </c>
       <c r="M6">
-        <v>-10.39</v>
+        <v>-11.19</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>28.73</v>
+        <v>28.09</v>
       </c>
       <c r="Q6">
-        <v>29.23</v>
+        <v>29.11</v>
       </c>
       <c r="R6">
-        <v>30.17</v>
+        <v>30.05</v>
       </c>
       <c r="S6">
-        <v>35.03</v>
+        <v>34.94</v>
       </c>
       <c r="T6">
-        <v>-19.93</v>
+        <v>-22.03</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1451,43 +1410,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>41.3</v>
+        <v>37.4</v>
       </c>
       <c r="Z6">
-        <v>-0.38</v>
+        <v>-0.49</v>
       </c>
       <c r="AA6">
-        <v>-0.27</v>
+        <v>-0.32</v>
       </c>
       <c r="AB6">
-        <v>-0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="AC6">
-        <v>25.93</v>
+        <v>17.6</v>
       </c>
       <c r="AD6">
-        <v>39.59</v>
+        <v>25.12</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>16.35</v>
+        <v>-29.84</v>
       </c>
       <c r="AG6">
-        <v>31</v>
+        <v>31.08</v>
       </c>
       <c r="AH6">
-        <v>27.46</v>
+        <v>27.14</v>
       </c>
       <c r="AI6">
-        <v>31.12</v>
+        <v>30.83</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>31.57</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1498,10 +1457,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1309</v>
+        <v>1313.1</v>
       </c>
       <c r="D7">
-        <v>2.51</v>
+        <v>0.31</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1510,46 +1469,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-17.41</v>
+        <v>-17.15</v>
       </c>
       <c r="H7">
-        <v>3.99</v>
+        <v>4.31</v>
       </c>
       <c r="I7">
-        <v>-0.61</v>
+        <v>1.16</v>
       </c>
       <c r="J7">
-        <v>-0.76</v>
+        <v>1.72</v>
       </c>
       <c r="K7">
-        <v>0.14</v>
+        <v>1.19</v>
       </c>
       <c r="L7">
-        <v>-5.11</v>
+        <v>-2.8</v>
       </c>
       <c r="M7">
-        <v>4.98</v>
+        <v>4.79</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="P7">
-        <v>1290.64</v>
+        <v>1293.66</v>
       </c>
       <c r="Q7">
-        <v>1310.26</v>
+        <v>1311.92</v>
       </c>
       <c r="R7">
-        <v>1303.18</v>
+        <v>1303.25</v>
       </c>
       <c r="S7">
-        <v>1388.88</v>
+        <v>1387.89</v>
       </c>
       <c r="T7">
-        <v>-5.75</v>
+        <v>-5.39</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1564,34 +1523,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>51.48</v>
+        <v>52.73</v>
       </c>
       <c r="Z7">
-        <v>-3.06</v>
+        <v>-1.89</v>
       </c>
       <c r="AA7">
-        <v>-0.21</v>
+        <v>-0.55</v>
       </c>
       <c r="AB7">
-        <v>-2.85</v>
+        <v>-1.34</v>
       </c>
       <c r="AC7">
-        <v>30.92</v>
+        <v>56.49</v>
       </c>
       <c r="AD7">
-        <v>13.06</v>
+        <v>30.51</v>
       </c>
       <c r="AE7">
-        <v>20.81</v>
+        <v>21.38</v>
       </c>
       <c r="AF7">
-        <v>13.51</v>
+        <v>18.79</v>
       </c>
       <c r="AG7">
-        <v>1344.14</v>
+        <v>1342.66</v>
       </c>
       <c r="AH7">
-        <v>1276.38</v>
+        <v>1281.17</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1600,7 +1559,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>31.08</v>
+        <v>27.11</v>
       </c>
     </row>
   </sheetData>
@@ -1741,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1761,910 +1720,855 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-4.98</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-5.31</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-10.32</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-10.6</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-0.7</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-0.84</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-4.53</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-9.35</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-4.82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-0.76</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.72</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>3.14</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0.18</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.24</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1.21</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-4.98</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.57</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.18</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-5.89</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-10.32</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-4.43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-1.7</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-0.91</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-0.7</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>7.66</v>
+      </c>
+      <c r="D16" s="5">
+        <v>7.75</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-7.54</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-4.53</v>
-      </c>
-      <c r="E12" s="9">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-7.61</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-10.54</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-2.36</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-0.76</v>
-      </c>
-      <c r="E13" s="9">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-0.61</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1.16</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>0.46</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-1.24</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-21.33</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-20.52</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0.47</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-0.57</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-28.77</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-29.23</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-0.27</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-3</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-23.94</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-24</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>6.81</v>
-      </c>
-      <c r="D17" s="7">
-        <v>7.66</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-12.95</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-13.73</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-10.25</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-7.61</v>
-      </c>
-      <c r="E18" s="9">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-46.82</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-48.44</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-2.5</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-0.61</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-5.11</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-2.8</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-20.97</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-21.33</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>5.35</v>
+      </c>
+      <c r="D25" s="5">
+        <v>4.39</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-2.18</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>33.12</v>
+      </c>
+      <c r="D28" s="5">
+        <v>32.72</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-5.84</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-9.17</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-3.33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0.14</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-24.13</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-23.91</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-30.37</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-31.43</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-25.68</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-25.35</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-18.04</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-18.94</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-50.11</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-51.55</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-17.41</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-17.15</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>27.77</v>
+      </c>
+      <c r="D37" s="5">
+        <v>27.85</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="D38" s="5">
+        <v>10.34</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>235.85</v>
+      </c>
+      <c r="D39" s="5">
+        <v>236.9</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>705.65</v>
+      </c>
+      <c r="D40" s="5">
+        <v>697.85</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-7.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>28.05</v>
+      </c>
+      <c r="D41" s="5">
+        <v>27.24</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1309</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1313.1</v>
+      </c>
+      <c r="E42" s="6">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>48.83</v>
+      </c>
+      <c r="D43" s="5">
+        <v>49.97</v>
+      </c>
+      <c r="E43" s="6">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>41</v>
+      </c>
+      <c r="D44" s="5">
+        <v>35.67</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-5.33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>38.27</v>
+      </c>
+      <c r="D45" s="5">
+        <v>39.98</v>
+      </c>
+      <c r="E45" s="6">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>57.99</v>
+      </c>
+      <c r="D46" s="5">
+        <v>55.43</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>41.3</v>
+      </c>
+      <c r="D47" s="5">
+        <v>37.4</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>51.48</v>
+      </c>
+      <c r="D48" s="5">
+        <v>52.73</v>
+      </c>
+      <c r="E48" s="6">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>20.9</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-11.83</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-32.73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
         <v>-27.62</v>
       </c>
-      <c r="D21" s="7">
-        <v>-28.77</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="D50" s="5">
+        <v>-1.98</v>
+      </c>
+      <c r="E50" s="6">
+        <v>25.64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-23.56</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-23.94</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-28.97</v>
+      </c>
+      <c r="D51" s="5">
+        <v>19.11</v>
+      </c>
+      <c r="E51" s="6">
+        <v>48.08</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-13.41</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-12.95</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>61.55</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-40.25</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-101.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-49.09</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-46.82</v>
-      </c>
-      <c r="E24" s="9">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>16.35</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-29.84</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-46.19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-7.37</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-5.11</v>
-      </c>
-      <c r="E25" s="9">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>6.56</v>
-      </c>
-      <c r="D26" s="7">
-        <v>5.35</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-0.37</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-0.1</v>
-      </c>
-      <c r="E27" s="9">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>1.56</v>
-      </c>
-      <c r="D28" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>34.13</v>
-      </c>
-      <c r="D29" s="7">
-        <v>33.12</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-10.04</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-5.84</v>
-      </c>
-      <c r="E30" s="9">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-2.41</v>
-      </c>
-      <c r="D31" s="7">
-        <v>0.14</v>
-      </c>
-      <c r="E31" s="9">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-22.76</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-24.13</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-29.44</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-30.37</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-23.95</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-25.68</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-17.51</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-18.04</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-51.57</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-50.11</v>
-      </c>
-      <c r="E36" s="9">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-19.43</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-17.41</v>
-      </c>
-      <c r="E37" s="9">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="7">
-        <v>28.27</v>
-      </c>
-      <c r="D38" s="7">
-        <v>27.77</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="7">
-        <v>10.64</v>
-      </c>
-      <c r="D39" s="7">
-        <v>10.5</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="7">
-        <v>241.35</v>
-      </c>
-      <c r="D40" s="7">
-        <v>235.85</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="7">
-        <v>710.2</v>
-      </c>
-      <c r="D41" s="7">
-        <v>705.65</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="7">
-        <v>27.23</v>
-      </c>
-      <c r="D42" s="7">
-        <v>28.05</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1277</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1309</v>
-      </c>
-      <c r="E43" s="9">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="7">
-        <v>56.27</v>
-      </c>
-      <c r="D44" s="7">
-        <v>48.83</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-7.44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="7">
-        <v>46.67</v>
-      </c>
-      <c r="D45" s="7">
-        <v>41</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-5.67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="7">
-        <v>44.4</v>
-      </c>
-      <c r="D46" s="7">
-        <v>38.27</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-6.13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="7">
-        <v>59.47</v>
-      </c>
-      <c r="D47" s="7">
-        <v>57.99</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="7">
-        <v>34.91</v>
-      </c>
-      <c r="D48" s="7">
-        <v>41.3</v>
-      </c>
-      <c r="E48" s="9">
-        <v>6.39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="7">
-        <v>39.98</v>
-      </c>
-      <c r="D49" s="7">
-        <v>51.48</v>
-      </c>
-      <c r="E49" s="9">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="7">
-        <v>147.17</v>
-      </c>
-      <c r="D50" s="7">
-        <v>20.9</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-126.27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="7">
-        <v>57.37</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-27.62</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-84.98999999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="7">
-        <v>40.9</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-28.97</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-69.87</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="7">
-        <v>791.03</v>
-      </c>
-      <c r="D53" s="7">
-        <v>61.55</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-729.48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="7">
-        <v>352.61</v>
-      </c>
-      <c r="D54" s="7">
-        <v>16.35</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-336.26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="7">
-        <v>252.99</v>
-      </c>
-      <c r="D55" s="7">
+      <c r="C54" s="5">
         <v>13.51</v>
       </c>
-      <c r="E55" s="8">
-        <v>-239.48</v>
+      <c r="D54" s="5">
+        <v>18.79</v>
+      </c>
+      <c r="E54" s="6">
+        <v>5.28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2684,60 +2588,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>75</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="12">
-        <v>46.5</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>45.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="12">
-        <v>-3.5</v>
-      </c>
-      <c r="G2" s="12">
-        <v>5.5</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-3.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>4.6</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2839,43 +2743,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="15">
-        <v>0.0498</v>
-      </c>
-      <c r="B2" s="15">
-        <v>-0.0171</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0593</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.09949999999999999</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1039</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.1455</v>
+      <c r="A2" s="13">
+        <v>0.0479</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0156</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.066</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.099</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1119</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1496</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,46 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.0 → 50.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>52.7 → 49.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.7</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -371,17 +410,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -892,10 +933,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.85</v>
+        <v>27.87</v>
       </c>
       <c r="D2">
-        <v>0.29</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -904,46 +945,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-23.91</v>
+        <v>-23.85</v>
       </c>
       <c r="H2">
-        <v>21.19</v>
+        <v>21.28</v>
       </c>
       <c r="I2">
-        <v>0.61</v>
+        <v>-0.89</v>
       </c>
       <c r="J2">
         <v>1.57</v>
       </c>
       <c r="K2">
-        <v>4.39</v>
+        <v>1.75</v>
       </c>
       <c r="L2">
-        <v>-20.52</v>
+        <v>-20.33</v>
       </c>
       <c r="M2">
-        <v>-9.9</v>
+        <v>-10.66</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P2">
-        <v>28.06</v>
+        <v>28.01</v>
       </c>
       <c r="Q2">
-        <v>27.69</v>
+        <v>27.72</v>
       </c>
       <c r="R2">
-        <v>28.18</v>
+        <v>28.09</v>
       </c>
       <c r="S2">
-        <v>28.6</v>
+        <v>28.58</v>
       </c>
       <c r="T2">
-        <v>-2.62</v>
+        <v>-2.47</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -958,34 +999,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>49.97</v>
+        <v>50.26</v>
       </c>
       <c r="Z2">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AA2">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AB2">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="AC2">
-        <v>53.76</v>
+        <v>35.18</v>
       </c>
       <c r="AD2">
-        <v>74.58</v>
+        <v>54.49</v>
       </c>
       <c r="AE2">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="AF2">
-        <v>-11.83</v>
+        <v>-51.67</v>
       </c>
       <c r="AG2">
-        <v>28.48</v>
+        <v>28.49</v>
       </c>
       <c r="AH2">
-        <v>26.9</v>
+        <v>26.94</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -994,7 +1035,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>32.24</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1005,10 +1046,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.34</v>
+        <v>10.26</v>
       </c>
       <c r="D3">
-        <v>-1.52</v>
+        <v>-0.77</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1017,25 +1058,25 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-31.43</v>
+        <v>-31.96</v>
       </c>
       <c r="H3">
-        <v>16.57</v>
+        <v>15.67</v>
       </c>
       <c r="I3">
-        <v>-2.18</v>
+        <v>-2.75</v>
       </c>
       <c r="J3">
-        <v>-5.31</v>
+        <v>-5.87</v>
       </c>
       <c r="K3">
-        <v>-2.18</v>
+        <v>-7.4</v>
       </c>
       <c r="L3">
-        <v>-29.23</v>
+        <v>-29.19</v>
       </c>
       <c r="M3">
-        <v>-14.96</v>
+        <v>-15.46</v>
       </c>
       <c r="N3">
         <v>34</v>
@@ -1044,19 +1085,19 @@
         <v>21</v>
       </c>
       <c r="P3">
-        <v>10.52</v>
+        <v>10.46</v>
       </c>
       <c r="Q3">
-        <v>10.62</v>
+        <v>10.59</v>
       </c>
       <c r="R3">
-        <v>10.89</v>
+        <v>10.85</v>
       </c>
       <c r="S3">
-        <v>11.18</v>
+        <v>11.17</v>
       </c>
       <c r="T3">
-        <v>-7.55</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1071,43 +1112,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.67</v>
+        <v>33.34</v>
       </c>
       <c r="Z3">
+        <v>-0.12</v>
+      </c>
+      <c r="AA3">
         <v>-0.11</v>
       </c>
-      <c r="AA3">
-        <v>-0.1</v>
-      </c>
       <c r="AB3">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>52.81</v>
+        <v>19.48</v>
       </c>
       <c r="AD3">
-        <v>68.45999999999999</v>
+        <v>48.94</v>
       </c>
       <c r="AE3">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AF3">
-        <v>-1.98</v>
+        <v>-21.26</v>
       </c>
       <c r="AG3">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
       <c r="AH3">
-        <v>10.34</v>
+        <v>10.29</v>
       </c>
       <c r="AI3">
-        <v>11.11</v>
+        <v>11.06</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>27.17</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1118,10 +1159,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>236.9</v>
+        <v>237.45</v>
       </c>
       <c r="D4">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1130,46 +1171,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-25.35</v>
+        <v>-25.18</v>
       </c>
       <c r="H4">
-        <v>5.71</v>
+        <v>5.96</v>
       </c>
       <c r="I4">
-        <v>-1.7</v>
+        <v>-0.27</v>
       </c>
       <c r="J4">
-        <v>-10.6</v>
+        <v>-9.35</v>
       </c>
       <c r="K4">
-        <v>0.49</v>
+        <v>0.24</v>
       </c>
       <c r="L4">
-        <v>-24</v>
+        <v>-24.39</v>
       </c>
       <c r="M4">
-        <v>-1.56</v>
+        <v>-1.49</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P4">
-        <v>238.12</v>
+        <v>237.99</v>
       </c>
       <c r="Q4">
-        <v>246.57</v>
+        <v>245.29</v>
       </c>
       <c r="R4">
-        <v>243.61</v>
+        <v>243.58</v>
       </c>
       <c r="S4">
-        <v>256.5</v>
+        <v>256.12</v>
       </c>
       <c r="T4">
-        <v>-7.64</v>
+        <v>-7.29</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1184,34 +1225,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>39.98</v>
+        <v>40.9</v>
       </c>
       <c r="Z4">
-        <v>-2.5</v>
+        <v>-2.63</v>
       </c>
       <c r="AA4">
-        <v>-0.98</v>
+        <v>-1.31</v>
       </c>
       <c r="AB4">
-        <v>-1.52</v>
+        <v>-1.32</v>
       </c>
       <c r="AC4">
-        <v>13.78</v>
+        <v>11.45</v>
       </c>
       <c r="AD4">
-        <v>11.35</v>
+        <v>11.79</v>
       </c>
       <c r="AE4">
-        <v>5.06</v>
+        <v>4.99</v>
       </c>
       <c r="AF4">
-        <v>19.11</v>
+        <v>-28.22</v>
       </c>
       <c r="AG4">
-        <v>261.92</v>
+        <v>259.03</v>
       </c>
       <c r="AH4">
-        <v>231.22</v>
+        <v>231.55</v>
       </c>
       <c r="AI4">
         <v>250.03</v>
@@ -1220,7 +1261,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>31.95</v>
+        <v>30.89</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1231,10 +1272,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>697.85</v>
+        <v>697.35</v>
       </c>
       <c r="D5">
-        <v>-1.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1243,46 +1284,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-18.94</v>
+        <v>-19</v>
       </c>
       <c r="H5">
-        <v>42.22</v>
+        <v>42.11</v>
       </c>
       <c r="I5">
-        <v>7.75</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J5">
-        <v>-0.84</v>
+        <v>2.1</v>
       </c>
       <c r="K5">
-        <v>32.72</v>
+        <v>33.18</v>
       </c>
       <c r="L5">
-        <v>-13.73</v>
+        <v>-14.45</v>
       </c>
       <c r="M5">
-        <v>-6.6</v>
+        <v>-6.82</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>691.75</v>
+        <v>703.12</v>
       </c>
       <c r="Q5">
-        <v>678.9</v>
+        <v>679.6900000000001</v>
       </c>
       <c r="R5">
-        <v>667.59</v>
+        <v>670.52</v>
       </c>
       <c r="S5">
-        <v>626.54</v>
+        <v>626.17</v>
       </c>
       <c r="T5">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1297,34 +1338,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>55.43</v>
+        <v>55.26</v>
       </c>
       <c r="Z5">
-        <v>3.98</v>
+        <v>4.7</v>
       </c>
       <c r="AA5">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="AB5">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="AC5">
-        <v>91.2</v>
+        <v>84.5</v>
       </c>
       <c r="AD5">
-        <v>85.17</v>
+        <v>91.11</v>
       </c>
       <c r="AE5">
-        <v>25.73</v>
+        <v>25.09</v>
       </c>
       <c r="AF5">
-        <v>-40.25</v>
+        <v>-35.8</v>
       </c>
       <c r="AG5">
-        <v>717.36</v>
+        <v>719.02</v>
       </c>
       <c r="AH5">
-        <v>640.4299999999999</v>
+        <v>640.35</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1333,7 +1374,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>28.84</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1344,10 +1385,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>27.24</v>
+        <v>27.55</v>
       </c>
       <c r="D6">
-        <v>-2.89</v>
+        <v>1.14</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1356,46 +1397,46 @@
         <v>27.23</v>
       </c>
       <c r="G6">
-        <v>-51.55</v>
+        <v>-51</v>
       </c>
       <c r="H6">
-        <v>0.04</v>
+        <v>1.18</v>
       </c>
       <c r="I6">
-        <v>-10.54</v>
+        <v>-5.46</v>
       </c>
       <c r="J6">
-        <v>-9.35</v>
+        <v>-6.93</v>
       </c>
       <c r="K6">
-        <v>-9.17</v>
+        <v>-17.54</v>
       </c>
       <c r="L6">
-        <v>-48.44</v>
+        <v>-48.56</v>
       </c>
       <c r="M6">
-        <v>-11.19</v>
+        <v>-11.88</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>28.09</v>
+        <v>27.77</v>
       </c>
       <c r="Q6">
-        <v>29.11</v>
+        <v>28.99</v>
       </c>
       <c r="R6">
-        <v>30.05</v>
+        <v>29.94</v>
       </c>
       <c r="S6">
-        <v>34.94</v>
+        <v>34.84</v>
       </c>
       <c r="T6">
-        <v>-22.03</v>
+        <v>-20.92</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1410,43 +1451,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>37.4</v>
+        <v>39.74</v>
       </c>
       <c r="Z6">
-        <v>-0.49</v>
+        <v>-0.55</v>
       </c>
       <c r="AA6">
-        <v>-0.32</v>
+        <v>-0.37</v>
       </c>
       <c r="AB6">
-        <v>-0.17</v>
+        <v>-0.19</v>
       </c>
       <c r="AC6">
-        <v>17.6</v>
+        <v>24.43</v>
       </c>
       <c r="AD6">
-        <v>25.12</v>
+        <v>22.65</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>-29.84</v>
+        <v>-51.79</v>
       </c>
       <c r="AG6">
-        <v>31.08</v>
+        <v>31.04</v>
       </c>
       <c r="AH6">
-        <v>27.14</v>
+        <v>26.95</v>
       </c>
       <c r="AI6">
-        <v>30.83</v>
+        <v>30.76</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>32.51</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1457,10 +1498,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1313.1</v>
+        <v>1302.5</v>
       </c>
       <c r="D7">
-        <v>0.31</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1469,46 +1510,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-17.15</v>
+        <v>-17.82</v>
       </c>
       <c r="H7">
-        <v>4.31</v>
+        <v>3.47</v>
       </c>
       <c r="I7">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="J7">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="K7">
-        <v>1.19</v>
+        <v>0.89</v>
       </c>
       <c r="L7">
-        <v>-2.8</v>
+        <v>-3.35</v>
       </c>
       <c r="M7">
-        <v>4.79</v>
+        <v>3.78</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P7">
-        <v>1293.66</v>
+        <v>1297.72</v>
       </c>
       <c r="Q7">
-        <v>1311.92</v>
+        <v>1310.79</v>
       </c>
       <c r="R7">
-        <v>1303.25</v>
+        <v>1303.03</v>
       </c>
       <c r="S7">
-        <v>1387.89</v>
+        <v>1386.84</v>
       </c>
       <c r="T7">
-        <v>-5.39</v>
+        <v>-6.08</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1523,34 +1564,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>52.73</v>
+        <v>49.2</v>
       </c>
       <c r="Z7">
-        <v>-1.89</v>
+        <v>-1.8</v>
       </c>
       <c r="AA7">
-        <v>-0.55</v>
+        <v>-0.8</v>
       </c>
       <c r="AB7">
-        <v>-1.34</v>
+        <v>-1</v>
       </c>
       <c r="AC7">
-        <v>56.49</v>
+        <v>77.97</v>
       </c>
       <c r="AD7">
-        <v>30.51</v>
+        <v>55.12</v>
       </c>
       <c r="AE7">
-        <v>21.38</v>
+        <v>20.88</v>
       </c>
       <c r="AF7">
-        <v>18.79</v>
+        <v>-15.47</v>
       </c>
       <c r="AG7">
-        <v>1342.66</v>
+        <v>1341.17</v>
       </c>
       <c r="AH7">
-        <v>1281.17</v>
+        <v>1280.41</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1559,7 +1600,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>27.11</v>
+        <v>23.67</v>
       </c>
     </row>
   </sheetData>
@@ -1720,855 +1761,893 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-5.31</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-5.87</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-10.6</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-9.35</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-0.84</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-9.35</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-6.93</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1.72</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="B13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0.61</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-0.89</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-4.98</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-5.31</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-2.18</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-2.75</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-10.32</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-1.7</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.27</v>
+      </c>
+      <c r="E15" s="9">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>7.75</v>
+      </c>
+      <c r="D16" s="7">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-10.54</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-5.46</v>
+      </c>
+      <c r="E17" s="9">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1.16</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1.58</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-20.52</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-20.33</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-29.23</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-29.19</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-24</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-24.39</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-13.73</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-14.45</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-48.44</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-48.56</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-2.8</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-3.35</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="7">
+        <v>4.39</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-2.18</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-7.4</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-5.22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="D27" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7">
+        <v>32.72</v>
+      </c>
+      <c r="D28" s="7">
+        <v>33.18</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-9.17</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-17.54</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-8.369999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>1.19</v>
+      </c>
+      <c r="D30" s="7">
+        <v>0.89</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-23.91</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-23.85</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-31.43</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-31.96</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-25.35</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-25.18</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-18.94</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-19</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-51.55</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-51</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-17.15</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-17.82</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="7">
+        <v>27.85</v>
+      </c>
+      <c r="D37" s="7">
+        <v>27.87</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7">
+        <v>10.34</v>
+      </c>
+      <c r="D38" s="7">
+        <v>10.26</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7">
+        <v>236.9</v>
+      </c>
+      <c r="D39" s="7">
+        <v>237.45</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="7">
+        <v>697.85</v>
+      </c>
+      <c r="D40" s="7">
+        <v>697.35</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="7">
+        <v>27.24</v>
+      </c>
+      <c r="D41" s="7">
+        <v>27.55</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7">
+        <v>1313.1</v>
+      </c>
+      <c r="D42" s="7">
+        <v>1302.5</v>
+      </c>
+      <c r="E42" s="8">
         <v>-10.6</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="7">
+        <v>49.97</v>
+      </c>
+      <c r="D43" s="7">
+        <v>50.26</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="7">
+        <v>35.67</v>
+      </c>
+      <c r="D44" s="7">
+        <v>33.34</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="7">
+        <v>39.98</v>
+      </c>
+      <c r="D45" s="7">
+        <v>40.9</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-0.7</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-0.84</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="7">
+        <v>55.43</v>
+      </c>
+      <c r="D46" s="7">
+        <v>55.26</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-4.53</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-9.35</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-4.82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="7">
+        <v>37.4</v>
+      </c>
+      <c r="D47" s="7">
+        <v>39.74</v>
+      </c>
+      <c r="E47" s="9">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-0.76</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1.72</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="7">
+        <v>52.73</v>
+      </c>
+      <c r="D48" s="7">
+        <v>49.2</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-3.53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-1.24</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0.61</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B49" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-11.83</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-51.67</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-39.84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-0.57</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-2.18</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B50" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-1.98</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-21.26</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-19.28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-3</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-1.7</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B51" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="7">
+        <v>19.11</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-28.22</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-47.33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>7.66</v>
-      </c>
-      <c r="D16" s="5">
-        <v>7.75</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-40.25</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-35.8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-7.61</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-10.54</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-29.84</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-51.79</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-21.95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-0.61</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.16</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-21.33</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-20.52</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-28.77</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-29.23</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-23.94</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-24</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-12.95</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-13.73</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-46.82</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-48.44</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-5.11</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-2.8</v>
-      </c>
-      <c r="E24" s="6">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>5.35</v>
-      </c>
-      <c r="D25" s="5">
-        <v>4.39</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-0.1</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-2.18</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="D27" s="5">
-        <v>0.49</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>33.12</v>
-      </c>
-      <c r="D28" s="5">
-        <v>32.72</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-5.84</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-9.17</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-3.33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>0.14</v>
-      </c>
-      <c r="D30" s="5">
-        <v>1.19</v>
-      </c>
-      <c r="E30" s="6">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-24.13</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-23.91</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-30.37</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-31.43</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-25.68</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-25.35</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-18.04</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-18.94</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-50.11</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-51.55</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-17.41</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-17.15</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>27.77</v>
-      </c>
-      <c r="D37" s="5">
-        <v>27.85</v>
-      </c>
-      <c r="E37" s="6">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>10.5</v>
-      </c>
-      <c r="D38" s="5">
-        <v>10.34</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>235.85</v>
-      </c>
-      <c r="D39" s="5">
-        <v>236.9</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>705.65</v>
-      </c>
-      <c r="D40" s="5">
-        <v>697.85</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-7.8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>28.05</v>
-      </c>
-      <c r="D41" s="5">
-        <v>27.24</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1309</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1313.1</v>
-      </c>
-      <c r="E42" s="6">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>48.83</v>
-      </c>
-      <c r="D43" s="5">
-        <v>49.97</v>
-      </c>
-      <c r="E43" s="6">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>41</v>
-      </c>
-      <c r="D44" s="5">
-        <v>35.67</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-5.33</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>38.27</v>
-      </c>
-      <c r="D45" s="5">
-        <v>39.98</v>
-      </c>
-      <c r="E45" s="6">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>57.99</v>
-      </c>
-      <c r="D46" s="5">
-        <v>55.43</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-2.56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>41.3</v>
-      </c>
-      <c r="D47" s="5">
-        <v>37.4</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>51.48</v>
-      </c>
-      <c r="D48" s="5">
-        <v>52.73</v>
-      </c>
-      <c r="E48" s="6">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="B54" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="5">
-        <v>20.9</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-11.83</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-32.73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-27.62</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-1.98</v>
-      </c>
-      <c r="E50" s="6">
-        <v>25.64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-28.97</v>
-      </c>
-      <c r="D51" s="5">
-        <v>19.11</v>
-      </c>
-      <c r="E51" s="6">
-        <v>48.08</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>61.55</v>
-      </c>
-      <c r="D52" s="5">
-        <v>-40.25</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-101.8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>16.35</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-29.84</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-46.19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>13.51</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C54" s="7">
         <v>18.79</v>
       </c>
-      <c r="E54" s="6">
-        <v>5.28</v>
+      <c r="D54" s="7">
+        <v>-15.47</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-34.26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2588,60 +2667,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
+      <c r="B1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="12">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="13">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>45.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="12">
+        <v>44.8</v>
+      </c>
+      <c r="E2" s="12">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-3.8</v>
-      </c>
-      <c r="G2" s="10">
-        <v>4.6</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="12">
+        <v>-2.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>1.9</v>
+      </c>
+      <c r="H2" s="12">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>20</v>
       </c>
     </row>
@@ -2743,43 +2822,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.0479</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0156</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.066</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.099</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1119</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1496</v>
+      <c r="A2" s="15">
+        <v>0.0378</v>
+      </c>
+      <c r="B2" s="15">
+        <v>-0.0149</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0682</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.1066</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.1188</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.1546</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,28 +187,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.0 → 50.3</t>
+    <t>49.2 → 55.1</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>52.7 → 49.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.7</t>
-  </si>
-  <si>
     <t>49.2</t>
+  </si>
+  <si>
+    <t>55.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -410,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -418,11 +406,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -933,10 +920,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.87</v>
+        <v>27.97</v>
       </c>
       <c r="D2">
-        <v>0.07000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -945,46 +932,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-23.85</v>
+        <v>-23.58</v>
       </c>
       <c r="H2">
-        <v>21.28</v>
+        <v>21.71</v>
       </c>
       <c r="I2">
-        <v>-0.89</v>
+        <v>-1.2</v>
       </c>
       <c r="J2">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="K2">
-        <v>1.75</v>
+        <v>3.59</v>
       </c>
       <c r="L2">
-        <v>-20.33</v>
+        <v>-22.22</v>
       </c>
       <c r="M2">
-        <v>-10.66</v>
+        <v>-10.82</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P2">
-        <v>28.01</v>
+        <v>27.95</v>
       </c>
       <c r="Q2">
-        <v>27.72</v>
+        <v>27.75</v>
       </c>
       <c r="R2">
-        <v>28.09</v>
+        <v>28.02</v>
       </c>
       <c r="S2">
-        <v>28.58</v>
+        <v>28.56</v>
       </c>
       <c r="T2">
-        <v>-2.47</v>
+        <v>-2.05</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -999,34 +986,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>50.26</v>
+        <v>51.81</v>
       </c>
       <c r="Z2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AA2">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AB2">
         <v>0.04</v>
       </c>
       <c r="AC2">
-        <v>35.18</v>
+        <v>44.11</v>
       </c>
       <c r="AD2">
-        <v>54.49</v>
+        <v>44.35</v>
       </c>
       <c r="AE2">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="AF2">
-        <v>-51.67</v>
+        <v>-36.69</v>
       </c>
       <c r="AG2">
-        <v>28.49</v>
+        <v>28.51</v>
       </c>
       <c r="AH2">
-        <v>26.94</v>
+        <v>26.99</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1035,7 +1022,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>30.79</v>
+        <v>29.53</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,10 +1033,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.26</v>
+        <v>10.52</v>
       </c>
       <c r="D3">
-        <v>-0.77</v>
+        <v>2.53</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1058,46 +1045,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-31.96</v>
+        <v>-30.24</v>
       </c>
       <c r="H3">
-        <v>15.67</v>
+        <v>18.6</v>
       </c>
       <c r="I3">
-        <v>-2.75</v>
+        <v>-0.47</v>
       </c>
       <c r="J3">
-        <v>-5.87</v>
+        <v>-2.86</v>
       </c>
       <c r="K3">
-        <v>-7.4</v>
+        <v>-2.59</v>
       </c>
       <c r="L3">
-        <v>-29.19</v>
+        <v>-27.8</v>
       </c>
       <c r="M3">
-        <v>-15.46</v>
+        <v>-15.19</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>10.46</v>
+        <v>10.45</v>
       </c>
       <c r="Q3">
-        <v>10.59</v>
+        <v>10.57</v>
       </c>
       <c r="R3">
-        <v>10.85</v>
+        <v>10.83</v>
       </c>
       <c r="S3">
-        <v>11.17</v>
+        <v>11.16</v>
       </c>
       <c r="T3">
-        <v>-8.140000000000001</v>
+        <v>-5.7</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1112,34 +1099,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.34</v>
+        <v>45.76</v>
       </c>
       <c r="Z3">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AA3">
         <v>-0.11</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="AC3">
-        <v>19.48</v>
+        <v>33.25</v>
       </c>
       <c r="AD3">
-        <v>48.94</v>
+        <v>35.18</v>
       </c>
       <c r="AE3">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>-21.26</v>
+        <v>22.71</v>
       </c>
       <c r="AG3">
-        <v>10.89</v>
+        <v>10.83</v>
       </c>
       <c r="AH3">
-        <v>10.29</v>
+        <v>10.31</v>
       </c>
       <c r="AI3">
         <v>11.06</v>
@@ -1148,7 +1135,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>24.09</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1159,10 +1146,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>237.45</v>
+        <v>239.5</v>
       </c>
       <c r="D4">
-        <v>0.23</v>
+        <v>0.86</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1171,46 +1158,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-25.18</v>
+        <v>-24.53</v>
       </c>
       <c r="H4">
-        <v>5.96</v>
+        <v>6.87</v>
       </c>
       <c r="I4">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="J4">
-        <v>-9.35</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="K4">
-        <v>0.24</v>
+        <v>4.65</v>
       </c>
       <c r="L4">
-        <v>-24.39</v>
+        <v>-23.18</v>
       </c>
       <c r="M4">
-        <v>-1.49</v>
+        <v>-1.21</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>237.99</v>
+        <v>238.21</v>
       </c>
       <c r="Q4">
-        <v>245.29</v>
+        <v>244.42</v>
       </c>
       <c r="R4">
-        <v>243.58</v>
+        <v>243.59</v>
       </c>
       <c r="S4">
-        <v>256.12</v>
+        <v>255.79</v>
       </c>
       <c r="T4">
-        <v>-7.29</v>
+        <v>-6.37</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1225,34 +1212,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>40.9</v>
+        <v>44.32</v>
       </c>
       <c r="Z4">
-        <v>-2.63</v>
+        <v>-2.54</v>
       </c>
       <c r="AA4">
-        <v>-1.31</v>
+        <v>-1.56</v>
       </c>
       <c r="AB4">
-        <v>-1.32</v>
+        <v>-0.99</v>
       </c>
       <c r="AC4">
-        <v>11.45</v>
+        <v>35.46</v>
       </c>
       <c r="AD4">
-        <v>11.79</v>
+        <v>20.23</v>
       </c>
       <c r="AE4">
-        <v>4.99</v>
+        <v>4.86</v>
       </c>
       <c r="AF4">
-        <v>-28.22</v>
+        <v>-4.76</v>
       </c>
       <c r="AG4">
-        <v>259.03</v>
+        <v>257.26</v>
       </c>
       <c r="AH4">
-        <v>231.55</v>
+        <v>231.59</v>
       </c>
       <c r="AI4">
         <v>250.03</v>
@@ -1261,7 +1248,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>30.89</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1272,10 +1259,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>697.35</v>
+        <v>692.85</v>
       </c>
       <c r="D5">
-        <v>-0.07000000000000001</v>
+        <v>-0.65</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1284,46 +1271,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-19</v>
+        <v>-19.52</v>
       </c>
       <c r="H5">
-        <v>42.11</v>
+        <v>41.2</v>
       </c>
       <c r="I5">
-        <v>8.880000000000001</v>
+        <v>-1.66</v>
       </c>
       <c r="J5">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="K5">
-        <v>33.18</v>
+        <v>33.96</v>
       </c>
       <c r="L5">
-        <v>-14.45</v>
+        <v>-15.45</v>
       </c>
       <c r="M5">
-        <v>-6.82</v>
+        <v>-6.88</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>703.12</v>
+        <v>700.78</v>
       </c>
       <c r="Q5">
-        <v>679.6900000000001</v>
+        <v>680.16</v>
       </c>
       <c r="R5">
-        <v>670.52</v>
+        <v>673.63</v>
       </c>
       <c r="S5">
-        <v>626.17</v>
+        <v>625.75</v>
       </c>
       <c r="T5">
-        <v>11.37</v>
+        <v>10.72</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1338,34 +1325,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>55.26</v>
+        <v>53.68</v>
       </c>
       <c r="Z5">
-        <v>4.7</v>
+        <v>4.86</v>
       </c>
       <c r="AA5">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="AB5">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="AC5">
-        <v>84.5</v>
+        <v>77.64</v>
       </c>
       <c r="AD5">
-        <v>91.11</v>
+        <v>84.45</v>
       </c>
       <c r="AE5">
-        <v>25.09</v>
+        <v>23.96</v>
       </c>
       <c r="AF5">
-        <v>-35.8</v>
+        <v>-61.37</v>
       </c>
       <c r="AG5">
-        <v>719.02</v>
+        <v>719.91</v>
       </c>
       <c r="AH5">
-        <v>640.35</v>
+        <v>640.42</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1374,7 +1361,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>30.7</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1385,10 +1372,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>27.55</v>
+        <v>28.38</v>
       </c>
       <c r="D6">
-        <v>1.14</v>
+        <v>3.01</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1397,46 +1384,46 @@
         <v>27.23</v>
       </c>
       <c r="G6">
-        <v>-51</v>
+        <v>-49.52</v>
       </c>
       <c r="H6">
-        <v>1.18</v>
+        <v>4.22</v>
       </c>
       <c r="I6">
-        <v>-5.46</v>
+        <v>-1.46</v>
       </c>
       <c r="J6">
-        <v>-6.93</v>
+        <v>-5.12</v>
       </c>
       <c r="K6">
-        <v>-17.54</v>
+        <v>-10.95</v>
       </c>
       <c r="L6">
-        <v>-48.56</v>
+        <v>-47.22</v>
       </c>
       <c r="M6">
-        <v>-11.88</v>
+        <v>-11.45</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>27.77</v>
+        <v>27.69</v>
       </c>
       <c r="Q6">
-        <v>28.99</v>
+        <v>28.94</v>
       </c>
       <c r="R6">
-        <v>29.94</v>
+        <v>29.85</v>
       </c>
       <c r="S6">
-        <v>34.84</v>
+        <v>34.75</v>
       </c>
       <c r="T6">
-        <v>-20.92</v>
+        <v>-18.33</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1451,34 +1438,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>39.74</v>
+        <v>45.62</v>
       </c>
       <c r="Z6">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="AA6">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="AB6">
-        <v>-0.19</v>
+        <v>-0.13</v>
       </c>
       <c r="AC6">
-        <v>24.43</v>
+        <v>30.54</v>
       </c>
       <c r="AD6">
-        <v>22.65</v>
+        <v>24.19</v>
       </c>
       <c r="AE6">
         <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>-51.79</v>
+        <v>-47.68</v>
       </c>
       <c r="AG6">
-        <v>31.04</v>
+        <v>30.98</v>
       </c>
       <c r="AH6">
-        <v>26.95</v>
+        <v>26.89</v>
       </c>
       <c r="AI6">
         <v>30.76</v>
@@ -1487,7 +1474,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>33.33</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1498,10 +1485,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1302.5</v>
+        <v>1322</v>
       </c>
       <c r="D7">
-        <v>-0.8100000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1510,22 +1497,22 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-17.82</v>
+        <v>-16.59</v>
       </c>
       <c r="H7">
-        <v>3.47</v>
+        <v>5.02</v>
       </c>
       <c r="I7">
-        <v>1.58</v>
+        <v>2.72</v>
       </c>
       <c r="J7">
-        <v>1.76</v>
+        <v>-0.23</v>
       </c>
       <c r="K7">
-        <v>0.89</v>
+        <v>4.65</v>
       </c>
       <c r="L7">
-        <v>-3.35</v>
+        <v>-2.81</v>
       </c>
       <c r="M7">
         <v>3.78</v>
@@ -1534,22 +1521,22 @@
         <v>83</v>
       </c>
       <c r="O7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P7">
-        <v>1297.72</v>
+        <v>1304.72</v>
       </c>
       <c r="Q7">
-        <v>1310.79</v>
+        <v>1310.15</v>
       </c>
       <c r="R7">
-        <v>1303.03</v>
+        <v>1303.11</v>
       </c>
       <c r="S7">
-        <v>1386.84</v>
+        <v>1385.89</v>
       </c>
       <c r="T7">
-        <v>-6.08</v>
+        <v>-4.61</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1564,34 +1551,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>49.2</v>
+        <v>55.15</v>
       </c>
       <c r="Z7">
-        <v>-1.8</v>
+        <v>-0.15</v>
       </c>
       <c r="AA7">
-        <v>-0.8</v>
+        <v>-0.67</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>0.52</v>
       </c>
       <c r="AC7">
-        <v>77.97</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="AD7">
-        <v>55.12</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="AE7">
-        <v>20.88</v>
+        <v>21.56</v>
       </c>
       <c r="AF7">
-        <v>-15.47</v>
+        <v>20.84</v>
       </c>
       <c r="AG7">
-        <v>1341.17</v>
+        <v>1338.89</v>
       </c>
       <c r="AH7">
-        <v>1280.41</v>
+        <v>1281.41</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1600,7 +1587,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>23.67</v>
+        <v>23.99</v>
       </c>
     </row>
   </sheetData>
@@ -1781,7 +1768,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1799,855 +1786,852 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.57</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-5.87</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-2.86</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-9.35</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.66</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-6.93</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.12</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1.76</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-0.23</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-0.89</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-1.2</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-5.31</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-5.87</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.75</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.47</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-10.6</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-9.35</v>
-      </c>
-      <c r="E9" s="9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.27</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.46</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-0.84</v>
-      </c>
-      <c r="D10" s="7">
-        <v>2.1</v>
-      </c>
-      <c r="E10" s="9">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.66</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-10.54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-9.35</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-6.93</v>
-      </c>
-      <c r="E11" s="9">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-5.46</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-1.46</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1.58</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2.72</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-20.33</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-22.22</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-29.19</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-27.8</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-24.39</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-23.18</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-14.45</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-15.45</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-48.56</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-47.22</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-3.35</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2.81</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1.75</v>
+      </c>
+      <c r="D25" s="6">
+        <v>3.59</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-7.4</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-2.59</v>
+      </c>
+      <c r="E26" s="7">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="D27" s="6">
+        <v>4.65</v>
+      </c>
+      <c r="E27" s="7">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>33.18</v>
+      </c>
+      <c r="D28" s="6">
+        <v>33.96</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-17.54</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-10.95</v>
+      </c>
+      <c r="E29" s="7">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.89</v>
+      </c>
+      <c r="D30" s="6">
+        <v>4.65</v>
+      </c>
+      <c r="E30" s="7">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-23.85</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-23.58</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-31.96</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-30.24</v>
+      </c>
+      <c r="E32" s="7">
         <v>1.72</v>
       </c>
-      <c r="D12" s="7">
-        <v>1.76</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-25.18</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-24.53</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-19</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-19.52</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-51</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-49.52</v>
+      </c>
+      <c r="E35" s="7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-17.82</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-16.59</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7">
-        <v>0.61</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-0.89</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>27.87</v>
+      </c>
+      <c r="D37" s="6">
+        <v>27.97</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-2.18</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-2.75</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>10.26</v>
+      </c>
+      <c r="D38" s="6">
+        <v>10.52</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-1.7</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-0.27</v>
-      </c>
-      <c r="E15" s="9">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>237.45</v>
+      </c>
+      <c r="D39" s="6">
+        <v>239.5</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>7.75</v>
-      </c>
-      <c r="D16" s="7">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>697.35</v>
+      </c>
+      <c r="D40" s="6">
+        <v>692.85</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-10.54</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-5.46</v>
-      </c>
-      <c r="E17" s="9">
-        <v>5.08</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>27.55</v>
+      </c>
+      <c r="D41" s="6">
+        <v>28.38</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>1.16</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1.58</v>
-      </c>
-      <c r="E18" s="9">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1302.5</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1322</v>
+      </c>
+      <c r="E42" s="7">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-20.52</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-20.33</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>50.26</v>
+      </c>
+      <c r="D43" s="6">
+        <v>51.81</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-29.23</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-29.19</v>
-      </c>
-      <c r="E20" s="9">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>33.34</v>
+      </c>
+      <c r="D44" s="6">
+        <v>45.76</v>
+      </c>
+      <c r="E44" s="7">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-24</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-24.39</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>40.9</v>
+      </c>
+      <c r="D45" s="6">
+        <v>44.32</v>
+      </c>
+      <c r="E45" s="7">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-13.73</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-14.45</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>55.26</v>
+      </c>
+      <c r="D46" s="6">
+        <v>53.68</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-48.44</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-48.56</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>39.74</v>
+      </c>
+      <c r="D47" s="6">
+        <v>45.62</v>
+      </c>
+      <c r="E47" s="7">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-2.8</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-3.35</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>49.2</v>
+      </c>
+      <c r="D48" s="6">
+        <v>55.15</v>
+      </c>
+      <c r="E48" s="7">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>4.39</v>
-      </c>
-      <c r="D25" s="7">
-        <v>1.75</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-51.67</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-36.69</v>
+      </c>
+      <c r="E49" s="7">
+        <v>14.98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-2.18</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-7.4</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-5.22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-21.26</v>
+      </c>
+      <c r="D50" s="6">
+        <v>22.71</v>
+      </c>
+      <c r="E50" s="7">
+        <v>43.97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>0.49</v>
-      </c>
-      <c r="D27" s="7">
-        <v>0.24</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-28.22</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-4.76</v>
+      </c>
+      <c r="E51" s="7">
+        <v>23.46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>32.72</v>
-      </c>
-      <c r="D28" s="7">
-        <v>33.18</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-35.8</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-61.37</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-25.57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-9.17</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-17.54</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-8.369999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-51.79</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-47.68</v>
+      </c>
+      <c r="E53" s="7">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>1.19</v>
-      </c>
-      <c r="D30" s="7">
-        <v>0.89</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-23.91</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-23.85</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-31.43</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-31.96</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-25.35</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-25.18</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-18.94</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-19</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-51.55</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-51</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-17.15</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-17.82</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="7">
-        <v>27.85</v>
-      </c>
-      <c r="D37" s="7">
-        <v>27.87</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="7">
-        <v>10.34</v>
-      </c>
-      <c r="D38" s="7">
-        <v>10.26</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="7">
-        <v>236.9</v>
-      </c>
-      <c r="D39" s="7">
-        <v>237.45</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="7">
-        <v>697.85</v>
-      </c>
-      <c r="D40" s="7">
-        <v>697.35</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="7">
-        <v>27.24</v>
-      </c>
-      <c r="D41" s="7">
-        <v>27.55</v>
-      </c>
-      <c r="E41" s="9">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="7">
-        <v>1313.1</v>
-      </c>
-      <c r="D42" s="7">
-        <v>1302.5</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-10.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="7">
-        <v>49.97</v>
-      </c>
-      <c r="D43" s="7">
-        <v>50.26</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="7">
-        <v>35.67</v>
-      </c>
-      <c r="D44" s="7">
-        <v>33.34</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="7">
-        <v>39.98</v>
-      </c>
-      <c r="D45" s="7">
-        <v>40.9</v>
-      </c>
-      <c r="E45" s="9">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="7">
-        <v>55.43</v>
-      </c>
-      <c r="D46" s="7">
-        <v>55.26</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="7">
-        <v>37.4</v>
-      </c>
-      <c r="D47" s="7">
-        <v>39.74</v>
-      </c>
-      <c r="E47" s="9">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="7">
-        <v>52.73</v>
-      </c>
-      <c r="D48" s="7">
-        <v>49.2</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-3.53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="7">
-        <v>-11.83</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-51.67</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-39.84</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-1.98</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-21.26</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-19.28</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="7">
-        <v>19.11</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-28.22</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-47.33</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-40.25</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-35.8</v>
-      </c>
-      <c r="E52" s="9">
-        <v>4.45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-29.84</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-51.79</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-21.95</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="7">
-        <v>18.79</v>
-      </c>
-      <c r="D54" s="7">
+      <c r="C54" s="6">
         <v>-15.47</v>
       </c>
-      <c r="E54" s="8">
-        <v>-34.26</v>
+      <c r="D54" s="6">
+        <v>20.84</v>
+      </c>
+      <c r="E54" s="7">
+        <v>36.31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2667,60 +2651,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="12">
-        <v>44.8</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>49.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="12">
-        <v>-2.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>1.9</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-2.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2822,43 +2806,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>0.0378</v>
       </c>
-      <c r="B2" s="15">
-        <v>-0.0149</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0682</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.1066</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1188</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.1546</v>
+      <c r="B2" s="14">
+        <v>-0.0121</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0688</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1082</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1145</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1519</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,19 +184,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>49.2 → 55.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.2</t>
-  </si>
-  <si>
-    <t>55.1</t>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +276,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +316,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -920,10 +914,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.97</v>
+        <v>27.9</v>
       </c>
       <c r="D2">
-        <v>0.36</v>
+        <v>-0.25</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -932,46 +926,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-23.58</v>
+        <v>-23.77</v>
       </c>
       <c r="H2">
-        <v>21.71</v>
+        <v>21.41</v>
       </c>
       <c r="I2">
-        <v>-1.2</v>
+        <v>-1.31</v>
       </c>
       <c r="J2">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="K2">
-        <v>3.59</v>
+        <v>2.88</v>
       </c>
       <c r="L2">
-        <v>-22.22</v>
+        <v>-22.97</v>
       </c>
       <c r="M2">
-        <v>-10.82</v>
+        <v>-10.56</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P2">
-        <v>27.95</v>
+        <v>27.87</v>
       </c>
       <c r="Q2">
-        <v>27.75</v>
+        <v>27.78</v>
       </c>
       <c r="R2">
-        <v>28.02</v>
+        <v>27.99</v>
       </c>
       <c r="S2">
-        <v>28.56</v>
+        <v>28.54</v>
       </c>
       <c r="T2">
-        <v>-2.05</v>
+        <v>-2.23</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -986,34 +980,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>51.81</v>
+        <v>50.62</v>
       </c>
       <c r="Z2">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AA2">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AB2">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AC2">
-        <v>44.11</v>
+        <v>46.08</v>
       </c>
       <c r="AD2">
-        <v>44.35</v>
+        <v>41.79</v>
       </c>
       <c r="AE2">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="AF2">
-        <v>-36.69</v>
+        <v>-43.51</v>
       </c>
       <c r="AG2">
         <v>28.51</v>
       </c>
       <c r="AH2">
-        <v>26.99</v>
+        <v>27.05</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1022,7 +1016,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>29.53</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1033,10 +1027,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.52</v>
+        <v>10.38</v>
       </c>
       <c r="D3">
-        <v>2.53</v>
+        <v>-1.33</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1045,22 +1039,22 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-30.24</v>
+        <v>-31.17</v>
       </c>
       <c r="H3">
-        <v>18.6</v>
+        <v>17.02</v>
       </c>
       <c r="I3">
-        <v>-0.47</v>
+        <v>-2.44</v>
       </c>
       <c r="J3">
-        <v>-2.86</v>
+        <v>-4.86</v>
       </c>
       <c r="K3">
-        <v>-2.59</v>
+        <v>-4.07</v>
       </c>
       <c r="L3">
-        <v>-27.8</v>
+        <v>-29.63</v>
       </c>
       <c r="M3">
         <v>-15.19</v>
@@ -1069,22 +1063,22 @@
         <v>34</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P3">
-        <v>10.45</v>
+        <v>10.4</v>
       </c>
       <c r="Q3">
-        <v>10.57</v>
+        <v>10.55</v>
       </c>
       <c r="R3">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="S3">
-        <v>11.16</v>
+        <v>11.14</v>
       </c>
       <c r="T3">
-        <v>-5.7</v>
+        <v>-6.84</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1099,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.76</v>
+        <v>41.3</v>
       </c>
       <c r="Z3">
         <v>-0.11</v>
@@ -1111,22 +1105,22 @@
         <v>-0.01</v>
       </c>
       <c r="AC3">
-        <v>33.25</v>
+        <v>50.96</v>
       </c>
       <c r="AD3">
-        <v>35.18</v>
+        <v>34.56</v>
       </c>
       <c r="AE3">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AF3">
-        <v>22.71</v>
+        <v>-39.08</v>
       </c>
       <c r="AG3">
-        <v>10.83</v>
+        <v>10.8</v>
       </c>
       <c r="AH3">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
       <c r="AI3">
         <v>11.06</v>
@@ -1135,7 +1129,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>23.69</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1146,10 +1140,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>239.5</v>
+        <v>234.4</v>
       </c>
       <c r="D4">
-        <v>0.86</v>
+        <v>-2.13</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1158,49 +1152,49 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-24.53</v>
+        <v>-26.14</v>
       </c>
       <c r="H4">
-        <v>6.87</v>
+        <v>4.6</v>
       </c>
       <c r="I4">
-        <v>0.46</v>
+        <v>-2.88</v>
       </c>
       <c r="J4">
-        <v>-8.970000000000001</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="K4">
-        <v>4.65</v>
+        <v>0.08</v>
       </c>
       <c r="L4">
-        <v>-23.18</v>
+        <v>-25.28</v>
       </c>
       <c r="M4">
-        <v>-1.21</v>
+        <v>-1.9</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>238.21</v>
+        <v>236.82</v>
       </c>
       <c r="Q4">
-        <v>244.42</v>
+        <v>243.44</v>
       </c>
       <c r="R4">
-        <v>243.59</v>
+        <v>243.54</v>
       </c>
       <c r="S4">
-        <v>255.79</v>
+        <v>255.44</v>
       </c>
       <c r="T4">
-        <v>-6.37</v>
+        <v>-8.24</v>
       </c>
       <c r="U4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V4" t="s">
         <v>44</v>
@@ -1209,37 +1203,37 @@
         <v>44</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>44.32</v>
+        <v>38.37</v>
       </c>
       <c r="Z4">
-        <v>-2.54</v>
+        <v>-2.85</v>
       </c>
       <c r="AA4">
-        <v>-1.56</v>
+        <v>-1.82</v>
       </c>
       <c r="AB4">
-        <v>-0.99</v>
+        <v>-1.04</v>
       </c>
       <c r="AC4">
-        <v>35.46</v>
+        <v>31.35</v>
       </c>
       <c r="AD4">
-        <v>20.23</v>
+        <v>26.09</v>
       </c>
       <c r="AE4">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="AF4">
-        <v>-4.76</v>
+        <v>-17.43</v>
       </c>
       <c r="AG4">
-        <v>257.26</v>
+        <v>256.19</v>
       </c>
       <c r="AH4">
-        <v>231.59</v>
+        <v>230.69</v>
       </c>
       <c r="AI4">
         <v>250.03</v>
@@ -1248,7 +1242,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>29.79</v>
+        <v>31.06</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1259,10 +1253,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>692.85</v>
+        <v>698.75</v>
       </c>
       <c r="D5">
-        <v>-0.65</v>
+        <v>0.85</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1271,25 +1265,25 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-19.52</v>
+        <v>-18.84</v>
       </c>
       <c r="H5">
-        <v>41.2</v>
+        <v>42.4</v>
       </c>
       <c r="I5">
-        <v>-1.66</v>
+        <v>-1.61</v>
       </c>
       <c r="J5">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="K5">
-        <v>33.96</v>
+        <v>31.88</v>
       </c>
       <c r="L5">
-        <v>-15.45</v>
+        <v>-14.67</v>
       </c>
       <c r="M5">
-        <v>-6.88</v>
+        <v>-6.73</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1298,19 +1292,19 @@
         <v>63</v>
       </c>
       <c r="P5">
-        <v>700.78</v>
+        <v>698.49</v>
       </c>
       <c r="Q5">
-        <v>680.16</v>
+        <v>680.72</v>
       </c>
       <c r="R5">
-        <v>673.63</v>
+        <v>677.09</v>
       </c>
       <c r="S5">
-        <v>625.75</v>
+        <v>625.41</v>
       </c>
       <c r="T5">
-        <v>10.72</v>
+        <v>11.73</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1325,34 +1319,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>53.68</v>
+        <v>55.48</v>
       </c>
       <c r="Z5">
-        <v>4.86</v>
+        <v>5.4</v>
       </c>
       <c r="AA5">
-        <v>2.85</v>
+        <v>3.36</v>
       </c>
       <c r="AB5">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AC5">
-        <v>77.64</v>
+        <v>77.72</v>
       </c>
       <c r="AD5">
-        <v>84.45</v>
+        <v>79.95</v>
       </c>
       <c r="AE5">
-        <v>23.96</v>
+        <v>23.41</v>
       </c>
       <c r="AF5">
-        <v>-61.37</v>
+        <v>-50.86</v>
       </c>
       <c r="AG5">
-        <v>719.91</v>
+        <v>721.21</v>
       </c>
       <c r="AH5">
-        <v>640.42</v>
+        <v>640.23</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1361,7 +1355,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>31.38</v>
+        <v>32.45</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1372,10 +1366,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>28.38</v>
+        <v>27.64</v>
       </c>
       <c r="D6">
-        <v>3.01</v>
+        <v>-2.61</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1384,46 +1378,46 @@
         <v>27.23</v>
       </c>
       <c r="G6">
-        <v>-49.52</v>
+        <v>-50.84</v>
       </c>
       <c r="H6">
-        <v>4.22</v>
+        <v>1.51</v>
       </c>
       <c r="I6">
-        <v>-1.46</v>
+        <v>1.51</v>
       </c>
       <c r="J6">
-        <v>-5.12</v>
+        <v>-6.5</v>
       </c>
       <c r="K6">
-        <v>-10.95</v>
+        <v>-13.41</v>
       </c>
       <c r="L6">
-        <v>-47.22</v>
+        <v>-49.43</v>
       </c>
       <c r="M6">
-        <v>-11.45</v>
+        <v>-11.55</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>27.69</v>
+        <v>27.77</v>
       </c>
       <c r="Q6">
-        <v>28.94</v>
+        <v>28.85</v>
       </c>
       <c r="R6">
-        <v>29.85</v>
+        <v>29.78</v>
       </c>
       <c r="S6">
-        <v>34.75</v>
+        <v>34.66</v>
       </c>
       <c r="T6">
-        <v>-18.33</v>
+        <v>-20.25</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1438,34 +1432,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>45.62</v>
+        <v>41.71</v>
       </c>
       <c r="Z6">
-        <v>-0.52</v>
+        <v>-0.55</v>
       </c>
       <c r="AA6">
-        <v>-0.4</v>
+        <v>-0.43</v>
       </c>
       <c r="AB6">
         <v>-0.13</v>
       </c>
       <c r="AC6">
+        <v>36.65</v>
+      </c>
+      <c r="AD6">
         <v>30.54</v>
       </c>
-      <c r="AD6">
-        <v>24.19</v>
-      </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>-47.68</v>
+        <v>-16.95</v>
       </c>
       <c r="AG6">
-        <v>30.98</v>
+        <v>30.97</v>
       </c>
       <c r="AH6">
-        <v>26.89</v>
+        <v>26.73</v>
       </c>
       <c r="AI6">
         <v>30.76</v>
@@ -1474,7 +1468,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>30.44</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1485,10 +1479,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1322</v>
+        <v>1309.5</v>
       </c>
       <c r="D7">
-        <v>1.5</v>
+        <v>-0.95</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1497,46 +1491,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-16.59</v>
+        <v>-17.38</v>
       </c>
       <c r="H7">
-        <v>5.02</v>
+        <v>4.03</v>
       </c>
       <c r="I7">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="J7">
-        <v>-0.23</v>
+        <v>-1.9</v>
       </c>
       <c r="K7">
-        <v>4.65</v>
+        <v>3.18</v>
       </c>
       <c r="L7">
-        <v>-2.81</v>
+        <v>-4.16</v>
       </c>
       <c r="M7">
-        <v>3.78</v>
+        <v>3.44</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P7">
-        <v>1304.72</v>
+        <v>1311.22</v>
       </c>
       <c r="Q7">
-        <v>1310.15</v>
+        <v>1309.26</v>
       </c>
       <c r="R7">
-        <v>1303.11</v>
+        <v>1303.28</v>
       </c>
       <c r="S7">
-        <v>1385.89</v>
+        <v>1384.88</v>
       </c>
       <c r="T7">
-        <v>-4.61</v>
+        <v>-5.44</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1551,34 +1545,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>55.15</v>
+        <v>51.02</v>
       </c>
       <c r="Z7">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="AA7">
-        <v>-0.67</v>
+        <v>-0.5</v>
       </c>
       <c r="AB7">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="AC7">
-        <v>84.51000000000001</v>
+        <v>79.09</v>
       </c>
       <c r="AD7">
-        <v>72.98999999999999</v>
+        <v>80.52</v>
       </c>
       <c r="AE7">
-        <v>21.56</v>
+        <v>21.62</v>
       </c>
       <c r="AF7">
-        <v>20.84</v>
+        <v>-2.15</v>
       </c>
       <c r="AG7">
-        <v>1338.89</v>
+        <v>1336.85</v>
       </c>
       <c r="AH7">
-        <v>1281.41</v>
+        <v>1281.67</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1587,7 +1581,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>23.99</v>
+        <v>23.59</v>
       </c>
     </row>
   </sheetData>
@@ -1768,7 +1762,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1780,15 +1774,15 @@
         <v>56</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1800,16 +1794,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1820,13 +1814,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="D7" s="6">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="E7" s="7">
-        <v>0.66</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1837,13 +1831,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-5.87</v>
+        <v>-2.86</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.86</v>
+        <v>-4.86</v>
       </c>
       <c r="E8" s="7">
-        <v>3.01</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1854,13 +1848,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-9.35</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="D9" s="6">
-        <v>-8.970000000000001</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.38</v>
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1871,13 +1865,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="D10" s="6">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="E10" s="8">
-        <v>-0.44</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1888,13 +1882,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-6.93</v>
+        <v>-5.12</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.12</v>
+        <v>-6.5</v>
       </c>
       <c r="E11" s="7">
-        <v>1.81</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1905,13 +1899,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>1.76</v>
+        <v>-0.23</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.99</v>
+        <v>-1.9</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1922,13 +1916,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.89</v>
+        <v>-1.2</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.2</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.31</v>
+        <v>-1.31</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1939,13 +1933,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.75</v>
+        <v>-0.47</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.47</v>
+        <v>-2.44</v>
       </c>
       <c r="E14" s="7">
-        <v>2.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1956,13 +1950,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="D15" s="6">
-        <v>0.46</v>
+        <v>-2.88</v>
       </c>
       <c r="E15" s="7">
-        <v>0.73</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1973,13 +1967,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>8.880000000000001</v>
+        <v>-1.66</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.66</v>
+        <v>-1.61</v>
       </c>
       <c r="E16" s="8">
-        <v>-10.54</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1990,13 +1984,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.46</v>
+        <v>-1.46</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.46</v>
-      </c>
-      <c r="E17" s="7">
-        <v>4</v>
+        <v>1.51</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.97</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2007,13 +2001,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>1.58</v>
+        <v>2.72</v>
       </c>
       <c r="D18" s="6">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="E18" s="7">
-        <v>1.14</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2024,13 +2018,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-20.33</v>
+        <v>-22.22</v>
       </c>
       <c r="D19" s="6">
-        <v>-22.22</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-1.89</v>
+        <v>-22.97</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2041,13 +2035,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-29.19</v>
+        <v>-27.8</v>
       </c>
       <c r="D20" s="6">
-        <v>-27.8</v>
+        <v>-29.63</v>
       </c>
       <c r="E20" s="7">
-        <v>1.39</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2058,13 +2052,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-24.39</v>
+        <v>-23.18</v>
       </c>
       <c r="D21" s="6">
-        <v>-23.18</v>
+        <v>-25.28</v>
       </c>
       <c r="E21" s="7">
-        <v>1.21</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2075,13 +2069,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-14.45</v>
+        <v>-15.45</v>
       </c>
       <c r="D22" s="6">
-        <v>-15.45</v>
+        <v>-14.67</v>
       </c>
       <c r="E22" s="8">
-        <v>-1</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2092,13 +2086,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-48.56</v>
+        <v>-47.22</v>
       </c>
       <c r="D23" s="6">
-        <v>-47.22</v>
+        <v>-49.43</v>
       </c>
       <c r="E23" s="7">
-        <v>1.34</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2109,13 +2103,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.35</v>
+        <v>-2.81</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.81</v>
+        <v>-4.16</v>
       </c>
       <c r="E24" s="7">
-        <v>0.54</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2126,13 +2120,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>1.75</v>
+        <v>3.59</v>
       </c>
       <c r="D25" s="6">
-        <v>3.59</v>
+        <v>2.88</v>
       </c>
       <c r="E25" s="7">
-        <v>1.84</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2143,13 +2137,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-7.4</v>
+        <v>-2.59</v>
       </c>
       <c r="D26" s="6">
-        <v>-2.59</v>
+        <v>-4.07</v>
       </c>
       <c r="E26" s="7">
-        <v>4.81</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2160,13 +2154,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>0.24</v>
+        <v>4.65</v>
       </c>
       <c r="D27" s="6">
-        <v>4.65</v>
+        <v>0.08</v>
       </c>
       <c r="E27" s="7">
-        <v>4.41</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2177,13 +2171,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>33.18</v>
+        <v>33.96</v>
       </c>
       <c r="D28" s="6">
-        <v>33.96</v>
+        <v>31.88</v>
       </c>
       <c r="E28" s="7">
-        <v>0.78</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2194,13 +2188,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-17.54</v>
+        <v>-10.95</v>
       </c>
       <c r="D29" s="6">
-        <v>-10.95</v>
+        <v>-13.41</v>
       </c>
       <c r="E29" s="7">
-        <v>6.59</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2211,13 +2205,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>0.89</v>
+        <v>4.65</v>
       </c>
       <c r="D30" s="6">
-        <v>4.65</v>
+        <v>3.18</v>
       </c>
       <c r="E30" s="7">
-        <v>3.76</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2228,13 +2222,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-23.85</v>
+        <v>-23.58</v>
       </c>
       <c r="D31" s="6">
-        <v>-23.58</v>
+        <v>-23.77</v>
       </c>
       <c r="E31" s="7">
-        <v>0.27</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2245,13 +2239,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-31.96</v>
+        <v>-30.24</v>
       </c>
       <c r="D32" s="6">
-        <v>-30.24</v>
+        <v>-31.17</v>
       </c>
       <c r="E32" s="7">
-        <v>1.72</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2262,13 +2256,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-25.18</v>
+        <v>-24.53</v>
       </c>
       <c r="D33" s="6">
-        <v>-24.53</v>
+        <v>-26.14</v>
       </c>
       <c r="E33" s="7">
-        <v>0.65</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2279,13 +2273,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-19</v>
+        <v>-19.52</v>
       </c>
       <c r="D34" s="6">
-        <v>-19.52</v>
+        <v>-18.84</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.52</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2296,13 +2290,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-51</v>
+        <v>-49.52</v>
       </c>
       <c r="D35" s="6">
-        <v>-49.52</v>
+        <v>-50.84</v>
       </c>
       <c r="E35" s="7">
-        <v>1.48</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2313,13 +2307,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-17.82</v>
+        <v>-16.59</v>
       </c>
       <c r="D36" s="6">
-        <v>-16.59</v>
+        <v>-17.38</v>
       </c>
       <c r="E36" s="7">
-        <v>1.23</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2330,13 +2324,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>27.87</v>
+        <v>27.97</v>
       </c>
       <c r="D37" s="6">
-        <v>27.97</v>
+        <v>27.9</v>
       </c>
       <c r="E37" s="7">
-        <v>0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2347,13 +2341,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>10.26</v>
+        <v>10.52</v>
       </c>
       <c r="D38" s="6">
-        <v>10.52</v>
+        <v>10.38</v>
       </c>
       <c r="E38" s="7">
-        <v>0.26</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2364,13 +2358,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>237.45</v>
+        <v>239.5</v>
       </c>
       <c r="D39" s="6">
-        <v>239.5</v>
+        <v>234.4</v>
       </c>
       <c r="E39" s="7">
-        <v>2.05</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2381,13 +2375,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>697.35</v>
+        <v>692.85</v>
       </c>
       <c r="D40" s="6">
-        <v>692.85</v>
+        <v>698.75</v>
       </c>
       <c r="E40" s="8">
-        <v>-4.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2398,13 +2392,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>27.55</v>
+        <v>28.38</v>
       </c>
       <c r="D41" s="6">
-        <v>28.38</v>
+        <v>27.64</v>
       </c>
       <c r="E41" s="7">
-        <v>0.83</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2415,13 +2409,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1302.5</v>
+        <v>1322</v>
       </c>
       <c r="D42" s="6">
-        <v>1322</v>
+        <v>1309.5</v>
       </c>
       <c r="E42" s="7">
-        <v>19.5</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2432,13 +2426,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>50.26</v>
+        <v>51.81</v>
       </c>
       <c r="D43" s="6">
-        <v>51.81</v>
+        <v>50.62</v>
       </c>
       <c r="E43" s="7">
-        <v>1.55</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2449,13 +2443,13 @@
         <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>33.34</v>
+        <v>45.76</v>
       </c>
       <c r="D44" s="6">
-        <v>45.76</v>
+        <v>41.3</v>
       </c>
       <c r="E44" s="7">
-        <v>12.42</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2466,13 +2460,13 @@
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>40.9</v>
+        <v>44.32</v>
       </c>
       <c r="D45" s="6">
-        <v>44.32</v>
+        <v>38.37</v>
       </c>
       <c r="E45" s="7">
-        <v>3.42</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2483,13 +2477,13 @@
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>55.26</v>
+        <v>53.68</v>
       </c>
       <c r="D46" s="6">
-        <v>53.68</v>
+        <v>55.48</v>
       </c>
       <c r="E46" s="8">
-        <v>-1.58</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2500,13 +2494,13 @@
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>39.74</v>
+        <v>45.62</v>
       </c>
       <c r="D47" s="6">
-        <v>45.62</v>
+        <v>41.71</v>
       </c>
       <c r="E47" s="7">
-        <v>5.88</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2517,13 +2511,13 @@
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>49.2</v>
+        <v>55.15</v>
       </c>
       <c r="D48" s="6">
-        <v>55.15</v>
+        <v>51.02</v>
       </c>
       <c r="E48" s="7">
-        <v>5.95</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2534,13 +2528,13 @@
         <v>31</v>
       </c>
       <c r="C49" s="6">
-        <v>-51.67</v>
+        <v>-36.69</v>
       </c>
       <c r="D49" s="6">
-        <v>-36.69</v>
+        <v>-43.51</v>
       </c>
       <c r="E49" s="7">
-        <v>14.98</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2551,13 +2545,13 @@
         <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>-21.26</v>
+        <v>22.71</v>
       </c>
       <c r="D50" s="6">
-        <v>22.71</v>
+        <v>-39.08</v>
       </c>
       <c r="E50" s="7">
-        <v>43.97</v>
+        <v>-61.79</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2568,13 +2562,13 @@
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-28.22</v>
+        <v>-4.76</v>
       </c>
       <c r="D51" s="6">
-        <v>-4.76</v>
+        <v>-17.43</v>
       </c>
       <c r="E51" s="7">
-        <v>23.46</v>
+        <v>-12.67</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2585,13 +2579,13 @@
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>-35.8</v>
+        <v>-61.37</v>
       </c>
       <c r="D52" s="6">
-        <v>-61.37</v>
+        <v>-50.86</v>
       </c>
       <c r="E52" s="8">
-        <v>-25.57</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2602,13 +2596,13 @@
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>-51.79</v>
+        <v>-47.68</v>
       </c>
       <c r="D53" s="6">
-        <v>-47.68</v>
-      </c>
-      <c r="E53" s="7">
-        <v>4.11</v>
+        <v>-16.95</v>
+      </c>
+      <c r="E53" s="8">
+        <v>30.73</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2619,13 +2613,13 @@
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-15.47</v>
+        <v>20.84</v>
       </c>
       <c r="D54" s="6">
-        <v>20.84</v>
+        <v>-2.15</v>
       </c>
       <c r="E54" s="7">
-        <v>36.31</v>
+        <v>-22.99</v>
       </c>
     </row>
   </sheetData>
@@ -2655,28 +2649,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2690,16 +2684,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>49.4</v>
+        <v>46.4</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.2</v>
+        <v>-2.9</v>
       </c>
       <c r="G2" s="11">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="H2" s="11">
         <v>58.2</v>
@@ -2827,19 +2821,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.0378</v>
+        <v>0.0344</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0121</v>
+        <v>-0.019</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0688</v>
+        <v>-0.0673</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1082</v>
+        <v>-0.1056</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1145</v>
+        <v>-0.1155</v>
       </c>
       <c r="F2" s="14">
         <v>-0.1519</v>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,13 +184,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.6 → 40.4</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>40.4</t>
+  </si>
+  <si>
+    <t>51.0 → 46.6</t>
+  </si>
+  <si>
+    <t>51.0</t>
+  </si>
+  <si>
+    <t>46.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -775,7 +790,10 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -914,10 +932,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.9</v>
+        <v>27.18</v>
       </c>
       <c r="D2">
-        <v>-0.25</v>
+        <v>-2.58</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -926,46 +944,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-23.77</v>
+        <v>-25.74</v>
       </c>
       <c r="H2">
-        <v>21.41</v>
+        <v>18.28</v>
       </c>
       <c r="I2">
-        <v>-1.31</v>
+        <v>-2.12</v>
       </c>
       <c r="J2">
-        <v>2.12</v>
+        <v>-0.29</v>
       </c>
       <c r="K2">
-        <v>2.88</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>-22.97</v>
+        <v>-25.19</v>
       </c>
       <c r="M2">
-        <v>-10.56</v>
+        <v>-11.03</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P2">
-        <v>27.87</v>
+        <v>27.75</v>
       </c>
       <c r="Q2">
         <v>27.78</v>
       </c>
       <c r="R2">
-        <v>27.99</v>
+        <v>27.95</v>
       </c>
       <c r="S2">
-        <v>28.54</v>
+        <v>28.51</v>
       </c>
       <c r="T2">
-        <v>-2.23</v>
+        <v>-4.68</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -980,28 +998,28 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>50.62</v>
+        <v>40.38</v>
       </c>
       <c r="Z2">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="AA2">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AB2">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="AC2">
-        <v>46.08</v>
+        <v>32.62</v>
       </c>
       <c r="AD2">
-        <v>41.79</v>
+        <v>40.94</v>
       </c>
       <c r="AE2">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="AF2">
-        <v>-43.51</v>
+        <v>0.92</v>
       </c>
       <c r="AG2">
         <v>28.51</v>
@@ -1016,7 +1034,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>28.43</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1027,10 +1045,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="D3">
-        <v>-1.33</v>
+        <v>-0.87</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1039,25 +1057,25 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-31.17</v>
+        <v>-31.76</v>
       </c>
       <c r="H3">
-        <v>17.02</v>
+        <v>16.01</v>
       </c>
       <c r="I3">
-        <v>-2.44</v>
+        <v>-2</v>
       </c>
       <c r="J3">
-        <v>-4.86</v>
+        <v>-4.81</v>
       </c>
       <c r="K3">
-        <v>-4.07</v>
+        <v>-3.47</v>
       </c>
       <c r="L3">
-        <v>-29.63</v>
+        <v>-29.86</v>
       </c>
       <c r="M3">
-        <v>-15.19</v>
+        <v>-15.55</v>
       </c>
       <c r="N3">
         <v>34</v>
@@ -1066,19 +1084,19 @@
         <v>24</v>
       </c>
       <c r="P3">
-        <v>10.4</v>
+        <v>10.36</v>
       </c>
       <c r="Q3">
-        <v>10.55</v>
+        <v>10.53</v>
       </c>
       <c r="R3">
-        <v>10.82</v>
+        <v>10.8</v>
       </c>
       <c r="S3">
-        <v>11.14</v>
+        <v>11.13</v>
       </c>
       <c r="T3">
-        <v>-6.84</v>
+        <v>-7.52</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1093,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.3</v>
+        <v>38.69</v>
       </c>
       <c r="Z3">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="AA3">
         <v>-0.11</v>
@@ -1105,31 +1123,31 @@
         <v>-0.01</v>
       </c>
       <c r="AC3">
-        <v>50.96</v>
+        <v>64.33</v>
       </c>
       <c r="AD3">
-        <v>34.56</v>
+        <v>49.51</v>
       </c>
       <c r="AE3">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AF3">
-        <v>-39.08</v>
+        <v>-29.34</v>
       </c>
       <c r="AG3">
-        <v>10.8</v>
+        <v>10.78</v>
       </c>
       <c r="AH3">
-        <v>10.3</v>
+        <v>10.27</v>
       </c>
       <c r="AI3">
-        <v>11.06</v>
+        <v>11.02</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>23.34</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1140,10 +1158,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>234.4</v>
+        <v>233.15</v>
       </c>
       <c r="D4">
-        <v>-2.13</v>
+        <v>-0.53</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1152,46 +1170,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-26.14</v>
+        <v>-26.53</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>4.04</v>
       </c>
       <c r="I4">
-        <v>-2.88</v>
+        <v>-1.14</v>
       </c>
       <c r="J4">
-        <v>-8.720000000000001</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="K4">
-        <v>0.08</v>
+        <v>1.29</v>
       </c>
       <c r="L4">
-        <v>-25.28</v>
+        <v>-24.66</v>
       </c>
       <c r="M4">
-        <v>-1.9</v>
+        <v>-2.07</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>236.82</v>
+        <v>236.28</v>
       </c>
       <c r="Q4">
-        <v>243.44</v>
+        <v>242.46</v>
       </c>
       <c r="R4">
-        <v>243.54</v>
+        <v>243.47</v>
       </c>
       <c r="S4">
-        <v>255.44</v>
+        <v>255.07</v>
       </c>
       <c r="T4">
-        <v>-8.24</v>
+        <v>-8.59</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1206,43 +1224,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.37</v>
+        <v>37.05</v>
       </c>
       <c r="Z4">
-        <v>-2.85</v>
+        <v>-3.16</v>
       </c>
       <c r="AA4">
-        <v>-1.82</v>
+        <v>-2.08</v>
       </c>
       <c r="AB4">
-        <v>-1.04</v>
+        <v>-1.08</v>
       </c>
       <c r="AC4">
-        <v>31.35</v>
+        <v>24.4</v>
       </c>
       <c r="AD4">
-        <v>26.09</v>
+        <v>30.4</v>
       </c>
       <c r="AE4">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
       <c r="AF4">
-        <v>-17.43</v>
+        <v>-26.98</v>
       </c>
       <c r="AG4">
-        <v>256.19</v>
+        <v>255.21</v>
       </c>
       <c r="AH4">
-        <v>230.69</v>
+        <v>229.71</v>
       </c>
       <c r="AI4">
-        <v>250.03</v>
+        <v>247.72</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>31.06</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1253,10 +1271,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>698.75</v>
+        <v>694.25</v>
       </c>
       <c r="D5">
-        <v>0.85</v>
+        <v>-0.64</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1265,46 +1283,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-18.84</v>
+        <v>-19.36</v>
       </c>
       <c r="H5">
-        <v>42.4</v>
+        <v>41.48</v>
       </c>
       <c r="I5">
-        <v>-1.61</v>
+        <v>-1.62</v>
       </c>
       <c r="J5">
-        <v>2.26</v>
+        <v>0.97</v>
       </c>
       <c r="K5">
-        <v>31.88</v>
+        <v>29.73</v>
       </c>
       <c r="L5">
-        <v>-14.67</v>
+        <v>-15.48</v>
       </c>
       <c r="M5">
-        <v>-6.73</v>
+        <v>-7.01</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>698.49</v>
+        <v>696.21</v>
       </c>
       <c r="Q5">
-        <v>680.72</v>
+        <v>680.6900000000001</v>
       </c>
       <c r="R5">
-        <v>677.09</v>
+        <v>680.48</v>
       </c>
       <c r="S5">
-        <v>625.41</v>
+        <v>625.05</v>
       </c>
       <c r="T5">
-        <v>11.73</v>
+        <v>11.07</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1319,34 +1337,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>55.48</v>
+        <v>53.76</v>
       </c>
       <c r="Z5">
         <v>5.4</v>
       </c>
       <c r="AA5">
-        <v>3.36</v>
+        <v>3.77</v>
       </c>
       <c r="AB5">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AC5">
-        <v>77.72</v>
+        <v>75.34</v>
       </c>
       <c r="AD5">
-        <v>79.95</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AE5">
-        <v>23.41</v>
+        <v>23.13</v>
       </c>
       <c r="AF5">
-        <v>-50.86</v>
+        <v>-38.74</v>
       </c>
       <c r="AG5">
-        <v>721.21</v>
+        <v>721.13</v>
       </c>
       <c r="AH5">
-        <v>640.23</v>
+        <v>640.25</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1355,7 +1373,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>32.45</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1366,10 +1384,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>27.64</v>
+        <v>27.3</v>
       </c>
       <c r="D6">
-        <v>-2.61</v>
+        <v>-1.23</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1378,25 +1396,25 @@
         <v>27.23</v>
       </c>
       <c r="G6">
-        <v>-50.84</v>
+        <v>-51.44</v>
       </c>
       <c r="H6">
-        <v>1.51</v>
+        <v>0.26</v>
       </c>
       <c r="I6">
-        <v>1.51</v>
+        <v>-2.67</v>
       </c>
       <c r="J6">
-        <v>-6.5</v>
+        <v>-6.89</v>
       </c>
       <c r="K6">
-        <v>-13.41</v>
+        <v>-10.2</v>
       </c>
       <c r="L6">
-        <v>-49.43</v>
+        <v>-49.44</v>
       </c>
       <c r="M6">
-        <v>-11.55</v>
+        <v>-11.68</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1405,19 +1423,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>27.77</v>
+        <v>27.62</v>
       </c>
       <c r="Q6">
-        <v>28.85</v>
+        <v>28.76</v>
       </c>
       <c r="R6">
-        <v>29.78</v>
+        <v>29.69</v>
       </c>
       <c r="S6">
-        <v>34.66</v>
+        <v>34.57</v>
       </c>
       <c r="T6">
-        <v>-20.25</v>
+        <v>-21.03</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1432,43 +1450,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>41.71</v>
+        <v>40.02</v>
       </c>
       <c r="Z6">
-        <v>-0.55</v>
+        <v>-0.6</v>
       </c>
       <c r="AA6">
-        <v>-0.43</v>
+        <v>-0.46</v>
       </c>
       <c r="AB6">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AC6">
-        <v>36.65</v>
+        <v>35.73</v>
       </c>
       <c r="AD6">
-        <v>30.54</v>
+        <v>34.31</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>-16.95</v>
+        <v>-50.81</v>
       </c>
       <c r="AG6">
-        <v>30.97</v>
+        <v>30.98</v>
       </c>
       <c r="AH6">
-        <v>26.73</v>
+        <v>26.54</v>
       </c>
       <c r="AI6">
-        <v>30.76</v>
+        <v>30.51</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>29.14</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1479,10 +1497,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1309.5</v>
+        <v>1294.9</v>
       </c>
       <c r="D7">
-        <v>-0.95</v>
+        <v>-1.11</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1491,46 +1509,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-17.38</v>
+        <v>-18.3</v>
       </c>
       <c r="H7">
-        <v>4.03</v>
+        <v>2.87</v>
       </c>
       <c r="I7">
-        <v>2.55</v>
+        <v>-1.08</v>
       </c>
       <c r="J7">
-        <v>-1.9</v>
+        <v>-2.44</v>
       </c>
       <c r="K7">
-        <v>3.18</v>
+        <v>2.87</v>
       </c>
       <c r="L7">
-        <v>-4.16</v>
+        <v>-4.3</v>
       </c>
       <c r="M7">
-        <v>3.44</v>
+        <v>3.29</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P7">
-        <v>1311.22</v>
+        <v>1308.4</v>
       </c>
       <c r="Q7">
-        <v>1309.26</v>
+        <v>1307.81</v>
       </c>
       <c r="R7">
-        <v>1303.28</v>
+        <v>1303.3</v>
       </c>
       <c r="S7">
-        <v>1384.88</v>
+        <v>1383.65</v>
       </c>
       <c r="T7">
-        <v>-5.44</v>
+        <v>-6.41</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1545,34 +1563,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>51.02</v>
+        <v>46.64</v>
       </c>
       <c r="Z7">
-        <v>0.15</v>
+        <v>-0.78</v>
       </c>
       <c r="AA7">
-        <v>-0.5</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AB7">
-        <v>0.65</v>
+        <v>-0.22</v>
       </c>
       <c r="AC7">
-        <v>79.09</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="AD7">
-        <v>80.52</v>
+        <v>78.61</v>
       </c>
       <c r="AE7">
-        <v>21.62</v>
+        <v>21.61</v>
       </c>
       <c r="AF7">
-        <v>-2.15</v>
+        <v>-6.24</v>
       </c>
       <c r="AG7">
-        <v>1336.85</v>
+        <v>1335.2</v>
       </c>
       <c r="AH7">
-        <v>1281.67</v>
+        <v>1280.42</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1581,7 +1599,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>23.59</v>
+        <v>21.34</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1740,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1762,7 +1780,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1774,858 +1792,878 @@
         <v>56</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2.23</v>
-      </c>
-      <c r="D7" s="6">
-        <v>2.12</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.11</v>
+      <c r="B7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-2.86</v>
+        <v>2.12</v>
       </c>
       <c r="D8" s="6">
-        <v>-4.86</v>
+        <v>-0.29</v>
       </c>
       <c r="E8" s="7">
-        <v>-2</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-8.970000000000001</v>
+        <v>-4.86</v>
       </c>
       <c r="D9" s="6">
-        <v>-8.720000000000001</v>
+        <v>-4.81</v>
       </c>
       <c r="E9" s="8">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>1.66</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="D10" s="6">
-        <v>2.26</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="E10" s="8">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.12</v>
+        <v>2.26</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.5</v>
+        <v>0.97</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.38</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.23</v>
+        <v>-6.5</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.9</v>
+        <v>-6.89</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.67</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.2</v>
+        <v>-1.9</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.31</v>
+        <v>-2.44</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.11</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-0.47</v>
+        <v>-1.31</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.44</v>
+        <v>-2.12</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.97</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>0.46</v>
+        <v>-2.44</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.88</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-3.34</v>
+        <v>-2</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.44</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.66</v>
+        <v>-2.88</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.61</v>
+        <v>-1.14</v>
       </c>
       <c r="E16" s="8">
-        <v>0.05</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.46</v>
+        <v>-1.61</v>
       </c>
       <c r="D17" s="6">
-        <v>1.51</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.97</v>
+        <v>-1.62</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>2.72</v>
+        <v>1.51</v>
       </c>
       <c r="D18" s="6">
-        <v>2.55</v>
+        <v>-2.67</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.17</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-22.22</v>
+        <v>2.55</v>
       </c>
       <c r="D19" s="6">
-        <v>-22.97</v>
+        <v>-1.08</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.75</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-27.8</v>
+        <v>-22.97</v>
       </c>
       <c r="D20" s="6">
-        <v>-29.63</v>
+        <v>-25.19</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.83</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-23.18</v>
+        <v>-29.63</v>
       </c>
       <c r="D21" s="6">
-        <v>-25.28</v>
+        <v>-29.86</v>
       </c>
       <c r="E21" s="7">
-        <v>-2.1</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-15.45</v>
+        <v>-25.28</v>
       </c>
       <c r="D22" s="6">
-        <v>-14.67</v>
+        <v>-24.66</v>
       </c>
       <c r="E22" s="8">
-        <v>0.78</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-47.22</v>
+        <v>-14.67</v>
       </c>
       <c r="D23" s="6">
-        <v>-49.43</v>
+        <v>-15.48</v>
       </c>
       <c r="E23" s="7">
-        <v>-2.21</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.81</v>
+        <v>-49.43</v>
       </c>
       <c r="D24" s="6">
-        <v>-4.16</v>
+        <v>-49.44</v>
       </c>
       <c r="E24" s="7">
-        <v>-1.35</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>3.59</v>
+        <v>-4.16</v>
       </c>
       <c r="D25" s="6">
-        <v>2.88</v>
+        <v>-4.3</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.71</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-2.59</v>
+        <v>2.88</v>
       </c>
       <c r="D26" s="6">
-        <v>-4.07</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.48</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>4.65</v>
+        <v>-4.07</v>
       </c>
       <c r="D27" s="6">
-        <v>0.08</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-4.57</v>
+        <v>-3.47</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>33.96</v>
+        <v>0.08</v>
       </c>
       <c r="D28" s="6">
-        <v>31.88</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.08</v>
+        <v>1.29</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1.21</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-10.95</v>
+        <v>31.88</v>
       </c>
       <c r="D29" s="6">
-        <v>-13.41</v>
+        <v>29.73</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.46</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>4.65</v>
+        <v>-13.41</v>
       </c>
       <c r="D30" s="6">
-        <v>3.18</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.47</v>
+        <v>-10.2</v>
+      </c>
+      <c r="E30" s="8">
+        <v>3.21</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-23.58</v>
+        <v>3.18</v>
       </c>
       <c r="D31" s="6">
-        <v>-23.77</v>
+        <v>2.87</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.19</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-30.24</v>
+        <v>-23.77</v>
       </c>
       <c r="D32" s="6">
-        <v>-31.17</v>
+        <v>-25.74</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.93</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-24.53</v>
+        <v>-31.17</v>
       </c>
       <c r="D33" s="6">
-        <v>-26.14</v>
+        <v>-31.76</v>
       </c>
       <c r="E33" s="7">
-        <v>-1.61</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-19.52</v>
+        <v>-26.14</v>
       </c>
       <c r="D34" s="6">
-        <v>-18.84</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.68</v>
+        <v>-26.53</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-49.52</v>
+        <v>-18.84</v>
       </c>
       <c r="D35" s="6">
-        <v>-50.84</v>
+        <v>-19.36</v>
       </c>
       <c r="E35" s="7">
-        <v>-1.32</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-16.59</v>
+        <v>-50.84</v>
       </c>
       <c r="D36" s="6">
-        <v>-17.38</v>
+        <v>-51.44</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.79</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>27.97</v>
+        <v>-17.38</v>
       </c>
       <c r="D37" s="6">
-        <v>27.9</v>
+        <v>-18.3</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>10.52</v>
+        <v>27.9</v>
       </c>
       <c r="D38" s="6">
-        <v>10.38</v>
+        <v>27.18</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.14</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>239.5</v>
+        <v>10.38</v>
       </c>
       <c r="D39" s="6">
-        <v>234.4</v>
+        <v>10.29</v>
       </c>
       <c r="E39" s="7">
-        <v>-5.1</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>692.85</v>
+        <v>234.4</v>
       </c>
       <c r="D40" s="6">
-        <v>698.75</v>
-      </c>
-      <c r="E40" s="8">
-        <v>5.9</v>
+        <v>233.15</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>28.38</v>
+        <v>698.75</v>
       </c>
       <c r="D41" s="6">
-        <v>27.64</v>
+        <v>694.25</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.74</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1322</v>
+        <v>27.64</v>
       </c>
       <c r="D42" s="6">
-        <v>1309.5</v>
+        <v>27.3</v>
       </c>
       <c r="E42" s="7">
-        <v>-12.5</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>51.81</v>
+        <v>1309.5</v>
       </c>
       <c r="D43" s="6">
-        <v>50.62</v>
+        <v>1294.9</v>
       </c>
       <c r="E43" s="7">
-        <v>-1.19</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>45.76</v>
+        <v>50.62</v>
       </c>
       <c r="D44" s="6">
-        <v>41.3</v>
+        <v>40.38</v>
       </c>
       <c r="E44" s="7">
-        <v>-4.46</v>
+        <v>-10.24</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>44.32</v>
+        <v>41.3</v>
       </c>
       <c r="D45" s="6">
-        <v>38.37</v>
+        <v>38.69</v>
       </c>
       <c r="E45" s="7">
-        <v>-5.95</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>53.68</v>
+        <v>38.37</v>
       </c>
       <c r="D46" s="6">
-        <v>55.48</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.8</v>
+        <v>37.05</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>45.62</v>
+        <v>55.48</v>
       </c>
       <c r="D47" s="6">
-        <v>41.71</v>
+        <v>53.76</v>
       </c>
       <c r="E47" s="7">
-        <v>-3.91</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>55.15</v>
+        <v>41.71</v>
       </c>
       <c r="D48" s="6">
-        <v>51.02</v>
+        <v>40.02</v>
       </c>
       <c r="E48" s="7">
-        <v>-4.13</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>-36.69</v>
+        <v>51.02</v>
       </c>
       <c r="D49" s="6">
-        <v>-43.51</v>
+        <v>46.64</v>
       </c>
       <c r="E49" s="7">
-        <v>-6.82</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>22.71</v>
+        <v>-43.51</v>
       </c>
       <c r="D50" s="6">
-        <v>-39.08</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-61.79</v>
+        <v>0.92</v>
+      </c>
+      <c r="E50" s="8">
+        <v>44.43</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-4.76</v>
+        <v>-39.08</v>
       </c>
       <c r="D51" s="6">
-        <v>-17.43</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-12.67</v>
+        <v>-29.34</v>
+      </c>
+      <c r="E51" s="8">
+        <v>9.74</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>-61.37</v>
+        <v>-17.43</v>
       </c>
       <c r="D52" s="6">
-        <v>-50.86</v>
-      </c>
-      <c r="E52" s="8">
-        <v>10.51</v>
+        <v>-26.98</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-9.550000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>-47.68</v>
+        <v>-50.86</v>
       </c>
       <c r="D53" s="6">
-        <v>-16.95</v>
+        <v>-38.74</v>
       </c>
       <c r="E53" s="8">
-        <v>30.73</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>20.84</v>
+        <v>-16.95</v>
       </c>
       <c r="D54" s="6">
+        <v>-50.81</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-33.86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
         <v>-2.15</v>
       </c>
-      <c r="E54" s="7">
-        <v>-22.99</v>
+      <c r="D55" s="6">
+        <v>-6.24</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-4.09</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2649,28 +2687,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2684,16 +2722,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>46.4</v>
+        <v>42.8</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.9</v>
+        <v>-3.6</v>
       </c>
       <c r="G2" s="11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H2" s="11">
         <v>58.2</v>
@@ -2821,22 +2859,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.0344</v>
+        <v>0.0329</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.019</v>
+        <v>-0.0207</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0673</v>
+        <v>-0.0701</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1056</v>
+        <v>-0.1103</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1155</v>
+        <v>-0.1168</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.1519</v>
+        <v>-0.1555</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,28 +184,25 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.6 → 40.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>40.4</t>
-  </si>
-  <si>
-    <t>51.0 → 46.6</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>46.6</t>
+    <t>53.8 → 48.1</t>
+  </si>
+  <si>
+    <t>53.8</t>
+  </si>
+  <si>
+    <t>48.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -417,8 +414,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -790,10 +787,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -932,10 +926,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.18</v>
+        <v>27.21</v>
       </c>
       <c r="D2">
-        <v>-2.58</v>
+        <v>0.11</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -944,46 +938,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-25.74</v>
+        <v>-25.66</v>
       </c>
       <c r="H2">
-        <v>18.28</v>
+        <v>18.41</v>
       </c>
       <c r="I2">
-        <v>-2.12</v>
+        <v>-2.3</v>
       </c>
       <c r="J2">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3.03</v>
       </c>
       <c r="L2">
-        <v>-25.19</v>
+        <v>-24.31</v>
       </c>
       <c r="M2">
-        <v>-11.03</v>
+        <v>-11.19</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P2">
-        <v>27.75</v>
+        <v>27.63</v>
       </c>
       <c r="Q2">
-        <v>27.78</v>
+        <v>27.79</v>
       </c>
       <c r="R2">
-        <v>27.95</v>
+        <v>27.91</v>
       </c>
       <c r="S2">
-        <v>28.51</v>
+        <v>28.49</v>
       </c>
       <c r="T2">
-        <v>-4.68</v>
+        <v>-4.51</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -998,34 +992,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.38</v>
+        <v>40.91</v>
       </c>
       <c r="Z2">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="AA2">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AB2">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="AC2">
-        <v>32.62</v>
+        <v>15.62</v>
       </c>
       <c r="AD2">
-        <v>40.94</v>
+        <v>31.44</v>
       </c>
       <c r="AE2">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AF2">
-        <v>0.92</v>
+        <v>-35.29</v>
       </c>
       <c r="AG2">
-        <v>28.51</v>
+        <v>28.48</v>
       </c>
       <c r="AH2">
-        <v>27.05</v>
+        <v>27.1</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1034,7 +1028,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>28.82</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1045,10 +1039,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.29</v>
+        <v>10.22</v>
       </c>
       <c r="D3">
-        <v>-0.87</v>
+        <v>-0.68</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1057,46 +1051,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-31.76</v>
+        <v>-32.23</v>
       </c>
       <c r="H3">
-        <v>16.01</v>
+        <v>15.22</v>
       </c>
       <c r="I3">
-        <v>-2</v>
+        <v>-1.16</v>
       </c>
       <c r="J3">
-        <v>-4.81</v>
+        <v>-5.02</v>
       </c>
       <c r="K3">
-        <v>-3.47</v>
+        <v>-1.26</v>
       </c>
       <c r="L3">
-        <v>-29.86</v>
+        <v>-30.1</v>
       </c>
       <c r="M3">
-        <v>-15.55</v>
+        <v>-15.45</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P3">
-        <v>10.36</v>
+        <v>10.33</v>
       </c>
       <c r="Q3">
-        <v>10.53</v>
+        <v>10.5</v>
       </c>
       <c r="R3">
-        <v>10.8</v>
+        <v>10.78</v>
       </c>
       <c r="S3">
-        <v>11.13</v>
+        <v>11.11</v>
       </c>
       <c r="T3">
-        <v>-7.52</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1111,43 +1105,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.69</v>
+        <v>36.74</v>
       </c>
       <c r="Z3">
+        <v>-0.13</v>
+      </c>
+      <c r="AA3">
         <v>-0.12</v>
       </c>
-      <c r="AA3">
-        <v>-0.11</v>
-      </c>
       <c r="AB3">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>64.33</v>
+        <v>41.77</v>
       </c>
       <c r="AD3">
-        <v>49.51</v>
+        <v>52.35</v>
       </c>
       <c r="AE3">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AF3">
-        <v>-29.34</v>
+        <v>-43.16</v>
       </c>
       <c r="AG3">
         <v>10.78</v>
       </c>
       <c r="AH3">
-        <v>10.27</v>
+        <v>10.22</v>
       </c>
       <c r="AI3">
-        <v>11.02</v>
+        <v>10.92</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>20.33</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1158,10 +1152,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>233.15</v>
+        <v>231</v>
       </c>
       <c r="D4">
-        <v>-0.53</v>
+        <v>-0.92</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1170,46 +1164,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-26.53</v>
+        <v>-27.21</v>
       </c>
       <c r="H4">
-        <v>4.04</v>
+        <v>3.08</v>
       </c>
       <c r="I4">
-        <v>-1.14</v>
+        <v>-2.49</v>
       </c>
       <c r="J4">
-        <v>-8.210000000000001</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="K4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="L4">
-        <v>-24.66</v>
+        <v>-25.34</v>
       </c>
       <c r="M4">
-        <v>-2.07</v>
+        <v>-2.37</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>236.28</v>
+        <v>235.1</v>
       </c>
       <c r="Q4">
-        <v>242.46</v>
+        <v>241.21</v>
       </c>
       <c r="R4">
-        <v>243.47</v>
+        <v>243.29</v>
       </c>
       <c r="S4">
-        <v>255.07</v>
+        <v>254.7</v>
       </c>
       <c r="T4">
-        <v>-8.59</v>
+        <v>-9.31</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1224,43 +1218,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.05</v>
+        <v>34.84</v>
       </c>
       <c r="Z4">
-        <v>-3.16</v>
+        <v>-3.54</v>
       </c>
       <c r="AA4">
-        <v>-2.08</v>
+        <v>-2.37</v>
       </c>
       <c r="AB4">
-        <v>-1.08</v>
+        <v>-1.16</v>
       </c>
       <c r="AC4">
-        <v>24.4</v>
+        <v>0.4</v>
       </c>
       <c r="AD4">
-        <v>30.4</v>
+        <v>18.72</v>
       </c>
       <c r="AE4">
-        <v>4.68</v>
+        <v>4.53</v>
       </c>
       <c r="AF4">
-        <v>-26.98</v>
+        <v>-11.63</v>
       </c>
       <c r="AG4">
-        <v>255.21</v>
+        <v>253.24</v>
       </c>
       <c r="AH4">
-        <v>229.71</v>
+        <v>229.18</v>
       </c>
       <c r="AI4">
-        <v>247.72</v>
+        <v>245.38</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>33.1</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1271,10 +1265,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>694.25</v>
+        <v>678.45</v>
       </c>
       <c r="D5">
-        <v>-0.64</v>
+        <v>-2.28</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1283,88 +1277,88 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-19.36</v>
+        <v>-21.2</v>
       </c>
       <c r="H5">
-        <v>41.48</v>
+        <v>38.26</v>
       </c>
       <c r="I5">
-        <v>-1.62</v>
+        <v>-2.78</v>
       </c>
       <c r="J5">
-        <v>0.97</v>
+        <v>-2.37</v>
       </c>
       <c r="K5">
-        <v>29.73</v>
+        <v>28.03</v>
       </c>
       <c r="L5">
-        <v>-15.48</v>
+        <v>-17.37</v>
       </c>
       <c r="M5">
-        <v>-7.01</v>
+        <v>-7.35</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>696.21</v>
+        <v>692.33</v>
       </c>
       <c r="Q5">
-        <v>680.6900000000001</v>
+        <v>680.24</v>
       </c>
       <c r="R5">
-        <v>680.48</v>
+        <v>683.0700000000001</v>
       </c>
       <c r="S5">
-        <v>625.05</v>
+        <v>624.7</v>
       </c>
       <c r="T5">
-        <v>11.07</v>
+        <v>8.6</v>
       </c>
       <c r="U5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V5" t="s">
         <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>53.76</v>
+        <v>48.14</v>
       </c>
       <c r="Z5">
-        <v>5.4</v>
+        <v>4.08</v>
       </c>
       <c r="AA5">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="AB5">
-        <v>1.63</v>
+        <v>0.25</v>
       </c>
       <c r="AC5">
-        <v>75.34</v>
+        <v>66.53</v>
       </c>
       <c r="AD5">
-        <v>76.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="AE5">
-        <v>23.13</v>
+        <v>23.05</v>
       </c>
       <c r="AF5">
-        <v>-38.74</v>
+        <v>-43.35</v>
       </c>
       <c r="AG5">
-        <v>721.13</v>
+        <v>720.5599999999999</v>
       </c>
       <c r="AH5">
-        <v>640.25</v>
+        <v>639.91</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1373,7 +1367,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>33.8</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1384,58 +1378,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>27.3</v>
+        <v>26.92</v>
       </c>
       <c r="D6">
-        <v>-1.23</v>
+        <v>-1.39</v>
       </c>
       <c r="E6">
         <v>56.22</v>
       </c>
       <c r="F6">
-        <v>27.23</v>
+        <v>26.92</v>
       </c>
       <c r="G6">
-        <v>-51.44</v>
+        <v>-52.12</v>
       </c>
       <c r="H6">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-2.67</v>
+        <v>-1.17</v>
       </c>
       <c r="J6">
-        <v>-6.89</v>
+        <v>-7.62</v>
       </c>
       <c r="K6">
-        <v>-10.2</v>
+        <v>-9.42</v>
       </c>
       <c r="L6">
-        <v>-49.44</v>
+        <v>-50.19</v>
       </c>
       <c r="M6">
-        <v>-11.68</v>
+        <v>-11.75</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>27.62</v>
+        <v>27.56</v>
       </c>
       <c r="Q6">
-        <v>28.76</v>
+        <v>28.67</v>
       </c>
       <c r="R6">
-        <v>29.69</v>
+        <v>29.58</v>
       </c>
       <c r="S6">
-        <v>34.57</v>
+        <v>34.48</v>
       </c>
       <c r="T6">
-        <v>-21.03</v>
+        <v>-21.92</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1450,43 +1444,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>40.02</v>
+        <v>38.15</v>
       </c>
       <c r="Z6">
-        <v>-0.6</v>
+        <v>-0.66</v>
       </c>
       <c r="AA6">
-        <v>-0.46</v>
+        <v>-0.5</v>
       </c>
       <c r="AB6">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="AC6">
-        <v>35.73</v>
+        <v>24.14</v>
       </c>
       <c r="AD6">
-        <v>34.31</v>
+        <v>32.17</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF6">
-        <v>-50.81</v>
+        <v>-52.31</v>
       </c>
       <c r="AG6">
-        <v>30.98</v>
+        <v>31.04</v>
       </c>
       <c r="AH6">
-        <v>26.54</v>
+        <v>26.3</v>
       </c>
       <c r="AI6">
-        <v>30.51</v>
+        <v>30.07</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>28.08</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1497,10 +1491,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1294.9</v>
+        <v>1279</v>
       </c>
       <c r="D7">
-        <v>-1.11</v>
+        <v>-1.23</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1509,46 +1503,46 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-18.3</v>
+        <v>-19.3</v>
       </c>
       <c r="H7">
-        <v>2.87</v>
+        <v>1.6</v>
       </c>
       <c r="I7">
-        <v>-1.08</v>
+        <v>-2.6</v>
       </c>
       <c r="J7">
-        <v>-2.44</v>
+        <v>-3.39</v>
       </c>
       <c r="K7">
-        <v>2.87</v>
+        <v>1.27</v>
       </c>
       <c r="L7">
-        <v>-4.3</v>
+        <v>-6.55</v>
       </c>
       <c r="M7">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P7">
-        <v>1308.4</v>
+        <v>1301.58</v>
       </c>
       <c r="Q7">
-        <v>1307.81</v>
+        <v>1305.31</v>
       </c>
       <c r="R7">
-        <v>1303.3</v>
+        <v>1302.72</v>
       </c>
       <c r="S7">
-        <v>1383.65</v>
+        <v>1382.34</v>
       </c>
       <c r="T7">
-        <v>-6.41</v>
+        <v>-7.48</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1563,34 +1557,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>46.64</v>
+        <v>42.37</v>
       </c>
       <c r="Z7">
-        <v>-0.78</v>
+        <v>-2.77</v>
       </c>
       <c r="AA7">
-        <v>-0.5600000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AB7">
-        <v>-0.22</v>
+        <v>-1.77</v>
       </c>
       <c r="AC7">
-        <v>72.23999999999999</v>
+        <v>44.16</v>
       </c>
       <c r="AD7">
-        <v>78.61</v>
+        <v>65.16</v>
       </c>
       <c r="AE7">
-        <v>21.61</v>
+        <v>21.33</v>
       </c>
       <c r="AF7">
-        <v>-6.24</v>
+        <v>15.45</v>
       </c>
       <c r="AG7">
-        <v>1335.2</v>
+        <v>1333.67</v>
       </c>
       <c r="AH7">
-        <v>1280.42</v>
+        <v>1276.95</v>
       </c>
       <c r="AI7">
         <v>1340.16</v>
@@ -1599,7 +1593,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>21.34</v>
+        <v>21.5</v>
       </c>
     </row>
   </sheetData>
@@ -1740,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1780,890 +1774,910 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="4" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2.12</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-0.29</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.86</v>
+        <v>-0.29</v>
       </c>
       <c r="D9" s="6">
-        <v>-4.81</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.05</v>
+        <v>0</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-8.720000000000001</v>
+        <v>-4.81</v>
       </c>
       <c r="D10" s="6">
-        <v>-8.210000000000001</v>
+        <v>-5.02</v>
       </c>
       <c r="E10" s="8">
-        <v>0.51</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>2.26</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="D11" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.29</v>
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.5</v>
+        <v>0.97</v>
       </c>
       <c r="D12" s="6">
-        <v>-6.89</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.39</v>
+        <v>-2.37</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-3.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.9</v>
+        <v>-6.89</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.54</v>
+        <v>-7.62</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.31</v>
+        <v>-2.44</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.12</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-3.39</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.44</v>
+        <v>-2.12</v>
       </c>
       <c r="D15" s="6">
-        <v>-2</v>
+        <v>-2.3</v>
       </c>
       <c r="E15" s="8">
-        <v>0.44</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.88</v>
+        <v>-2</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.74</v>
+        <v>-1.16</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.84</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.61</v>
+        <v>-1.14</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.62</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.01</v>
+        <v>-2.49</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>1.51</v>
+        <v>-1.62</v>
       </c>
       <c r="D18" s="6">
-        <v>-2.67</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-4.18</v>
+        <v>-2.78</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>2.55</v>
+        <v>-2.67</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.08</v>
+        <v>-1.17</v>
       </c>
       <c r="E19" s="7">
-        <v>-3.63</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-22.97</v>
+        <v>-1.08</v>
       </c>
       <c r="D20" s="6">
-        <v>-25.19</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2.22</v>
+        <v>-2.6</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-29.63</v>
+        <v>-25.19</v>
       </c>
       <c r="D21" s="6">
-        <v>-29.86</v>
+        <v>-24.31</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.23</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-25.28</v>
+        <v>-29.86</v>
       </c>
       <c r="D22" s="6">
-        <v>-24.66</v>
+        <v>-30.1</v>
       </c>
       <c r="E22" s="8">
-        <v>0.62</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-14.67</v>
+        <v>-24.66</v>
       </c>
       <c r="D23" s="6">
-        <v>-15.48</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-25.34</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-49.43</v>
+        <v>-15.48</v>
       </c>
       <c r="D24" s="6">
-        <v>-49.44</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.01</v>
+        <v>-17.37</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-4.16</v>
+        <v>-49.44</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.3</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.14</v>
+        <v>-50.19</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>2.88</v>
+        <v>-4.3</v>
       </c>
       <c r="D26" s="6">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.88</v>
+        <v>-6.55</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-4.07</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6">
-        <v>-3.47</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.6</v>
+        <v>3.03</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.03</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>0.08</v>
+        <v>-3.47</v>
       </c>
       <c r="D28" s="6">
-        <v>1.29</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.21</v>
+        <v>-1.26</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.21</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>31.88</v>
+        <v>1.29</v>
       </c>
       <c r="D29" s="6">
-        <v>29.73</v>
+        <v>1.31</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.15</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-13.41</v>
+        <v>29.73</v>
       </c>
       <c r="D30" s="6">
-        <v>-10.2</v>
+        <v>28.03</v>
       </c>
       <c r="E30" s="8">
-        <v>3.21</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>3.18</v>
+        <v>-10.2</v>
       </c>
       <c r="D31" s="6">
-        <v>2.87</v>
+        <v>-9.42</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.31</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-23.77</v>
+        <v>2.87</v>
       </c>
       <c r="D32" s="6">
-        <v>-25.74</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.97</v>
+        <v>1.27</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-31.17</v>
+        <v>-25.74</v>
       </c>
       <c r="D33" s="6">
-        <v>-31.76</v>
+        <v>-25.66</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.59</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-26.14</v>
+        <v>-31.76</v>
       </c>
       <c r="D34" s="6">
-        <v>-26.53</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.39</v>
+        <v>-32.23</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-18.84</v>
+        <v>-26.53</v>
       </c>
       <c r="D35" s="6">
-        <v>-19.36</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.52</v>
+        <v>-27.21</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-50.84</v>
+        <v>-19.36</v>
       </c>
       <c r="D36" s="6">
-        <v>-51.44</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.6</v>
+        <v>-21.2</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-17.38</v>
+        <v>-51.44</v>
       </c>
       <c r="D37" s="6">
-        <v>-18.3</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.92</v>
+        <v>-52.12</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>27.9</v>
+        <v>-18.3</v>
       </c>
       <c r="D38" s="6">
-        <v>27.18</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.72</v>
+        <v>-19.3</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>10.38</v>
+        <v>27.18</v>
       </c>
       <c r="D39" s="6">
-        <v>10.29</v>
+        <v>27.21</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>234.4</v>
+        <v>10.29</v>
       </c>
       <c r="D40" s="6">
-        <v>233.15</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.25</v>
+        <v>10.22</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>698.75</v>
+        <v>233.15</v>
       </c>
       <c r="D41" s="6">
-        <v>694.25</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-4.5</v>
+        <v>231</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>27.64</v>
+        <v>694.25</v>
       </c>
       <c r="D42" s="6">
-        <v>27.3</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.34</v>
+        <v>678.45</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-15.8</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>1309.5</v>
+        <v>27.3</v>
       </c>
       <c r="D43" s="6">
-        <v>1294.9</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-14.6</v>
+        <v>26.92</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>50.62</v>
+        <v>1294.9</v>
       </c>
       <c r="D44" s="6">
-        <v>40.38</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-10.24</v>
+        <v>1279</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-15.9</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>41.3</v>
+        <v>40.38</v>
       </c>
       <c r="D45" s="6">
-        <v>38.69</v>
+        <v>40.91</v>
       </c>
       <c r="E45" s="7">
-        <v>-2.61</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>38.37</v>
+        <v>38.69</v>
       </c>
       <c r="D46" s="6">
-        <v>37.05</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.32</v>
+        <v>36.74</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>55.48</v>
+        <v>37.05</v>
       </c>
       <c r="D47" s="6">
-        <v>53.76</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.72</v>
+        <v>34.84</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>41.71</v>
+        <v>53.76</v>
       </c>
       <c r="D48" s="6">
-        <v>40.02</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.69</v>
+        <v>48.14</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-5.62</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>51.02</v>
+        <v>40.02</v>
       </c>
       <c r="D49" s="6">
-        <v>46.64</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-4.38</v>
+        <v>38.15</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>-43.51</v>
+        <v>46.64</v>
       </c>
       <c r="D50" s="6">
-        <v>0.92</v>
+        <v>42.37</v>
       </c>
       <c r="E50" s="8">
-        <v>44.43</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-39.08</v>
+        <v>0.92</v>
       </c>
       <c r="D51" s="6">
-        <v>-29.34</v>
+        <v>-35.29</v>
       </c>
       <c r="E51" s="8">
-        <v>9.74</v>
+        <v>-36.21</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>-17.43</v>
+        <v>-29.34</v>
       </c>
       <c r="D52" s="6">
-        <v>-26.98</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-9.550000000000001</v>
+        <v>-43.16</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-13.82</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>-50.86</v>
+        <v>-26.98</v>
       </c>
       <c r="D53" s="6">
-        <v>-38.74</v>
-      </c>
-      <c r="E53" s="8">
-        <v>12.12</v>
+        <v>-11.63</v>
+      </c>
+      <c r="E53" s="7">
+        <v>15.35</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-16.95</v>
+        <v>-38.74</v>
       </c>
       <c r="D54" s="6">
-        <v>-50.81</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-33.86</v>
+        <v>-43.35</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-4.61</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="6">
-        <v>-2.15</v>
+        <v>-50.81</v>
       </c>
       <c r="D55" s="6">
+        <v>-52.31</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
         <v>-6.24</v>
       </c>
-      <c r="E55" s="7">
-        <v>-4.09</v>
+      <c r="D56" s="6">
+        <v>15.45</v>
+      </c>
+      <c r="E56" s="7">
+        <v>21.69</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2687,28 +2701,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2722,22 +2736,22 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>42.8</v>
+        <v>40.2</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.6</v>
+        <v>-4.5</v>
       </c>
       <c r="G2" s="11">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="H2" s="11">
         <v>58.2</v>
       </c>
       <c r="I2" s="11">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2859,22 +2873,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.0329</v>
+        <v>0.0309</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0207</v>
+        <v>-0.0237</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0701</v>
+        <v>-0.0735</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1103</v>
+        <v>-0.1119</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1168</v>
+        <v>-0.1175</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.1555</v>
+        <v>-0.1545</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,40 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>53.8 → 48.1</t>
-  </si>
-  <si>
-    <t>53.8</t>
-  </si>
-  <si>
-    <t>48.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -288,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,18 +371,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -926,10 +892,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.21</v>
+        <v>27.05</v>
       </c>
       <c r="D2">
-        <v>0.11</v>
+        <v>-0.59</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -938,46 +904,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-25.66</v>
+        <v>-26.09</v>
       </c>
       <c r="H2">
-        <v>18.41</v>
+        <v>17.71</v>
       </c>
       <c r="I2">
-        <v>-2.3</v>
+        <v>-2.94</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="K2">
-        <v>3.03</v>
+        <v>-0.48</v>
       </c>
       <c r="L2">
-        <v>-24.31</v>
+        <v>-24.67</v>
       </c>
       <c r="M2">
-        <v>-11.19</v>
+        <v>-11.4</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P2">
-        <v>27.63</v>
+        <v>27.46</v>
       </c>
       <c r="Q2">
-        <v>27.79</v>
+        <v>27.76</v>
       </c>
       <c r="R2">
-        <v>27.91</v>
+        <v>27.85</v>
       </c>
       <c r="S2">
-        <v>28.49</v>
+        <v>28.48</v>
       </c>
       <c r="T2">
-        <v>-4.51</v>
+        <v>-5.01</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -992,34 +958,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.91</v>
+        <v>38.9</v>
       </c>
       <c r="Z2">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="AA2">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="AB2">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AC2">
-        <v>15.62</v>
+        <v>1.08</v>
       </c>
       <c r="AD2">
-        <v>31.44</v>
+        <v>16.44</v>
       </c>
       <c r="AE2">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AF2">
-        <v>-35.29</v>
+        <v>-19.78</v>
       </c>
       <c r="AG2">
-        <v>28.48</v>
+        <v>28.52</v>
       </c>
       <c r="AH2">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>29.08</v>
@@ -1028,7 +994,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>29.16</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1039,10 +1005,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.22</v>
+        <v>10.17</v>
       </c>
       <c r="D3">
-        <v>-0.68</v>
+        <v>-0.49</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1051,46 +1017,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-32.23</v>
+        <v>-32.56</v>
       </c>
       <c r="H3">
-        <v>15.22</v>
+        <v>14.66</v>
       </c>
       <c r="I3">
-        <v>-1.16</v>
+        <v>-0.88</v>
       </c>
       <c r="J3">
-        <v>-5.02</v>
+        <v>-4.69</v>
       </c>
       <c r="K3">
-        <v>-1.26</v>
+        <v>-4.78</v>
       </c>
       <c r="L3">
-        <v>-30.1</v>
+        <v>-31.28</v>
       </c>
       <c r="M3">
-        <v>-15.45</v>
+        <v>-15.41</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P3">
-        <v>10.33</v>
+        <v>10.32</v>
       </c>
       <c r="Q3">
-        <v>10.5</v>
+        <v>10.48</v>
       </c>
       <c r="R3">
-        <v>10.78</v>
+        <v>10.75</v>
       </c>
       <c r="S3">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="T3">
-        <v>-8.029999999999999</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1105,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.74</v>
+        <v>35.37</v>
       </c>
       <c r="Z3">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AA3">
         <v>-0.12</v>
@@ -1117,31 +1083,31 @@
         <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>41.77</v>
+        <v>26.95</v>
       </c>
       <c r="AD3">
-        <v>52.35</v>
+        <v>44.35</v>
       </c>
       <c r="AE3">
         <v>0.22</v>
       </c>
       <c r="AF3">
-        <v>-43.16</v>
+        <v>-34.2</v>
       </c>
       <c r="AG3">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
       <c r="AH3">
-        <v>10.22</v>
+        <v>10.18</v>
       </c>
       <c r="AI3">
-        <v>10.92</v>
+        <v>10.86</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>18.7</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1152,10 +1118,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>231</v>
+        <v>230.25</v>
       </c>
       <c r="D4">
-        <v>-0.92</v>
+        <v>-0.32</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1164,46 +1130,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-27.21</v>
+        <v>-27.45</v>
       </c>
       <c r="H4">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="I4">
-        <v>-2.49</v>
+        <v>-3.03</v>
       </c>
       <c r="J4">
-        <v>-8.609999999999999</v>
+        <v>-10.08</v>
       </c>
       <c r="K4">
-        <v>1.31</v>
+        <v>-2.39</v>
       </c>
       <c r="L4">
-        <v>-25.34</v>
+        <v>-25.99</v>
       </c>
       <c r="M4">
-        <v>-2.37</v>
+        <v>-2.47</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>235.1</v>
+        <v>233.66</v>
       </c>
       <c r="Q4">
-        <v>241.21</v>
+        <v>239.94</v>
       </c>
       <c r="R4">
-        <v>243.29</v>
+        <v>243.1</v>
       </c>
       <c r="S4">
-        <v>254.7</v>
+        <v>254.35</v>
       </c>
       <c r="T4">
-        <v>-9.31</v>
+        <v>-9.48</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1218,43 +1184,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.84</v>
+        <v>34.08</v>
       </c>
       <c r="Z4">
-        <v>-3.54</v>
+        <v>-3.85</v>
       </c>
       <c r="AA4">
-        <v>-2.37</v>
+        <v>-2.67</v>
       </c>
       <c r="AB4">
-        <v>-1.16</v>
+        <v>-1.18</v>
       </c>
       <c r="AC4">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>18.72</v>
+        <v>8.27</v>
       </c>
       <c r="AE4">
-        <v>4.53</v>
+        <v>4.43</v>
       </c>
       <c r="AF4">
-        <v>-11.63</v>
+        <v>-27.66</v>
       </c>
       <c r="AG4">
-        <v>253.24</v>
+        <v>250.88</v>
       </c>
       <c r="AH4">
-        <v>229.18</v>
+        <v>229</v>
       </c>
       <c r="AI4">
-        <v>245.38</v>
+        <v>243.98</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>35.78</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1265,10 +1231,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>678.45</v>
+        <v>668.75</v>
       </c>
       <c r="D5">
-        <v>-2.28</v>
+        <v>-1.43</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1277,46 +1243,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-21.2</v>
+        <v>-22.32</v>
       </c>
       <c r="H5">
-        <v>38.26</v>
+        <v>36.28</v>
       </c>
       <c r="I5">
-        <v>-2.78</v>
+        <v>-4.1</v>
       </c>
       <c r="J5">
-        <v>-2.37</v>
+        <v>-2.72</v>
       </c>
       <c r="K5">
-        <v>28.03</v>
+        <v>24.26</v>
       </c>
       <c r="L5">
-        <v>-17.37</v>
+        <v>-18.86</v>
       </c>
       <c r="M5">
-        <v>-7.35</v>
+        <v>-7.54</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>692.33</v>
+        <v>686.61</v>
       </c>
       <c r="Q5">
-        <v>680.24</v>
+        <v>679.78</v>
       </c>
       <c r="R5">
-        <v>683.0700000000001</v>
+        <v>685.34</v>
       </c>
       <c r="S5">
-        <v>624.7</v>
+        <v>624.3</v>
       </c>
       <c r="T5">
-        <v>8.6</v>
+        <v>7.12</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1331,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>48.14</v>
+        <v>45.03</v>
       </c>
       <c r="Z5">
-        <v>4.08</v>
+        <v>2.22</v>
       </c>
       <c r="AA5">
-        <v>3.83</v>
+        <v>3.51</v>
       </c>
       <c r="AB5">
-        <v>0.25</v>
+        <v>-1.29</v>
       </c>
       <c r="AC5">
-        <v>66.53</v>
+        <v>49.91</v>
       </c>
       <c r="AD5">
-        <v>73.2</v>
+        <v>63.93</v>
       </c>
       <c r="AE5">
-        <v>23.05</v>
+        <v>23.29</v>
       </c>
       <c r="AF5">
-        <v>-43.35</v>
+        <v>-14.23</v>
       </c>
       <c r="AG5">
-        <v>720.5599999999999</v>
+        <v>720.42</v>
       </c>
       <c r="AH5">
-        <v>639.91</v>
+        <v>639.14</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1367,7 +1333,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>31.5</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1378,58 +1344,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.92</v>
+        <v>26.83</v>
       </c>
       <c r="D6">
-        <v>-1.39</v>
+        <v>-0.33</v>
       </c>
       <c r="E6">
         <v>56.22</v>
       </c>
       <c r="F6">
-        <v>26.92</v>
+        <v>26.83</v>
       </c>
       <c r="G6">
-        <v>-52.12</v>
+        <v>-52.28</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-1.17</v>
+        <v>-2.61</v>
       </c>
       <c r="J6">
-        <v>-7.62</v>
+        <v>-6.55</v>
       </c>
       <c r="K6">
-        <v>-9.42</v>
+        <v>-14.85</v>
       </c>
       <c r="L6">
-        <v>-50.19</v>
+        <v>-51.24</v>
       </c>
       <c r="M6">
-        <v>-11.75</v>
+        <v>-12.01</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>27.56</v>
+        <v>27.41</v>
       </c>
       <c r="Q6">
-        <v>28.67</v>
+        <v>28.56</v>
       </c>
       <c r="R6">
-        <v>29.58</v>
+        <v>29.45</v>
       </c>
       <c r="S6">
-        <v>34.48</v>
+        <v>34.39</v>
       </c>
       <c r="T6">
-        <v>-21.92</v>
+        <v>-21.98</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1444,43 +1410,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>38.15</v>
+        <v>37.7</v>
       </c>
       <c r="Z6">
-        <v>-0.66</v>
+        <v>-0.7</v>
       </c>
       <c r="AA6">
-        <v>-0.5</v>
+        <v>-0.54</v>
       </c>
       <c r="AB6">
         <v>-0.16</v>
       </c>
       <c r="AC6">
-        <v>24.14</v>
+        <v>17.34</v>
       </c>
       <c r="AD6">
-        <v>32.17</v>
+        <v>25.74</v>
       </c>
       <c r="AE6">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AF6">
-        <v>-52.31</v>
+        <v>-60.44</v>
       </c>
       <c r="AG6">
-        <v>31.04</v>
+        <v>31.06</v>
       </c>
       <c r="AH6">
-        <v>26.3</v>
+        <v>26.06</v>
       </c>
       <c r="AI6">
-        <v>30.07</v>
+        <v>29.88</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>28.39</v>
+        <v>28.89</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1491,10 +1457,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="D7">
-        <v>-1.23</v>
+        <v>-0.39</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1503,25 +1469,25 @@
         <v>1258.8</v>
       </c>
       <c r="G7">
-        <v>-19.3</v>
+        <v>-19.62</v>
       </c>
       <c r="H7">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="I7">
-        <v>-2.6</v>
+        <v>-2.19</v>
       </c>
       <c r="J7">
-        <v>-3.39</v>
+        <v>-4.14</v>
       </c>
       <c r="K7">
-        <v>1.27</v>
+        <v>-1.47</v>
       </c>
       <c r="L7">
-        <v>-6.55</v>
+        <v>-7.15</v>
       </c>
       <c r="M7">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1530,19 +1496,19 @@
         <v>46</v>
       </c>
       <c r="P7">
-        <v>1301.58</v>
+        <v>1295.88</v>
       </c>
       <c r="Q7">
-        <v>1305.31</v>
+        <v>1303.16</v>
       </c>
       <c r="R7">
-        <v>1302.72</v>
+        <v>1302.13</v>
       </c>
       <c r="S7">
-        <v>1382.34</v>
+        <v>1381.07</v>
       </c>
       <c r="T7">
-        <v>-7.48</v>
+        <v>-7.75</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1557,43 +1523,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>42.37</v>
+        <v>41.09</v>
       </c>
       <c r="Z7">
-        <v>-2.77</v>
+        <v>-4.7</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>-1.74</v>
       </c>
       <c r="AB7">
-        <v>-1.77</v>
+        <v>-2.96</v>
       </c>
       <c r="AC7">
-        <v>44.16</v>
+        <v>22.34</v>
       </c>
       <c r="AD7">
-        <v>65.16</v>
+        <v>46.25</v>
       </c>
       <c r="AE7">
-        <v>21.33</v>
+        <v>21.16</v>
       </c>
       <c r="AF7">
-        <v>15.45</v>
+        <v>-12.7</v>
       </c>
       <c r="AG7">
-        <v>1333.67</v>
+        <v>1334.18</v>
       </c>
       <c r="AH7">
-        <v>1276.95</v>
+        <v>1272.14</v>
       </c>
       <c r="AI7">
-        <v>1340.16</v>
+        <v>1339.29</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>21.5</v>
+        <v>23.35</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1754,930 +1720,855 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-5.02</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-4.69</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.33</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-10.08</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-2.37</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-2.72</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-7.62</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-6.55</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-3.39</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-4.14</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-0.29</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-2.3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-2.94</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-4.81</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5.02</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.16</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-0.88</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-2.49</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-3.03</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-2.37</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-3.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.78</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-4.1</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-6.89</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-7.62</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-1.17</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-2.61</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.6</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-2.19</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.12</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.3</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-24.31</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-24.67</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-2</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-30.1</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-31.28</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.49</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-25.34</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-25.99</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.62</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.78</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-17.37</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-18.86</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.67</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.17</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-50.19</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-51.24</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.08</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.6</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-6.55</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-7.15</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-25.19</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-24.31</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>3.03</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-0.48</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-3.51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-29.86</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-30.1</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-1.26</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-4.78</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3.52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1.31</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-2.39</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>28.03</v>
+      </c>
+      <c r="D28" s="5">
+        <v>24.26</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-9.42</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-14.85</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-5.43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1.27</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-1.47</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-25.66</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-26.09</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-32.23</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-32.56</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-27.21</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-27.45</v>
+      </c>
+      <c r="E33" s="7">
         <v>-0.24</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-21.2</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-22.32</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-52.12</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-52.28</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-19.3</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-19.62</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>27.21</v>
+      </c>
+      <c r="D37" s="5">
+        <v>27.05</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>10.22</v>
+      </c>
+      <c r="D38" s="5">
+        <v>10.17</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-24.66</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-25.34</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>231</v>
+      </c>
+      <c r="D39" s="5">
+        <v>230.25</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-15.48</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-17.37</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>678.45</v>
+      </c>
+      <c r="D40" s="5">
+        <v>668.75</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-9.699999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-49.44</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-50.19</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>26.92</v>
+      </c>
+      <c r="D41" s="5">
+        <v>26.83</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-4.3</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-6.55</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1279</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1274</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>1</v>
-      </c>
-      <c r="D27" s="6">
-        <v>3.03</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>40.91</v>
+      </c>
+      <c r="D43" s="5">
+        <v>38.9</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-3.47</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-1.26</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>36.74</v>
+      </c>
+      <c r="D44" s="5">
+        <v>35.37</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>1.29</v>
-      </c>
-      <c r="D29" s="6">
-        <v>1.31</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>34.84</v>
+      </c>
+      <c r="D45" s="5">
+        <v>34.08</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>29.73</v>
-      </c>
-      <c r="D30" s="6">
-        <v>28.03</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>48.14</v>
+      </c>
+      <c r="D46" s="5">
+        <v>45.03</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-10.2</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-9.42</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>38.15</v>
+      </c>
+      <c r="D47" s="5">
+        <v>37.7</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>2.87</v>
-      </c>
-      <c r="D32" s="6">
-        <v>1.27</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>42.37</v>
+      </c>
+      <c r="D48" s="5">
+        <v>41.09</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-25.74</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-25.66</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-35.29</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-19.78</v>
+      </c>
+      <c r="E49" s="6">
+        <v>15.51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-31.76</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-32.23</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-43.16</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-34.2</v>
+      </c>
+      <c r="E50" s="6">
+        <v>8.960000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-26.53</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-27.21</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-11.63</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-27.66</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-16.03</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-19.36</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-21.2</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>-43.35</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-14.23</v>
+      </c>
+      <c r="E52" s="6">
+        <v>29.12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-51.44</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-52.12</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-52.31</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-60.44</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-8.130000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-18.3</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-19.3</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>27.18</v>
-      </c>
-      <c r="D39" s="6">
-        <v>27.21</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>10.29</v>
-      </c>
-      <c r="D40" s="6">
-        <v>10.22</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>233.15</v>
-      </c>
-      <c r="D41" s="6">
-        <v>231</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>694.25</v>
-      </c>
-      <c r="D42" s="6">
-        <v>678.45</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-15.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>27.3</v>
-      </c>
-      <c r="D43" s="6">
-        <v>26.92</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1294.9</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1279</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-15.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>40.38</v>
-      </c>
-      <c r="D45" s="6">
-        <v>40.91</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>38.69</v>
-      </c>
-      <c r="D46" s="6">
-        <v>36.74</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>37.05</v>
-      </c>
-      <c r="D47" s="6">
-        <v>34.84</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>53.76</v>
-      </c>
-      <c r="D48" s="6">
-        <v>48.14</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-5.62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>40.02</v>
-      </c>
-      <c r="D49" s="6">
-        <v>38.15</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>46.64</v>
-      </c>
-      <c r="D50" s="6">
-        <v>42.37</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-4.27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="6">
-        <v>0.92</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-35.29</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-36.21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-29.34</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-43.16</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-13.82</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-26.98</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-11.63</v>
-      </c>
-      <c r="E53" s="7">
-        <v>15.35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>-38.74</v>
-      </c>
-      <c r="D54" s="6">
-        <v>-43.35</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-4.61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>-50.81</v>
-      </c>
-      <c r="D55" s="6">
-        <v>-52.31</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="6">
-        <v>-6.24</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="C54" s="5">
         <v>15.45</v>
       </c>
-      <c r="E56" s="7">
-        <v>21.69</v>
+      <c r="D54" s="5">
+        <v>-12.7</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-28.15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2697,60 +2588,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>40.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-4.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2852,43 +2743,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.0309</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0237</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0735</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1119</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1175</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1545</v>
+      <c r="A2" s="13">
+        <v>0.0348</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0247</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.07539999999999999</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.114</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1201</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1541</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +276,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +316,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,14 +392,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -753,7 +775,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -892,10 +916,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>27.05</v>
+        <v>26.98</v>
       </c>
       <c r="D2">
-        <v>-0.59</v>
+        <v>-0.26</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -904,46 +928,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.09</v>
+        <v>-26.28</v>
       </c>
       <c r="H2">
-        <v>17.71</v>
+        <v>17.41</v>
       </c>
       <c r="I2">
-        <v>-2.94</v>
+        <v>-3.54</v>
       </c>
       <c r="J2">
-        <v>0.22</v>
+        <v>-2.56</v>
       </c>
       <c r="K2">
-        <v>-0.48</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L2">
-        <v>-24.67</v>
+        <v>-24.19</v>
       </c>
       <c r="M2">
-        <v>-11.4</v>
+        <v>-11.44</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="P2">
-        <v>27.46</v>
+        <v>27.26</v>
       </c>
       <c r="Q2">
-        <v>27.76</v>
+        <v>27.73</v>
       </c>
       <c r="R2">
-        <v>27.85</v>
+        <v>27.8</v>
       </c>
       <c r="S2">
-        <v>28.48</v>
+        <v>28.46</v>
       </c>
       <c r="T2">
-        <v>-5.01</v>
+        <v>-5.2</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -958,43 +982,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.9</v>
+        <v>38.02</v>
       </c>
       <c r="Z2">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="AA2">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="AB2">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="AC2">
         <v>1.08</v>
       </c>
       <c r="AD2">
-        <v>16.44</v>
+        <v>5.93</v>
       </c>
       <c r="AE2">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="AF2">
-        <v>-19.78</v>
+        <v>-19.76</v>
       </c>
       <c r="AG2">
-        <v>28.52</v>
+        <v>28.56</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="AI2">
-        <v>29.08</v>
+        <v>29.03</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>29.8</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1005,10 +1029,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.17</v>
+        <v>10.23</v>
       </c>
       <c r="D3">
-        <v>-0.49</v>
+        <v>0.59</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1017,46 +1041,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-32.56</v>
+        <v>-32.16</v>
       </c>
       <c r="H3">
-        <v>14.66</v>
+        <v>15.33</v>
       </c>
       <c r="I3">
-        <v>-0.88</v>
+        <v>-2.76</v>
       </c>
       <c r="J3">
-        <v>-4.69</v>
+        <v>-4.57</v>
       </c>
       <c r="K3">
-        <v>-4.78</v>
+        <v>-8.74</v>
       </c>
       <c r="L3">
-        <v>-31.28</v>
+        <v>-30.27</v>
       </c>
       <c r="M3">
-        <v>-15.41</v>
+        <v>-15.31</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P3">
-        <v>10.32</v>
+        <v>10.26</v>
       </c>
       <c r="Q3">
-        <v>10.48</v>
+        <v>10.46</v>
       </c>
       <c r="R3">
-        <v>10.75</v>
+        <v>10.73</v>
       </c>
       <c r="S3">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="T3">
-        <v>-8.380000000000001</v>
+        <v>-7.72</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1071,43 +1095,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.37</v>
+        <v>38.34</v>
       </c>
       <c r="Z3">
         <v>-0.14</v>
       </c>
       <c r="AA3">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AB3">
         <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>26.95</v>
+        <v>26.09</v>
       </c>
       <c r="AD3">
-        <v>44.35</v>
+        <v>31.6</v>
       </c>
       <c r="AE3">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="AF3">
-        <v>-34.2</v>
+        <v>-4.63</v>
       </c>
       <c r="AG3">
         <v>10.77</v>
       </c>
       <c r="AH3">
-        <v>10.18</v>
+        <v>10.15</v>
       </c>
       <c r="AI3">
-        <v>10.86</v>
+        <v>10.82</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>19.52</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1118,10 +1142,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>230.25</v>
+        <v>229.9</v>
       </c>
       <c r="D4">
-        <v>-0.32</v>
+        <v>-0.15</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1130,25 +1154,25 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-27.45</v>
+        <v>-27.56</v>
       </c>
       <c r="H4">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="I4">
-        <v>-3.03</v>
+        <v>-4.01</v>
       </c>
       <c r="J4">
-        <v>-10.08</v>
+        <v>-10.05</v>
       </c>
       <c r="K4">
-        <v>-2.39</v>
+        <v>-4.02</v>
       </c>
       <c r="L4">
-        <v>-25.99</v>
+        <v>-25.35</v>
       </c>
       <c r="M4">
-        <v>-2.47</v>
+        <v>-2.51</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1157,19 +1181,19 @@
         <v>26</v>
       </c>
       <c r="P4">
-        <v>233.66</v>
+        <v>231.74</v>
       </c>
       <c r="Q4">
-        <v>239.94</v>
+        <v>238.98</v>
       </c>
       <c r="R4">
-        <v>243.1</v>
+        <v>242.91</v>
       </c>
       <c r="S4">
-        <v>254.35</v>
+        <v>254</v>
       </c>
       <c r="T4">
-        <v>-9.48</v>
+        <v>-9.49</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1184,43 +1208,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.08</v>
+        <v>33.71</v>
       </c>
       <c r="Z4">
-        <v>-3.85</v>
+        <v>-4.08</v>
       </c>
       <c r="AA4">
-        <v>-2.67</v>
+        <v>-2.95</v>
       </c>
       <c r="AB4">
-        <v>-1.18</v>
+        <v>-1.13</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>8.27</v>
+        <v>0.13</v>
       </c>
       <c r="AE4">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="AF4">
-        <v>-27.66</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="AG4">
-        <v>250.88</v>
+        <v>249.92</v>
       </c>
       <c r="AH4">
-        <v>229</v>
+        <v>228.05</v>
       </c>
       <c r="AI4">
-        <v>243.98</v>
+        <v>242.3</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>38.75</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1231,10 +1255,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>668.75</v>
+        <v>665.55</v>
       </c>
       <c r="D5">
-        <v>-1.43</v>
+        <v>-0.48</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1243,25 +1267,25 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-22.32</v>
+        <v>-22.7</v>
       </c>
       <c r="H5">
-        <v>36.28</v>
+        <v>35.63</v>
       </c>
       <c r="I5">
-        <v>-4.1</v>
+        <v>-3.94</v>
       </c>
       <c r="J5">
-        <v>-2.72</v>
+        <v>-1.81</v>
       </c>
       <c r="K5">
-        <v>24.26</v>
+        <v>23.25</v>
       </c>
       <c r="L5">
-        <v>-18.86</v>
+        <v>-20.88</v>
       </c>
       <c r="M5">
-        <v>-7.54</v>
+        <v>-7.63</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1270,19 +1294,19 @@
         <v>56</v>
       </c>
       <c r="P5">
-        <v>686.61</v>
+        <v>681.15</v>
       </c>
       <c r="Q5">
-        <v>679.78</v>
+        <v>679.01</v>
       </c>
       <c r="R5">
-        <v>685.34</v>
+        <v>687.65</v>
       </c>
       <c r="S5">
-        <v>624.3</v>
+        <v>623.91</v>
       </c>
       <c r="T5">
-        <v>7.12</v>
+        <v>6.67</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1297,34 +1321,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>45.03</v>
+        <v>44.02</v>
       </c>
       <c r="Z5">
-        <v>2.22</v>
+        <v>0.49</v>
       </c>
       <c r="AA5">
-        <v>3.51</v>
+        <v>2.9</v>
       </c>
       <c r="AB5">
-        <v>-1.29</v>
+        <v>-2.42</v>
       </c>
       <c r="AC5">
-        <v>49.91</v>
+        <v>34.4</v>
       </c>
       <c r="AD5">
-        <v>63.93</v>
+        <v>50.28</v>
       </c>
       <c r="AE5">
-        <v>23.29</v>
+        <v>22.6</v>
       </c>
       <c r="AF5">
-        <v>-14.23</v>
+        <v>-63.45</v>
       </c>
       <c r="AG5">
-        <v>720.42</v>
+        <v>720.14</v>
       </c>
       <c r="AH5">
-        <v>639.14</v>
+        <v>637.88</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1333,7 +1357,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>27.93</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1344,37 +1368,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.83</v>
+        <v>26.64</v>
       </c>
       <c r="D6">
-        <v>-0.33</v>
+        <v>-0.71</v>
       </c>
       <c r="E6">
         <v>56.22</v>
       </c>
       <c r="F6">
-        <v>26.83</v>
+        <v>26.64</v>
       </c>
       <c r="G6">
-        <v>-52.28</v>
+        <v>-52.61</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-2.61</v>
+        <v>-6.13</v>
       </c>
       <c r="J6">
-        <v>-6.55</v>
+        <v>-8.17</v>
       </c>
       <c r="K6">
-        <v>-14.85</v>
+        <v>-18.13</v>
       </c>
       <c r="L6">
-        <v>-51.24</v>
+        <v>-51.06</v>
       </c>
       <c r="M6">
-        <v>-12.01</v>
+        <v>-12.13</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1383,19 +1407,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>27.41</v>
+        <v>27.07</v>
       </c>
       <c r="Q6">
-        <v>28.56</v>
+        <v>28.44</v>
       </c>
       <c r="R6">
-        <v>29.45</v>
+        <v>29.33</v>
       </c>
       <c r="S6">
-        <v>34.39</v>
+        <v>34.3</v>
       </c>
       <c r="T6">
-        <v>-21.98</v>
+        <v>-22.33</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1410,43 +1434,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>37.7</v>
+        <v>36.72</v>
       </c>
       <c r="Z6">
-        <v>-0.7</v>
+        <v>-0.75</v>
       </c>
       <c r="AA6">
-        <v>-0.54</v>
+        <v>-0.58</v>
       </c>
       <c r="AB6">
         <v>-0.16</v>
       </c>
       <c r="AC6">
-        <v>17.34</v>
+        <v>12.66</v>
       </c>
       <c r="AD6">
-        <v>25.74</v>
+        <v>18.05</v>
       </c>
       <c r="AE6">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AF6">
-        <v>-60.44</v>
+        <v>-46.02</v>
       </c>
       <c r="AG6">
-        <v>31.06</v>
+        <v>31.08</v>
       </c>
       <c r="AH6">
-        <v>26.06</v>
+        <v>25.81</v>
       </c>
       <c r="AI6">
-        <v>29.88</v>
+        <v>29.41</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>28.89</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1457,37 +1481,37 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1274</v>
+        <v>1257.5</v>
       </c>
       <c r="D7">
-        <v>-0.39</v>
+        <v>-1.3</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
       </c>
       <c r="F7">
-        <v>1258.8</v>
+        <v>1257.5</v>
       </c>
       <c r="G7">
-        <v>-19.62</v>
+        <v>-20.66</v>
       </c>
       <c r="H7">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-2.19</v>
+        <v>-4.88</v>
       </c>
       <c r="J7">
-        <v>-4.14</v>
+        <v>-4.52</v>
       </c>
       <c r="K7">
-        <v>-1.47</v>
+        <v>-3.79</v>
       </c>
       <c r="L7">
-        <v>-7.15</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M7">
-        <v>3.48</v>
+        <v>3.21</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1496,22 +1520,22 @@
         <v>46</v>
       </c>
       <c r="P7">
-        <v>1295.88</v>
+        <v>1282.98</v>
       </c>
       <c r="Q7">
-        <v>1303.16</v>
+        <v>1300.53</v>
       </c>
       <c r="R7">
-        <v>1302.13</v>
+        <v>1301.2</v>
       </c>
       <c r="S7">
-        <v>1381.07</v>
+        <v>1379.69</v>
       </c>
       <c r="T7">
-        <v>-7.75</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="U7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V7" t="s">
         <v>44</v>
@@ -1520,46 +1544,46 @@
         <v>44</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>41.09</v>
+        <v>37.12</v>
       </c>
       <c r="Z7">
-        <v>-4.7</v>
+        <v>-7.47</v>
       </c>
       <c r="AA7">
-        <v>-1.74</v>
+        <v>-2.89</v>
       </c>
       <c r="AB7">
-        <v>-2.96</v>
+        <v>-4.58</v>
       </c>
       <c r="AC7">
-        <v>22.34</v>
+        <v>7.7</v>
       </c>
       <c r="AD7">
-        <v>46.25</v>
+        <v>24.73</v>
       </c>
       <c r="AE7">
-        <v>21.16</v>
+        <v>21.15</v>
       </c>
       <c r="AF7">
-        <v>-12.7</v>
+        <v>-18.05</v>
       </c>
       <c r="AG7">
-        <v>1334.18</v>
+        <v>1337.45</v>
       </c>
       <c r="AH7">
-        <v>1272.14</v>
+        <v>1263.62</v>
       </c>
       <c r="AI7">
-        <v>1339.29</v>
+        <v>1323.65</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>23.35</v>
+        <v>26.58</v>
       </c>
     </row>
   </sheetData>
@@ -1720,12 +1744,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1733,836 +1792,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>0.22</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.22</v>
+      <c r="D7" s="6">
+        <v>-2.56</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-2.78</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-5.02</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-4.69</v>
       </c>
-      <c r="E8" s="6">
-        <v>0.33</v>
+      <c r="D8" s="6">
+        <v>-4.57</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-10.08</v>
       </c>
-      <c r="E9" s="7">
+      <c r="D9" s="6">
+        <v>-10.05</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-2.72</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-1.81</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-6.55</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-8.17</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-4.14</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-4.52</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-2.94</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-3.54</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-0.88</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.76</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.03</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-4.01</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-4.1</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.94</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.61</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.13</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.19</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-4.88</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-24.67</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-24.19</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-31.28</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-30.27</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-25.99</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-25.35</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-18.86</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-20.88</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-51.24</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-51.06</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-7.15</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-0.48</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-7.91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-4.78</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-8.74</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3.96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-2.39</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-4.02</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>24.26</v>
+      </c>
+      <c r="D28" s="6">
+        <v>23.25</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-14.85</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-18.13</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
         <v>-1.47</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-3.79</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-26.09</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-26.28</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-32.56</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-32.16</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-27.45</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-27.56</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-2.37</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-2.72</v>
-      </c>
-      <c r="E10" s="7">
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-22.32</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-22.7</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-52.28</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-52.61</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-19.62</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-20.66</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>27.05</v>
+      </c>
+      <c r="D37" s="6">
+        <v>26.98</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>10.17</v>
+      </c>
+      <c r="D38" s="6">
+        <v>10.23</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>230.25</v>
+      </c>
+      <c r="D39" s="6">
+        <v>229.9</v>
+      </c>
+      <c r="E39" s="7">
         <v>-0.35</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>668.75</v>
+      </c>
+      <c r="D40" s="6">
+        <v>665.55</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-7.62</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-6.55</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>26.83</v>
+      </c>
+      <c r="D41" s="6">
+        <v>26.64</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-3.39</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-4.14</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1274</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1257.5</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-16.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-2.3</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-2.94</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>38.9</v>
+      </c>
+      <c r="D43" s="6">
+        <v>38.02</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-1.16</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-0.88</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>35.37</v>
+      </c>
+      <c r="D44" s="6">
+        <v>38.34</v>
+      </c>
+      <c r="E44" s="8">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-2.49</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-3.03</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>34.08</v>
+      </c>
+      <c r="D45" s="6">
+        <v>33.71</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.78</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-4.1</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>45.03</v>
+      </c>
+      <c r="D46" s="6">
+        <v>44.02</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-1.17</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-2.61</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>37.7</v>
+      </c>
+      <c r="D47" s="6">
+        <v>36.72</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-2.6</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.19</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>41.09</v>
+      </c>
+      <c r="D48" s="6">
+        <v>37.12</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-3.97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-24.31</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-24.67</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-19.78</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-19.76</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-30.1</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-31.28</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-34.2</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-4.63</v>
+      </c>
+      <c r="E50" s="8">
+        <v>29.57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-25.34</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-25.99</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-27.66</v>
+      </c>
+      <c r="D51" s="6">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="E51" s="8">
+        <v>108.81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-17.37</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-18.86</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-14.23</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-63.45</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-49.22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-50.19</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-51.24</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-60.44</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-46.02</v>
+      </c>
+      <c r="E53" s="8">
+        <v>14.42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-6.55</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-7.15</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>3.03</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-0.48</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-3.51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-1.26</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-4.78</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>1.31</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-2.39</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>28.03</v>
-      </c>
-      <c r="D28" s="5">
-        <v>24.26</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-9.42</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-14.85</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-5.43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>1.27</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-1.47</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-25.66</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-26.09</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-32.23</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-32.56</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-27.21</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-27.45</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-21.2</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-22.32</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-52.12</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-52.28</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-19.3</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-19.62</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>27.21</v>
-      </c>
-      <c r="D37" s="5">
-        <v>27.05</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>10.22</v>
-      </c>
-      <c r="D38" s="5">
-        <v>10.17</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>231</v>
-      </c>
-      <c r="D39" s="5">
-        <v>230.25</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>678.45</v>
-      </c>
-      <c r="D40" s="5">
-        <v>668.75</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-9.699999999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>26.92</v>
-      </c>
-      <c r="D41" s="5">
-        <v>26.83</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1279</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1274</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>40.91</v>
-      </c>
-      <c r="D43" s="5">
-        <v>38.9</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>36.74</v>
-      </c>
-      <c r="D44" s="5">
-        <v>35.37</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>34.84</v>
-      </c>
-      <c r="D45" s="5">
-        <v>34.08</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>48.14</v>
-      </c>
-      <c r="D46" s="5">
-        <v>45.03</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-3.11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>38.15</v>
-      </c>
-      <c r="D47" s="5">
-        <v>37.7</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>42.37</v>
-      </c>
-      <c r="D48" s="5">
-        <v>41.09</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="5">
-        <v>-35.29</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-19.78</v>
-      </c>
-      <c r="E49" s="6">
-        <v>15.51</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-43.16</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-34.2</v>
-      </c>
-      <c r="E50" s="6">
-        <v>8.960000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-11.63</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-27.66</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-16.03</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>-43.35</v>
-      </c>
-      <c r="D52" s="5">
-        <v>-14.23</v>
-      </c>
-      <c r="E52" s="6">
-        <v>29.12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-52.31</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-60.44</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-8.130000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>15.45</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C54" s="6">
         <v>-12.7</v>
       </c>
+      <c r="D54" s="6">
+        <v>-18.05</v>
+      </c>
       <c r="E54" s="7">
-        <v>-28.15</v>
+        <v>-5.35</v>
       </c>
     </row>
   </sheetData>
@@ -2588,60 +2647,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>62</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>38.7</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>38</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-4.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-5.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-3.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2743,43 +2802,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.0348</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0247</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.07539999999999999</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.114</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1201</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1541</v>
+      <c r="A2" s="14">
+        <v>0.0321</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0251</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.07629999999999999</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1144</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1213</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1531</v>
       </c>
     </row>
   </sheetData>
